--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S232"/>
+  <dimension ref="A1:S241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15528,6 +15528,591 @@
         <v>16</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>77</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Altoona, PA</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>4</v>
+      </c>
+      <c r="E233" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F233" t="n">
+        <v>240</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>18</v>
+      </c>
+      <c r="I233" t="n">
+        <v>4</v>
+      </c>
+      <c r="J233" t="n">
+        <v>4</v>
+      </c>
+      <c r="K233" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="L233" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="M233" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="N233" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O233" t="n">
+        <v>7.049499999999999</v>
+      </c>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>2.229089148274632</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0.4235269381721801</v>
+      </c>
+      <c r="S233" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>77</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Altoona, PA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>4</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F234" t="n">
+        <v>240</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>18</v>
+      </c>
+      <c r="I234" t="n">
+        <v>6</v>
+      </c>
+      <c r="J234" t="n">
+        <v>6</v>
+      </c>
+      <c r="K234" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="L234" t="n">
+        <v>8</v>
+      </c>
+      <c r="M234" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O234" t="n">
+        <v>6.6335</v>
+      </c>
+      <c r="P234" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>3.343633722411948</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0.6352904072582701</v>
+      </c>
+      <c r="S234" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>77</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Altoona, PA</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>4</v>
+      </c>
+      <c r="E235" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F235" t="n">
+        <v>240</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>18</v>
+      </c>
+      <c r="I235" t="n">
+        <v>8</v>
+      </c>
+      <c r="J235" t="n">
+        <v>8</v>
+      </c>
+      <c r="K235" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="L235" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="M235" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N235" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O235" t="n">
+        <v>6.564</v>
+      </c>
+      <c r="P235" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>4.458178296549264</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.8470538763443601</v>
+      </c>
+      <c r="S235" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>78</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Chester, PA</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F236" t="n">
+        <v>150</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>90</v>
+      </c>
+      <c r="I236" t="n">
+        <v>4</v>
+      </c>
+      <c r="J236" t="n">
+        <v>4</v>
+      </c>
+      <c r="K236" t="n">
+        <v>10</v>
+      </c>
+      <c r="L236" t="n">
+        <v>10</v>
+      </c>
+      <c r="M236" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="N236" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O236" t="n">
+        <v>8.196999999999999</v>
+      </c>
+      <c r="P236" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0.6368826137927521</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.1210076966206229</v>
+      </c>
+      <c r="S236" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>78</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Chester, PA</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F237" t="n">
+        <v>150</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>90</v>
+      </c>
+      <c r="I237" t="n">
+        <v>7</v>
+      </c>
+      <c r="J237" t="n">
+        <v>7</v>
+      </c>
+      <c r="K237" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="L237" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="M237" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="N237" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="O237" t="n">
+        <v>9.027500000000002</v>
+      </c>
+      <c r="P237" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>1.114544574137316</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.2117634690860901</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>78</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Chester, PA</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F238" t="n">
+        <v>150</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>90</v>
+      </c>
+      <c r="I238" t="n">
+        <v>10</v>
+      </c>
+      <c r="J238" t="n">
+        <v>10</v>
+      </c>
+      <c r="K238" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="L238" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M238" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="N238" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="O238" t="n">
+        <v>8.957999999999998</v>
+      </c>
+      <c r="P238" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>1.59220653448188</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0.3025192415515572</v>
+      </c>
+      <c r="S238" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>79</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>With six people sharing a tank tonight, how long should showers be?</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Johnstown, PA</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>6</v>
+      </c>
+      <c r="E239" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F239" t="n">
+        <v>340</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>40</v>
+      </c>
+      <c r="I239" t="n">
+        <v>5</v>
+      </c>
+      <c r="J239" t="n">
+        <v>5</v>
+      </c>
+      <c r="K239" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="L239" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M239" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="N239" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O239" t="n">
+        <v>7.4975</v>
+      </c>
+      <c r="P239" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>1.86683130496422</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0.3546979479432018</v>
+      </c>
+      <c r="S239" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>79</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>With six people sharing a tank tonight, how long should showers be?</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Johnstown, PA</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>6</v>
+      </c>
+      <c r="E240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F240" t="n">
+        <v>340</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>40</v>
+      </c>
+      <c r="I240" t="n">
+        <v>8</v>
+      </c>
+      <c r="J240" t="n">
+        <v>8</v>
+      </c>
+      <c r="K240" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="L240" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M240" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N240" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O240" t="n">
+        <v>7.6015</v>
+      </c>
+      <c r="P240" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>2.986930087942751</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.5675167167091227</v>
+      </c>
+      <c r="S240" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>79</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>With six people sharing a tank tonight, how long should showers be?</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Johnstown, PA</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>6</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F241" t="n">
+        <v>340</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>40</v>
+      </c>
+      <c r="I241" t="n">
+        <v>12</v>
+      </c>
+      <c r="J241" t="n">
+        <v>12</v>
+      </c>
+      <c r="K241" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L241" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="M241" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="N241" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="O241" t="n">
+        <v>6.305</v>
+      </c>
+      <c r="P241" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>4.480395131914127</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0.8512750750636842</v>
+      </c>
+      <c r="S241" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>occupants</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -544,8 +544,10 @@
       <c r="H2" t="n">
         <v>28</v>
       </c>
-      <c r="I2" t="n">
-        <v>3</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -609,8 +611,10 @@
       <c r="H3" t="n">
         <v>28</v>
       </c>
-      <c r="I3" t="n">
-        <v>5</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -674,8 +678,10 @@
       <c r="H4" t="n">
         <v>28</v>
       </c>
-      <c r="I4" t="n">
-        <v>8</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J4" t="n">
         <v>8</v>
@@ -739,8 +745,10 @@
       <c r="H5" t="n">
         <v>85</v>
       </c>
-      <c r="I5" t="n">
-        <v>4</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -804,8 +812,10 @@
       <c r="H6" t="n">
         <v>85</v>
       </c>
-      <c r="I6" t="n">
-        <v>7</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J6" t="n">
         <v>7</v>
@@ -869,8 +879,10 @@
       <c r="H7" t="n">
         <v>85</v>
       </c>
-      <c r="I7" t="n">
-        <v>10</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -934,8 +946,10 @@
       <c r="H8" t="n">
         <v>18</v>
       </c>
-      <c r="I8" t="n">
-        <v>5</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -999,8 +1013,10 @@
       <c r="H9" t="n">
         <v>18</v>
       </c>
-      <c r="I9" t="n">
-        <v>8</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -1064,8 +1080,10 @@
       <c r="H10" t="n">
         <v>18</v>
       </c>
-      <c r="I10" t="n">
-        <v>12</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J10" t="n">
         <v>12</v>
@@ -1129,8 +1147,10 @@
       <c r="H11" t="n">
         <v>75</v>
       </c>
-      <c r="I11" t="n">
-        <v>5</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -1194,8 +1214,10 @@
       <c r="H12" t="n">
         <v>75</v>
       </c>
-      <c r="I12" t="n">
-        <v>7</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J12" t="n">
         <v>7</v>
@@ -1259,8 +1281,10 @@
       <c r="H13" t="n">
         <v>75</v>
       </c>
-      <c r="I13" t="n">
-        <v>10</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J13" t="n">
         <v>10</v>
@@ -1324,8 +1348,10 @@
       <c r="H14" t="n">
         <v>78</v>
       </c>
-      <c r="I14" t="n">
-        <v>5</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -1389,8 +1415,10 @@
       <c r="H15" t="n">
         <v>78</v>
       </c>
-      <c r="I15" t="n">
-        <v>7</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J15" t="n">
         <v>7</v>
@@ -1454,8 +1482,10 @@
       <c r="H16" t="n">
         <v>78</v>
       </c>
-      <c r="I16" t="n">
-        <v>10</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J16" t="n">
         <v>10</v>
@@ -1519,8 +1549,10 @@
       <c r="H17" t="n">
         <v>28</v>
       </c>
-      <c r="I17" t="n">
-        <v>6</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J17" t="n">
         <v>6</v>
@@ -1584,8 +1616,10 @@
       <c r="H18" t="n">
         <v>28</v>
       </c>
-      <c r="I18" t="n">
-        <v>9</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="J18" t="n">
         <v>9</v>
@@ -1649,8 +1683,10 @@
       <c r="H19" t="n">
         <v>28</v>
       </c>
-      <c r="I19" t="n">
-        <v>12</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J19" t="n">
         <v>12</v>
@@ -1714,8 +1750,10 @@
       <c r="H20" t="n">
         <v>32</v>
       </c>
-      <c r="I20" t="n">
-        <v>5</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -1779,8 +1817,10 @@
       <c r="H21" t="n">
         <v>32</v>
       </c>
-      <c r="I21" t="n">
-        <v>7</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J21" t="n">
         <v>7</v>
@@ -1844,8 +1884,10 @@
       <c r="H22" t="n">
         <v>32</v>
       </c>
-      <c r="I22" t="n">
-        <v>10</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J22" t="n">
         <v>10</v>
@@ -1909,8 +1951,10 @@
       <c r="H23" t="n">
         <v>30</v>
       </c>
-      <c r="I23" t="n">
-        <v>3</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -1974,8 +2018,10 @@
       <c r="H24" t="n">
         <v>30</v>
       </c>
-      <c r="I24" t="n">
-        <v>6</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J24" t="n">
         <v>6</v>
@@ -2039,8 +2085,10 @@
       <c r="H25" t="n">
         <v>30</v>
       </c>
-      <c r="I25" t="n">
-        <v>9</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="J25" t="n">
         <v>9</v>
@@ -2104,8 +2152,10 @@
       <c r="H26" t="n">
         <v>82</v>
       </c>
-      <c r="I26" t="n">
-        <v>5</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -2169,8 +2219,10 @@
       <c r="H27" t="n">
         <v>82</v>
       </c>
-      <c r="I27" t="n">
-        <v>8</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J27" t="n">
         <v>8</v>
@@ -2234,8 +2286,10 @@
       <c r="H28" t="n">
         <v>82</v>
       </c>
-      <c r="I28" t="n">
-        <v>12</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J28" t="n">
         <v>12</v>
@@ -2299,8 +2353,10 @@
       <c r="H29" t="n">
         <v>20</v>
       </c>
-      <c r="I29" t="n">
-        <v>8</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J29" t="n">
         <v>8</v>
@@ -2364,8 +2420,10 @@
       <c r="H30" t="n">
         <v>20</v>
       </c>
-      <c r="I30" t="n">
-        <v>12</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J30" t="n">
         <v>12</v>
@@ -2429,8 +2487,10 @@
       <c r="H31" t="n">
         <v>20</v>
       </c>
-      <c r="I31" t="n">
-        <v>16</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J31" t="n">
         <v>16</v>
@@ -2494,8 +2554,10 @@
       <c r="H32" t="n">
         <v>82</v>
       </c>
-      <c r="I32" t="n">
-        <v>10</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J32" t="n">
         <v>10</v>
@@ -2559,8 +2621,10 @@
       <c r="H33" t="n">
         <v>82</v>
       </c>
-      <c r="I33" t="n">
-        <v>15</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J33" t="n">
         <v>15</v>
@@ -2624,8 +2688,10 @@
       <c r="H34" t="n">
         <v>82</v>
       </c>
-      <c r="I34" t="n">
-        <v>18</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J34" t="n">
         <v>18</v>
@@ -2689,8 +2755,10 @@
       <c r="H35" t="n">
         <v>30</v>
       </c>
-      <c r="I35" t="n">
-        <v>6</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J35" t="n">
         <v>6</v>
@@ -2754,8 +2822,10 @@
       <c r="H36" t="n">
         <v>30</v>
       </c>
-      <c r="I36" t="n">
-        <v>10</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J36" t="n">
         <v>10</v>
@@ -2819,8 +2889,10 @@
       <c r="H37" t="n">
         <v>30</v>
       </c>
-      <c r="I37" t="n">
-        <v>15</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J37" t="n">
         <v>15</v>
@@ -2884,8 +2956,10 @@
       <c r="H38" t="n">
         <v>85</v>
       </c>
-      <c r="I38" t="n">
-        <v>6</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J38" t="n">
         <v>6</v>
@@ -2949,8 +3023,10 @@
       <c r="H39" t="n">
         <v>85</v>
       </c>
-      <c r="I39" t="n">
-        <v>9</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="J39" t="n">
         <v>9</v>
@@ -3014,8 +3090,10 @@
       <c r="H40" t="n">
         <v>85</v>
       </c>
-      <c r="I40" t="n">
-        <v>12</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J40" t="n">
         <v>12</v>
@@ -3079,8 +3157,10 @@
       <c r="H41" t="n">
         <v>25</v>
       </c>
-      <c r="I41" t="n">
-        <v>6</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J41" t="n">
         <v>6</v>
@@ -3144,8 +3224,10 @@
       <c r="H42" t="n">
         <v>25</v>
       </c>
-      <c r="I42" t="n">
-        <v>10</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J42" t="n">
         <v>10</v>
@@ -3209,8 +3291,10 @@
       <c r="H43" t="n">
         <v>25</v>
       </c>
-      <c r="I43" t="n">
-        <v>15</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J43" t="n">
         <v>15</v>
@@ -3274,8 +3358,10 @@
       <c r="H44" t="n">
         <v>90</v>
       </c>
-      <c r="I44" t="n">
-        <v>7</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J44" t="n">
         <v>7</v>
@@ -3339,8 +3425,10 @@
       <c r="H45" t="n">
         <v>90</v>
       </c>
-      <c r="I45" t="n">
-        <v>12</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J45" t="n">
         <v>12</v>
@@ -3404,8 +3492,10 @@
       <c r="H46" t="n">
         <v>90</v>
       </c>
-      <c r="I46" t="n">
-        <v>16</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J46" t="n">
         <v>16</v>
@@ -3469,8 +3559,10 @@
       <c r="H47" t="n">
         <v>15</v>
       </c>
-      <c r="I47" t="n">
-        <v>12</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J47" t="n">
         <v>12</v>
@@ -3534,8 +3626,10 @@
       <c r="H48" t="n">
         <v>15</v>
       </c>
-      <c r="I48" t="n">
-        <v>15</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J48" t="n">
         <v>15</v>
@@ -3599,8 +3693,10 @@
       <c r="H49" t="n">
         <v>15</v>
       </c>
-      <c r="I49" t="n">
-        <v>18</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J49" t="n">
         <v>18</v>
@@ -3664,8 +3760,10 @@
       <c r="H50" t="n">
         <v>78</v>
       </c>
-      <c r="I50" t="n">
-        <v>5</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J50" t="n">
         <v>5</v>
@@ -3729,8 +3827,10 @@
       <c r="H51" t="n">
         <v>78</v>
       </c>
-      <c r="I51" t="n">
-        <v>8</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J51" t="n">
         <v>8</v>
@@ -3794,8 +3894,10 @@
       <c r="H52" t="n">
         <v>78</v>
       </c>
-      <c r="I52" t="n">
-        <v>12</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J52" t="n">
         <v>12</v>
@@ -3859,8 +3961,10 @@
       <c r="H53" t="n">
         <v>88</v>
       </c>
-      <c r="I53" t="n">
-        <v>10</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J53" t="n">
         <v>10</v>
@@ -3924,8 +4028,10 @@
       <c r="H54" t="n">
         <v>88</v>
       </c>
-      <c r="I54" t="n">
-        <v>14</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J54" t="n">
         <v>14</v>
@@ -3989,8 +4095,10 @@
       <c r="H55" t="n">
         <v>88</v>
       </c>
-      <c r="I55" t="n">
-        <v>18</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J55" t="n">
         <v>18</v>
@@ -4054,8 +4162,10 @@
       <c r="H56" t="n">
         <v>22</v>
       </c>
-      <c r="I56" t="n">
-        <v>2</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
@@ -4119,8 +4229,10 @@
       <c r="H57" t="n">
         <v>22</v>
       </c>
-      <c r="I57" t="n">
-        <v>3</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J57" t="n">
         <v>3</v>
@@ -4184,8 +4296,10 @@
       <c r="H58" t="n">
         <v>22</v>
       </c>
-      <c r="I58" t="n">
-        <v>5</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J58" t="n">
         <v>5</v>
@@ -4249,8 +4363,10 @@
       <c r="H59" t="n">
         <v>80</v>
       </c>
-      <c r="I59" t="n">
-        <v>3</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J59" t="n">
         <v>3</v>
@@ -4314,8 +4430,10 @@
       <c r="H60" t="n">
         <v>80</v>
       </c>
-      <c r="I60" t="n">
-        <v>5</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J60" t="n">
         <v>5</v>
@@ -4379,8 +4497,10 @@
       <c r="H61" t="n">
         <v>80</v>
       </c>
-      <c r="I61" t="n">
-        <v>8</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J61" t="n">
         <v>8</v>
@@ -4444,8 +4564,10 @@
       <c r="H62" t="n">
         <v>12</v>
       </c>
-      <c r="I62" t="n">
-        <v>8</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J62" t="n">
         <v>8</v>
@@ -4509,8 +4631,10 @@
       <c r="H63" t="n">
         <v>12</v>
       </c>
-      <c r="I63" t="n">
-        <v>12</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J63" t="n">
         <v>12</v>
@@ -4574,8 +4698,10 @@
       <c r="H64" t="n">
         <v>12</v>
       </c>
-      <c r="I64" t="n">
-        <v>15</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J64" t="n">
         <v>15</v>
@@ -4639,8 +4765,10 @@
       <c r="H65" t="n">
         <v>92</v>
       </c>
-      <c r="I65" t="n">
-        <v>5</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J65" t="n">
         <v>5</v>
@@ -4704,8 +4832,10 @@
       <c r="H66" t="n">
         <v>92</v>
       </c>
-      <c r="I66" t="n">
-        <v>8</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J66" t="n">
         <v>8</v>
@@ -4769,8 +4899,10 @@
       <c r="H67" t="n">
         <v>92</v>
       </c>
-      <c r="I67" t="n">
-        <v>12</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J67" t="n">
         <v>12</v>
@@ -4834,8 +4966,10 @@
       <c r="H68" t="n">
         <v>30</v>
       </c>
-      <c r="I68" t="n">
-        <v>5</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J68" t="n">
         <v>5</v>
@@ -4899,8 +5033,10 @@
       <c r="H69" t="n">
         <v>30</v>
       </c>
-      <c r="I69" t="n">
-        <v>8</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J69" t="n">
         <v>8</v>
@@ -4964,8 +5100,10 @@
       <c r="H70" t="n">
         <v>30</v>
       </c>
-      <c r="I70" t="n">
-        <v>12</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J70" t="n">
         <v>12</v>
@@ -5029,8 +5167,10 @@
       <c r="H71" t="n">
         <v>70</v>
       </c>
-      <c r="I71" t="n">
-        <v>4</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J71" t="n">
         <v>4</v>
@@ -5094,8 +5234,10 @@
       <c r="H72" t="n">
         <v>70</v>
       </c>
-      <c r="I72" t="n">
-        <v>7</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J72" t="n">
         <v>7</v>
@@ -5159,8 +5301,10 @@
       <c r="H73" t="n">
         <v>70</v>
       </c>
-      <c r="I73" t="n">
-        <v>10</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J73" t="n">
         <v>10</v>
@@ -5224,8 +5368,10 @@
       <c r="H74" t="n">
         <v>55</v>
       </c>
-      <c r="I74" t="n">
-        <v>4</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J74" t="n">
         <v>4</v>
@@ -5289,8 +5435,10 @@
       <c r="H75" t="n">
         <v>55</v>
       </c>
-      <c r="I75" t="n">
-        <v>7</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J75" t="n">
         <v>7</v>
@@ -5354,8 +5502,10 @@
       <c r="H76" t="n">
         <v>55</v>
       </c>
-      <c r="I76" t="n">
-        <v>10</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J76" t="n">
         <v>10</v>
@@ -5419,8 +5569,10 @@
       <c r="H77" t="n">
         <v>58</v>
       </c>
-      <c r="I77" t="n">
-        <v>3</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J77" t="n">
         <v>3</v>
@@ -5484,8 +5636,10 @@
       <c r="H78" t="n">
         <v>58</v>
       </c>
-      <c r="I78" t="n">
-        <v>8</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J78" t="n">
         <v>8</v>
@@ -5549,8 +5703,10 @@
       <c r="H79" t="n">
         <v>58</v>
       </c>
-      <c r="I79" t="n">
-        <v>15</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J79" t="n">
         <v>15</v>
@@ -5614,8 +5770,10 @@
       <c r="H80" t="n">
         <v>65</v>
       </c>
-      <c r="I80" t="n">
-        <v>4</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J80" t="n">
         <v>4</v>
@@ -5679,8 +5837,10 @@
       <c r="H81" t="n">
         <v>65</v>
       </c>
-      <c r="I81" t="n">
-        <v>10</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J81" t="n">
         <v>10</v>
@@ -5744,8 +5904,10 @@
       <c r="H82" t="n">
         <v>65</v>
       </c>
-      <c r="I82" t="n">
-        <v>18</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J82" t="n">
         <v>18</v>
@@ -5809,8 +5971,10 @@
       <c r="H83" t="n">
         <v>50</v>
       </c>
-      <c r="I83" t="n">
-        <v>5</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J83" t="n">
         <v>5</v>
@@ -5874,8 +6038,10 @@
       <c r="H84" t="n">
         <v>50</v>
       </c>
-      <c r="I84" t="n">
-        <v>12</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J84" t="n">
         <v>12</v>
@@ -5939,8 +6105,10 @@
       <c r="H85" t="n">
         <v>50</v>
       </c>
-      <c r="I85" t="n">
-        <v>20</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="J85" t="n">
         <v>20</v>
@@ -6004,8 +6172,10 @@
       <c r="H86" t="n">
         <v>40</v>
       </c>
-      <c r="I86" t="n">
-        <v>2</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
@@ -6069,8 +6239,10 @@
       <c r="H87" t="n">
         <v>40</v>
       </c>
-      <c r="I87" t="n">
-        <v>7</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J87" t="n">
         <v>7</v>
@@ -6134,8 +6306,10 @@
       <c r="H88" t="n">
         <v>40</v>
       </c>
-      <c r="I88" t="n">
-        <v>14</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J88" t="n">
         <v>14</v>
@@ -6199,8 +6373,10 @@
       <c r="H89" t="n">
         <v>72</v>
       </c>
-      <c r="I89" t="n">
-        <v>6</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J89" t="n">
         <v>6</v>
@@ -6264,8 +6440,10 @@
       <c r="H90" t="n">
         <v>72</v>
       </c>
-      <c r="I90" t="n">
-        <v>10</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J90" t="n">
         <v>10</v>
@@ -6329,8 +6507,10 @@
       <c r="H91" t="n">
         <v>72</v>
       </c>
-      <c r="I91" t="n">
-        <v>16</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J91" t="n">
         <v>16</v>
@@ -6394,8 +6574,10 @@
       <c r="H92" t="n">
         <v>52</v>
       </c>
-      <c r="I92" t="n">
-        <v>5</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J92" t="n">
         <v>5</v>
@@ -6459,8 +6641,10 @@
       <c r="H93" t="n">
         <v>52</v>
       </c>
-      <c r="I93" t="n">
-        <v>8</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J93" t="n">
         <v>8</v>
@@ -6524,8 +6708,10 @@
       <c r="H94" t="n">
         <v>52</v>
       </c>
-      <c r="I94" t="n">
-        <v>12</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J94" t="n">
         <v>12</v>
@@ -6589,8 +6775,10 @@
       <c r="H95" t="n">
         <v>45</v>
       </c>
-      <c r="I95" t="n">
-        <v>5</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J95" t="n">
         <v>5</v>
@@ -6654,8 +6842,10 @@
       <c r="H96" t="n">
         <v>45</v>
       </c>
-      <c r="I96" t="n">
-        <v>8</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J96" t="n">
         <v>8</v>
@@ -6719,8 +6909,10 @@
       <c r="H97" t="n">
         <v>45</v>
       </c>
-      <c r="I97" t="n">
-        <v>12</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J97" t="n">
         <v>12</v>
@@ -6784,8 +6976,10 @@
       <c r="H98" t="n">
         <v>60</v>
       </c>
-      <c r="I98" t="n">
-        <v>5</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J98" t="n">
         <v>5</v>
@@ -6849,8 +7043,10 @@
       <c r="H99" t="n">
         <v>60</v>
       </c>
-      <c r="I99" t="n">
-        <v>8</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J99" t="n">
         <v>8</v>
@@ -6914,8 +7110,10 @@
       <c r="H100" t="n">
         <v>60</v>
       </c>
-      <c r="I100" t="n">
-        <v>12</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J100" t="n">
         <v>12</v>
@@ -6979,8 +7177,10 @@
       <c r="H101" t="n">
         <v>55</v>
       </c>
-      <c r="I101" t="n">
-        <v>5</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J101" t="n">
         <v>5</v>
@@ -7044,8 +7244,10 @@
       <c r="H102" t="n">
         <v>55</v>
       </c>
-      <c r="I102" t="n">
-        <v>8</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J102" t="n">
         <v>8</v>
@@ -7109,8 +7311,10 @@
       <c r="H103" t="n">
         <v>55</v>
       </c>
-      <c r="I103" t="n">
-        <v>12</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J103" t="n">
         <v>12</v>
@@ -7174,8 +7378,10 @@
       <c r="H104" t="n">
         <v>48</v>
       </c>
-      <c r="I104" t="n">
-        <v>5</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J104" t="n">
         <v>5</v>
@@ -7239,8 +7445,10 @@
       <c r="H105" t="n">
         <v>48</v>
       </c>
-      <c r="I105" t="n">
-        <v>8</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J105" t="n">
         <v>8</v>
@@ -7304,8 +7512,10 @@
       <c r="H106" t="n">
         <v>48</v>
       </c>
-      <c r="I106" t="n">
-        <v>12</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J106" t="n">
         <v>12</v>
@@ -7369,8 +7579,10 @@
       <c r="H107" t="n">
         <v>55</v>
       </c>
-      <c r="I107" t="n">
-        <v>8</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J107" t="n">
         <v>8</v>
@@ -7434,8 +7646,10 @@
       <c r="H108" t="n">
         <v>55</v>
       </c>
-      <c r="I108" t="n">
-        <v>10</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J108" t="n">
         <v>10</v>
@@ -7499,8 +7713,10 @@
       <c r="H109" t="n">
         <v>55</v>
       </c>
-      <c r="I109" t="n">
-        <v>12</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J109" t="n">
         <v>12</v>
@@ -7564,8 +7780,10 @@
       <c r="H110" t="n">
         <v>50</v>
       </c>
-      <c r="I110" t="n">
-        <v>8</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J110" t="n">
         <v>8</v>
@@ -7629,8 +7847,10 @@
       <c r="H111" t="n">
         <v>50</v>
       </c>
-      <c r="I111" t="n">
-        <v>10</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J111" t="n">
         <v>10</v>
@@ -7694,8 +7914,10 @@
       <c r="H112" t="n">
         <v>50</v>
       </c>
-      <c r="I112" t="n">
-        <v>12</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J112" t="n">
         <v>12</v>
@@ -7759,8 +7981,10 @@
       <c r="H113" t="n">
         <v>60</v>
       </c>
-      <c r="I113" t="n">
-        <v>8</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J113" t="n">
         <v>8</v>
@@ -7824,8 +8048,10 @@
       <c r="H114" t="n">
         <v>60</v>
       </c>
-      <c r="I114" t="n">
-        <v>10</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J114" t="n">
         <v>10</v>
@@ -7889,8 +8115,10 @@
       <c r="H115" t="n">
         <v>60</v>
       </c>
-      <c r="I115" t="n">
-        <v>12</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J115" t="n">
         <v>12</v>
@@ -7954,8 +8182,10 @@
       <c r="H116" t="n">
         <v>55</v>
       </c>
-      <c r="I116" t="n">
-        <v>8</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J116" t="n">
         <v>8</v>
@@ -8019,8 +8249,10 @@
       <c r="H117" t="n">
         <v>55</v>
       </c>
-      <c r="I117" t="n">
-        <v>10</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J117" t="n">
         <v>10</v>
@@ -8084,8 +8316,10 @@
       <c r="H118" t="n">
         <v>55</v>
       </c>
-      <c r="I118" t="n">
-        <v>12</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J118" t="n">
         <v>12</v>
@@ -8149,8 +8383,10 @@
       <c r="H119" t="n">
         <v>58</v>
       </c>
-      <c r="I119" t="n">
-        <v>8</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J119" t="n">
         <v>8</v>
@@ -8214,8 +8450,10 @@
       <c r="H120" t="n">
         <v>58</v>
       </c>
-      <c r="I120" t="n">
-        <v>10</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J120" t="n">
         <v>10</v>
@@ -8279,8 +8517,10 @@
       <c r="H121" t="n">
         <v>58</v>
       </c>
-      <c r="I121" t="n">
-        <v>12</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J121" t="n">
         <v>12</v>
@@ -8344,8 +8584,10 @@
       <c r="H122" t="n">
         <v>10</v>
       </c>
-      <c r="I122" t="n">
-        <v>5</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J122" t="n">
         <v>5</v>
@@ -8409,8 +8651,10 @@
       <c r="H123" t="n">
         <v>10</v>
       </c>
-      <c r="I123" t="n">
-        <v>8</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J123" t="n">
         <v>8</v>
@@ -8474,8 +8718,10 @@
       <c r="H124" t="n">
         <v>10</v>
       </c>
-      <c r="I124" t="n">
-        <v>12</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J124" t="n">
         <v>12</v>
@@ -8539,8 +8785,10 @@
       <c r="H125" t="n">
         <v>20</v>
       </c>
-      <c r="I125" t="n">
-        <v>5</v>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J125" t="n">
         <v>5</v>
@@ -8604,8 +8852,10 @@
       <c r="H126" t="n">
         <v>20</v>
       </c>
-      <c r="I126" t="n">
-        <v>8</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J126" t="n">
         <v>8</v>
@@ -8669,8 +8919,10 @@
       <c r="H127" t="n">
         <v>20</v>
       </c>
-      <c r="I127" t="n">
-        <v>12</v>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J127" t="n">
         <v>12</v>
@@ -8734,8 +8986,10 @@
       <c r="H128" t="n">
         <v>32</v>
       </c>
-      <c r="I128" t="n">
-        <v>5</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J128" t="n">
         <v>5</v>
@@ -8799,8 +9053,10 @@
       <c r="H129" t="n">
         <v>32</v>
       </c>
-      <c r="I129" t="n">
-        <v>8</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J129" t="n">
         <v>8</v>
@@ -8864,8 +9120,10 @@
       <c r="H130" t="n">
         <v>32</v>
       </c>
-      <c r="I130" t="n">
-        <v>12</v>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J130" t="n">
         <v>12</v>
@@ -8929,8 +9187,10 @@
       <c r="H131" t="n">
         <v>75</v>
       </c>
-      <c r="I131" t="n">
-        <v>5</v>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J131" t="n">
         <v>5</v>
@@ -8994,8 +9254,10 @@
       <c r="H132" t="n">
         <v>75</v>
       </c>
-      <c r="I132" t="n">
-        <v>8</v>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J132" t="n">
         <v>8</v>
@@ -9059,8 +9321,10 @@
       <c r="H133" t="n">
         <v>75</v>
       </c>
-      <c r="I133" t="n">
-        <v>12</v>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J133" t="n">
         <v>12</v>
@@ -9124,8 +9388,10 @@
       <c r="H134" t="n">
         <v>92</v>
       </c>
-      <c r="I134" t="n">
-        <v>5</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J134" t="n">
         <v>5</v>
@@ -9189,8 +9455,10 @@
       <c r="H135" t="n">
         <v>92</v>
       </c>
-      <c r="I135" t="n">
-        <v>8</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J135" t="n">
         <v>8</v>
@@ -9254,8 +9522,10 @@
       <c r="H136" t="n">
         <v>92</v>
       </c>
-      <c r="I136" t="n">
-        <v>12</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J136" t="n">
         <v>12</v>
@@ -9319,8 +9589,10 @@
       <c r="H137" t="n">
         <v>42</v>
       </c>
-      <c r="I137" t="n">
-        <v>4</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J137" t="n">
         <v>4</v>
@@ -9384,8 +9656,10 @@
       <c r="H138" t="n">
         <v>42</v>
       </c>
-      <c r="I138" t="n">
-        <v>7</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J138" t="n">
         <v>7</v>
@@ -9449,8 +9723,10 @@
       <c r="H139" t="n">
         <v>42</v>
       </c>
-      <c r="I139" t="n">
-        <v>10</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J139" t="n">
         <v>10</v>
@@ -9514,8 +9790,10 @@
       <c r="H140" t="n">
         <v>38</v>
       </c>
-      <c r="I140" t="n">
-        <v>4</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J140" t="n">
         <v>4</v>
@@ -9579,8 +9857,10 @@
       <c r="H141" t="n">
         <v>38</v>
       </c>
-      <c r="I141" t="n">
-        <v>7</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J141" t="n">
         <v>7</v>
@@ -9644,8 +9924,10 @@
       <c r="H142" t="n">
         <v>38</v>
       </c>
-      <c r="I142" t="n">
-        <v>10</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J142" t="n">
         <v>10</v>
@@ -9709,8 +9991,10 @@
       <c r="H143" t="n">
         <v>55</v>
       </c>
-      <c r="I143" t="n">
-        <v>1</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J143" t="n">
         <v>1</v>
@@ -9774,8 +10058,10 @@
       <c r="H144" t="n">
         <v>55</v>
       </c>
-      <c r="I144" t="n">
-        <v>6</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J144" t="n">
         <v>6</v>
@@ -9839,8 +10125,10 @@
       <c r="H145" t="n">
         <v>55</v>
       </c>
-      <c r="I145" t="n">
-        <v>12</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J145" t="n">
         <v>12</v>
@@ -9904,8 +10192,10 @@
       <c r="H146" t="n">
         <v>62</v>
       </c>
-      <c r="I146" t="n">
-        <v>7</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J146" t="n">
         <v>7</v>
@@ -9969,8 +10259,10 @@
       <c r="H147" t="n">
         <v>62</v>
       </c>
-      <c r="I147" t="n">
-        <v>14</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J147" t="n">
         <v>14</v>
@@ -10034,8 +10326,10 @@
       <c r="H148" t="n">
         <v>62</v>
       </c>
-      <c r="I148" t="n">
-        <v>22</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="J148" t="n">
         <v>22</v>
@@ -10099,8 +10393,10 @@
       <c r="H149" t="n">
         <v>50</v>
       </c>
-      <c r="I149" t="n">
-        <v>5</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J149" t="n">
         <v>5</v>
@@ -10164,8 +10460,10 @@
       <c r="H150" t="n">
         <v>50</v>
       </c>
-      <c r="I150" t="n">
-        <v>8</v>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J150" t="n">
         <v>8</v>
@@ -10229,8 +10527,10 @@
       <c r="H151" t="n">
         <v>50</v>
       </c>
-      <c r="I151" t="n">
-        <v>12</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J151" t="n">
         <v>12</v>
@@ -10294,8 +10594,10 @@
       <c r="H152" t="n">
         <v>58</v>
       </c>
-      <c r="I152" t="n">
-        <v>5</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J152" t="n">
         <v>5</v>
@@ -10359,8 +10661,10 @@
       <c r="H153" t="n">
         <v>58</v>
       </c>
-      <c r="I153" t="n">
-        <v>8</v>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J153" t="n">
         <v>8</v>
@@ -10424,8 +10728,10 @@
       <c r="H154" t="n">
         <v>58</v>
       </c>
-      <c r="I154" t="n">
-        <v>12</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J154" t="n">
         <v>12</v>
@@ -10489,8 +10795,10 @@
       <c r="H155" t="n">
         <v>55</v>
       </c>
-      <c r="I155" t="n">
-        <v>6</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J155" t="n">
         <v>6</v>
@@ -10554,8 +10862,10 @@
       <c r="H156" t="n">
         <v>55</v>
       </c>
-      <c r="I156" t="n">
-        <v>8</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J156" t="n">
         <v>8</v>
@@ -10619,8 +10929,10 @@
       <c r="H157" t="n">
         <v>55</v>
       </c>
-      <c r="I157" t="n">
-        <v>10</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J157" t="n">
         <v>10</v>
@@ -10684,8 +10996,10 @@
       <c r="H158" t="n">
         <v>58</v>
       </c>
-      <c r="I158" t="n">
-        <v>8</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J158" t="n">
         <v>8</v>
@@ -10749,8 +11063,10 @@
       <c r="H159" t="n">
         <v>58</v>
       </c>
-      <c r="I159" t="n">
-        <v>10</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J159" t="n">
         <v>10</v>
@@ -10814,8 +11130,10 @@
       <c r="H160" t="n">
         <v>58</v>
       </c>
-      <c r="I160" t="n">
-        <v>12</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J160" t="n">
         <v>12</v>
@@ -10879,8 +11197,10 @@
       <c r="H161" t="n">
         <v>5</v>
       </c>
-      <c r="I161" t="n">
-        <v>5</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J161" t="n">
         <v>5</v>
@@ -10944,8 +11264,10 @@
       <c r="H162" t="n">
         <v>5</v>
       </c>
-      <c r="I162" t="n">
-        <v>8</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J162" t="n">
         <v>8</v>
@@ -11009,8 +11331,10 @@
       <c r="H163" t="n">
         <v>5</v>
       </c>
-      <c r="I163" t="n">
-        <v>12</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J163" t="n">
         <v>12</v>
@@ -11074,8 +11398,10 @@
       <c r="H164" t="n">
         <v>85</v>
       </c>
-      <c r="I164" t="n">
-        <v>5</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J164" t="n">
         <v>5</v>
@@ -11139,8 +11465,10 @@
       <c r="H165" t="n">
         <v>85</v>
       </c>
-      <c r="I165" t="n">
-        <v>8</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J165" t="n">
         <v>8</v>
@@ -11204,8 +11532,10 @@
       <c r="H166" t="n">
         <v>85</v>
       </c>
-      <c r="I166" t="n">
-        <v>12</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J166" t="n">
         <v>12</v>
@@ -11269,8 +11599,10 @@
       <c r="H167" t="n">
         <v>65</v>
       </c>
-      <c r="I167" t="n">
-        <v>3</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J167" t="n">
         <v>3</v>
@@ -11334,8 +11666,10 @@
       <c r="H168" t="n">
         <v>65</v>
       </c>
-      <c r="I168" t="n">
-        <v>5</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J168" t="n">
         <v>5</v>
@@ -11399,8 +11733,10 @@
       <c r="H169" t="n">
         <v>65</v>
       </c>
-      <c r="I169" t="n">
-        <v>8</v>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J169" t="n">
         <v>8</v>
@@ -11464,8 +11800,10 @@
       <c r="H170" t="n">
         <v>78</v>
       </c>
-      <c r="I170" t="n">
-        <v>3</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J170" t="n">
         <v>3</v>
@@ -11529,8 +11867,10 @@
       <c r="H171" t="n">
         <v>78</v>
       </c>
-      <c r="I171" t="n">
-        <v>5</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J171" t="n">
         <v>5</v>
@@ -11594,8 +11934,10 @@
       <c r="H172" t="n">
         <v>78</v>
       </c>
-      <c r="I172" t="n">
-        <v>8</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J172" t="n">
         <v>8</v>
@@ -11659,8 +12001,10 @@
       <c r="H173" t="n">
         <v>72</v>
       </c>
-      <c r="I173" t="n">
-        <v>3</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J173" t="n">
         <v>3</v>
@@ -11724,8 +12068,10 @@
       <c r="H174" t="n">
         <v>72</v>
       </c>
-      <c r="I174" t="n">
-        <v>5</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J174" t="n">
         <v>5</v>
@@ -11789,8 +12135,10 @@
       <c r="H175" t="n">
         <v>72</v>
       </c>
-      <c r="I175" t="n">
-        <v>8</v>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J175" t="n">
         <v>8</v>
@@ -11854,8 +12202,10 @@
       <c r="H176" t="n">
         <v>58</v>
       </c>
-      <c r="I176" t="n">
-        <v>3</v>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J176" t="n">
         <v>3</v>
@@ -11919,8 +12269,10 @@
       <c r="H177" t="n">
         <v>58</v>
       </c>
-      <c r="I177" t="n">
-        <v>5</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J177" t="n">
         <v>5</v>
@@ -11984,8 +12336,10 @@
       <c r="H178" t="n">
         <v>58</v>
       </c>
-      <c r="I178" t="n">
-        <v>8</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J178" t="n">
         <v>8</v>
@@ -12049,8 +12403,10 @@
       <c r="H179" t="n">
         <v>35</v>
       </c>
-      <c r="I179" t="n">
-        <v>4</v>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J179" t="n">
         <v>4</v>
@@ -12114,8 +12470,10 @@
       <c r="H180" t="n">
         <v>35</v>
       </c>
-      <c r="I180" t="n">
-        <v>6</v>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J180" t="n">
         <v>6</v>
@@ -12179,8 +12537,10 @@
       <c r="H181" t="n">
         <v>35</v>
       </c>
-      <c r="I181" t="n">
-        <v>10</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J181" t="n">
         <v>10</v>
@@ -12244,8 +12604,10 @@
       <c r="H182" t="n">
         <v>48</v>
       </c>
-      <c r="I182" t="n">
-        <v>4</v>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J182" t="n">
         <v>4</v>
@@ -12309,8 +12671,10 @@
       <c r="H183" t="n">
         <v>48</v>
       </c>
-      <c r="I183" t="n">
-        <v>6</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J183" t="n">
         <v>6</v>
@@ -12374,8 +12738,10 @@
       <c r="H184" t="n">
         <v>48</v>
       </c>
-      <c r="I184" t="n">
-        <v>10</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J184" t="n">
         <v>10</v>
@@ -12439,8 +12805,10 @@
       <c r="H185" t="n">
         <v>62</v>
       </c>
-      <c r="I185" t="n">
-        <v>3</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J185" t="n">
         <v>3</v>
@@ -12504,8 +12872,10 @@
       <c r="H186" t="n">
         <v>62</v>
       </c>
-      <c r="I186" t="n">
-        <v>5</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J186" t="n">
         <v>5</v>
@@ -12569,8 +12939,10 @@
       <c r="H187" t="n">
         <v>62</v>
       </c>
-      <c r="I187" t="n">
-        <v>8</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J187" t="n">
         <v>8</v>
@@ -12634,8 +13006,10 @@
       <c r="H188" t="n">
         <v>70</v>
       </c>
-      <c r="I188" t="n">
-        <v>3</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J188" t="n">
         <v>3</v>
@@ -12699,8 +13073,10 @@
       <c r="H189" t="n">
         <v>70</v>
       </c>
-      <c r="I189" t="n">
-        <v>4</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J189" t="n">
         <v>4</v>
@@ -12764,8 +13140,10 @@
       <c r="H190" t="n">
         <v>70</v>
       </c>
-      <c r="I190" t="n">
-        <v>6</v>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J190" t="n">
         <v>6</v>
@@ -12829,8 +13207,10 @@
       <c r="H191" t="n">
         <v>28</v>
       </c>
-      <c r="I191" t="n">
-        <v>3</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J191" t="n">
         <v>3</v>
@@ -12894,8 +13274,10 @@
       <c r="H192" t="n">
         <v>28</v>
       </c>
-      <c r="I192" t="n">
-        <v>5</v>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J192" t="n">
         <v>5</v>
@@ -12959,8 +13341,10 @@
       <c r="H193" t="n">
         <v>28</v>
       </c>
-      <c r="I193" t="n">
-        <v>8</v>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J193" t="n">
         <v>8</v>
@@ -13024,8 +13408,10 @@
       <c r="H194" t="n">
         <v>62</v>
       </c>
-      <c r="I194" t="n">
-        <v>3</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J194" t="n">
         <v>3</v>
@@ -13089,8 +13475,10 @@
       <c r="H195" t="n">
         <v>62</v>
       </c>
-      <c r="I195" t="n">
-        <v>5</v>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J195" t="n">
         <v>5</v>
@@ -13154,8 +13542,10 @@
       <c r="H196" t="n">
         <v>62</v>
       </c>
-      <c r="I196" t="n">
-        <v>8</v>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J196" t="n">
         <v>8</v>
@@ -13219,8 +13609,10 @@
       <c r="H197" t="n">
         <v>75</v>
       </c>
-      <c r="I197" t="n">
-        <v>3</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J197" t="n">
         <v>3</v>
@@ -13284,8 +13676,10 @@
       <c r="H198" t="n">
         <v>75</v>
       </c>
-      <c r="I198" t="n">
-        <v>5</v>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J198" t="n">
         <v>5</v>
@@ -13349,8 +13743,10 @@
       <c r="H199" t="n">
         <v>75</v>
       </c>
-      <c r="I199" t="n">
-        <v>8</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J199" t="n">
         <v>8</v>
@@ -13414,8 +13810,10 @@
       <c r="H200" t="n">
         <v>55</v>
       </c>
-      <c r="I200" t="n">
-        <v>3</v>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J200" t="n">
         <v>3</v>
@@ -13479,8 +13877,10 @@
       <c r="H201" t="n">
         <v>55</v>
       </c>
-      <c r="I201" t="n">
-        <v>5</v>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J201" t="n">
         <v>5</v>
@@ -13544,8 +13944,10 @@
       <c r="H202" t="n">
         <v>55</v>
       </c>
-      <c r="I202" t="n">
-        <v>7</v>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J202" t="n">
         <v>7</v>
@@ -13609,8 +14011,10 @@
       <c r="H203" t="n">
         <v>62</v>
       </c>
-      <c r="I203" t="n">
-        <v>3</v>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J203" t="n">
         <v>3</v>
@@ -13674,8 +14078,10 @@
       <c r="H204" t="n">
         <v>62</v>
       </c>
-      <c r="I204" t="n">
-        <v>5</v>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J204" t="n">
         <v>5</v>
@@ -13739,8 +14145,10 @@
       <c r="H205" t="n">
         <v>62</v>
       </c>
-      <c r="I205" t="n">
-        <v>8</v>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J205" t="n">
         <v>8</v>
@@ -13804,8 +14212,10 @@
       <c r="H206" t="n">
         <v>48</v>
       </c>
-      <c r="I206" t="n">
-        <v>3</v>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J206" t="n">
         <v>3</v>
@@ -13869,8 +14279,10 @@
       <c r="H207" t="n">
         <v>48</v>
       </c>
-      <c r="I207" t="n">
-        <v>5</v>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J207" t="n">
         <v>5</v>
@@ -13934,8 +14346,10 @@
       <c r="H208" t="n">
         <v>48</v>
       </c>
-      <c r="I208" t="n">
-        <v>8</v>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J208" t="n">
         <v>8</v>
@@ -13999,8 +14413,10 @@
       <c r="H209" t="n">
         <v>70</v>
       </c>
-      <c r="I209" t="n">
-        <v>3</v>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J209" t="n">
         <v>3</v>
@@ -14064,8 +14480,10 @@
       <c r="H210" t="n">
         <v>70</v>
       </c>
-      <c r="I210" t="n">
-        <v>5</v>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J210" t="n">
         <v>5</v>
@@ -14129,8 +14547,10 @@
       <c r="H211" t="n">
         <v>70</v>
       </c>
-      <c r="I211" t="n">
-        <v>7</v>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J211" t="n">
         <v>7</v>
@@ -14194,8 +14614,10 @@
       <c r="H212" t="n">
         <v>38</v>
       </c>
-      <c r="I212" t="n">
-        <v>4</v>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J212" t="n">
         <v>4</v>
@@ -14259,8 +14681,10 @@
       <c r="H213" t="n">
         <v>38</v>
       </c>
-      <c r="I213" t="n">
-        <v>6</v>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J213" t="n">
         <v>6</v>
@@ -14324,8 +14748,10 @@
       <c r="H214" t="n">
         <v>38</v>
       </c>
-      <c r="I214" t="n">
-        <v>10</v>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J214" t="n">
         <v>10</v>
@@ -14389,8 +14815,10 @@
       <c r="H215" t="n">
         <v>45</v>
       </c>
-      <c r="I215" t="n">
-        <v>4</v>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J215" t="n">
         <v>4</v>
@@ -14454,8 +14882,10 @@
       <c r="H216" t="n">
         <v>45</v>
       </c>
-      <c r="I216" t="n">
-        <v>6</v>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J216" t="n">
         <v>6</v>
@@ -14519,8 +14949,10 @@
       <c r="H217" t="n">
         <v>45</v>
       </c>
-      <c r="I217" t="n">
-        <v>10</v>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J217" t="n">
         <v>10</v>
@@ -14584,8 +15016,10 @@
       <c r="H218" t="n">
         <v>52</v>
       </c>
-      <c r="I218" t="n">
-        <v>3</v>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J218" t="n">
         <v>3</v>
@@ -14649,8 +15083,10 @@
       <c r="H219" t="n">
         <v>52</v>
       </c>
-      <c r="I219" t="n">
-        <v>5</v>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J219" t="n">
         <v>5</v>
@@ -14714,8 +15150,10 @@
       <c r="H220" t="n">
         <v>52</v>
       </c>
-      <c r="I220" t="n">
-        <v>8</v>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J220" t="n">
         <v>8</v>
@@ -14779,8 +15217,10 @@
       <c r="H221" t="n">
         <v>48</v>
       </c>
-      <c r="I221" t="n">
-        <v>3</v>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J221" t="n">
         <v>3</v>
@@ -14844,8 +15284,10 @@
       <c r="H222" t="n">
         <v>48</v>
       </c>
-      <c r="I222" t="n">
-        <v>5</v>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J222" t="n">
         <v>5</v>
@@ -14909,8 +15351,10 @@
       <c r="H223" t="n">
         <v>48</v>
       </c>
-      <c r="I223" t="n">
-        <v>8</v>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J223" t="n">
         <v>8</v>
@@ -14974,8 +15418,10 @@
       <c r="H224" t="n">
         <v>35</v>
       </c>
-      <c r="I224" t="n">
-        <v>3</v>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J224" t="n">
         <v>3</v>
@@ -15039,8 +15485,10 @@
       <c r="H225" t="n">
         <v>35</v>
       </c>
-      <c r="I225" t="n">
-        <v>5</v>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J225" t="n">
         <v>5</v>
@@ -15104,8 +15552,10 @@
       <c r="H226" t="n">
         <v>35</v>
       </c>
-      <c r="I226" t="n">
-        <v>8</v>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J226" t="n">
         <v>8</v>
@@ -15169,8 +15619,10 @@
       <c r="H227" t="n">
         <v>60</v>
       </c>
-      <c r="I227" t="n">
-        <v>3</v>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J227" t="n">
         <v>3</v>
@@ -15234,8 +15686,10 @@
       <c r="H228" t="n">
         <v>60</v>
       </c>
-      <c r="I228" t="n">
-        <v>5</v>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J228" t="n">
         <v>5</v>
@@ -15299,8 +15753,10 @@
       <c r="H229" t="n">
         <v>60</v>
       </c>
-      <c r="I229" t="n">
-        <v>8</v>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J229" t="n">
         <v>8</v>
@@ -15364,8 +15820,10 @@
       <c r="H230" t="n">
         <v>42</v>
       </c>
-      <c r="I230" t="n">
-        <v>3</v>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J230" t="n">
         <v>3</v>
@@ -15429,8 +15887,10 @@
       <c r="H231" t="n">
         <v>42</v>
       </c>
-      <c r="I231" t="n">
-        <v>5</v>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J231" t="n">
         <v>5</v>
@@ -15494,8 +15954,10 @@
       <c r="H232" t="n">
         <v>42</v>
       </c>
-      <c r="I232" t="n">
-        <v>8</v>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J232" t="n">
         <v>8</v>
@@ -15559,8 +16021,10 @@
       <c r="H233" t="n">
         <v>18</v>
       </c>
-      <c r="I233" t="n">
-        <v>4</v>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J233" t="n">
         <v>4</v>
@@ -15624,8 +16088,10 @@
       <c r="H234" t="n">
         <v>18</v>
       </c>
-      <c r="I234" t="n">
-        <v>6</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J234" t="n">
         <v>6</v>
@@ -15689,8 +16155,10 @@
       <c r="H235" t="n">
         <v>18</v>
       </c>
-      <c r="I235" t="n">
-        <v>8</v>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J235" t="n">
         <v>8</v>
@@ -15754,8 +16222,10 @@
       <c r="H236" t="n">
         <v>90</v>
       </c>
-      <c r="I236" t="n">
-        <v>4</v>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J236" t="n">
         <v>4</v>
@@ -15819,8 +16289,10 @@
       <c r="H237" t="n">
         <v>90</v>
       </c>
-      <c r="I237" t="n">
-        <v>7</v>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J237" t="n">
         <v>7</v>
@@ -15884,8 +16356,10 @@
       <c r="H238" t="n">
         <v>90</v>
       </c>
-      <c r="I238" t="n">
-        <v>10</v>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J238" t="n">
         <v>10</v>
@@ -15949,8 +16423,10 @@
       <c r="H239" t="n">
         <v>40</v>
       </c>
-      <c r="I239" t="n">
-        <v>5</v>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J239" t="n">
         <v>5</v>
@@ -16014,8 +16490,10 @@
       <c r="H240" t="n">
         <v>40</v>
       </c>
-      <c r="I240" t="n">
-        <v>8</v>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J240" t="n">
         <v>8</v>
@@ -16079,8 +16557,10 @@
       <c r="H241" t="n">
         <v>40</v>
       </c>
-      <c r="I241" t="n">
-        <v>12</v>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="J241" t="n">
         <v>12</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -626,13 +626,13 @@
         <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.63</v>
+        <v>4.76</v>
       </c>
       <c r="N3" t="n">
         <v>3.48</v>
       </c>
       <c r="O3" t="n">
-        <v>7.977</v>
+        <v>7.803</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -693,13 +693,13 @@
         <v>9.33</v>
       </c>
       <c r="M4" t="n">
-        <v>8.56</v>
+        <v>7.11</v>
       </c>
       <c r="N4" t="n">
         <v>7.6</v>
       </c>
       <c r="O4" t="n">
-        <v>8.6435</v>
+        <v>8.3535</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -961,16 +961,16 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N8" t="n">
         <v>3.48</v>
       </c>
       <c r="O8" t="n">
-        <v>8.337</v>
+        <v>8.190999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>1.19415490086141</v>
@@ -1028,13 +1028,13 @@
         <v>9.33</v>
       </c>
       <c r="M9" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N9" t="n">
         <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>8.923499999999999</v>
+        <v>8.669499999999999</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1095,16 +1095,16 @@
         <v>8.44</v>
       </c>
       <c r="M10" t="n">
-        <v>9.210000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="N10" t="n">
         <v>9.25</v>
       </c>
       <c r="O10" t="n">
-        <v>8.307499999999999</v>
+        <v>8.3675</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>2.865971762067384</v>
@@ -1564,13 +1564,13 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>8.42</v>
+        <v>7.4</v>
       </c>
       <c r="N17" t="n">
         <v>5.01</v>
       </c>
       <c r="O17" t="n">
-        <v>7.872</v>
+        <v>7.668</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1631,13 +1631,13 @@
         <v>7.78</v>
       </c>
       <c r="M18" t="n">
-        <v>9.369999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>5.19</v>
       </c>
       <c r="O18" t="n">
-        <v>7.196499999999999</v>
+        <v>7.0945</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1698,13 +1698,13 @@
         <v>6.67</v>
       </c>
       <c r="M19" t="n">
-        <v>7.62</v>
+        <v>7.97</v>
       </c>
       <c r="N19" t="n">
         <v>6.69</v>
       </c>
       <c r="O19" t="n">
-        <v>6.178999999999999</v>
+        <v>6.249</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1765,13 +1765,13 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N20" t="n">
         <v>3.48</v>
       </c>
       <c r="O20" t="n">
-        <v>8.337</v>
+        <v>8.190999999999999</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1832,16 +1832,16 @@
         <v>9.56</v>
       </c>
       <c r="M21" t="n">
-        <v>9.32</v>
+        <v>8.07</v>
       </c>
       <c r="N21" t="n">
         <v>6.37</v>
       </c>
       <c r="O21" t="n">
-        <v>8.7935</v>
+        <v>8.5435</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>1.671816861205974</v>
@@ -1899,16 +1899,16 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>9.59</v>
+        <v>9.85</v>
       </c>
       <c r="N22" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>8.622</v>
+        <v>8.673999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>2.38830980172282</v>
@@ -2033,13 +2033,13 @@
         <v>9.779999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>8.42</v>
+        <v>7.4</v>
       </c>
       <c r="N24" t="n">
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>8.5855</v>
+        <v>8.381499999999999</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2100,13 +2100,13 @@
         <v>9.109999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>9.369999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>5.19</v>
       </c>
       <c r="O25" t="n">
-        <v>8.267999999999999</v>
+        <v>8.165999999999999</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
@@ -2368,13 +2368,13 @@
         <v>6.96</v>
       </c>
       <c r="M29" t="n">
-        <v>9.220000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="N29" t="n">
         <v>4.64</v>
       </c>
       <c r="O29" t="n">
-        <v>6.428</v>
+        <v>6.154</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2435,13 +2435,13 @@
         <v>4.89</v>
       </c>
       <c r="M30" t="n">
-        <v>6.77</v>
+        <v>7.15</v>
       </c>
       <c r="N30" t="n">
         <v>6.69</v>
       </c>
       <c r="O30" t="n">
-        <v>4.579</v>
+        <v>4.655</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2770,13 +2770,13 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>8.42</v>
+        <v>7.4</v>
       </c>
       <c r="N35" t="n">
         <v>5.01</v>
       </c>
       <c r="O35" t="n">
-        <v>7.872</v>
+        <v>7.668</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2837,13 +2837,13 @@
         <v>7.41</v>
       </c>
       <c r="M36" t="n">
-        <v>8.82</v>
+        <v>9.09</v>
       </c>
       <c r="N36" t="n">
         <v>5.71</v>
       </c>
       <c r="O36" t="n">
-        <v>6.866999999999999</v>
+        <v>6.920999999999998</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
@@ -3172,13 +3172,13 @@
         <v>8</v>
       </c>
       <c r="M41" t="n">
-        <v>8.42</v>
+        <v>7.4</v>
       </c>
       <c r="N41" t="n">
         <v>1.51</v>
       </c>
       <c r="O41" t="n">
-        <v>6.6335</v>
+        <v>6.4295</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3239,13 +3239,13 @@
         <v>5.93</v>
       </c>
       <c r="M42" t="n">
-        <v>8.82</v>
+        <v>9.09</v>
       </c>
       <c r="N42" t="n">
         <v>5.71</v>
       </c>
       <c r="O42" t="n">
-        <v>5.677</v>
+        <v>5.730999999999999</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
@@ -3574,13 +3574,13 @@
         <v>4</v>
       </c>
       <c r="M47" t="n">
-        <v>6.77</v>
+        <v>7.15</v>
       </c>
       <c r="N47" t="n">
         <v>6.69</v>
       </c>
       <c r="O47" t="n">
-        <v>3.8625</v>
+        <v>3.9385</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -4253,7 +4253,7 @@
         <v>7.332999999999999</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>0.955323920689128</v>
@@ -4311,16 +4311,16 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>5.63</v>
+        <v>4.76</v>
       </c>
       <c r="N58" t="n">
         <v>1.51</v>
       </c>
       <c r="O58" t="n">
-        <v>7.383999999999999</v>
+        <v>7.209999999999999</v>
       </c>
       <c r="P58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
         <v>1.59220653448188</v>
@@ -4579,13 +4579,13 @@
         <v>7.56</v>
       </c>
       <c r="M62" t="n">
-        <v>9.9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N62" t="n">
         <v>4.64</v>
       </c>
       <c r="O62" t="n">
-        <v>7.041</v>
+        <v>6.785</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4646,13 +4646,13 @@
         <v>5.78</v>
       </c>
       <c r="M63" t="n">
-        <v>7.62</v>
+        <v>7.97</v>
       </c>
       <c r="N63" t="n">
         <v>6.69</v>
       </c>
       <c r="O63" t="n">
-        <v>5.462499999999999</v>
+        <v>5.5325</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
@@ -4981,13 +4981,13 @@
         <v>8.52</v>
       </c>
       <c r="M68" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N68" t="n">
         <v>1.51</v>
       </c>
       <c r="O68" t="n">
-        <v>6.851499999999999</v>
+        <v>6.705499999999999</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5048,13 +5048,13 @@
         <v>6.96</v>
       </c>
       <c r="M69" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N69" t="n">
         <v>4.64</v>
       </c>
       <c r="O69" t="n">
-        <v>6.576</v>
+        <v>6.321999999999999</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5115,13 +5115,13 @@
         <v>4.89</v>
       </c>
       <c r="M70" t="n">
-        <v>9.210000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="N70" t="n">
         <v>6.69</v>
       </c>
       <c r="O70" t="n">
-        <v>5.067</v>
+        <v>5.127</v>
       </c>
       <c r="P70" t="n">
         <v>3</v>
@@ -5182,13 +5182,13 @@
         <v>9.039999999999999</v>
       </c>
       <c r="M71" t="n">
-        <v>6.34</v>
+        <v>6.26</v>
       </c>
       <c r="N71" t="n">
         <v>2.86</v>
       </c>
       <c r="O71" t="n">
-        <v>7.531</v>
+        <v>7.515</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5249,13 +5249,13 @@
         <v>7.48</v>
       </c>
       <c r="M72" t="n">
-        <v>9.32</v>
+        <v>9.08</v>
       </c>
       <c r="N72" t="n">
         <v>3.07</v>
       </c>
       <c r="O72" t="n">
-        <v>7.1145</v>
+        <v>7.0665</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
@@ -5316,13 +5316,13 @@
         <v>5.93</v>
       </c>
       <c r="M73" t="n">
-        <v>9.59</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N73" t="n">
         <v>5.71</v>
       </c>
       <c r="O73" t="n">
-        <v>6.524</v>
+        <v>6.534</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
@@ -5383,13 +5383,13 @@
         <v>8.74</v>
       </c>
       <c r="M74" t="n">
-        <v>6.34</v>
+        <v>6.07</v>
       </c>
       <c r="N74" t="n">
         <v>2.86</v>
       </c>
       <c r="O74" t="n">
-        <v>7.204</v>
+        <v>7.15</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -5450,13 +5450,13 @@
         <v>6.96</v>
       </c>
       <c r="M75" t="n">
-        <v>9.32</v>
+        <v>8.49</v>
       </c>
       <c r="N75" t="n">
         <v>3.07</v>
       </c>
       <c r="O75" t="n">
-        <v>6.5485</v>
+        <v>6.3825</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5517,13 +5517,13 @@
         <v>5.19</v>
       </c>
       <c r="M76" t="n">
-        <v>8.82</v>
+        <v>9.07</v>
       </c>
       <c r="N76" t="n">
         <v>5.71</v>
       </c>
       <c r="O76" t="n">
-        <v>5.562</v>
+        <v>5.611999999999999</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
@@ -5651,13 +5651,13 @@
         <v>8.74</v>
       </c>
       <c r="M78" t="n">
-        <v>9.9</v>
+        <v>9.24</v>
       </c>
       <c r="N78" t="n">
         <v>4.64</v>
       </c>
       <c r="O78" t="n">
-        <v>8.210000000000001</v>
+        <v>8.077999999999999</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -5785,13 +5785,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>6.34</v>
+        <v>6.19</v>
       </c>
       <c r="N80" t="n">
         <v>2.86</v>
       </c>
       <c r="O80" t="n">
-        <v>7.899500000000001</v>
+        <v>7.869500000000001</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -5852,13 +5852,13 @@
         <v>7.41</v>
       </c>
       <c r="M81" t="n">
-        <v>9.59</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N81" t="n">
         <v>5.71</v>
       </c>
       <c r="O81" t="n">
-        <v>7.449999999999999</v>
+        <v>7.471999999999999</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
@@ -5986,13 +5986,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M83" t="n">
-        <v>7.43</v>
+        <v>6.85</v>
       </c>
       <c r="N83" t="n">
         <v>3.48</v>
       </c>
       <c r="O83" t="n">
-        <v>8.1325</v>
+        <v>8.016500000000001</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -6053,13 +6053,13 @@
         <v>7.56</v>
       </c>
       <c r="M84" t="n">
-        <v>7.62</v>
+        <v>7.84</v>
       </c>
       <c r="N84" t="n">
         <v>6.69</v>
       </c>
       <c r="O84" t="n">
-        <v>7.1175</v>
+        <v>7.161499999999999</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
@@ -6254,13 +6254,13 @@
         <v>8.52</v>
       </c>
       <c r="M87" t="n">
-        <v>9.32</v>
+        <v>8.07</v>
       </c>
       <c r="N87" t="n">
         <v>6.37</v>
       </c>
       <c r="O87" t="n">
-        <v>8.0305</v>
+        <v>7.780499999999999</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
@@ -6321,13 +6321,13 @@
         <v>5.93</v>
       </c>
       <c r="M88" t="n">
-        <v>8.81</v>
+        <v>8.92</v>
       </c>
       <c r="N88" t="n">
         <v>5.71</v>
       </c>
       <c r="O88" t="n">
-        <v>5.819</v>
+        <v>5.840999999999999</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6388,13 +6388,13 @@
         <v>9.33</v>
       </c>
       <c r="M89" t="n">
-        <v>8.42</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N89" t="n">
         <v>5.01</v>
       </c>
       <c r="O89" t="n">
-        <v>8.478999999999999</v>
+        <v>8.452999999999999</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -6455,13 +6455,13 @@
         <v>8.15</v>
       </c>
       <c r="M90" t="n">
-        <v>9.59</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="N90" t="n">
         <v>5.71</v>
       </c>
       <c r="O90" t="n">
-        <v>8.032999999999999</v>
+        <v>8.039</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6589,13 +6589,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M92" t="n">
-        <v>5.63</v>
+        <v>4.98</v>
       </c>
       <c r="N92" t="n">
         <v>3.48</v>
       </c>
       <c r="O92" t="n">
-        <v>7.7845</v>
+        <v>7.654500000000001</v>
       </c>
       <c r="P92" t="n">
         <v>2</v>
@@ -6656,13 +6656,13 @@
         <v>8.74</v>
       </c>
       <c r="M93" t="n">
-        <v>8.56</v>
+        <v>7.55</v>
       </c>
       <c r="N93" t="n">
         <v>7.6</v>
       </c>
       <c r="O93" t="n">
-        <v>8.335000000000001</v>
+        <v>8.132999999999999</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -6723,13 +6723,13 @@
         <v>7.56</v>
       </c>
       <c r="M94" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="N94" t="n">
         <v>6.69</v>
       </c>
       <c r="O94" t="n">
-        <v>7.1605</v>
+        <v>7.2005</v>
       </c>
       <c r="P94" t="n">
         <v>3</v>
@@ -6790,13 +6790,13 @@
         <v>9.26</v>
       </c>
       <c r="M95" t="n">
-        <v>5.63</v>
+        <v>4.84</v>
       </c>
       <c r="N95" t="n">
         <v>3.48</v>
       </c>
       <c r="O95" t="n">
-        <v>7.466</v>
+        <v>7.308</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6857,13 +6857,13 @@
         <v>8.15</v>
       </c>
       <c r="M96" t="n">
-        <v>8.56</v>
+        <v>7.27</v>
       </c>
       <c r="N96" t="n">
         <v>4.64</v>
       </c>
       <c r="O96" t="n">
-        <v>7.384499999999999</v>
+        <v>7.126499999999999</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -6924,13 +6924,13 @@
         <v>6.67</v>
       </c>
       <c r="M97" t="n">
-        <v>7.7</v>
+        <v>7.99</v>
       </c>
       <c r="N97" t="n">
         <v>6.69</v>
       </c>
       <c r="O97" t="n">
-        <v>6.399</v>
+        <v>6.457</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -6991,13 +6991,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>7.43</v>
+        <v>7.04</v>
       </c>
       <c r="N98" t="n">
         <v>3.48</v>
       </c>
       <c r="O98" t="n">
-        <v>8.186499999999999</v>
+        <v>8.108499999999999</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7058,13 +7058,13 @@
         <v>8.74</v>
       </c>
       <c r="M99" t="n">
-        <v>9.960000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N99" t="n">
         <v>7.6</v>
       </c>
       <c r="O99" t="n">
-        <v>8.680999999999999</v>
+        <v>8.567</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7125,13 +7125,13 @@
         <v>7.56</v>
       </c>
       <c r="M100" t="n">
-        <v>9.210000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="N100" t="n">
         <v>6.69</v>
       </c>
       <c r="O100" t="n">
-        <v>7.5615</v>
+        <v>7.581499999999999</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
@@ -7192,13 +7192,13 @@
         <v>9.26</v>
       </c>
       <c r="M101" t="n">
-        <v>7.43</v>
+        <v>6.94</v>
       </c>
       <c r="N101" t="n">
         <v>3.48</v>
       </c>
       <c r="O101" t="n">
-        <v>7.892</v>
+        <v>7.794</v>
       </c>
       <c r="P101" t="n">
         <v>2</v>
@@ -7259,13 +7259,13 @@
         <v>8.15</v>
       </c>
       <c r="M102" t="n">
-        <v>9.960000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="N102" t="n">
         <v>7.6</v>
       </c>
       <c r="O102" t="n">
-        <v>8.2135</v>
+        <v>8.0595</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
@@ -7326,13 +7326,13 @@
         <v>6.67</v>
       </c>
       <c r="M103" t="n">
-        <v>9.210000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="N103" t="n">
         <v>6.69</v>
       </c>
       <c r="O103" t="n">
-        <v>6.857</v>
+        <v>6.885</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
@@ -7393,13 +7393,13 @@
         <v>9.26</v>
       </c>
       <c r="M104" t="n">
-        <v>6.57</v>
+        <v>5.9</v>
       </c>
       <c r="N104" t="n">
         <v>3.48</v>
       </c>
       <c r="O104" t="n">
-        <v>7.675</v>
+        <v>7.541</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -7460,13 +7460,13 @@
         <v>8.15</v>
       </c>
       <c r="M105" t="n">
-        <v>9.220000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N105" t="n">
         <v>4.64</v>
       </c>
       <c r="O105" t="n">
-        <v>7.5495</v>
+        <v>7.3275</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7527,13 +7527,13 @@
         <v>6.67</v>
       </c>
       <c r="M106" t="n">
-        <v>6.77</v>
+        <v>7.04</v>
       </c>
       <c r="N106" t="n">
         <v>6.69</v>
       </c>
       <c r="O106" t="n">
-        <v>6.258</v>
+        <v>6.311999999999999</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -7594,13 +7594,13 @@
         <v>8.15</v>
       </c>
       <c r="M107" t="n">
-        <v>9.9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N107" t="n">
         <v>4.64</v>
       </c>
       <c r="O107" t="n">
-        <v>7.7575</v>
+        <v>7.6015</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
@@ -7661,13 +7661,13 @@
         <v>7.41</v>
       </c>
       <c r="M108" t="n">
-        <v>8.82</v>
+        <v>9.07</v>
       </c>
       <c r="N108" t="n">
         <v>5.71</v>
       </c>
       <c r="O108" t="n">
-        <v>7.167</v>
+        <v>7.217</v>
       </c>
       <c r="P108" t="n">
         <v>2</v>
@@ -7728,13 +7728,13 @@
         <v>6.67</v>
       </c>
       <c r="M109" t="n">
-        <v>7.62</v>
+        <v>7.79</v>
       </c>
       <c r="N109" t="n">
         <v>6.69</v>
       </c>
       <c r="O109" t="n">
-        <v>6.539</v>
+        <v>6.573</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
@@ -7795,13 +7795,13 @@
         <v>7.56</v>
       </c>
       <c r="M110" t="n">
-        <v>9.9</v>
+        <v>8.93</v>
       </c>
       <c r="N110" t="n">
         <v>4.64</v>
       </c>
       <c r="O110" t="n">
-        <v>7.266</v>
+        <v>7.071999999999999</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
@@ -7862,13 +7862,13 @@
         <v>6.67</v>
       </c>
       <c r="M111" t="n">
-        <v>8.82</v>
+        <v>9.15</v>
       </c>
       <c r="N111" t="n">
         <v>5.71</v>
       </c>
       <c r="O111" t="n">
-        <v>6.553999999999999</v>
+        <v>6.619999999999999</v>
       </c>
       <c r="P111" t="n">
         <v>2</v>
@@ -7929,13 +7929,13 @@
         <v>5.78</v>
       </c>
       <c r="M112" t="n">
-        <v>7.62</v>
+        <v>7.84</v>
       </c>
       <c r="N112" t="n">
         <v>6.69</v>
       </c>
       <c r="O112" t="n">
-        <v>5.8015</v>
+        <v>5.8455</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
@@ -7996,13 +7996,13 @@
         <v>8.15</v>
       </c>
       <c r="M113" t="n">
-        <v>9.9</v>
+        <v>9.32</v>
       </c>
       <c r="N113" t="n">
         <v>4.64</v>
       </c>
       <c r="O113" t="n">
-        <v>7.8085</v>
+        <v>7.6925</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -8063,13 +8063,13 @@
         <v>7.41</v>
       </c>
       <c r="M114" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="N114" t="n">
         <v>5.71</v>
       </c>
       <c r="O114" t="n">
-        <v>7.23</v>
+        <v>7.265999999999999</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -8130,13 +8130,13 @@
         <v>6.67</v>
       </c>
       <c r="M115" t="n">
-        <v>7.62</v>
+        <v>7.74</v>
       </c>
       <c r="N115" t="n">
         <v>6.69</v>
       </c>
       <c r="O115" t="n">
-        <v>6.616999999999999</v>
+        <v>6.640999999999999</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8197,13 +8197,13 @@
         <v>8.74</v>
       </c>
       <c r="M116" t="n">
-        <v>9.9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N116" t="n">
         <v>4.64</v>
       </c>
       <c r="O116" t="n">
-        <v>8.183</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
@@ -8264,13 +8264,13 @@
         <v>8.15</v>
       </c>
       <c r="M117" t="n">
-        <v>8.82</v>
+        <v>9.07</v>
       </c>
       <c r="N117" t="n">
         <v>5.71</v>
       </c>
       <c r="O117" t="n">
-        <v>7.702</v>
+        <v>7.752</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
@@ -8331,13 +8331,13 @@
         <v>7.56</v>
       </c>
       <c r="M118" t="n">
-        <v>7.62</v>
+        <v>7.79</v>
       </c>
       <c r="N118" t="n">
         <v>6.69</v>
       </c>
       <c r="O118" t="n">
-        <v>7.1805</v>
+        <v>7.2145</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
@@ -8398,13 +8398,13 @@
         <v>8.15</v>
       </c>
       <c r="M119" t="n">
-        <v>9.9</v>
+        <v>9.24</v>
       </c>
       <c r="N119" t="n">
         <v>4.64</v>
       </c>
       <c r="O119" t="n">
-        <v>7.7875</v>
+        <v>7.655499999999999</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
@@ -8465,13 +8465,13 @@
         <v>7.41</v>
       </c>
       <c r="M120" t="n">
-        <v>8.82</v>
+        <v>9.02</v>
       </c>
       <c r="N120" t="n">
         <v>5.71</v>
       </c>
       <c r="O120" t="n">
-        <v>7.206</v>
+        <v>7.246</v>
       </c>
       <c r="P120" t="n">
         <v>2</v>
@@ -8532,13 +8532,13 @@
         <v>6.67</v>
       </c>
       <c r="M121" t="n">
-        <v>7.62</v>
+        <v>7.76</v>
       </c>
       <c r="N121" t="n">
         <v>6.69</v>
       </c>
       <c r="O121" t="n">
-        <v>6.584</v>
+        <v>6.611999999999999</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
@@ -8599,13 +8599,13 @@
         <v>9.26</v>
       </c>
       <c r="M122" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N122" t="n">
         <v>3.48</v>
       </c>
       <c r="O122" t="n">
-        <v>7.742</v>
+        <v>7.596</v>
       </c>
       <c r="P122" t="n">
         <v>1</v>
@@ -8666,13 +8666,13 @@
         <v>8.15</v>
       </c>
       <c r="M123" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N123" t="n">
         <v>4.64</v>
       </c>
       <c r="O123" t="n">
-        <v>7.5295</v>
+        <v>7.275499999999999</v>
       </c>
       <c r="P123" t="n">
         <v>2</v>
@@ -8733,13 +8733,13 @@
         <v>6.67</v>
       </c>
       <c r="M124" t="n">
-        <v>9.210000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="N124" t="n">
         <v>6.69</v>
       </c>
       <c r="O124" t="n">
-        <v>6.497</v>
+        <v>6.556999999999999</v>
       </c>
       <c r="P124" t="n">
         <v>3</v>
@@ -8800,13 +8800,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M125" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N125" t="n">
         <v>3.48</v>
       </c>
       <c r="O125" t="n">
-        <v>8.039499999999999</v>
+        <v>7.8935</v>
       </c>
       <c r="P125" t="n">
         <v>2</v>
@@ -8867,13 +8867,13 @@
         <v>8.74</v>
       </c>
       <c r="M126" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N126" t="n">
         <v>7.6</v>
       </c>
       <c r="O126" t="n">
-        <v>8.449999999999999</v>
+        <v>8.196</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
@@ -8934,13 +8934,13 @@
         <v>7.56</v>
       </c>
       <c r="M127" t="n">
-        <v>9.210000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="N127" t="n">
         <v>6.69</v>
       </c>
       <c r="O127" t="n">
-        <v>7.210500000000001</v>
+        <v>7.2705</v>
       </c>
       <c r="P127" t="n">
         <v>3</v>
@@ -9001,13 +9001,13 @@
         <v>9.26</v>
       </c>
       <c r="M128" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N128" t="n">
         <v>3.48</v>
       </c>
       <c r="O128" t="n">
-        <v>7.742</v>
+        <v>7.596</v>
       </c>
       <c r="P128" t="n">
         <v>1</v>
@@ -9068,13 +9068,13 @@
         <v>8.15</v>
       </c>
       <c r="M129" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N129" t="n">
         <v>4.64</v>
       </c>
       <c r="O129" t="n">
-        <v>7.5295</v>
+        <v>7.275499999999999</v>
       </c>
       <c r="P129" t="n">
         <v>2</v>
@@ -9135,13 +9135,13 @@
         <v>6.67</v>
       </c>
       <c r="M130" t="n">
-        <v>9.210000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="N130" t="n">
         <v>6.69</v>
       </c>
       <c r="O130" t="n">
-        <v>6.497</v>
+        <v>6.556999999999999</v>
       </c>
       <c r="P130" t="n">
         <v>3</v>
@@ -9604,13 +9604,13 @@
         <v>9.33</v>
       </c>
       <c r="M137" t="n">
-        <v>6.34</v>
+        <v>5.95</v>
       </c>
       <c r="N137" t="n">
         <v>2.86</v>
       </c>
       <c r="O137" t="n">
-        <v>7.5515</v>
+        <v>7.4735</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
@@ -9671,13 +9671,13 @@
         <v>8</v>
       </c>
       <c r="M138" t="n">
-        <v>9.32</v>
+        <v>8.1</v>
       </c>
       <c r="N138" t="n">
         <v>3.07</v>
       </c>
       <c r="O138" t="n">
-        <v>7.155499999999999</v>
+        <v>6.911499999999999</v>
       </c>
       <c r="P138" t="n">
         <v>2</v>
@@ -9738,13 +9738,13 @@
         <v>6.67</v>
       </c>
       <c r="M139" t="n">
-        <v>9.59</v>
+        <v>9.9</v>
       </c>
       <c r="N139" t="n">
         <v>5.71</v>
       </c>
       <c r="O139" t="n">
-        <v>6.582</v>
+        <v>6.644</v>
       </c>
       <c r="P139" t="n">
         <v>3</v>
@@ -9805,13 +9805,13 @@
         <v>8.74</v>
       </c>
       <c r="M140" t="n">
-        <v>6.34</v>
+        <v>5.94</v>
       </c>
       <c r="N140" t="n">
         <v>1.51</v>
       </c>
       <c r="O140" t="n">
-        <v>6.860499999999999</v>
+        <v>6.7805</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
@@ -9872,13 +9872,13 @@
         <v>6.96</v>
       </c>
       <c r="M141" t="n">
-        <v>9.32</v>
+        <v>8.07</v>
       </c>
       <c r="N141" t="n">
         <v>3.07</v>
       </c>
       <c r="O141" t="n">
-        <v>6.299499999999999</v>
+        <v>6.049499999999999</v>
       </c>
       <c r="P141" t="n">
         <v>2</v>
@@ -9939,13 +9939,13 @@
         <v>5.19</v>
       </c>
       <c r="M142" t="n">
-        <v>8.82</v>
+        <v>9.09</v>
       </c>
       <c r="N142" t="n">
         <v>5.71</v>
       </c>
       <c r="O142" t="n">
-        <v>5.205</v>
+        <v>5.258999999999999</v>
       </c>
       <c r="P142" t="n">
         <v>3</v>
@@ -10073,13 +10073,13 @@
         <v>9.33</v>
       </c>
       <c r="M144" t="n">
-        <v>8.42</v>
+        <v>7.74</v>
       </c>
       <c r="N144" t="n">
         <v>5.01</v>
       </c>
       <c r="O144" t="n">
-        <v>8.370999999999999</v>
+        <v>8.234999999999999</v>
       </c>
       <c r="P144" t="n">
         <v>1</v>
@@ -10140,13 +10140,13 @@
         <v>7.56</v>
       </c>
       <c r="M145" t="n">
-        <v>9.210000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="N145" t="n">
         <v>6.69</v>
       </c>
       <c r="O145" t="n">
-        <v>7.498500000000001</v>
+        <v>7.5265</v>
       </c>
       <c r="P145" t="n">
         <v>2</v>
@@ -10207,13 +10207,13 @@
         <v>8.52</v>
       </c>
       <c r="M146" t="n">
-        <v>9.32</v>
+        <v>8.74</v>
       </c>
       <c r="N146" t="n">
         <v>6.37</v>
       </c>
       <c r="O146" t="n">
-        <v>8.231499999999999</v>
+        <v>8.115499999999999</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
@@ -10274,13 +10274,13 @@
         <v>5.93</v>
       </c>
       <c r="M147" t="n">
-        <v>8.81</v>
+        <v>8.84</v>
       </c>
       <c r="N147" t="n">
         <v>5.71</v>
       </c>
       <c r="O147" t="n">
-        <v>6.221</v>
+        <v>6.226999999999999</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
@@ -10408,13 +10408,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M149" t="n">
-        <v>5.63</v>
+        <v>4.94</v>
       </c>
       <c r="N149" t="n">
         <v>3.48</v>
       </c>
       <c r="O149" t="n">
-        <v>7.772500000000001</v>
+        <v>7.634500000000001</v>
       </c>
       <c r="P149" t="n">
         <v>2</v>
@@ -10475,13 +10475,13 @@
         <v>8.74</v>
       </c>
       <c r="M150" t="n">
-        <v>8.56</v>
+        <v>7.46</v>
       </c>
       <c r="N150" t="n">
         <v>4.64</v>
       </c>
       <c r="O150" t="n">
-        <v>7.875999999999999</v>
+        <v>7.656</v>
       </c>
       <c r="P150" t="n">
         <v>1</v>
@@ -10542,13 +10542,13 @@
         <v>7.56</v>
       </c>
       <c r="M151" t="n">
-        <v>7.7</v>
+        <v>7.92</v>
       </c>
       <c r="N151" t="n">
         <v>6.69</v>
       </c>
       <c r="O151" t="n">
-        <v>7.1335</v>
+        <v>7.177499999999999</v>
       </c>
       <c r="P151" t="n">
         <v>3</v>
@@ -10609,13 +10609,13 @@
         <v>9.26</v>
       </c>
       <c r="M152" t="n">
-        <v>6.57</v>
+        <v>6.1</v>
       </c>
       <c r="N152" t="n">
         <v>3.48</v>
       </c>
       <c r="O152" t="n">
-        <v>7.738</v>
+        <v>7.643999999999999</v>
       </c>
       <c r="P152" t="n">
         <v>2</v>
@@ -10676,13 +10676,13 @@
         <v>8.15</v>
       </c>
       <c r="M153" t="n">
-        <v>9.289999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="N153" t="n">
         <v>7.6</v>
       </c>
       <c r="O153" t="n">
-        <v>8.109499999999999</v>
+        <v>7.969499999999999</v>
       </c>
       <c r="P153" t="n">
         <v>1</v>
@@ -10743,13 +10743,13 @@
         <v>6.67</v>
       </c>
       <c r="M154" t="n">
-        <v>8.48</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="N154" t="n">
         <v>6.69</v>
       </c>
       <c r="O154" t="n">
-        <v>6.755999999999999</v>
+        <v>6.781999999999999</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -10810,13 +10810,13 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>8.42</v>
+        <v>7.74</v>
       </c>
       <c r="N155" t="n">
         <v>1.51</v>
       </c>
       <c r="O155" t="n">
-        <v>7.527</v>
+        <v>7.391</v>
       </c>
       <c r="P155" t="n">
         <v>2</v>
@@ -10877,13 +10877,13 @@
         <v>8.15</v>
       </c>
       <c r="M156" t="n">
-        <v>9.9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N156" t="n">
         <v>4.64</v>
       </c>
       <c r="O156" t="n">
-        <v>7.7575</v>
+        <v>7.6015</v>
       </c>
       <c r="P156" t="n">
         <v>1</v>
@@ -10944,13 +10944,13 @@
         <v>7.41</v>
       </c>
       <c r="M157" t="n">
-        <v>8.82</v>
+        <v>9.07</v>
       </c>
       <c r="N157" t="n">
         <v>5.71</v>
       </c>
       <c r="O157" t="n">
-        <v>7.167</v>
+        <v>7.217</v>
       </c>
       <c r="P157" t="n">
         <v>3</v>
@@ -11011,13 +11011,13 @@
         <v>8.15</v>
       </c>
       <c r="M158" t="n">
-        <v>9.9</v>
+        <v>9.24</v>
       </c>
       <c r="N158" t="n">
         <v>4.64</v>
       </c>
       <c r="O158" t="n">
-        <v>7.7875</v>
+        <v>7.655499999999999</v>
       </c>
       <c r="P158" t="n">
         <v>1</v>
@@ -11078,13 +11078,13 @@
         <v>7.41</v>
       </c>
       <c r="M159" t="n">
-        <v>8.82</v>
+        <v>9.02</v>
       </c>
       <c r="N159" t="n">
         <v>5.71</v>
       </c>
       <c r="O159" t="n">
-        <v>7.206</v>
+        <v>7.246</v>
       </c>
       <c r="P159" t="n">
         <v>2</v>
@@ -11145,13 +11145,13 @@
         <v>6.67</v>
       </c>
       <c r="M160" t="n">
-        <v>7.62</v>
+        <v>7.76</v>
       </c>
       <c r="N160" t="n">
         <v>6.69</v>
       </c>
       <c r="O160" t="n">
-        <v>6.584</v>
+        <v>6.611999999999999</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
@@ -11212,13 +11212,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M161" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N161" t="n">
         <v>3.48</v>
       </c>
       <c r="O161" t="n">
-        <v>8.039499999999999</v>
+        <v>7.8935</v>
       </c>
       <c r="P161" t="n">
         <v>2</v>
@@ -11279,13 +11279,13 @@
         <v>8.74</v>
       </c>
       <c r="M162" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N162" t="n">
         <v>7.6</v>
       </c>
       <c r="O162" t="n">
-        <v>8.449999999999999</v>
+        <v>8.196</v>
       </c>
       <c r="P162" t="n">
         <v>1</v>
@@ -11346,13 +11346,13 @@
         <v>7.56</v>
       </c>
       <c r="M163" t="n">
-        <v>9.210000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="N163" t="n">
         <v>6.69</v>
       </c>
       <c r="O163" t="n">
-        <v>7.210500000000001</v>
+        <v>7.2705</v>
       </c>
       <c r="P163" t="n">
         <v>3</v>
@@ -11681,13 +11681,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M168" t="n">
-        <v>7.43</v>
+        <v>7.15</v>
       </c>
       <c r="N168" t="n">
         <v>3.48</v>
       </c>
       <c r="O168" t="n">
-        <v>8.2105</v>
+        <v>8.154500000000001</v>
       </c>
       <c r="P168" t="n">
         <v>2</v>
@@ -11748,13 +11748,13 @@
         <v>8.74</v>
       </c>
       <c r="M169" t="n">
-        <v>9.960000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="N169" t="n">
         <v>7.6</v>
       </c>
       <c r="O169" t="n">
-        <v>8.722999999999999</v>
+        <v>8.654999999999999</v>
       </c>
       <c r="P169" t="n">
         <v>1</v>
@@ -12083,13 +12083,13 @@
         <v>9.26</v>
       </c>
       <c r="M174" t="n">
-        <v>7.43</v>
+        <v>7.34</v>
       </c>
       <c r="N174" t="n">
         <v>3.48</v>
       </c>
       <c r="O174" t="n">
-        <v>8.002999999999998</v>
+        <v>7.984999999999999</v>
       </c>
       <c r="P174" t="n">
         <v>1</v>
@@ -12150,13 +12150,13 @@
         <v>8.15</v>
       </c>
       <c r="M175" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="N175" t="n">
         <v>4.64</v>
       </c>
       <c r="O175" t="n">
-        <v>7.946499999999999</v>
+        <v>7.9525</v>
       </c>
       <c r="P175" t="n">
         <v>2</v>
@@ -12284,13 +12284,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M177" t="n">
-        <v>7.43</v>
+        <v>7</v>
       </c>
       <c r="N177" t="n">
         <v>3.48</v>
       </c>
       <c r="O177" t="n">
-        <v>8.1745</v>
+        <v>8.0885</v>
       </c>
       <c r="P177" t="n">
         <v>2</v>
@@ -12351,13 +12351,13 @@
         <v>8.74</v>
       </c>
       <c r="M178" t="n">
-        <v>9.960000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="N178" t="n">
         <v>7.6</v>
       </c>
       <c r="O178" t="n">
-        <v>8.666</v>
+        <v>8.536</v>
       </c>
       <c r="P178" t="n">
         <v>1</v>
@@ -12418,13 +12418,13 @@
         <v>10</v>
       </c>
       <c r="M179" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="N179" t="n">
         <v>2.86</v>
       </c>
       <c r="O179" t="n">
-        <v>7.734999999999999</v>
+        <v>7.638999999999999</v>
       </c>
       <c r="P179" t="n">
         <v>3</v>
@@ -12485,13 +12485,13 @@
         <v>9.779999999999999</v>
       </c>
       <c r="M180" t="n">
-        <v>6.79</v>
+        <v>5.6</v>
       </c>
       <c r="N180" t="n">
         <v>5.01</v>
       </c>
       <c r="O180" t="n">
-        <v>8.2745</v>
+        <v>8.036499999999998</v>
       </c>
       <c r="P180" t="n">
         <v>2</v>
@@ -12552,13 +12552,13 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M181" t="n">
-        <v>8.140000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="N181" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="O181" t="n">
-        <v>8.356</v>
+        <v>8.414</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
@@ -12619,13 +12619,13 @@
         <v>9.93</v>
       </c>
       <c r="M182" t="n">
-        <v>6.34</v>
+        <v>6</v>
       </c>
       <c r="N182" t="n">
         <v>2.86</v>
       </c>
       <c r="O182" t="n">
-        <v>8.0345</v>
+        <v>7.9665</v>
       </c>
       <c r="P182" t="n">
         <v>3</v>
@@ -12686,16 +12686,16 @@
         <v>9.33</v>
       </c>
       <c r="M183" t="n">
-        <v>8.42</v>
+        <v>7.56</v>
       </c>
       <c r="N183" t="n">
         <v>5.01</v>
       </c>
       <c r="O183" t="n">
-        <v>8.328999999999999</v>
+        <v>8.157</v>
       </c>
       <c r="P183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q183" t="n">
         <v>1.673668264153046</v>
@@ -12753,16 +12753,16 @@
         <v>8.15</v>
       </c>
       <c r="M184" t="n">
-        <v>9.59</v>
+        <v>9.94</v>
       </c>
       <c r="N184" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="O184" t="n">
-        <v>8.195</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="P184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q184" t="n">
         <v>2.789447106921743</v>
@@ -12829,7 +12829,7 @@
         <v>7.802</v>
       </c>
       <c r="P185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q185" t="n">
         <v>0.916444458800617</v>
@@ -12887,13 +12887,13 @@
         <v>9.26</v>
       </c>
       <c r="M186" t="n">
-        <v>7.43</v>
+        <v>7.08</v>
       </c>
       <c r="N186" t="n">
         <v>3.48</v>
       </c>
       <c r="O186" t="n">
-        <v>7.937</v>
+        <v>7.867000000000001</v>
       </c>
       <c r="P186" t="n">
         <v>1</v>
@@ -12954,16 +12954,16 @@
         <v>8.15</v>
       </c>
       <c r="M187" t="n">
-        <v>9.960000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="N187" t="n">
         <v>4.64</v>
       </c>
       <c r="O187" t="n">
-        <v>7.841499999999999</v>
+        <v>7.745499999999999</v>
       </c>
       <c r="P187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q187" t="n">
         <v>2.443851890134979</v>
@@ -13088,13 +13088,13 @@
         <v>9.33</v>
       </c>
       <c r="M189" t="n">
-        <v>6.34</v>
+        <v>6.26</v>
       </c>
       <c r="N189" t="n">
         <v>2.86</v>
       </c>
       <c r="O189" t="n">
-        <v>7.7255</v>
+        <v>7.7095</v>
       </c>
       <c r="P189" t="n">
         <v>1</v>
@@ -13155,13 +13155,13 @@
         <v>8.44</v>
       </c>
       <c r="M190" t="n">
-        <v>8.42</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N190" t="n">
         <v>1.51</v>
       </c>
       <c r="O190" t="n">
-        <v>7.345499999999999</v>
+        <v>7.305499999999999</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
@@ -13289,13 +13289,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M192" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N192" t="n">
         <v>3.48</v>
       </c>
       <c r="O192" t="n">
-        <v>8.039499999999999</v>
+        <v>7.8935</v>
       </c>
       <c r="P192" t="n">
         <v>2</v>
@@ -13356,13 +13356,13 @@
         <v>8.74</v>
       </c>
       <c r="M193" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N193" t="n">
         <v>7.6</v>
       </c>
       <c r="O193" t="n">
-        <v>8.449999999999999</v>
+        <v>8.196</v>
       </c>
       <c r="P193" t="n">
         <v>1</v>
@@ -13432,7 +13432,7 @@
         <v>7.802</v>
       </c>
       <c r="P194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q194" t="n">
         <v>0.916444458800617</v>
@@ -13490,13 +13490,13 @@
         <v>9.26</v>
       </c>
       <c r="M195" t="n">
-        <v>7.43</v>
+        <v>7.08</v>
       </c>
       <c r="N195" t="n">
         <v>3.48</v>
       </c>
       <c r="O195" t="n">
-        <v>7.937</v>
+        <v>7.867000000000001</v>
       </c>
       <c r="P195" t="n">
         <v>1</v>
@@ -13557,16 +13557,16 @@
         <v>8.15</v>
       </c>
       <c r="M196" t="n">
-        <v>9.960000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="N196" t="n">
         <v>4.64</v>
       </c>
       <c r="O196" t="n">
-        <v>7.841499999999999</v>
+        <v>7.745499999999999</v>
       </c>
       <c r="P196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q196" t="n">
         <v>2.443851890134979</v>
@@ -13892,13 +13892,13 @@
         <v>9.26</v>
       </c>
       <c r="M201" t="n">
-        <v>7.43</v>
+        <v>6.94</v>
       </c>
       <c r="N201" t="n">
         <v>3.48</v>
       </c>
       <c r="O201" t="n">
-        <v>7.892</v>
+        <v>7.794</v>
       </c>
       <c r="P201" t="n">
         <v>1</v>
@@ -13959,13 +13959,13 @@
         <v>8.52</v>
       </c>
       <c r="M202" t="n">
-        <v>9.32</v>
+        <v>8.49</v>
       </c>
       <c r="N202" t="n">
         <v>3.07</v>
       </c>
       <c r="O202" t="n">
-        <v>7.6735</v>
+        <v>7.5075</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
@@ -14093,13 +14093,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M204" t="n">
-        <v>7.43</v>
+        <v>7.08</v>
       </c>
       <c r="N204" t="n">
         <v>3.48</v>
       </c>
       <c r="O204" t="n">
-        <v>8.195499999999999</v>
+        <v>8.125500000000001</v>
       </c>
       <c r="P204" t="n">
         <v>2</v>
@@ -14160,13 +14160,13 @@
         <v>8.74</v>
       </c>
       <c r="M205" t="n">
-        <v>9.960000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="N205" t="n">
         <v>7.6</v>
       </c>
       <c r="O205" t="n">
-        <v>8.699</v>
+        <v>8.603</v>
       </c>
       <c r="P205" t="n">
         <v>1</v>
@@ -14236,7 +14236,7 @@
         <v>7.747999999999999</v>
       </c>
       <c r="P206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q206" t="n">
         <v>1.046042665095654</v>
@@ -14294,16 +14294,16 @@
         <v>9.26</v>
       </c>
       <c r="M207" t="n">
-        <v>7.43</v>
+        <v>6.81</v>
       </c>
       <c r="N207" t="n">
         <v>3.48</v>
       </c>
       <c r="O207" t="n">
-        <v>7.847</v>
+        <v>7.723</v>
       </c>
       <c r="P207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q207" t="n">
         <v>1.743404441826089</v>
@@ -14361,13 +14361,13 @@
         <v>8.15</v>
       </c>
       <c r="M208" t="n">
-        <v>9.960000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="N208" t="n">
         <v>4.64</v>
       </c>
       <c r="O208" t="n">
-        <v>7.6975</v>
+        <v>7.4915</v>
       </c>
       <c r="P208" t="n">
         <v>3</v>
@@ -14495,13 +14495,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M210" t="n">
-        <v>7.43</v>
+        <v>7.28</v>
       </c>
       <c r="N210" t="n">
         <v>3.48</v>
       </c>
       <c r="O210" t="n">
-        <v>8.237499999999999</v>
+        <v>8.2075</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -14562,13 +14562,13 @@
         <v>9.039999999999999</v>
       </c>
       <c r="M211" t="n">
-        <v>9.32</v>
+        <v>9.08</v>
       </c>
       <c r="N211" t="n">
         <v>6.37</v>
       </c>
       <c r="O211" t="n">
-        <v>8.653499999999999</v>
+        <v>8.605499999999999</v>
       </c>
       <c r="P211" t="n">
         <v>1</v>
@@ -14629,13 +14629,13 @@
         <v>10</v>
       </c>
       <c r="M212" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="N212" t="n">
         <v>2.86</v>
       </c>
       <c r="O212" t="n">
-        <v>7.744</v>
+        <v>7.648</v>
       </c>
       <c r="P212" t="n">
         <v>3</v>
@@ -14696,13 +14696,13 @@
         <v>9.779999999999999</v>
       </c>
       <c r="M213" t="n">
-        <v>6.79</v>
+        <v>5.6</v>
       </c>
       <c r="N213" t="n">
         <v>5.01</v>
       </c>
       <c r="O213" t="n">
-        <v>8.2895</v>
+        <v>8.051499999999999</v>
       </c>
       <c r="P213" t="n">
         <v>2</v>
@@ -14763,13 +14763,13 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M214" t="n">
-        <v>8.140000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="N214" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="O214" t="n">
-        <v>8.379999999999999</v>
+        <v>8.437999999999999</v>
       </c>
       <c r="P214" t="n">
         <v>1</v>
@@ -14830,13 +14830,13 @@
         <v>9.93</v>
       </c>
       <c r="M215" t="n">
-        <v>6.34</v>
+        <v>5.98</v>
       </c>
       <c r="N215" t="n">
         <v>2.86</v>
       </c>
       <c r="O215" t="n">
-        <v>8.022499999999999</v>
+        <v>7.9505</v>
       </c>
       <c r="P215" t="n">
         <v>3</v>
@@ -14897,16 +14897,16 @@
         <v>9.33</v>
       </c>
       <c r="M216" t="n">
-        <v>8.42</v>
+        <v>7.5</v>
       </c>
       <c r="N216" t="n">
         <v>5.01</v>
       </c>
       <c r="O216" t="n">
-        <v>8.308</v>
+        <v>8.123999999999999</v>
       </c>
       <c r="P216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q216" t="n">
         <v>1.718101934882773</v>
@@ -14964,16 +14964,16 @@
         <v>8.15</v>
       </c>
       <c r="M217" t="n">
-        <v>9.59</v>
+        <v>9.99</v>
       </c>
       <c r="N217" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="O217" t="n">
-        <v>8.161999999999999</v>
+        <v>8.241999999999999</v>
       </c>
       <c r="P217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q217" t="n">
         <v>2.863503224804621</v>
@@ -15098,13 +15098,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M219" t="n">
-        <v>7.43</v>
+        <v>6.88</v>
       </c>
       <c r="N219" t="n">
         <v>3.48</v>
       </c>
       <c r="O219" t="n">
-        <v>8.144499999999999</v>
+        <v>8.0345</v>
       </c>
       <c r="P219" t="n">
         <v>2</v>
@@ -15165,13 +15165,13 @@
         <v>8.74</v>
       </c>
       <c r="M220" t="n">
-        <v>9.960000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="N220" t="n">
         <v>7.6</v>
       </c>
       <c r="O220" t="n">
-        <v>8.615</v>
+        <v>8.436999999999999</v>
       </c>
       <c r="P220" t="n">
         <v>1</v>
@@ -15241,7 +15241,7 @@
         <v>7.747999999999999</v>
       </c>
       <c r="P221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q221" t="n">
         <v>1.046042665095654</v>
@@ -15299,16 +15299,16 @@
         <v>9.26</v>
       </c>
       <c r="M222" t="n">
-        <v>7.43</v>
+        <v>6.81</v>
       </c>
       <c r="N222" t="n">
         <v>3.48</v>
       </c>
       <c r="O222" t="n">
-        <v>7.847</v>
+        <v>7.723</v>
       </c>
       <c r="P222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q222" t="n">
         <v>1.743404441826089</v>
@@ -15366,13 +15366,13 @@
         <v>8.15</v>
       </c>
       <c r="M223" t="n">
-        <v>9.960000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="N223" t="n">
         <v>4.64</v>
       </c>
       <c r="O223" t="n">
-        <v>7.6975</v>
+        <v>7.4915</v>
       </c>
       <c r="P223" t="n">
         <v>3</v>
@@ -15500,13 +15500,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M225" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N225" t="n">
         <v>3.48</v>
       </c>
       <c r="O225" t="n">
-        <v>8.054499999999999</v>
+        <v>7.9085</v>
       </c>
       <c r="P225" t="n">
         <v>2</v>
@@ -15567,13 +15567,13 @@
         <v>8.74</v>
       </c>
       <c r="M226" t="n">
-        <v>9.960000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="N226" t="n">
         <v>7.6</v>
       </c>
       <c r="O226" t="n">
-        <v>8.474</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="P226" t="n">
         <v>1</v>
@@ -15643,7 +15643,7 @@
         <v>7.795999999999999</v>
       </c>
       <c r="P227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q227" t="n">
         <v>0.9349584882713364</v>
@@ -15701,13 +15701,13 @@
         <v>9.26</v>
       </c>
       <c r="M228" t="n">
-        <v>7.43</v>
+        <v>7.04</v>
       </c>
       <c r="N228" t="n">
         <v>3.48</v>
       </c>
       <c r="O228" t="n">
-        <v>7.925</v>
+        <v>7.847</v>
       </c>
       <c r="P228" t="n">
         <v>1</v>
@@ -15768,16 +15768,16 @@
         <v>8.15</v>
       </c>
       <c r="M229" t="n">
-        <v>9.960000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N229" t="n">
         <v>4.64</v>
       </c>
       <c r="O229" t="n">
-        <v>7.8205</v>
+        <v>7.7065</v>
       </c>
       <c r="P229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q229" t="n">
         <v>2.49322263539023</v>
@@ -15902,13 +15902,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M231" t="n">
-        <v>7.43</v>
+        <v>6.72</v>
       </c>
       <c r="N231" t="n">
         <v>3.48</v>
       </c>
       <c r="O231" t="n">
-        <v>8.090499999999999</v>
+        <v>7.9485</v>
       </c>
       <c r="P231" t="n">
         <v>2</v>
@@ -15969,13 +15969,13 @@
         <v>8.74</v>
       </c>
       <c r="M232" t="n">
-        <v>9.960000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="N232" t="n">
         <v>7.6</v>
       </c>
       <c r="O232" t="n">
-        <v>8.530999999999999</v>
+        <v>8.286999999999999</v>
       </c>
       <c r="P232" t="n">
         <v>1</v>
@@ -16036,13 +16036,13 @@
         <v>9.039999999999999</v>
       </c>
       <c r="M233" t="n">
-        <v>6.34</v>
+        <v>5.94</v>
       </c>
       <c r="N233" t="n">
         <v>1.51</v>
       </c>
       <c r="O233" t="n">
-        <v>7.049499999999999</v>
+        <v>6.9695</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -16103,13 +16103,13 @@
         <v>8</v>
       </c>
       <c r="M234" t="n">
-        <v>8.42</v>
+        <v>7.4</v>
       </c>
       <c r="N234" t="n">
         <v>1.51</v>
       </c>
       <c r="O234" t="n">
-        <v>6.6335</v>
+        <v>6.4295</v>
       </c>
       <c r="P234" t="n">
         <v>2</v>
@@ -16170,13 +16170,13 @@
         <v>6.96</v>
       </c>
       <c r="M235" t="n">
-        <v>9.9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N235" t="n">
         <v>4.64</v>
       </c>
       <c r="O235" t="n">
-        <v>6.564</v>
+        <v>6.308</v>
       </c>
       <c r="P235" t="n">
         <v>3</v>
@@ -16438,16 +16438,16 @@
         <v>9.26</v>
       </c>
       <c r="M239" t="n">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="N239" t="n">
         <v>1.51</v>
       </c>
       <c r="O239" t="n">
-        <v>7.4975</v>
+        <v>7.3515</v>
       </c>
       <c r="P239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q239" t="n">
         <v>1.86683130496422</v>
@@ -16505,16 +16505,16 @@
         <v>8.15</v>
       </c>
       <c r="M240" t="n">
-        <v>9.9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N240" t="n">
         <v>4.64</v>
       </c>
       <c r="O240" t="n">
-        <v>7.6015</v>
+        <v>7.345499999999999</v>
       </c>
       <c r="P240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q240" t="n">
         <v>2.986930087942751</v>
@@ -16572,13 +16572,13 @@
         <v>6.67</v>
       </c>
       <c r="M241" t="n">
-        <v>7.62</v>
+        <v>7.97</v>
       </c>
       <c r="N241" t="n">
         <v>6.69</v>
       </c>
       <c r="O241" t="n">
-        <v>6.305</v>
+        <v>6.375</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -1162,13 +1162,13 @@
         <v>9.26</v>
       </c>
       <c r="M11" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="N11" t="n">
         <v>3.48</v>
       </c>
       <c r="O11" t="n">
-        <v>8.020999999999999</v>
+        <v>8.009</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -1229,13 +1229,13 @@
         <v>8.52</v>
       </c>
       <c r="M12" t="n">
-        <v>9.32</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>6.37</v>
       </c>
       <c r="O12" t="n">
-        <v>8.3515</v>
+        <v>8.3315</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1296,13 +1296,13 @@
         <v>7.41</v>
       </c>
       <c r="M13" t="n">
-        <v>9.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>5.71</v>
       </c>
       <c r="O13" t="n">
-        <v>7.581999999999999</v>
+        <v>7.585999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
@@ -5182,13 +5182,13 @@
         <v>9.039999999999999</v>
       </c>
       <c r="M71" t="n">
-        <v>6.26</v>
+        <v>6.23</v>
       </c>
       <c r="N71" t="n">
         <v>2.86</v>
       </c>
       <c r="O71" t="n">
-        <v>7.515</v>
+        <v>7.509</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5249,13 +5249,13 @@
         <v>7.48</v>
       </c>
       <c r="M72" t="n">
-        <v>9.08</v>
+        <v>8.99</v>
       </c>
       <c r="N72" t="n">
         <v>3.07</v>
       </c>
       <c r="O72" t="n">
-        <v>7.0665</v>
+        <v>7.0485</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
@@ -5316,13 +5316,13 @@
         <v>5.93</v>
       </c>
       <c r="M73" t="n">
-        <v>9.640000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="N73" t="n">
         <v>5.71</v>
       </c>
       <c r="O73" t="n">
-        <v>6.534</v>
+        <v>6.537999999999999</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
@@ -5383,13 +5383,13 @@
         <v>8.74</v>
       </c>
       <c r="M74" t="n">
-        <v>6.07</v>
+        <v>6.05</v>
       </c>
       <c r="N74" t="n">
         <v>2.86</v>
       </c>
       <c r="O74" t="n">
-        <v>7.15</v>
+        <v>7.146</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -5450,13 +5450,13 @@
         <v>6.96</v>
       </c>
       <c r="M75" t="n">
-        <v>8.49</v>
+        <v>8.42</v>
       </c>
       <c r="N75" t="n">
         <v>3.07</v>
       </c>
       <c r="O75" t="n">
-        <v>6.3825</v>
+        <v>6.3685</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5517,13 +5517,13 @@
         <v>5.19</v>
       </c>
       <c r="M76" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="N76" t="n">
         <v>5.71</v>
       </c>
       <c r="O76" t="n">
-        <v>5.611999999999999</v>
+        <v>5.617999999999999</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
@@ -5651,13 +5651,13 @@
         <v>8.74</v>
       </c>
       <c r="M78" t="n">
-        <v>9.24</v>
+        <v>9.16</v>
       </c>
       <c r="N78" t="n">
         <v>4.64</v>
       </c>
       <c r="O78" t="n">
-        <v>8.077999999999999</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -5785,13 +5785,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>6.19</v>
+        <v>6.16</v>
       </c>
       <c r="N80" t="n">
         <v>2.86</v>
       </c>
       <c r="O80" t="n">
-        <v>7.869500000000001</v>
+        <v>7.863500000000001</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -5852,13 +5852,13 @@
         <v>7.41</v>
       </c>
       <c r="M81" t="n">
-        <v>9.699999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N81" t="n">
         <v>5.71</v>
       </c>
       <c r="O81" t="n">
-        <v>7.471999999999999</v>
+        <v>7.475999999999999</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
@@ -5986,13 +5986,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M83" t="n">
-        <v>6.85</v>
+        <v>6.81</v>
       </c>
       <c r="N83" t="n">
         <v>3.48</v>
       </c>
       <c r="O83" t="n">
-        <v>8.016500000000001</v>
+        <v>8.0085</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -6053,13 +6053,13 @@
         <v>7.56</v>
       </c>
       <c r="M84" t="n">
-        <v>7.84</v>
+        <v>7.87</v>
       </c>
       <c r="N84" t="n">
         <v>6.69</v>
       </c>
       <c r="O84" t="n">
-        <v>7.161499999999999</v>
+        <v>7.1675</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
@@ -6388,13 +6388,13 @@
         <v>9.33</v>
       </c>
       <c r="M89" t="n">
-        <v>8.289999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N89" t="n">
         <v>5.01</v>
       </c>
       <c r="O89" t="n">
-        <v>8.452999999999999</v>
+        <v>8.439</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -6455,13 +6455,13 @@
         <v>8.15</v>
       </c>
       <c r="M90" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N90" t="n">
         <v>5.71</v>
       </c>
       <c r="O90" t="n">
-        <v>8.039</v>
+        <v>8.042999999999999</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6589,13 +6589,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M92" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="N92" t="n">
         <v>3.48</v>
       </c>
       <c r="O92" t="n">
-        <v>7.654500000000001</v>
+        <v>7.646500000000001</v>
       </c>
       <c r="P92" t="n">
         <v>2</v>
@@ -6656,13 +6656,13 @@
         <v>8.74</v>
       </c>
       <c r="M93" t="n">
-        <v>7.55</v>
+        <v>7.46</v>
       </c>
       <c r="N93" t="n">
         <v>7.6</v>
       </c>
       <c r="O93" t="n">
-        <v>8.132999999999999</v>
+        <v>8.115</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -6723,13 +6723,13 @@
         <v>7.56</v>
       </c>
       <c r="M94" t="n">
-        <v>7.9</v>
+        <v>7.92</v>
       </c>
       <c r="N94" t="n">
         <v>6.69</v>
       </c>
       <c r="O94" t="n">
-        <v>7.2005</v>
+        <v>7.2045</v>
       </c>
       <c r="P94" t="n">
         <v>3</v>
@@ -6790,13 +6790,13 @@
         <v>9.26</v>
       </c>
       <c r="M95" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="N95" t="n">
         <v>3.48</v>
       </c>
       <c r="O95" t="n">
-        <v>7.308</v>
+        <v>7.3</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6857,13 +6857,13 @@
         <v>8.15</v>
       </c>
       <c r="M96" t="n">
-        <v>7.27</v>
+        <v>7.19</v>
       </c>
       <c r="N96" t="n">
         <v>4.64</v>
       </c>
       <c r="O96" t="n">
-        <v>7.126499999999999</v>
+        <v>7.1105</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -6924,13 +6924,13 @@
         <v>6.67</v>
       </c>
       <c r="M97" t="n">
-        <v>7.99</v>
+        <v>8.01</v>
       </c>
       <c r="N97" t="n">
         <v>6.69</v>
       </c>
       <c r="O97" t="n">
-        <v>6.457</v>
+        <v>6.461</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -6991,13 +6991,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>7.04</v>
+        <v>7</v>
       </c>
       <c r="N98" t="n">
         <v>3.48</v>
       </c>
       <c r="O98" t="n">
-        <v>8.108499999999999</v>
+        <v>8.1005</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7058,13 +7058,13 @@
         <v>8.74</v>
       </c>
       <c r="M99" t="n">
-        <v>9.390000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="N99" t="n">
         <v>7.6</v>
       </c>
       <c r="O99" t="n">
-        <v>8.567</v>
+        <v>8.551</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7125,13 +7125,13 @@
         <v>7.56</v>
       </c>
       <c r="M100" t="n">
-        <v>9.31</v>
+        <v>9.33</v>
       </c>
       <c r="N100" t="n">
         <v>6.69</v>
       </c>
       <c r="O100" t="n">
-        <v>7.581499999999999</v>
+        <v>7.585499999999999</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
@@ -7192,13 +7192,13 @@
         <v>9.26</v>
       </c>
       <c r="M101" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="N101" t="n">
         <v>3.48</v>
       </c>
       <c r="O101" t="n">
-        <v>7.794</v>
+        <v>7.786</v>
       </c>
       <c r="P101" t="n">
         <v>2</v>
@@ -7259,13 +7259,13 @@
         <v>8.15</v>
       </c>
       <c r="M102" t="n">
-        <v>9.19</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N102" t="n">
         <v>7.6</v>
       </c>
       <c r="O102" t="n">
-        <v>8.0595</v>
+        <v>8.0435</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
@@ -7326,13 +7326,13 @@
         <v>6.67</v>
       </c>
       <c r="M103" t="n">
-        <v>9.35</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="N103" t="n">
         <v>6.69</v>
       </c>
       <c r="O103" t="n">
-        <v>6.885</v>
+        <v>6.888999999999999</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
@@ -7393,13 +7393,13 @@
         <v>9.26</v>
       </c>
       <c r="M104" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
       <c r="N104" t="n">
         <v>3.48</v>
       </c>
       <c r="O104" t="n">
-        <v>7.541</v>
+        <v>7.532999999999999</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -7460,13 +7460,13 @@
         <v>8.15</v>
       </c>
       <c r="M105" t="n">
-        <v>8.109999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N105" t="n">
         <v>4.64</v>
       </c>
       <c r="O105" t="n">
-        <v>7.3275</v>
+        <v>7.3115</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7527,13 +7527,13 @@
         <v>6.67</v>
       </c>
       <c r="M106" t="n">
-        <v>7.04</v>
+        <v>7.07</v>
       </c>
       <c r="N106" t="n">
         <v>6.69</v>
       </c>
       <c r="O106" t="n">
-        <v>6.311999999999999</v>
+        <v>6.318</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -7594,13 +7594,13 @@
         <v>8.15</v>
       </c>
       <c r="M107" t="n">
-        <v>9.119999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N107" t="n">
         <v>4.64</v>
       </c>
       <c r="O107" t="n">
-        <v>7.6015</v>
+        <v>7.5855</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
@@ -7661,13 +7661,13 @@
         <v>7.41</v>
       </c>
       <c r="M108" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="N108" t="n">
         <v>5.71</v>
       </c>
       <c r="O108" t="n">
-        <v>7.217</v>
+        <v>7.223</v>
       </c>
       <c r="P108" t="n">
         <v>2</v>
@@ -7728,13 +7728,13 @@
         <v>6.67</v>
       </c>
       <c r="M109" t="n">
-        <v>7.79</v>
+        <v>7.81</v>
       </c>
       <c r="N109" t="n">
         <v>6.69</v>
       </c>
       <c r="O109" t="n">
-        <v>6.573</v>
+        <v>6.577</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
@@ -7795,13 +7795,13 @@
         <v>7.56</v>
       </c>
       <c r="M110" t="n">
-        <v>8.93</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N110" t="n">
         <v>4.64</v>
       </c>
       <c r="O110" t="n">
-        <v>7.071999999999999</v>
+        <v>7.058</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
@@ -7862,13 +7862,13 @@
         <v>6.67</v>
       </c>
       <c r="M111" t="n">
-        <v>9.15</v>
+        <v>9.19</v>
       </c>
       <c r="N111" t="n">
         <v>5.71</v>
       </c>
       <c r="O111" t="n">
-        <v>6.619999999999999</v>
+        <v>6.627999999999999</v>
       </c>
       <c r="P111" t="n">
         <v>2</v>
@@ -7929,13 +7929,13 @@
         <v>5.78</v>
       </c>
       <c r="M112" t="n">
-        <v>7.84</v>
+        <v>7.87</v>
       </c>
       <c r="N112" t="n">
         <v>6.69</v>
       </c>
       <c r="O112" t="n">
-        <v>5.8455</v>
+        <v>5.8515</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
@@ -7996,13 +7996,13 @@
         <v>8.15</v>
       </c>
       <c r="M113" t="n">
-        <v>9.32</v>
+        <v>9.24</v>
       </c>
       <c r="N113" t="n">
         <v>4.64</v>
       </c>
       <c r="O113" t="n">
-        <v>7.6925</v>
+        <v>7.6765</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -8063,13 +8063,13 @@
         <v>7.41</v>
       </c>
       <c r="M114" t="n">
-        <v>9</v>
+        <v>9.02</v>
       </c>
       <c r="N114" t="n">
         <v>5.71</v>
       </c>
       <c r="O114" t="n">
-        <v>7.265999999999999</v>
+        <v>7.27</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -8130,13 +8130,13 @@
         <v>6.67</v>
       </c>
       <c r="M115" t="n">
-        <v>7.74</v>
+        <v>7.76</v>
       </c>
       <c r="N115" t="n">
         <v>6.69</v>
       </c>
       <c r="O115" t="n">
-        <v>6.640999999999999</v>
+        <v>6.644999999999999</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8197,13 +8197,13 @@
         <v>8.74</v>
       </c>
       <c r="M116" t="n">
-        <v>9.119999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N116" t="n">
         <v>4.64</v>
       </c>
       <c r="O116" t="n">
-        <v>8.026999999999999</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
@@ -8264,13 +8264,13 @@
         <v>8.15</v>
       </c>
       <c r="M117" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="N117" t="n">
         <v>5.71</v>
       </c>
       <c r="O117" t="n">
-        <v>7.752</v>
+        <v>7.758</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
@@ -8331,13 +8331,13 @@
         <v>7.56</v>
       </c>
       <c r="M118" t="n">
-        <v>7.79</v>
+        <v>7.81</v>
       </c>
       <c r="N118" t="n">
         <v>6.69</v>
       </c>
       <c r="O118" t="n">
-        <v>7.2145</v>
+        <v>7.218500000000001</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
@@ -8398,13 +8398,13 @@
         <v>8.15</v>
       </c>
       <c r="M119" t="n">
-        <v>9.24</v>
+        <v>9.16</v>
       </c>
       <c r="N119" t="n">
         <v>4.64</v>
       </c>
       <c r="O119" t="n">
-        <v>7.655499999999999</v>
+        <v>7.639499999999999</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
@@ -8465,13 +8465,13 @@
         <v>7.41</v>
       </c>
       <c r="M120" t="n">
-        <v>9.02</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N120" t="n">
         <v>5.71</v>
       </c>
       <c r="O120" t="n">
-        <v>7.246</v>
+        <v>7.252</v>
       </c>
       <c r="P120" t="n">
         <v>2</v>
@@ -8532,13 +8532,13 @@
         <v>6.67</v>
       </c>
       <c r="M121" t="n">
-        <v>7.76</v>
+        <v>7.78</v>
       </c>
       <c r="N121" t="n">
         <v>6.69</v>
       </c>
       <c r="O121" t="n">
-        <v>6.611999999999999</v>
+        <v>6.616</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
@@ -9202,13 +9202,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M131" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="N131" t="n">
         <v>3.48</v>
       </c>
       <c r="O131" t="n">
-        <v>8.2645</v>
+        <v>8.2525</v>
       </c>
       <c r="P131" t="n">
         <v>2</v>
@@ -9269,13 +9269,13 @@
         <v>8.74</v>
       </c>
       <c r="M132" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="N132" t="n">
         <v>7.6</v>
       </c>
       <c r="O132" t="n">
-        <v>8.807</v>
+        <v>8.813000000000001</v>
       </c>
       <c r="P132" t="n">
         <v>1</v>
@@ -9336,13 +9336,13 @@
         <v>7.56</v>
       </c>
       <c r="M133" t="n">
-        <v>9.210000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N133" t="n">
         <v>6.69</v>
       </c>
       <c r="O133" t="n">
-        <v>7.7505</v>
+        <v>7.7525</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
@@ -9604,13 +9604,13 @@
         <v>9.33</v>
       </c>
       <c r="M137" t="n">
-        <v>5.95</v>
+        <v>5.94</v>
       </c>
       <c r="N137" t="n">
         <v>2.86</v>
       </c>
       <c r="O137" t="n">
-        <v>7.4735</v>
+        <v>7.471500000000001</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
@@ -9671,13 +9671,13 @@
         <v>8</v>
       </c>
       <c r="M138" t="n">
-        <v>8.1</v>
+        <v>8.07</v>
       </c>
       <c r="N138" t="n">
         <v>3.07</v>
       </c>
       <c r="O138" t="n">
-        <v>6.911499999999999</v>
+        <v>6.905499999999999</v>
       </c>
       <c r="P138" t="n">
         <v>2</v>
@@ -9738,13 +9738,13 @@
         <v>6.67</v>
       </c>
       <c r="M139" t="n">
-        <v>9.9</v>
+        <v>9.85</v>
       </c>
       <c r="N139" t="n">
         <v>5.71</v>
       </c>
       <c r="O139" t="n">
-        <v>6.644</v>
+        <v>6.633999999999999</v>
       </c>
       <c r="P139" t="n">
         <v>3</v>
@@ -10073,13 +10073,13 @@
         <v>9.33</v>
       </c>
       <c r="M144" t="n">
-        <v>7.74</v>
+        <v>7.69</v>
       </c>
       <c r="N144" t="n">
         <v>5.01</v>
       </c>
       <c r="O144" t="n">
-        <v>8.234999999999999</v>
+        <v>8.225</v>
       </c>
       <c r="P144" t="n">
         <v>1</v>
@@ -10140,13 +10140,13 @@
         <v>7.56</v>
       </c>
       <c r="M145" t="n">
-        <v>9.35</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="N145" t="n">
         <v>6.69</v>
       </c>
       <c r="O145" t="n">
-        <v>7.5265</v>
+        <v>7.5305</v>
       </c>
       <c r="P145" t="n">
         <v>2</v>
@@ -10207,13 +10207,13 @@
         <v>8.52</v>
       </c>
       <c r="M146" t="n">
-        <v>8.74</v>
+        <v>8.66</v>
       </c>
       <c r="N146" t="n">
         <v>6.37</v>
       </c>
       <c r="O146" t="n">
-        <v>8.115499999999999</v>
+        <v>8.099499999999999</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
@@ -10274,13 +10274,13 @@
         <v>5.93</v>
       </c>
       <c r="M147" t="n">
-        <v>8.84</v>
+        <v>8.85</v>
       </c>
       <c r="N147" t="n">
         <v>5.71</v>
       </c>
       <c r="O147" t="n">
-        <v>6.226999999999999</v>
+        <v>6.229</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
@@ -10408,13 +10408,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M149" t="n">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="N149" t="n">
         <v>3.48</v>
       </c>
       <c r="O149" t="n">
-        <v>7.634500000000001</v>
+        <v>7.626500000000001</v>
       </c>
       <c r="P149" t="n">
         <v>2</v>
@@ -10475,13 +10475,13 @@
         <v>8.74</v>
       </c>
       <c r="M150" t="n">
-        <v>7.46</v>
+        <v>7.38</v>
       </c>
       <c r="N150" t="n">
         <v>4.64</v>
       </c>
       <c r="O150" t="n">
-        <v>7.656</v>
+        <v>7.64</v>
       </c>
       <c r="P150" t="n">
         <v>1</v>
@@ -10542,13 +10542,13 @@
         <v>7.56</v>
       </c>
       <c r="M151" t="n">
-        <v>7.92</v>
+        <v>7.95</v>
       </c>
       <c r="N151" t="n">
         <v>6.69</v>
       </c>
       <c r="O151" t="n">
-        <v>7.177499999999999</v>
+        <v>7.1835</v>
       </c>
       <c r="P151" t="n">
         <v>3</v>
@@ -10609,13 +10609,13 @@
         <v>9.26</v>
       </c>
       <c r="M152" t="n">
-        <v>6.1</v>
+        <v>6.06</v>
       </c>
       <c r="N152" t="n">
         <v>3.48</v>
       </c>
       <c r="O152" t="n">
-        <v>7.643999999999999</v>
+        <v>7.635999999999999</v>
       </c>
       <c r="P152" t="n">
         <v>2</v>
@@ -10676,13 +10676,13 @@
         <v>8.15</v>
       </c>
       <c r="M153" t="n">
-        <v>8.59</v>
+        <v>8.5</v>
       </c>
       <c r="N153" t="n">
         <v>7.6</v>
       </c>
       <c r="O153" t="n">
-        <v>7.969499999999999</v>
+        <v>7.951499999999999</v>
       </c>
       <c r="P153" t="n">
         <v>1</v>
@@ -10743,13 +10743,13 @@
         <v>6.67</v>
       </c>
       <c r="M154" t="n">
-        <v>8.609999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N154" t="n">
         <v>6.69</v>
       </c>
       <c r="O154" t="n">
-        <v>6.781999999999999</v>
+        <v>6.786</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -10810,13 +10810,13 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>7.74</v>
+        <v>7.69</v>
       </c>
       <c r="N155" t="n">
         <v>1.51</v>
       </c>
       <c r="O155" t="n">
-        <v>7.391</v>
+        <v>7.381</v>
       </c>
       <c r="P155" t="n">
         <v>2</v>
@@ -10877,13 +10877,13 @@
         <v>8.15</v>
       </c>
       <c r="M156" t="n">
-        <v>9.119999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N156" t="n">
         <v>4.64</v>
       </c>
       <c r="O156" t="n">
-        <v>7.6015</v>
+        <v>7.5855</v>
       </c>
       <c r="P156" t="n">
         <v>1</v>
@@ -10944,13 +10944,13 @@
         <v>7.41</v>
       </c>
       <c r="M157" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="N157" t="n">
         <v>5.71</v>
       </c>
       <c r="O157" t="n">
-        <v>7.217</v>
+        <v>7.223</v>
       </c>
       <c r="P157" t="n">
         <v>3</v>
@@ -11011,13 +11011,13 @@
         <v>8.15</v>
       </c>
       <c r="M158" t="n">
-        <v>9.24</v>
+        <v>9.16</v>
       </c>
       <c r="N158" t="n">
         <v>4.64</v>
       </c>
       <c r="O158" t="n">
-        <v>7.655499999999999</v>
+        <v>7.639499999999999</v>
       </c>
       <c r="P158" t="n">
         <v>1</v>
@@ -11078,13 +11078,13 @@
         <v>7.41</v>
       </c>
       <c r="M159" t="n">
-        <v>9.02</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N159" t="n">
         <v>5.71</v>
       </c>
       <c r="O159" t="n">
-        <v>7.246</v>
+        <v>7.252</v>
       </c>
       <c r="P159" t="n">
         <v>2</v>
@@ -11145,13 +11145,13 @@
         <v>6.67</v>
       </c>
       <c r="M160" t="n">
-        <v>7.76</v>
+        <v>7.78</v>
       </c>
       <c r="N160" t="n">
         <v>6.69</v>
       </c>
       <c r="O160" t="n">
-        <v>6.611999999999999</v>
+        <v>6.616</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
@@ -11681,13 +11681,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M168" t="n">
-        <v>7.15</v>
+        <v>7.11</v>
       </c>
       <c r="N168" t="n">
         <v>3.48</v>
       </c>
       <c r="O168" t="n">
-        <v>8.154500000000001</v>
+        <v>8.146500000000001</v>
       </c>
       <c r="P168" t="n">
         <v>2</v>
@@ -11748,13 +11748,13 @@
         <v>8.74</v>
       </c>
       <c r="M169" t="n">
-        <v>9.619999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="N169" t="n">
         <v>7.6</v>
       </c>
       <c r="O169" t="n">
-        <v>8.654999999999999</v>
+        <v>8.636999999999999</v>
       </c>
       <c r="P169" t="n">
         <v>1</v>
@@ -12083,13 +12083,13 @@
         <v>9.26</v>
       </c>
       <c r="M174" t="n">
-        <v>7.34</v>
+        <v>7.28</v>
       </c>
       <c r="N174" t="n">
         <v>3.48</v>
       </c>
       <c r="O174" t="n">
-        <v>7.984999999999999</v>
+        <v>7.973</v>
       </c>
       <c r="P174" t="n">
         <v>1</v>
@@ -12150,13 +12150,13 @@
         <v>8.15</v>
       </c>
       <c r="M175" t="n">
-        <v>9.99</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="N175" t="n">
         <v>4.64</v>
       </c>
       <c r="O175" t="n">
-        <v>7.9525</v>
+        <v>7.930499999999999</v>
       </c>
       <c r="P175" t="n">
         <v>2</v>
@@ -12284,13 +12284,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M177" t="n">
-        <v>7</v>
+        <v>6.96</v>
       </c>
       <c r="N177" t="n">
         <v>3.48</v>
       </c>
       <c r="O177" t="n">
-        <v>8.0885</v>
+        <v>8.080500000000001</v>
       </c>
       <c r="P177" t="n">
         <v>2</v>
@@ -12351,13 +12351,13 @@
         <v>8.74</v>
       </c>
       <c r="M178" t="n">
-        <v>9.31</v>
+        <v>9.23</v>
       </c>
       <c r="N178" t="n">
         <v>7.6</v>
       </c>
       <c r="O178" t="n">
-        <v>8.536</v>
+        <v>8.52</v>
       </c>
       <c r="P178" t="n">
         <v>1</v>
@@ -12619,13 +12619,13 @@
         <v>9.93</v>
       </c>
       <c r="M182" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="N182" t="n">
         <v>2.86</v>
       </c>
       <c r="O182" t="n">
-        <v>7.9665</v>
+        <v>7.9645</v>
       </c>
       <c r="P182" t="n">
         <v>3</v>
@@ -12686,13 +12686,13 @@
         <v>9.33</v>
       </c>
       <c r="M183" t="n">
-        <v>7.56</v>
+        <v>7.52</v>
       </c>
       <c r="N183" t="n">
         <v>5.01</v>
       </c>
       <c r="O183" t="n">
-        <v>8.157</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
@@ -12753,13 +12753,13 @@
         <v>8.15</v>
       </c>
       <c r="M184" t="n">
-        <v>9.94</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N184" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="O184" t="n">
-        <v>8.265000000000001</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="P184" t="n">
         <v>1</v>
@@ -12887,13 +12887,13 @@
         <v>9.26</v>
       </c>
       <c r="M186" t="n">
-        <v>7.08</v>
+        <v>7.04</v>
       </c>
       <c r="N186" t="n">
         <v>3.48</v>
       </c>
       <c r="O186" t="n">
-        <v>7.867000000000001</v>
+        <v>7.859000000000001</v>
       </c>
       <c r="P186" t="n">
         <v>1</v>
@@ -12954,13 +12954,13 @@
         <v>8.15</v>
       </c>
       <c r="M187" t="n">
-        <v>9.48</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N187" t="n">
         <v>4.64</v>
       </c>
       <c r="O187" t="n">
-        <v>7.745499999999999</v>
+        <v>7.727499999999999</v>
       </c>
       <c r="P187" t="n">
         <v>3</v>
@@ -13088,13 +13088,13 @@
         <v>9.33</v>
       </c>
       <c r="M189" t="n">
-        <v>6.26</v>
+        <v>6.23</v>
       </c>
       <c r="N189" t="n">
         <v>2.86</v>
       </c>
       <c r="O189" t="n">
-        <v>7.7095</v>
+        <v>7.703500000000001</v>
       </c>
       <c r="P189" t="n">
         <v>1</v>
@@ -13155,13 +13155,13 @@
         <v>8.44</v>
       </c>
       <c r="M190" t="n">
-        <v>8.220000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N190" t="n">
         <v>1.51</v>
       </c>
       <c r="O190" t="n">
-        <v>7.305499999999999</v>
+        <v>7.289499999999999</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
@@ -13490,13 +13490,13 @@
         <v>9.26</v>
       </c>
       <c r="M195" t="n">
-        <v>7.08</v>
+        <v>7.04</v>
       </c>
       <c r="N195" t="n">
         <v>3.48</v>
       </c>
       <c r="O195" t="n">
-        <v>7.867000000000001</v>
+        <v>7.859000000000001</v>
       </c>
       <c r="P195" t="n">
         <v>1</v>
@@ -13557,13 +13557,13 @@
         <v>8.15</v>
       </c>
       <c r="M196" t="n">
-        <v>9.48</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N196" t="n">
         <v>4.64</v>
       </c>
       <c r="O196" t="n">
-        <v>7.745499999999999</v>
+        <v>7.727499999999999</v>
       </c>
       <c r="P196" t="n">
         <v>3</v>
@@ -13691,13 +13691,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M198" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="N198" t="n">
         <v>3.48</v>
       </c>
       <c r="O198" t="n">
-        <v>8.2645</v>
+        <v>8.2525</v>
       </c>
       <c r="P198" t="n">
         <v>2</v>
@@ -13758,13 +13758,13 @@
         <v>8.74</v>
       </c>
       <c r="M199" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="N199" t="n">
         <v>7.6</v>
       </c>
       <c r="O199" t="n">
-        <v>8.807</v>
+        <v>8.813000000000001</v>
       </c>
       <c r="P199" t="n">
         <v>1</v>
@@ -13892,13 +13892,13 @@
         <v>9.26</v>
       </c>
       <c r="M201" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="N201" t="n">
         <v>3.48</v>
       </c>
       <c r="O201" t="n">
-        <v>7.794</v>
+        <v>7.786</v>
       </c>
       <c r="P201" t="n">
         <v>1</v>
@@ -13959,13 +13959,13 @@
         <v>8.52</v>
       </c>
       <c r="M202" t="n">
-        <v>8.49</v>
+        <v>8.42</v>
       </c>
       <c r="N202" t="n">
         <v>3.07</v>
       </c>
       <c r="O202" t="n">
-        <v>7.5075</v>
+        <v>7.4935</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
@@ -14093,13 +14093,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M204" t="n">
-        <v>7.08</v>
+        <v>7.04</v>
       </c>
       <c r="N204" t="n">
         <v>3.48</v>
       </c>
       <c r="O204" t="n">
-        <v>8.125500000000001</v>
+        <v>8.1175</v>
       </c>
       <c r="P204" t="n">
         <v>2</v>
@@ -14160,13 +14160,13 @@
         <v>8.74</v>
       </c>
       <c r="M205" t="n">
-        <v>9.48</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N205" t="n">
         <v>7.6</v>
       </c>
       <c r="O205" t="n">
-        <v>8.603</v>
+        <v>8.584999999999999</v>
       </c>
       <c r="P205" t="n">
         <v>1</v>
@@ -14294,13 +14294,13 @@
         <v>9.26</v>
       </c>
       <c r="M207" t="n">
-        <v>6.81</v>
+        <v>6.78</v>
       </c>
       <c r="N207" t="n">
         <v>3.48</v>
       </c>
       <c r="O207" t="n">
-        <v>7.723</v>
+        <v>7.717</v>
       </c>
       <c r="P207" t="n">
         <v>2</v>
@@ -14361,13 +14361,13 @@
         <v>8.15</v>
       </c>
       <c r="M208" t="n">
-        <v>8.93</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N208" t="n">
         <v>4.64</v>
       </c>
       <c r="O208" t="n">
-        <v>7.4915</v>
+        <v>7.4775</v>
       </c>
       <c r="P208" t="n">
         <v>3</v>
@@ -14495,13 +14495,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M210" t="n">
-        <v>7.28</v>
+        <v>7.23</v>
       </c>
       <c r="N210" t="n">
         <v>3.48</v>
       </c>
       <c r="O210" t="n">
-        <v>8.2075</v>
+        <v>8.1975</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -14562,13 +14562,13 @@
         <v>9.039999999999999</v>
       </c>
       <c r="M211" t="n">
-        <v>9.08</v>
+        <v>8.99</v>
       </c>
       <c r="N211" t="n">
         <v>6.37</v>
       </c>
       <c r="O211" t="n">
-        <v>8.605499999999999</v>
+        <v>8.5875</v>
       </c>
       <c r="P211" t="n">
         <v>1</v>
@@ -14830,13 +14830,13 @@
         <v>9.93</v>
       </c>
       <c r="M215" t="n">
-        <v>5.98</v>
+        <v>5.96</v>
       </c>
       <c r="N215" t="n">
         <v>2.86</v>
       </c>
       <c r="O215" t="n">
-        <v>7.9505</v>
+        <v>7.9465</v>
       </c>
       <c r="P215" t="n">
         <v>3</v>
@@ -14897,13 +14897,13 @@
         <v>9.33</v>
       </c>
       <c r="M216" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="N216" t="n">
         <v>5.01</v>
       </c>
       <c r="O216" t="n">
-        <v>8.123999999999999</v>
+        <v>8.113999999999999</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -14964,13 +14964,13 @@
         <v>8.15</v>
       </c>
       <c r="M217" t="n">
-        <v>9.99</v>
+        <v>9.94</v>
       </c>
       <c r="N217" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="O217" t="n">
-        <v>8.241999999999999</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="P217" t="n">
         <v>1</v>
@@ -15098,13 +15098,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M219" t="n">
-        <v>6.88</v>
+        <v>6.85</v>
       </c>
       <c r="N219" t="n">
         <v>3.48</v>
       </c>
       <c r="O219" t="n">
-        <v>8.0345</v>
+        <v>8.028499999999999</v>
       </c>
       <c r="P219" t="n">
         <v>2</v>
@@ -15165,13 +15165,13 @@
         <v>8.74</v>
       </c>
       <c r="M220" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="N220" t="n">
         <v>7.6</v>
       </c>
       <c r="O220" t="n">
-        <v>8.436999999999999</v>
+        <v>8.423</v>
       </c>
       <c r="P220" t="n">
         <v>1</v>
@@ -15299,13 +15299,13 @@
         <v>9.26</v>
       </c>
       <c r="M222" t="n">
-        <v>6.81</v>
+        <v>6.78</v>
       </c>
       <c r="N222" t="n">
         <v>3.48</v>
       </c>
       <c r="O222" t="n">
-        <v>7.723</v>
+        <v>7.717</v>
       </c>
       <c r="P222" t="n">
         <v>2</v>
@@ -15366,13 +15366,13 @@
         <v>8.15</v>
       </c>
       <c r="M223" t="n">
-        <v>8.93</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N223" t="n">
         <v>4.64</v>
       </c>
       <c r="O223" t="n">
-        <v>7.4915</v>
+        <v>7.4775</v>
       </c>
       <c r="P223" t="n">
         <v>3</v>
@@ -15701,13 +15701,13 @@
         <v>9.26</v>
       </c>
       <c r="M228" t="n">
-        <v>7.04</v>
+        <v>7</v>
       </c>
       <c r="N228" t="n">
         <v>3.48</v>
       </c>
       <c r="O228" t="n">
-        <v>7.847</v>
+        <v>7.839</v>
       </c>
       <c r="P228" t="n">
         <v>1</v>
@@ -15768,13 +15768,13 @@
         <v>8.15</v>
       </c>
       <c r="M229" t="n">
-        <v>9.390000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="N229" t="n">
         <v>4.64</v>
       </c>
       <c r="O229" t="n">
-        <v>7.7065</v>
+        <v>7.6905</v>
       </c>
       <c r="P229" t="n">
         <v>3</v>
@@ -15902,13 +15902,13 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M231" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="N231" t="n">
         <v>3.48</v>
       </c>
       <c r="O231" t="n">
-        <v>7.9485</v>
+        <v>7.9445</v>
       </c>
       <c r="P231" t="n">
         <v>2</v>
@@ -15969,13 +15969,13 @@
         <v>8.74</v>
       </c>
       <c r="M232" t="n">
-        <v>8.74</v>
+        <v>8.69</v>
       </c>
       <c r="N232" t="n">
         <v>7.6</v>
       </c>
       <c r="O232" t="n">
-        <v>8.286999999999999</v>
+        <v>8.276999999999999</v>
       </c>
       <c r="P232" t="n">
         <v>1</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -620,10 +620,10 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>9.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>4.76</v>
@@ -632,7 +632,7 @@
         <v>3.48</v>
       </c>
       <c r="O3" t="n">
-        <v>7.803</v>
+        <v>7.58</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -687,10 +687,10 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>8.42</v>
+        <v>7.77</v>
       </c>
       <c r="L4" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>7.11</v>
@@ -699,7 +699,7 @@
         <v>7.6</v>
       </c>
       <c r="O4" t="n">
-        <v>8.3535</v>
+        <v>7.854</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -821,10 +821,10 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>9.539999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>9.56</v>
+        <v>8.85</v>
       </c>
       <c r="M6" t="n">
         <v>9.32</v>
@@ -833,7 +833,7 @@
         <v>6.37</v>
       </c>
       <c r="O6" t="n">
-        <v>9.027500000000002</v>
+        <v>8.700999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M7" t="n">
         <v>9.59</v>
@@ -900,7 +900,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.957999999999998</v>
+        <v>8.388</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -955,10 +955,10 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>9.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>6.7</v>
@@ -967,10 +967,10 @@
         <v>3.48</v>
       </c>
       <c r="O8" t="n">
-        <v>8.190999999999999</v>
+        <v>7.968</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>1.19415490086141</v>
@@ -1022,10 +1022,10 @@
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>8.42</v>
+        <v>7.77</v>
       </c>
       <c r="L9" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>8.69</v>
@@ -1034,7 +1034,7 @@
         <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>8.669499999999999</v>
+        <v>8.17</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1089,10 +1089,10 @@
         <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>7.08</v>
+        <v>5.95</v>
       </c>
       <c r="L10" t="n">
-        <v>8.44</v>
+        <v>6.92</v>
       </c>
       <c r="M10" t="n">
         <v>9.51</v>
@@ -1101,10 +1101,10 @@
         <v>9.25</v>
       </c>
       <c r="O10" t="n">
-        <v>8.3675</v>
+        <v>7.4965</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
         <v>2.865971762067384</v>
@@ -1156,10 +1156,10 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>9.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M11" t="n">
         <v>7.37</v>
@@ -1168,7 +1168,7 @@
         <v>3.48</v>
       </c>
       <c r="O11" t="n">
-        <v>8.009</v>
+        <v>7.5755</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -1223,10 +1223,10 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>8.5</v>
+        <v>7.87</v>
       </c>
       <c r="L12" t="n">
-        <v>8.52</v>
+        <v>7.05</v>
       </c>
       <c r="M12" t="n">
         <v>9.220000000000001</v>
@@ -1235,7 +1235,7 @@
         <v>6.37</v>
       </c>
       <c r="O12" t="n">
-        <v>8.3315</v>
+        <v>7.628</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1290,10 +1290,10 @@
         <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>7.38</v>
+        <v>6.36</v>
       </c>
       <c r="L13" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M13" t="n">
         <v>9.609999999999999</v>
@@ -1302,7 +1302,7 @@
         <v>5.71</v>
       </c>
       <c r="O13" t="n">
-        <v>7.585999999999999</v>
+        <v>6.481999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
@@ -1357,10 +1357,10 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>9.99</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>7.43</v>
@@ -1369,10 +1369,10 @@
         <v>3.48</v>
       </c>
       <c r="O14" t="n">
-        <v>8.504999999999999</v>
+        <v>8.341999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.79610326724094</v>
@@ -1424,10 +1424,10 @@
         <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>9.539999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>9.56</v>
+        <v>8.85</v>
       </c>
       <c r="M15" t="n">
         <v>9.32</v>
@@ -1436,7 +1436,7 @@
         <v>6.37</v>
       </c>
       <c r="O15" t="n">
-        <v>9.027500000000002</v>
+        <v>8.700999999999999</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
         <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M16" t="n">
         <v>8.82</v>
@@ -1503,10 +1503,10 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.803999999999998</v>
+        <v>8.234</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
         <v>1.59220653448188</v>
@@ -1558,10 +1558,10 @@
         <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>7.75</v>
+        <v>6.86</v>
       </c>
       <c r="L17" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M17" t="n">
         <v>7.4</v>
@@ -1570,7 +1570,7 @@
         <v>5.01</v>
       </c>
       <c r="O17" t="n">
-        <v>7.668</v>
+        <v>6.981</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1625,10 +1625,10 @@
         <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>6.07</v>
+        <v>4.59</v>
       </c>
       <c r="L18" t="n">
-        <v>7.78</v>
+        <v>5.77</v>
       </c>
       <c r="M18" t="n">
         <v>8.859999999999999</v>
@@ -1637,7 +1637,7 @@
         <v>5.19</v>
       </c>
       <c r="O18" t="n">
-        <v>7.0945</v>
+        <v>5.947</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1692,10 +1692,10 @@
         <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>4.39</v>
+        <v>2.32</v>
       </c>
       <c r="L19" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="n">
         <v>7.97</v>
@@ -1704,7 +1704,7 @@
         <v>6.69</v>
       </c>
       <c r="O19" t="n">
-        <v>6.249</v>
+        <v>4.641</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1759,10 +1759,10 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>9.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>6.7</v>
@@ -1771,7 +1771,7 @@
         <v>3.48</v>
       </c>
       <c r="O20" t="n">
-        <v>8.190999999999999</v>
+        <v>7.968</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1826,10 +1826,10 @@
         <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>8.76</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>9.56</v>
+        <v>8.85</v>
       </c>
       <c r="M21" t="n">
         <v>8.07</v>
@@ -1838,10 +1838,10 @@
         <v>6.37</v>
       </c>
       <c r="O21" t="n">
-        <v>8.5435</v>
+        <v>8.132999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
         <v>1.671816861205974</v>
@@ -1893,10 +1893,10 @@
         <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>7.75</v>
+        <v>6.86</v>
       </c>
       <c r="L22" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M22" t="n">
         <v>9.85</v>
@@ -1905,10 +1905,10 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>8.673999999999999</v>
+        <v>7.986999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>2.38830980172282</v>
@@ -1975,7 +1975,7 @@
         <v>7.856</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>0.7164929405168461</v>
@@ -2027,10 +2027,10 @@
         <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>9.09</v>
+        <v>8.68</v>
       </c>
       <c r="L24" t="n">
-        <v>9.779999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="M24" t="n">
         <v>7.4</v>
@@ -2039,7 +2039,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>8.381499999999999</v>
+        <v>8.066000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2094,10 +2094,10 @@
         <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>8.09</v>
+        <v>7.32</v>
       </c>
       <c r="L25" t="n">
-        <v>9.109999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="M25" t="n">
         <v>8.859999999999999</v>
@@ -2106,10 +2106,10 @@
         <v>5.19</v>
       </c>
       <c r="O25" t="n">
-        <v>8.165999999999999</v>
+        <v>7.5745</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>2.149478821550538</v>
@@ -2161,10 +2161,10 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>9.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M26" t="n">
         <v>7.43</v>
@@ -2173,7 +2173,7 @@
         <v>3.48</v>
       </c>
       <c r="O26" t="n">
-        <v>8.020999999999999</v>
+        <v>7.587499999999999</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2228,10 +2228,10 @@
         <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>8.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="L27" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M27" t="n">
         <v>9.9</v>
@@ -2240,7 +2240,7 @@
         <v>4.64</v>
       </c>
       <c r="O27" t="n">
-        <v>7.964499999999999</v>
+        <v>7.1305</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -2295,10 +2295,10 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>6.63</v>
+        <v>5.35</v>
       </c>
       <c r="L28" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M28" t="n">
         <v>7.62</v>
@@ -2307,7 +2307,7 @@
         <v>6.69</v>
       </c>
       <c r="O28" t="n">
-        <v>6.850999999999999</v>
+        <v>5.48</v>
       </c>
       <c r="P28" t="n">
         <v>3</v>
@@ -2362,10 +2362,10 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>4.84</v>
+        <v>2.93</v>
       </c>
       <c r="L29" t="n">
-        <v>6.96</v>
+        <v>4.36</v>
       </c>
       <c r="M29" t="n">
         <v>7.85</v>
@@ -2374,7 +2374,7 @@
         <v>4.64</v>
       </c>
       <c r="O29" t="n">
-        <v>6.154</v>
+        <v>4.671</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2429,10 +2429,10 @@
         <v>12</v>
       </c>
       <c r="K30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>4.89</v>
+        <v>0.77</v>
       </c>
       <c r="M30" t="n">
         <v>7.15</v>
@@ -2441,7 +2441,7 @@
         <v>6.69</v>
       </c>
       <c r="O30" t="n">
-        <v>4.655</v>
+        <v>2.703</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>3.36</v>
@@ -2508,7 +2508,7 @@
         <v>4.81</v>
       </c>
       <c r="O31" t="n">
-        <v>2.377</v>
+        <v>1.3935</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -2563,10 +2563,10 @@
         <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>5.88</v>
+        <v>4.34</v>
       </c>
       <c r="L32" t="n">
-        <v>5.93</v>
+        <v>2.56</v>
       </c>
       <c r="M32" t="n">
         <v>8.06</v>
@@ -2575,7 +2575,7 @@
         <v>5.71</v>
       </c>
       <c r="O32" t="n">
-        <v>6.308</v>
+        <v>4.666499999999999</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2630,10 +2630,10 @@
         <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.27</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>4.5</v>
@@ -2642,7 +2642,7 @@
         <v>5.19</v>
       </c>
       <c r="O33" t="n">
-        <v>3.825</v>
+        <v>1.9215</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2697,10 +2697,10 @@
         <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0.64</v>
@@ -2709,7 +2709,7 @@
         <v>4.02</v>
       </c>
       <c r="O34" t="n">
-        <v>1.864</v>
+        <v>0.7309999999999999</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -2764,10 +2764,10 @@
         <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>7.75</v>
+        <v>6.86</v>
       </c>
       <c r="L35" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M35" t="n">
         <v>7.4</v>
@@ -2776,7 +2776,7 @@
         <v>5.01</v>
       </c>
       <c r="O35" t="n">
-        <v>7.668</v>
+        <v>6.981</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2831,10 +2831,10 @@
         <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>5.51</v>
+        <v>3.84</v>
       </c>
       <c r="L36" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M36" t="n">
         <v>9.09</v>
@@ -2843,7 +2843,7 @@
         <v>5.71</v>
       </c>
       <c r="O36" t="n">
-        <v>6.920999999999998</v>
+        <v>5.621999999999999</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
@@ -2898,10 +2898,10 @@
         <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>2.71</v>
+        <v>0.06</v>
       </c>
       <c r="L37" t="n">
-        <v>5.56</v>
+        <v>1.92</v>
       </c>
       <c r="M37" t="n">
         <v>5.53</v>
@@ -2910,7 +2910,7 @@
         <v>5.19</v>
       </c>
       <c r="O37" t="n">
-        <v>4.6435</v>
+        <v>2.5745</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
@@ -2965,10 +2965,10 @@
         <v>6</v>
       </c>
       <c r="K38" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M38" t="n">
         <v>8.42</v>
@@ -2977,7 +2977,7 @@
         <v>5.01</v>
       </c>
       <c r="O38" t="n">
-        <v>8.207999999999998</v>
+        <v>7.638</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3032,10 +3032,10 @@
         <v>9</v>
       </c>
       <c r="K39" t="n">
-        <v>7.75</v>
+        <v>6.86</v>
       </c>
       <c r="L39" t="n">
-        <v>7.78</v>
+        <v>5.77</v>
       </c>
       <c r="M39" t="n">
         <v>9.779999999999999</v>
@@ -3044,7 +3044,7 @@
         <v>5.19</v>
       </c>
       <c r="O39" t="n">
-        <v>7.7825</v>
+        <v>6.812</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
@@ -3099,10 +3099,10 @@
         <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>6.63</v>
+        <v>5.35</v>
       </c>
       <c r="L40" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M40" t="n">
         <v>9.210000000000001</v>
@@ -3111,7 +3111,7 @@
         <v>6.69</v>
       </c>
       <c r="O40" t="n">
-        <v>7.169</v>
+        <v>5.798</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
@@ -3166,10 +3166,10 @@
         <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>6.41</v>
+        <v>5.05</v>
       </c>
       <c r="L41" t="n">
-        <v>8</v>
+        <v>6.15</v>
       </c>
       <c r="M41" t="n">
         <v>7.4</v>
@@ -3178,7 +3178,7 @@
         <v>1.51</v>
       </c>
       <c r="O41" t="n">
-        <v>6.4295</v>
+        <v>5.374</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3233,10 +3233,10 @@
         <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>3.27</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>5.93</v>
+        <v>2.56</v>
       </c>
       <c r="M42" t="n">
         <v>9.09</v>
@@ -3245,7 +3245,7 @@
         <v>5.71</v>
       </c>
       <c r="O42" t="n">
-        <v>5.730999999999999</v>
+        <v>3.8135</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>5.53</v>
@@ -3312,7 +3312,7 @@
         <v>5.19</v>
       </c>
       <c r="O43" t="n">
-        <v>3.05</v>
+        <v>1.8845</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
@@ -3367,10 +3367,10 @@
         <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>7.45</v>
+        <v>6.46</v>
       </c>
       <c r="L44" t="n">
-        <v>7.48</v>
+        <v>5.26</v>
       </c>
       <c r="M44" t="n">
         <v>9.32</v>
@@ -3379,7 +3379,7 @@
         <v>3.07</v>
       </c>
       <c r="O44" t="n">
-        <v>7.177499999999999</v>
+        <v>6.103499999999999</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3434,10 +3434,10 @@
         <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>4.84</v>
+        <v>2.93</v>
       </c>
       <c r="L45" t="n">
-        <v>4.89</v>
+        <v>0.77</v>
       </c>
       <c r="M45" t="n">
         <v>9.210000000000001</v>
@@ -3446,7 +3446,7 @@
         <v>6.69</v>
       </c>
       <c r="O45" t="n">
-        <v>6.009</v>
+        <v>3.994</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3501,10 +3501,10 @@
         <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>2.75</v>
+        <v>0.11</v>
       </c>
       <c r="L46" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>8.23</v>
@@ -3513,7 +3513,7 @@
         <v>4.81</v>
       </c>
       <c r="O46" t="n">
-        <v>4.176</v>
+        <v>2.4005</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
@@ -3568,10 +3568,10 @@
         <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>7.15</v>
@@ -3580,7 +3580,7 @@
         <v>6.69</v>
       </c>
       <c r="O47" t="n">
-        <v>3.9385</v>
+        <v>2.4335</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>4.5</v>
@@ -3647,7 +3647,7 @@
         <v>5.19</v>
       </c>
       <c r="O48" t="n">
-        <v>2.4555</v>
+        <v>1.6785</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0.64</v>
@@ -3714,7 +3714,7 @@
         <v>4.02</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8849999999999999</v>
+        <v>0.7309999999999999</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
@@ -3769,10 +3769,10 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>9.619999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M50" t="n">
         <v>7.43</v>
@@ -3781,7 +3781,7 @@
         <v>3.48</v>
       </c>
       <c r="O50" t="n">
-        <v>8.2645</v>
+        <v>7.9615</v>
       </c>
       <c r="P50" t="n">
         <v>2</v>
@@ -3836,10 +3836,10 @@
         <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>8.720000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="L51" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M51" t="n">
         <v>9.960000000000001</v>
@@ -3848,7 +3848,7 @@
         <v>7.6</v>
       </c>
       <c r="O51" t="n">
-        <v>8.807</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3903,10 +3903,10 @@
         <v>12</v>
       </c>
       <c r="K52" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="L52" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M52" t="n">
         <v>9.210000000000001</v>
@@ -3915,7 +3915,7 @@
         <v>6.69</v>
       </c>
       <c r="O52" t="n">
-        <v>7.7505</v>
+        <v>6.696499999999999</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -3970,10 +3970,10 @@
         <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>5.14</v>
+        <v>3.33</v>
       </c>
       <c r="L53" t="n">
-        <v>5.19</v>
+        <v>1.28</v>
       </c>
       <c r="M53" t="n">
         <v>8.06</v>
@@ -3982,7 +3982,7 @@
         <v>5.71</v>
       </c>
       <c r="O53" t="n">
-        <v>5.826999999999999</v>
+        <v>3.9155</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4037,10 +4037,10 @@
         <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>2.75</v>
+        <v>0.11</v>
       </c>
       <c r="L54" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>5.31</v>
@@ -4049,7 +4049,7 @@
         <v>5.71</v>
       </c>
       <c r="O54" t="n">
-        <v>3.727</v>
+        <v>1.9515</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
@@ -4104,10 +4104,10 @@
         <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.64</v>
@@ -4116,7 +4116,7 @@
         <v>4.02</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9899999999999999</v>
+        <v>0.7309999999999999</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
@@ -4238,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>9.77</v>
+        <v>9.58</v>
       </c>
       <c r="L57" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
         <v>2.2</v>
       </c>
       <c r="O57" t="n">
-        <v>7.332999999999999</v>
+        <v>7.276000000000001</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -4305,10 +4305,10 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M58" t="n">
         <v>4.76</v>
@@ -4317,7 +4317,7 @@
         <v>1.51</v>
       </c>
       <c r="O58" t="n">
-        <v>7.209999999999999</v>
+        <v>6.828999999999999</v>
       </c>
       <c r="P58" t="n">
         <v>2</v>
@@ -4372,10 +4372,10 @@
         <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>9.99</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M59" t="n">
         <v>5.13</v>
@@ -4384,10 +4384,10 @@
         <v>1.51</v>
       </c>
       <c r="O59" t="n">
-        <v>7.749499999999999</v>
+        <v>7.586499999999999</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
         <v>0.79610326724094</v>
@@ -4439,10 +4439,10 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>9.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M60" t="n">
         <v>7.43</v>
@@ -4451,10 +4451,10 @@
         <v>1.51</v>
       </c>
       <c r="O60" t="n">
-        <v>7.725499999999999</v>
+        <v>7.291999999999999</v>
       </c>
       <c r="P60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
         <v>1.3268387787349</v>
@@ -4506,10 +4506,10 @@
         <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>8.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="L61" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M61" t="n">
         <v>9.9</v>
@@ -4518,10 +4518,10 @@
         <v>4.64</v>
       </c>
       <c r="O61" t="n">
-        <v>7.964499999999999</v>
+        <v>7.1305</v>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q61" t="n">
         <v>2.12294204597584</v>
@@ -4573,10 +4573,10 @@
         <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>5.73</v>
+        <v>4.14</v>
       </c>
       <c r="L62" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M62" t="n">
         <v>8.619999999999999</v>
@@ -4585,7 +4585,7 @@
         <v>4.64</v>
       </c>
       <c r="O62" t="n">
-        <v>6.785</v>
+        <v>5.544999999999999</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4640,10 +4640,10 @@
         <v>12</v>
       </c>
       <c r="K63" t="n">
-        <v>3.04</v>
+        <v>0.51</v>
       </c>
       <c r="L63" t="n">
-        <v>5.78</v>
+        <v>2.31</v>
       </c>
       <c r="M63" t="n">
         <v>7.97</v>
@@ -4652,7 +4652,7 @@
         <v>6.69</v>
       </c>
       <c r="O63" t="n">
-        <v>5.5325</v>
+        <v>3.559</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
@@ -4707,10 +4707,10 @@
         <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
         <v>5.53</v>
@@ -4719,7 +4719,7 @@
         <v>5.19</v>
       </c>
       <c r="O64" t="n">
-        <v>3.7475</v>
+        <v>1.8845</v>
       </c>
       <c r="P64" t="n">
         <v>3</v>
@@ -4774,10 +4774,10 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>9.619999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M65" t="n">
         <v>7.43</v>
@@ -4786,7 +4786,7 @@
         <v>3.48</v>
       </c>
       <c r="O65" t="n">
-        <v>8.2645</v>
+        <v>7.9615</v>
       </c>
       <c r="P65" t="n">
         <v>2</v>
@@ -4841,10 +4841,10 @@
         <v>8</v>
       </c>
       <c r="K66" t="n">
-        <v>8.720000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="L66" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M66" t="n">
         <v>9.960000000000001</v>
@@ -4853,7 +4853,7 @@
         <v>7.6</v>
       </c>
       <c r="O66" t="n">
-        <v>8.807</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -4908,10 +4908,10 @@
         <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="L67" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M67" t="n">
         <v>9.210000000000001</v>
@@ -4920,7 +4920,7 @@
         <v>9.25</v>
       </c>
       <c r="O67" t="n">
-        <v>8.134499999999999</v>
+        <v>7.0805</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
@@ -4975,10 +4975,10 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>7.19</v>
+        <v>6.11</v>
       </c>
       <c r="L68" t="n">
-        <v>8.52</v>
+        <v>7.05</v>
       </c>
       <c r="M68" t="n">
         <v>6.7</v>
@@ -4987,7 +4987,7 @@
         <v>1.51</v>
       </c>
       <c r="O68" t="n">
-        <v>6.705499999999999</v>
+        <v>5.866999999999999</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5042,10 +5042,10 @@
         <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>4.84</v>
+        <v>2.93</v>
       </c>
       <c r="L69" t="n">
-        <v>6.96</v>
+        <v>4.36</v>
       </c>
       <c r="M69" t="n">
         <v>8.69</v>
@@ -5054,7 +5054,7 @@
         <v>4.64</v>
       </c>
       <c r="O69" t="n">
-        <v>6.321999999999999</v>
+        <v>4.839</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5109,10 +5109,10 @@
         <v>12</v>
       </c>
       <c r="K70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>4.89</v>
+        <v>0.77</v>
       </c>
       <c r="M70" t="n">
         <v>9.51</v>
@@ -5121,7 +5121,7 @@
         <v>6.69</v>
       </c>
       <c r="O70" t="n">
-        <v>5.127</v>
+        <v>3.175</v>
       </c>
       <c r="P70" t="n">
         <v>3</v>
@@ -5176,10 +5176,10 @@
         <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>8.9</v>
+        <v>8.41</v>
       </c>
       <c r="L71" t="n">
-        <v>9.039999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="M71" t="n">
         <v>6.23</v>
@@ -5188,7 +5188,7 @@
         <v>2.86</v>
       </c>
       <c r="O71" t="n">
-        <v>7.509</v>
+        <v>6.980500000000001</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5243,10 +5243,10 @@
         <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>7.24</v>
+        <v>6.17</v>
       </c>
       <c r="L72" t="n">
-        <v>7.48</v>
+        <v>5.26</v>
       </c>
       <c r="M72" t="n">
         <v>8.99</v>
@@ -5255,7 +5255,7 @@
         <v>3.07</v>
       </c>
       <c r="O72" t="n">
-        <v>7.0485</v>
+        <v>5.9505</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
@@ -5310,10 +5310,10 @@
         <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>5.58</v>
+        <v>3.93</v>
       </c>
       <c r="L73" t="n">
-        <v>5.93</v>
+        <v>2.56</v>
       </c>
       <c r="M73" t="n">
         <v>9.66</v>
@@ -5322,7 +5322,7 @@
         <v>5.71</v>
       </c>
       <c r="O73" t="n">
-        <v>6.537999999999999</v>
+        <v>4.8635</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
@@ -5377,10 +5377,10 @@
         <v>4</v>
       </c>
       <c r="K74" t="n">
-        <v>8.16</v>
+        <v>7.42</v>
       </c>
       <c r="L74" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M74" t="n">
         <v>6.05</v>
@@ -5389,7 +5389,7 @@
         <v>2.86</v>
       </c>
       <c r="O74" t="n">
-        <v>7.146</v>
+        <v>6.469</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -5444,10 +5444,10 @@
         <v>7</v>
       </c>
       <c r="K75" t="n">
-        <v>5.96</v>
+        <v>4.44</v>
       </c>
       <c r="L75" t="n">
-        <v>6.96</v>
+        <v>4.36</v>
       </c>
       <c r="M75" t="n">
         <v>8.42</v>
@@ -5456,7 +5456,7 @@
         <v>3.07</v>
       </c>
       <c r="O75" t="n">
-        <v>6.3685</v>
+        <v>5.0025</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5511,10 +5511,10 @@
         <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>3.75</v>
+        <v>1.46</v>
       </c>
       <c r="L76" t="n">
-        <v>5.19</v>
+        <v>1.28</v>
       </c>
       <c r="M76" t="n">
         <v>9.1</v>
@@ -5523,7 +5523,7 @@
         <v>5.71</v>
       </c>
       <c r="O76" t="n">
-        <v>5.617999999999999</v>
+        <v>3.5625</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
@@ -5578,7 +5578,7 @@
         <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L77" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
         <v>2.2</v>
       </c>
       <c r="O77" t="n">
-        <v>7.856</v>
+        <v>7.840999999999999</v>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0.7627780141936447</v>
@@ -5645,10 +5645,10 @@
         <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>8.25</v>
+        <v>7.54</v>
       </c>
       <c r="L78" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M78" t="n">
         <v>9.16</v>
@@ -5657,10 +5657,10 @@
         <v>4.64</v>
       </c>
       <c r="O78" t="n">
-        <v>8.061999999999999</v>
+        <v>7.393999999999999</v>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
         <v>2.034074704516386</v>
@@ -5712,10 +5712,10 @@
         <v>15</v>
       </c>
       <c r="K79" t="n">
-        <v>5.74</v>
+        <v>4.15</v>
       </c>
       <c r="L79" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M79" t="n">
         <v>5.53</v>
@@ -5724,7 +5724,7 @@
         <v>5.19</v>
       </c>
       <c r="O79" t="n">
-        <v>5.941</v>
+        <v>4.477</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
@@ -5779,10 +5779,10 @@
         <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>9.44</v>
+        <v>9.15</v>
       </c>
       <c r="L80" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M80" t="n">
         <v>6.16</v>
@@ -5791,7 +5791,7 @@
         <v>2.86</v>
       </c>
       <c r="O80" t="n">
-        <v>7.863500000000001</v>
+        <v>7.545500000000001</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -5846,10 +5846,10 @@
         <v>10</v>
       </c>
       <c r="K81" t="n">
-        <v>6.94</v>
+        <v>5.77</v>
       </c>
       <c r="L81" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M81" t="n">
         <v>9.720000000000001</v>
@@ -5858,7 +5858,7 @@
         <v>5.71</v>
       </c>
       <c r="O81" t="n">
-        <v>7.475999999999999</v>
+        <v>6.326999999999999</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
@@ -5913,10 +5913,10 @@
         <v>18</v>
       </c>
       <c r="K82" t="n">
-        <v>3.61</v>
+        <v>1.27</v>
       </c>
       <c r="L82" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>7.43</v>
@@ -5925,7 +5925,7 @@
         <v>4.02</v>
       </c>
       <c r="O82" t="n">
-        <v>4.726</v>
+        <v>2.47</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
@@ -5980,10 +5980,10 @@
         <v>5</v>
       </c>
       <c r="K83" t="n">
-        <v>9.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M83" t="n">
         <v>6.81</v>
@@ -5992,7 +5992,7 @@
         <v>3.48</v>
       </c>
       <c r="O83" t="n">
-        <v>8.0085</v>
+        <v>7.663500000000001</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -6047,10 +6047,10 @@
         <v>12</v>
       </c>
       <c r="K84" t="n">
-        <v>6.48</v>
+        <v>5.15</v>
       </c>
       <c r="L84" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M84" t="n">
         <v>7.87</v>
@@ -6059,7 +6059,7 @@
         <v>6.69</v>
       </c>
       <c r="O84" t="n">
-        <v>7.1675</v>
+        <v>6.0055</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
@@ -6114,10 +6114,10 @@
         <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>3.4</v>
+        <v>0.99</v>
       </c>
       <c r="L85" t="n">
-        <v>5.19</v>
+        <v>1.28</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
         <v>3.17</v>
       </c>
       <c r="O85" t="n">
-        <v>3.312</v>
+        <v>1.2205</v>
       </c>
       <c r="P85" t="n">
         <v>3</v>
@@ -6181,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="L86" t="n">
         <v>10</v>
@@ -6193,10 +6193,10 @@
         <v>1.51</v>
       </c>
       <c r="O86" t="n">
-        <v>7.084499999999999</v>
+        <v>7.078499999999999</v>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
         <v>0.7467325219856878</v>
@@ -6248,10 +6248,10 @@
         <v>7</v>
       </c>
       <c r="K87" t="n">
-        <v>7.43</v>
+        <v>6.43</v>
       </c>
       <c r="L87" t="n">
-        <v>8.52</v>
+        <v>7.05</v>
       </c>
       <c r="M87" t="n">
         <v>8.07</v>
@@ -6260,10 +6260,10 @@
         <v>6.37</v>
       </c>
       <c r="O87" t="n">
-        <v>7.780499999999999</v>
+        <v>6.965999999999999</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
         <v>2.613563826949908</v>
@@ -6315,10 +6315,10 @@
         <v>14</v>
       </c>
       <c r="K88" t="n">
-        <v>3.75</v>
+        <v>1.47</v>
       </c>
       <c r="L88" t="n">
-        <v>5.93</v>
+        <v>2.56</v>
       </c>
       <c r="M88" t="n">
         <v>8.92</v>
@@ -6327,7 +6327,7 @@
         <v>5.71</v>
       </c>
       <c r="O88" t="n">
-        <v>5.840999999999999</v>
+        <v>3.9775</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6382,10 +6382,10 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>9.26</v>
+        <v>8.9</v>
       </c>
       <c r="L89" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M89" t="n">
         <v>8.220000000000001</v>
@@ -6394,7 +6394,7 @@
         <v>5.01</v>
       </c>
       <c r="O89" t="n">
-        <v>8.439</v>
+        <v>8.0265</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -6449,10 +6449,10 @@
         <v>10</v>
       </c>
       <c r="K90" t="n">
-        <v>8.02</v>
+        <v>7.23</v>
       </c>
       <c r="L90" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M90" t="n">
         <v>9.640000000000001</v>
@@ -6461,7 +6461,7 @@
         <v>5.71</v>
       </c>
       <c r="O90" t="n">
-        <v>8.042999999999999</v>
+        <v>7.196999999999999</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6516,10 +6516,10 @@
         <v>16</v>
       </c>
       <c r="K91" t="n">
-        <v>6.16</v>
+        <v>4.72</v>
       </c>
       <c r="L91" t="n">
-        <v>6.37</v>
+        <v>3.33</v>
       </c>
       <c r="M91" t="n">
         <v>8.23</v>
@@ -6528,7 +6528,7 @@
         <v>4.81</v>
       </c>
       <c r="O91" t="n">
-        <v>6.444999999999999</v>
+        <v>4.949</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
@@ -6583,10 +6583,10 @@
         <v>5</v>
       </c>
       <c r="K92" t="n">
-        <v>9.220000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="L92" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M92" t="n">
         <v>4.94</v>
@@ -6595,7 +6595,7 @@
         <v>3.48</v>
       </c>
       <c r="O92" t="n">
-        <v>7.646500000000001</v>
+        <v>7.3015</v>
       </c>
       <c r="P92" t="n">
         <v>2</v>
@@ -6650,10 +6650,10 @@
         <v>8</v>
       </c>
       <c r="K93" t="n">
-        <v>8.08</v>
+        <v>7.31</v>
       </c>
       <c r="L93" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M93" t="n">
         <v>7.46</v>
@@ -6662,7 +6662,7 @@
         <v>7.6</v>
       </c>
       <c r="O93" t="n">
-        <v>8.115</v>
+        <v>7.428999999999999</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -6717,10 +6717,10 @@
         <v>12</v>
       </c>
       <c r="K94" t="n">
-        <v>6.57</v>
+        <v>5.27</v>
       </c>
       <c r="L94" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M94" t="n">
         <v>7.92</v>
@@ -6729,7 +6729,7 @@
         <v>6.69</v>
       </c>
       <c r="O94" t="n">
-        <v>7.2045</v>
+        <v>6.0515</v>
       </c>
       <c r="P94" t="n">
         <v>3</v>
@@ -6784,10 +6784,10 @@
         <v>5</v>
       </c>
       <c r="K95" t="n">
-        <v>8.59</v>
+        <v>8</v>
       </c>
       <c r="L95" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M95" t="n">
         <v>4.8</v>
@@ -6796,7 +6796,7 @@
         <v>3.48</v>
       </c>
       <c r="O95" t="n">
-        <v>7.3</v>
+        <v>6.7975</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6851,10 +6851,10 @@
         <v>8</v>
       </c>
       <c r="K96" t="n">
-        <v>7.08</v>
+        <v>5.96</v>
       </c>
       <c r="L96" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M96" t="n">
         <v>7.19</v>
@@ -6863,7 +6863,7 @@
         <v>4.64</v>
       </c>
       <c r="O96" t="n">
-        <v>7.1105</v>
+        <v>6.1655</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -6918,10 +6918,10 @@
         <v>12</v>
       </c>
       <c r="K97" t="n">
-        <v>5.07</v>
+        <v>3.24</v>
       </c>
       <c r="L97" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M97" t="n">
         <v>8.01</v>
@@ -6930,7 +6930,7 @@
         <v>6.69</v>
       </c>
       <c r="O97" t="n">
-        <v>6.461</v>
+        <v>4.925</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -6985,10 +6985,10 @@
         <v>5</v>
       </c>
       <c r="K98" t="n">
-        <v>9.359999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L98" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M98" t="n">
         <v>7</v>
@@ -6997,7 +6997,7 @@
         <v>3.48</v>
       </c>
       <c r="O98" t="n">
-        <v>8.1005</v>
+        <v>7.7705</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7052,10 +7052,10 @@
         <v>8</v>
       </c>
       <c r="K99" t="n">
-        <v>8.300000000000001</v>
+        <v>7.61</v>
       </c>
       <c r="L99" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M99" t="n">
         <v>9.31</v>
@@ -7064,7 +7064,7 @@
         <v>7.6</v>
       </c>
       <c r="O99" t="n">
-        <v>8.551</v>
+        <v>7.889</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7119,10 +7119,10 @@
         <v>12</v>
       </c>
       <c r="K100" t="n">
-        <v>6.9</v>
+        <v>5.72</v>
       </c>
       <c r="L100" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M100" t="n">
         <v>9.33</v>
@@ -7131,7 +7131,7 @@
         <v>6.69</v>
       </c>
       <c r="O100" t="n">
-        <v>7.585499999999999</v>
+        <v>6.4685</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
@@ -7186,10 +7186,10 @@
         <v>5</v>
       </c>
       <c r="K101" t="n">
-        <v>8.81</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L101" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M101" t="n">
         <v>6.9</v>
@@ -7198,10 +7198,10 @@
         <v>3.48</v>
       </c>
       <c r="O101" t="n">
-        <v>7.786</v>
+        <v>7.3045</v>
       </c>
       <c r="P101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
         <v>1.635405936580226</v>
@@ -7253,10 +7253,10 @@
         <v>8</v>
       </c>
       <c r="K102" t="n">
-        <v>7.43</v>
+        <v>6.43</v>
       </c>
       <c r="L102" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M102" t="n">
         <v>9.109999999999999</v>
@@ -7265,10 +7265,10 @@
         <v>7.6</v>
       </c>
       <c r="O102" t="n">
-        <v>8.0435</v>
+        <v>7.134499999999999</v>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q102" t="n">
         <v>2.616649498528361</v>
@@ -7320,10 +7320,10 @@
         <v>12</v>
       </c>
       <c r="K103" t="n">
-        <v>5.59</v>
+        <v>3.94</v>
       </c>
       <c r="L103" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M103" t="n">
         <v>9.369999999999999</v>
@@ -7332,7 +7332,7 @@
         <v>6.69</v>
       </c>
       <c r="O103" t="n">
-        <v>6.888999999999999</v>
+        <v>5.406999999999999</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
@@ -7387,10 +7387,10 @@
         <v>5</v>
       </c>
       <c r="K104" t="n">
-        <v>8.66</v>
+        <v>8.09</v>
       </c>
       <c r="L104" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M104" t="n">
         <v>5.86</v>
@@ -7399,7 +7399,7 @@
         <v>3.48</v>
       </c>
       <c r="O104" t="n">
-        <v>7.532999999999999</v>
+        <v>7.0365</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -7454,10 +7454,10 @@
         <v>8</v>
       </c>
       <c r="K105" t="n">
-        <v>7.19</v>
+        <v>6.1</v>
       </c>
       <c r="L105" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M105" t="n">
         <v>8.029999999999999</v>
@@ -7466,7 +7466,7 @@
         <v>4.64</v>
       </c>
       <c r="O105" t="n">
-        <v>7.3115</v>
+        <v>6.3755</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7521,10 +7521,10 @@
         <v>12</v>
       </c>
       <c r="K106" t="n">
-        <v>5.22</v>
+        <v>3.45</v>
       </c>
       <c r="L106" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M106" t="n">
         <v>7.07</v>
@@ -7533,7 +7533,7 @@
         <v>6.69</v>
       </c>
       <c r="O106" t="n">
-        <v>6.318</v>
+        <v>4.8</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -7588,10 +7588,10 @@
         <v>8</v>
       </c>
       <c r="K107" t="n">
-        <v>7.43</v>
+        <v>6.43</v>
       </c>
       <c r="L107" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M107" t="n">
         <v>9.039999999999999</v>
@@ -7600,7 +7600,7 @@
         <v>4.64</v>
       </c>
       <c r="O107" t="n">
-        <v>7.5855</v>
+        <v>6.676499999999999</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
@@ -7655,10 +7655,10 @@
         <v>10</v>
       </c>
       <c r="K108" t="n">
-        <v>6.51</v>
+        <v>5.19</v>
       </c>
       <c r="L108" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M108" t="n">
         <v>9.1</v>
@@ -7667,7 +7667,7 @@
         <v>5.71</v>
       </c>
       <c r="O108" t="n">
-        <v>7.223</v>
+        <v>6.029</v>
       </c>
       <c r="P108" t="n">
         <v>2</v>
@@ -7722,10 +7722,10 @@
         <v>12</v>
       </c>
       <c r="K109" t="n">
-        <v>5.59</v>
+        <v>3.94</v>
       </c>
       <c r="L109" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M109" t="n">
         <v>7.81</v>
@@ -7734,7 +7734,7 @@
         <v>6.69</v>
       </c>
       <c r="O109" t="n">
-        <v>6.577</v>
+        <v>5.095</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
@@ -7789,10 +7789,10 @@
         <v>8</v>
       </c>
       <c r="K110" t="n">
-        <v>6.48</v>
+        <v>5.15</v>
       </c>
       <c r="L110" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M110" t="n">
         <v>8.859999999999999</v>
@@ -7801,7 +7801,7 @@
         <v>4.64</v>
       </c>
       <c r="O110" t="n">
-        <v>7.058</v>
+        <v>5.896</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
@@ -7856,10 +7856,10 @@
         <v>10</v>
       </c>
       <c r="K111" t="n">
-        <v>5.33</v>
+        <v>3.59</v>
       </c>
       <c r="L111" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M111" t="n">
         <v>9.19</v>
@@ -7868,7 +7868,7 @@
         <v>5.71</v>
       </c>
       <c r="O111" t="n">
-        <v>6.627999999999999</v>
+        <v>5.119</v>
       </c>
       <c r="P111" t="n">
         <v>2</v>
@@ -7923,10 +7923,10 @@
         <v>12</v>
       </c>
       <c r="K112" t="n">
-        <v>4.17</v>
+        <v>2.03</v>
       </c>
       <c r="L112" t="n">
-        <v>5.78</v>
+        <v>2.31</v>
       </c>
       <c r="M112" t="n">
         <v>7.87</v>
@@ -7935,7 +7935,7 @@
         <v>6.69</v>
       </c>
       <c r="O112" t="n">
-        <v>5.8515</v>
+        <v>3.995</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
@@ -7990,10 +7990,10 @@
         <v>8</v>
       </c>
       <c r="K113" t="n">
-        <v>7.6</v>
+        <v>6.66</v>
       </c>
       <c r="L113" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M113" t="n">
         <v>9.24</v>
@@ -8002,7 +8002,7 @@
         <v>4.64</v>
       </c>
       <c r="O113" t="n">
-        <v>7.6765</v>
+        <v>6.7855</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -8057,10 +8057,10 @@
         <v>10</v>
       </c>
       <c r="K114" t="n">
-        <v>6.72</v>
+        <v>5.48</v>
       </c>
       <c r="L114" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M114" t="n">
         <v>9.02</v>
@@ -8069,7 +8069,7 @@
         <v>5.71</v>
       </c>
       <c r="O114" t="n">
-        <v>7.27</v>
+        <v>6.1</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -8124,10 +8124,10 @@
         <v>12</v>
       </c>
       <c r="K115" t="n">
-        <v>5.85</v>
+        <v>4.29</v>
       </c>
       <c r="L115" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M115" t="n">
         <v>7.76</v>
@@ -8136,7 +8136,7 @@
         <v>6.69</v>
       </c>
       <c r="O115" t="n">
-        <v>6.644999999999999</v>
+        <v>5.19</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8191,10 +8191,10 @@
         <v>8</v>
       </c>
       <c r="K116" t="n">
-        <v>8.16</v>
+        <v>7.42</v>
       </c>
       <c r="L116" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M116" t="n">
         <v>9.039999999999999</v>
@@ -8203,7 +8203,7 @@
         <v>4.64</v>
       </c>
       <c r="O116" t="n">
-        <v>8.010999999999999</v>
+        <v>7.334</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
@@ -8258,10 +8258,10 @@
         <v>10</v>
       </c>
       <c r="K117" t="n">
-        <v>7.43</v>
+        <v>6.43</v>
       </c>
       <c r="L117" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M117" t="n">
         <v>9.1</v>
@@ -8270,7 +8270,7 @@
         <v>5.71</v>
       </c>
       <c r="O117" t="n">
-        <v>7.758</v>
+        <v>6.848999999999999</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
@@ -8325,10 +8325,10 @@
         <v>12</v>
       </c>
       <c r="K118" t="n">
-        <v>6.69</v>
+        <v>5.43</v>
       </c>
       <c r="L118" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M118" t="n">
         <v>7.81</v>
@@ -8337,7 +8337,7 @@
         <v>6.69</v>
       </c>
       <c r="O118" t="n">
-        <v>7.218500000000001</v>
+        <v>6.0775</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
@@ -8392,10 +8392,10 @@
         <v>8</v>
       </c>
       <c r="K119" t="n">
-        <v>7.53</v>
+        <v>6.57</v>
       </c>
       <c r="L119" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M119" t="n">
         <v>9.16</v>
@@ -8404,7 +8404,7 @@
         <v>4.64</v>
       </c>
       <c r="O119" t="n">
-        <v>7.639499999999999</v>
+        <v>6.7425</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
@@ -8459,10 +8459,10 @@
         <v>10</v>
       </c>
       <c r="K120" t="n">
-        <v>6.64</v>
+        <v>5.36</v>
       </c>
       <c r="L120" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M120" t="n">
         <v>9.050000000000001</v>
@@ -8471,7 +8471,7 @@
         <v>5.71</v>
       </c>
       <c r="O120" t="n">
-        <v>7.252</v>
+        <v>6.07</v>
       </c>
       <c r="P120" t="n">
         <v>2</v>
@@ -8526,10 +8526,10 @@
         <v>12</v>
       </c>
       <c r="K121" t="n">
-        <v>5.74</v>
+        <v>4.15</v>
       </c>
       <c r="L121" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M121" t="n">
         <v>7.78</v>
@@ -8538,7 +8538,7 @@
         <v>6.69</v>
       </c>
       <c r="O121" t="n">
-        <v>6.616</v>
+        <v>5.152</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
@@ -8593,10 +8593,10 @@
         <v>5</v>
       </c>
       <c r="K122" t="n">
-        <v>8.31</v>
+        <v>7.62</v>
       </c>
       <c r="L122" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M122" t="n">
         <v>6.7</v>
@@ -8605,7 +8605,7 @@
         <v>3.48</v>
       </c>
       <c r="O122" t="n">
-        <v>7.596</v>
+        <v>7.063499999999999</v>
       </c>
       <c r="P122" t="n">
         <v>1</v>
@@ -8660,10 +8660,10 @@
         <v>8</v>
       </c>
       <c r="K123" t="n">
-        <v>6.63</v>
+        <v>5.35</v>
       </c>
       <c r="L123" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M123" t="n">
         <v>8.69</v>
@@ -8672,7 +8672,7 @@
         <v>4.64</v>
       </c>
       <c r="O123" t="n">
-        <v>7.275499999999999</v>
+        <v>6.282499999999999</v>
       </c>
       <c r="P123" t="n">
         <v>2</v>
@@ -8727,10 +8727,10 @@
         <v>12</v>
       </c>
       <c r="K124" t="n">
-        <v>4.39</v>
+        <v>2.32</v>
       </c>
       <c r="L124" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M124" t="n">
         <v>9.51</v>
@@ -8739,7 +8739,7 @@
         <v>6.69</v>
       </c>
       <c r="O124" t="n">
-        <v>6.556999999999999</v>
+        <v>4.949</v>
       </c>
       <c r="P124" t="n">
         <v>3</v>
@@ -8794,10 +8794,10 @@
         <v>5</v>
       </c>
       <c r="K125" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L125" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M125" t="n">
         <v>6.7</v>
@@ -8806,10 +8806,10 @@
         <v>3.48</v>
       </c>
       <c r="O125" t="n">
-        <v>7.8935</v>
+        <v>7.512499999999999</v>
       </c>
       <c r="P125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q125" t="n">
         <v>1.59220653448188</v>
@@ -8861,10 +8861,10 @@
         <v>8</v>
       </c>
       <c r="K126" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="L126" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M126" t="n">
         <v>8.69</v>
@@ -8873,10 +8873,10 @@
         <v>7.6</v>
       </c>
       <c r="O126" t="n">
-        <v>8.196</v>
+        <v>7.45</v>
       </c>
       <c r="P126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q126" t="n">
         <v>2.547530455171008</v>
@@ -8928,10 +8928,10 @@
         <v>12</v>
       </c>
       <c r="K127" t="n">
-        <v>5.73</v>
+        <v>4.14</v>
       </c>
       <c r="L127" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M127" t="n">
         <v>9.51</v>
@@ -8940,7 +8940,7 @@
         <v>6.69</v>
       </c>
       <c r="O127" t="n">
-        <v>7.2705</v>
+        <v>6.030499999999999</v>
       </c>
       <c r="P127" t="n">
         <v>3</v>
@@ -8995,10 +8995,10 @@
         <v>5</v>
       </c>
       <c r="K128" t="n">
-        <v>8.31</v>
+        <v>7.62</v>
       </c>
       <c r="L128" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M128" t="n">
         <v>6.7</v>
@@ -9007,7 +9007,7 @@
         <v>3.48</v>
       </c>
       <c r="O128" t="n">
-        <v>7.596</v>
+        <v>7.063499999999999</v>
       </c>
       <c r="P128" t="n">
         <v>1</v>
@@ -9062,10 +9062,10 @@
         <v>8</v>
       </c>
       <c r="K129" t="n">
-        <v>6.63</v>
+        <v>5.35</v>
       </c>
       <c r="L129" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M129" t="n">
         <v>8.69</v>
@@ -9074,7 +9074,7 @@
         <v>4.64</v>
       </c>
       <c r="O129" t="n">
-        <v>7.275499999999999</v>
+        <v>6.282499999999999</v>
       </c>
       <c r="P129" t="n">
         <v>2</v>
@@ -9129,10 +9129,10 @@
         <v>12</v>
       </c>
       <c r="K130" t="n">
-        <v>4.39</v>
+        <v>2.32</v>
       </c>
       <c r="L130" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M130" t="n">
         <v>9.51</v>
@@ -9141,7 +9141,7 @@
         <v>6.69</v>
       </c>
       <c r="O130" t="n">
-        <v>6.556999999999999</v>
+        <v>4.949</v>
       </c>
       <c r="P130" t="n">
         <v>3</v>
@@ -9196,10 +9196,10 @@
         <v>5</v>
       </c>
       <c r="K131" t="n">
-        <v>9.619999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L131" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M131" t="n">
         <v>7.37</v>
@@ -9208,7 +9208,7 @@
         <v>3.48</v>
       </c>
       <c r="O131" t="n">
-        <v>8.2525</v>
+        <v>7.9495</v>
       </c>
       <c r="P131" t="n">
         <v>2</v>
@@ -9263,10 +9263,10 @@
         <v>8</v>
       </c>
       <c r="K132" t="n">
-        <v>8.720000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="L132" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M132" t="n">
         <v>9.99</v>
@@ -9275,7 +9275,7 @@
         <v>7.6</v>
       </c>
       <c r="O132" t="n">
-        <v>8.813000000000001</v>
+        <v>8.193</v>
       </c>
       <c r="P132" t="n">
         <v>1</v>
@@ -9330,10 +9330,10 @@
         <v>12</v>
       </c>
       <c r="K133" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="L133" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M133" t="n">
         <v>9.220000000000001</v>
@@ -9342,7 +9342,7 @@
         <v>6.69</v>
       </c>
       <c r="O133" t="n">
-        <v>7.7525</v>
+        <v>6.6985</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
@@ -9397,10 +9397,10 @@
         <v>5</v>
       </c>
       <c r="K134" t="n">
-        <v>9.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L134" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M134" t="n">
         <v>7.43</v>
@@ -9409,7 +9409,7 @@
         <v>3.48</v>
       </c>
       <c r="O134" t="n">
-        <v>8.020999999999999</v>
+        <v>7.587499999999999</v>
       </c>
       <c r="P134" t="n">
         <v>1</v>
@@ -9464,10 +9464,10 @@
         <v>8</v>
       </c>
       <c r="K135" t="n">
-        <v>8.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="L135" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M135" t="n">
         <v>9.960000000000001</v>
@@ -9476,7 +9476,7 @@
         <v>4.64</v>
       </c>
       <c r="O135" t="n">
-        <v>7.976499999999999</v>
+        <v>7.142499999999999</v>
       </c>
       <c r="P135" t="n">
         <v>2</v>
@@ -9531,10 +9531,10 @@
         <v>12</v>
       </c>
       <c r="K136" t="n">
-        <v>6.63</v>
+        <v>5.35</v>
       </c>
       <c r="L136" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M136" t="n">
         <v>9.210000000000001</v>
@@ -9543,7 +9543,7 @@
         <v>6.69</v>
       </c>
       <c r="O136" t="n">
-        <v>7.169</v>
+        <v>5.798</v>
       </c>
       <c r="P136" t="n">
         <v>3</v>
@@ -9598,10 +9598,10 @@
         <v>4</v>
       </c>
       <c r="K137" t="n">
-        <v>8.630000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L137" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M137" t="n">
         <v>5.94</v>
@@ -9610,7 +9610,7 @@
         <v>2.86</v>
       </c>
       <c r="O137" t="n">
-        <v>7.471500000000001</v>
+        <v>6.993</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
@@ -9665,10 +9665,10 @@
         <v>7</v>
       </c>
       <c r="K138" t="n">
-        <v>6.77</v>
+        <v>5.54</v>
       </c>
       <c r="L138" t="n">
-        <v>8</v>
+        <v>6.15</v>
       </c>
       <c r="M138" t="n">
         <v>8.07</v>
@@ -9677,7 +9677,7 @@
         <v>3.07</v>
       </c>
       <c r="O138" t="n">
-        <v>6.905499999999999</v>
+        <v>5.888999999999999</v>
       </c>
       <c r="P138" t="n">
         <v>2</v>
@@ -9732,10 +9732,10 @@
         <v>10</v>
       </c>
       <c r="K139" t="n">
-        <v>4.91</v>
+        <v>3.03</v>
       </c>
       <c r="L139" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M139" t="n">
         <v>9.85</v>
@@ -9744,7 +9744,7 @@
         <v>5.71</v>
       </c>
       <c r="O139" t="n">
-        <v>6.633999999999999</v>
+        <v>5.082999999999999</v>
       </c>
       <c r="P139" t="n">
         <v>3</v>
@@ -9799,10 +9799,10 @@
         <v>4</v>
       </c>
       <c r="K140" t="n">
-        <v>7.69</v>
+        <v>6.78</v>
       </c>
       <c r="L140" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M140" t="n">
         <v>5.94</v>
@@ -9811,7 +9811,7 @@
         <v>1.51</v>
       </c>
       <c r="O140" t="n">
-        <v>6.7805</v>
+        <v>6.0525</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
@@ -9866,10 +9866,10 @@
         <v>7</v>
       </c>
       <c r="K141" t="n">
-        <v>5.13</v>
+        <v>3.32</v>
       </c>
       <c r="L141" t="n">
-        <v>6.96</v>
+        <v>4.36</v>
       </c>
       <c r="M141" t="n">
         <v>8.07</v>
@@ -9878,7 +9878,7 @@
         <v>3.07</v>
       </c>
       <c r="O141" t="n">
-        <v>6.049499999999999</v>
+        <v>4.5965</v>
       </c>
       <c r="P141" t="n">
         <v>2</v>
@@ -9933,10 +9933,10 @@
         <v>10</v>
       </c>
       <c r="K142" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>5.19</v>
+        <v>1.28</v>
       </c>
       <c r="M142" t="n">
         <v>9.09</v>
@@ -9945,7 +9945,7 @@
         <v>5.71</v>
       </c>
       <c r="O142" t="n">
-        <v>5.258999999999999</v>
+        <v>3.1225</v>
       </c>
       <c r="P142" t="n">
         <v>3</v>
@@ -10015,7 +10015,7 @@
         <v>6.7745</v>
       </c>
       <c r="P143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q143" t="n">
         <v>0.2616649498528361</v>
@@ -10067,10 +10067,10 @@
         <v>6</v>
       </c>
       <c r="K144" t="n">
-        <v>8.9</v>
+        <v>8.42</v>
       </c>
       <c r="L144" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M144" t="n">
         <v>7.69</v>
@@ -10079,7 +10079,7 @@
         <v>5.01</v>
       </c>
       <c r="O144" t="n">
-        <v>8.225</v>
+        <v>7.7765</v>
       </c>
       <c r="P144" t="n">
         <v>1</v>
@@ -10134,10 +10134,10 @@
         <v>12</v>
       </c>
       <c r="K145" t="n">
-        <v>6.69</v>
+        <v>5.43</v>
       </c>
       <c r="L145" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M145" t="n">
         <v>9.369999999999999</v>
@@ -10146,10 +10146,10 @@
         <v>6.69</v>
       </c>
       <c r="O145" t="n">
-        <v>7.5305</v>
+        <v>6.389499999999999</v>
       </c>
       <c r="P145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q145" t="n">
         <v>3.139979398234034</v>
@@ -10201,10 +10201,10 @@
         <v>7</v>
       </c>
       <c r="K146" t="n">
-        <v>8.1</v>
+        <v>7.34</v>
       </c>
       <c r="L146" t="n">
-        <v>8.52</v>
+        <v>7.05</v>
       </c>
       <c r="M146" t="n">
         <v>8.66</v>
@@ -10213,7 +10213,7 @@
         <v>6.37</v>
       </c>
       <c r="O146" t="n">
-        <v>8.099499999999999</v>
+        <v>7.356999999999999</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
@@ -10268,10 +10268,10 @@
         <v>14</v>
       </c>
       <c r="K147" t="n">
-        <v>5.09</v>
+        <v>3.27</v>
       </c>
       <c r="L147" t="n">
-        <v>5.93</v>
+        <v>2.56</v>
       </c>
       <c r="M147" t="n">
         <v>8.85</v>
@@ -10280,7 +10280,7 @@
         <v>5.71</v>
       </c>
       <c r="O147" t="n">
-        <v>6.229</v>
+        <v>4.5035</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
@@ -10335,10 +10335,10 @@
         <v>22</v>
       </c>
       <c r="K148" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>5.63</v>
@@ -10347,7 +10347,7 @@
         <v>2.27</v>
       </c>
       <c r="O148" t="n">
-        <v>2.9975</v>
+        <v>1.4665</v>
       </c>
       <c r="P148" t="n">
         <v>3</v>
@@ -10402,10 +10402,10 @@
         <v>5</v>
       </c>
       <c r="K149" t="n">
-        <v>9.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L149" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M149" t="n">
         <v>4.9</v>
@@ -10414,10 +10414,10 @@
         <v>3.48</v>
       </c>
       <c r="O149" t="n">
-        <v>7.626500000000001</v>
+        <v>7.281500000000001</v>
       </c>
       <c r="P149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q149" t="n">
         <v>1.370038180833246</v>
@@ -10469,10 +10469,10 @@
         <v>8</v>
       </c>
       <c r="K150" t="n">
-        <v>8.029999999999999</v>
+        <v>7.24</v>
       </c>
       <c r="L150" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M150" t="n">
         <v>7.38</v>
@@ -10481,10 +10481,10 @@
         <v>4.64</v>
       </c>
       <c r="O150" t="n">
-        <v>7.64</v>
+        <v>6.948</v>
       </c>
       <c r="P150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q150" t="n">
         <v>2.192061089333193</v>
@@ -10536,10 +10536,10 @@
         <v>12</v>
       </c>
       <c r="K151" t="n">
-        <v>6.48</v>
+        <v>5.15</v>
       </c>
       <c r="L151" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M151" t="n">
         <v>7.95</v>
@@ -10548,7 +10548,7 @@
         <v>6.69</v>
       </c>
       <c r="O151" t="n">
-        <v>7.1835</v>
+        <v>6.0215</v>
       </c>
       <c r="P151" t="n">
         <v>3</v>
@@ -10603,10 +10603,10 @@
         <v>5</v>
       </c>
       <c r="K152" t="n">
-        <v>8.869999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L152" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M152" t="n">
         <v>6.06</v>
@@ -10615,10 +10615,10 @@
         <v>3.48</v>
       </c>
       <c r="O152" t="n">
-        <v>7.635999999999999</v>
+        <v>7.1635</v>
       </c>
       <c r="P152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q152" t="n">
         <v>1.589120862903426</v>
@@ -10670,10 +10670,10 @@
         <v>8</v>
       </c>
       <c r="K153" t="n">
-        <v>7.53</v>
+        <v>6.57</v>
       </c>
       <c r="L153" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M153" t="n">
         <v>8.5</v>
@@ -10682,10 +10682,10 @@
         <v>7.6</v>
       </c>
       <c r="O153" t="n">
-        <v>7.951499999999999</v>
+        <v>7.0545</v>
       </c>
       <c r="P153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q153" t="n">
         <v>2.542593380645482</v>
@@ -10737,10 +10737,10 @@
         <v>12</v>
       </c>
       <c r="K154" t="n">
-        <v>5.74</v>
+        <v>4.15</v>
       </c>
       <c r="L154" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M154" t="n">
         <v>8.630000000000001</v>
@@ -10749,7 +10749,7 @@
         <v>6.69</v>
       </c>
       <c r="O154" t="n">
-        <v>6.786</v>
+        <v>5.322</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -10804,10 +10804,10 @@
         <v>6</v>
       </c>
       <c r="K155" t="n">
-        <v>8.35</v>
+        <v>7.67</v>
       </c>
       <c r="L155" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M155" t="n">
         <v>7.69</v>
@@ -10816,10 +10816,10 @@
         <v>1.51</v>
       </c>
       <c r="O155" t="n">
-        <v>7.381</v>
+        <v>6.757</v>
       </c>
       <c r="P155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q155" t="n">
         <v>1.962487123896271</v>
@@ -10871,10 +10871,10 @@
         <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>7.43</v>
+        <v>6.43</v>
       </c>
       <c r="L156" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M156" t="n">
         <v>9.039999999999999</v>
@@ -10883,10 +10883,10 @@
         <v>4.64</v>
       </c>
       <c r="O156" t="n">
-        <v>7.5855</v>
+        <v>6.676499999999999</v>
       </c>
       <c r="P156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q156" t="n">
         <v>2.616649498528361</v>
@@ -10938,10 +10938,10 @@
         <v>10</v>
       </c>
       <c r="K157" t="n">
-        <v>6.51</v>
+        <v>5.19</v>
       </c>
       <c r="L157" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M157" t="n">
         <v>9.1</v>
@@ -10950,7 +10950,7 @@
         <v>5.71</v>
       </c>
       <c r="O157" t="n">
-        <v>7.223</v>
+        <v>6.029</v>
       </c>
       <c r="P157" t="n">
         <v>3</v>
@@ -11005,10 +11005,10 @@
         <v>8</v>
       </c>
       <c r="K158" t="n">
-        <v>7.53</v>
+        <v>6.57</v>
       </c>
       <c r="L158" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M158" t="n">
         <v>9.16</v>
@@ -11017,7 +11017,7 @@
         <v>4.64</v>
       </c>
       <c r="O158" t="n">
-        <v>7.639499999999999</v>
+        <v>6.7425</v>
       </c>
       <c r="P158" t="n">
         <v>1</v>
@@ -11072,10 +11072,10 @@
         <v>10</v>
       </c>
       <c r="K159" t="n">
-        <v>6.64</v>
+        <v>5.36</v>
       </c>
       <c r="L159" t="n">
-        <v>7.41</v>
+        <v>5.13</v>
       </c>
       <c r="M159" t="n">
         <v>9.050000000000001</v>
@@ -11084,7 +11084,7 @@
         <v>5.71</v>
       </c>
       <c r="O159" t="n">
-        <v>7.252</v>
+        <v>6.07</v>
       </c>
       <c r="P159" t="n">
         <v>2</v>
@@ -11139,10 +11139,10 @@
         <v>12</v>
       </c>
       <c r="K160" t="n">
-        <v>5.74</v>
+        <v>4.15</v>
       </c>
       <c r="L160" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M160" t="n">
         <v>7.78</v>
@@ -11151,7 +11151,7 @@
         <v>6.69</v>
       </c>
       <c r="O160" t="n">
-        <v>6.616</v>
+        <v>5.152</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
@@ -11206,10 +11206,10 @@
         <v>5</v>
       </c>
       <c r="K161" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L161" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M161" t="n">
         <v>6.7</v>
@@ -11218,10 +11218,10 @@
         <v>3.48</v>
       </c>
       <c r="O161" t="n">
-        <v>7.8935</v>
+        <v>7.512499999999999</v>
       </c>
       <c r="P161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q161" t="n">
         <v>1.59220653448188</v>
@@ -11273,10 +11273,10 @@
         <v>8</v>
       </c>
       <c r="K162" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="L162" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M162" t="n">
         <v>8.69</v>
@@ -11285,10 +11285,10 @@
         <v>7.6</v>
       </c>
       <c r="O162" t="n">
-        <v>8.196</v>
+        <v>7.45</v>
       </c>
       <c r="P162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q162" t="n">
         <v>2.547530455171008</v>
@@ -11340,10 +11340,10 @@
         <v>12</v>
       </c>
       <c r="K163" t="n">
-        <v>5.73</v>
+        <v>4.14</v>
       </c>
       <c r="L163" t="n">
-        <v>7.56</v>
+        <v>5.38</v>
       </c>
       <c r="M163" t="n">
         <v>9.51</v>
@@ -11352,7 +11352,7 @@
         <v>6.69</v>
       </c>
       <c r="O163" t="n">
-        <v>7.2705</v>
+        <v>6.030499999999999</v>
       </c>
       <c r="P163" t="n">
         <v>3</v>
@@ -11407,10 +11407,10 @@
         <v>5</v>
       </c>
       <c r="K164" t="n">
-        <v>9.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L164" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M164" t="n">
         <v>7.43</v>
@@ -11419,7 +11419,7 @@
         <v>3.48</v>
       </c>
       <c r="O164" t="n">
-        <v>8.020999999999999</v>
+        <v>7.587499999999999</v>
       </c>
       <c r="P164" t="n">
         <v>1</v>
@@ -11474,10 +11474,10 @@
         <v>8</v>
       </c>
       <c r="K165" t="n">
-        <v>8.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="L165" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M165" t="n">
         <v>9.960000000000001</v>
@@ -11486,7 +11486,7 @@
         <v>4.64</v>
       </c>
       <c r="O165" t="n">
-        <v>7.976499999999999</v>
+        <v>7.142499999999999</v>
       </c>
       <c r="P165" t="n">
         <v>2</v>
@@ -11541,10 +11541,10 @@
         <v>12</v>
       </c>
       <c r="K166" t="n">
-        <v>6.63</v>
+        <v>5.35</v>
       </c>
       <c r="L166" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M166" t="n">
         <v>9.210000000000001</v>
@@ -11553,7 +11553,7 @@
         <v>6.69</v>
       </c>
       <c r="O166" t="n">
-        <v>7.169</v>
+        <v>5.798</v>
       </c>
       <c r="P166" t="n">
         <v>3</v>
@@ -11623,7 +11623,7 @@
         <v>7.856</v>
       </c>
       <c r="P167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q167" t="n">
         <v>0.7109387316756299</v>
@@ -11675,10 +11675,10 @@
         <v>5</v>
       </c>
       <c r="K168" t="n">
-        <v>9.44</v>
+        <v>9.15</v>
       </c>
       <c r="L168" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M168" t="n">
         <v>7.11</v>
@@ -11687,10 +11687,10 @@
         <v>3.48</v>
       </c>
       <c r="O168" t="n">
-        <v>8.146500000000001</v>
+        <v>7.8285</v>
       </c>
       <c r="P168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q168" t="n">
         <v>1.18489788612605</v>
@@ -11742,10 +11742,10 @@
         <v>8</v>
       </c>
       <c r="K169" t="n">
-        <v>8.44</v>
+        <v>7.8</v>
       </c>
       <c r="L169" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M169" t="n">
         <v>9.529999999999999</v>
@@ -11754,7 +11754,7 @@
         <v>7.6</v>
       </c>
       <c r="O169" t="n">
-        <v>8.636999999999999</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="P169" t="n">
         <v>1</v>
@@ -11809,10 +11809,10 @@
         <v>3</v>
       </c>
       <c r="K170" t="n">
-        <v>9.99</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L170" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M170" t="n">
         <v>5.13</v>
@@ -11821,10 +11821,10 @@
         <v>2.2</v>
       </c>
       <c r="O170" t="n">
-        <v>7.853</v>
+        <v>7.69</v>
       </c>
       <c r="P170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q170" t="n">
         <v>0.7961032672409399</v>
@@ -11876,10 +11876,10 @@
         <v>5</v>
       </c>
       <c r="K171" t="n">
-        <v>9.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L171" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M171" t="n">
         <v>7.43</v>
@@ -11888,10 +11888,10 @@
         <v>3.48</v>
       </c>
       <c r="O171" t="n">
-        <v>8.020999999999999</v>
+        <v>7.587499999999999</v>
       </c>
       <c r="P171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q171" t="n">
         <v>1.3268387787349</v>
@@ -11943,10 +11943,10 @@
         <v>8</v>
       </c>
       <c r="K172" t="n">
-        <v>8.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="L172" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M172" t="n">
         <v>9.960000000000001</v>
@@ -11955,10 +11955,10 @@
         <v>4.64</v>
       </c>
       <c r="O172" t="n">
-        <v>7.976499999999999</v>
+        <v>7.142499999999999</v>
       </c>
       <c r="P172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q172" t="n">
         <v>2.12294204597584</v>
@@ -12010,10 +12010,10 @@
         <v>3</v>
       </c>
       <c r="K173" t="n">
-        <v>9.949999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="L173" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M173" t="n">
         <v>5.13</v>
@@ -12022,10 +12022,10 @@
         <v>2.2</v>
       </c>
       <c r="O173" t="n">
-        <v>7.840999999999999</v>
+        <v>7.671999999999999</v>
       </c>
       <c r="P173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q173" t="n">
         <v>0.8238743114470191</v>
@@ -12077,10 +12077,10 @@
         <v>5</v>
       </c>
       <c r="K174" t="n">
-        <v>9.18</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L174" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M174" t="n">
         <v>7.28</v>
@@ -12089,10 +12089,10 @@
         <v>3.48</v>
       </c>
       <c r="O174" t="n">
-        <v>7.973</v>
+        <v>7.5305</v>
       </c>
       <c r="P174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q174" t="n">
         <v>1.373123852411698</v>
@@ -12144,10 +12144,10 @@
         <v>8</v>
       </c>
       <c r="K175" t="n">
-        <v>8.02</v>
+        <v>7.23</v>
       </c>
       <c r="L175" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M175" t="n">
         <v>9.880000000000001</v>
@@ -12156,10 +12156,10 @@
         <v>4.64</v>
       </c>
       <c r="O175" t="n">
-        <v>7.930499999999999</v>
+        <v>7.084499999999999</v>
       </c>
       <c r="P175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q175" t="n">
         <v>2.196998163858717</v>
@@ -12211,7 +12211,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L176" t="n">
         <v>10</v>
@@ -12223,10 +12223,10 @@
         <v>2.2</v>
       </c>
       <c r="O176" t="n">
-        <v>7.856</v>
+        <v>7.840999999999999</v>
       </c>
       <c r="P176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q176" t="n">
         <v>0.7627780141936447</v>
@@ -12278,10 +12278,10 @@
         <v>5</v>
       </c>
       <c r="K177" t="n">
-        <v>9.32</v>
+        <v>8.98</v>
       </c>
       <c r="L177" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M177" t="n">
         <v>6.96</v>
@@ -12290,10 +12290,10 @@
         <v>3.48</v>
       </c>
       <c r="O177" t="n">
-        <v>8.080500000000001</v>
+        <v>7.7475</v>
       </c>
       <c r="P177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q177" t="n">
         <v>1.271296690322741</v>
@@ -12345,10 +12345,10 @@
         <v>8</v>
       </c>
       <c r="K178" t="n">
-        <v>8.25</v>
+        <v>7.54</v>
       </c>
       <c r="L178" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M178" t="n">
         <v>9.23</v>
@@ -12357,7 +12357,7 @@
         <v>7.6</v>
       </c>
       <c r="O178" t="n">
-        <v>8.52</v>
+        <v>7.851999999999999</v>
       </c>
       <c r="P178" t="n">
         <v>1</v>
@@ -12412,7 +12412,7 @@
         <v>4</v>
       </c>
       <c r="K179" t="n">
-        <v>9.800000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L179" t="n">
         <v>10</v>
@@ -12424,7 +12424,7 @@
         <v>2.86</v>
       </c>
       <c r="O179" t="n">
-        <v>7.638999999999999</v>
+        <v>7.588000000000001</v>
       </c>
       <c r="P179" t="n">
         <v>3</v>
@@ -12479,10 +12479,10 @@
         <v>6</v>
       </c>
       <c r="K180" t="n">
-        <v>9.140000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="L180" t="n">
-        <v>9.779999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="M180" t="n">
         <v>5.6</v>
@@ -12491,7 +12491,7 @@
         <v>5.01</v>
       </c>
       <c r="O180" t="n">
-        <v>8.036499999999998</v>
+        <v>7.724</v>
       </c>
       <c r="P180" t="n">
         <v>2</v>
@@ -12546,10 +12546,10 @@
         <v>10</v>
       </c>
       <c r="K181" t="n">
-        <v>7.83</v>
+        <v>6.97</v>
       </c>
       <c r="L181" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M181" t="n">
         <v>8.43</v>
@@ -12558,7 +12558,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O181" t="n">
-        <v>8.414</v>
+        <v>7.736</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
@@ -12613,10 +12613,10 @@
         <v>4</v>
       </c>
       <c r="K182" t="n">
-        <v>9.539999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L182" t="n">
-        <v>9.93</v>
+        <v>9.49</v>
       </c>
       <c r="M182" t="n">
         <v>5.99</v>
@@ -12625,10 +12625,10 @@
         <v>2.86</v>
       </c>
       <c r="O182" t="n">
-        <v>7.9645</v>
+        <v>7.7325</v>
       </c>
       <c r="P182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q182" t="n">
         <v>1.115778842768697</v>
@@ -12680,10 +12680,10 @@
         <v>6</v>
       </c>
       <c r="K183" t="n">
-        <v>8.76</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L183" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M183" t="n">
         <v>7.52</v>
@@ -12692,7 +12692,7 @@
         <v>5.01</v>
       </c>
       <c r="O183" t="n">
-        <v>8.148999999999999</v>
+        <v>7.682500000000001</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
@@ -12747,10 +12747,10 @@
         <v>10</v>
       </c>
       <c r="K184" t="n">
-        <v>7.19</v>
+        <v>6.1</v>
       </c>
       <c r="L184" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M184" t="n">
         <v>9.970000000000001</v>
@@ -12759,10 +12759,10 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O184" t="n">
-        <v>8.271000000000001</v>
+        <v>7.335000000000001</v>
       </c>
       <c r="P184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q184" t="n">
         <v>2.789447106921743</v>
@@ -12814,10 +12814,10 @@
         <v>3</v>
       </c>
       <c r="K185" t="n">
-        <v>9.82</v>
+        <v>9.66</v>
       </c>
       <c r="L185" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M185" t="n">
         <v>5.13</v>
@@ -12826,10 +12826,10 @@
         <v>2.2</v>
       </c>
       <c r="O185" t="n">
-        <v>7.802</v>
+        <v>7.621</v>
       </c>
       <c r="P185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q185" t="n">
         <v>0.916444458800617</v>
@@ -12881,10 +12881,10 @@
         <v>5</v>
       </c>
       <c r="K186" t="n">
-        <v>8.960000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L186" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M186" t="n">
         <v>7.04</v>
@@ -12893,10 +12893,10 @@
         <v>3.48</v>
       </c>
       <c r="O186" t="n">
-        <v>7.859000000000001</v>
+        <v>7.3955</v>
       </c>
       <c r="P186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q186" t="n">
         <v>1.527407431334362</v>
@@ -12948,10 +12948,10 @@
         <v>8</v>
       </c>
       <c r="K187" t="n">
-        <v>7.67</v>
+        <v>6.76</v>
       </c>
       <c r="L187" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M187" t="n">
         <v>9.390000000000001</v>
@@ -12960,7 +12960,7 @@
         <v>4.64</v>
       </c>
       <c r="O187" t="n">
-        <v>7.727499999999999</v>
+        <v>6.845499999999999</v>
       </c>
       <c r="P187" t="n">
         <v>3</v>
@@ -13015,10 +13015,10 @@
         <v>3</v>
       </c>
       <c r="K188" t="n">
-        <v>9.69</v>
+        <v>9.48</v>
       </c>
       <c r="L188" t="n">
-        <v>9.779999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="M188" t="n">
         <v>5.13</v>
@@ -13027,10 +13027,10 @@
         <v>2.2</v>
       </c>
       <c r="O188" t="n">
-        <v>7.685999999999999</v>
+        <v>7.4305</v>
       </c>
       <c r="P188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q188" t="n">
         <v>1.010866009101286</v>
@@ -13082,10 +13082,10 @@
         <v>4</v>
       </c>
       <c r="K189" t="n">
-        <v>9.210000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="L189" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M189" t="n">
         <v>6.23</v>
@@ -13094,10 +13094,10 @@
         <v>2.86</v>
       </c>
       <c r="O189" t="n">
-        <v>7.703500000000001</v>
+        <v>7.288</v>
       </c>
       <c r="P189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q189" t="n">
         <v>1.347821345468382</v>
@@ -13149,10 +13149,10 @@
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>8.27</v>
+        <v>7.56</v>
       </c>
       <c r="L190" t="n">
-        <v>8.44</v>
+        <v>6.92</v>
       </c>
       <c r="M190" t="n">
         <v>8.140000000000001</v>
@@ -13161,7 +13161,7 @@
         <v>1.51</v>
       </c>
       <c r="O190" t="n">
-        <v>7.289499999999999</v>
+        <v>6.544499999999999</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
@@ -13216,7 +13216,7 @@
         <v>3</v>
       </c>
       <c r="K191" t="n">
-        <v>9.77</v>
+        <v>9.58</v>
       </c>
       <c r="L191" t="n">
         <v>10</v>
@@ -13228,10 +13228,10 @@
         <v>2.2</v>
       </c>
       <c r="O191" t="n">
-        <v>7.786999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="P191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q191" t="n">
         <v>0.955323920689128</v>
@@ -13283,10 +13283,10 @@
         <v>5</v>
       </c>
       <c r="K192" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L192" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M192" t="n">
         <v>6.7</v>
@@ -13295,7 +13295,7 @@
         <v>3.48</v>
       </c>
       <c r="O192" t="n">
-        <v>7.8935</v>
+        <v>7.512499999999999</v>
       </c>
       <c r="P192" t="n">
         <v>2</v>
@@ -13350,10 +13350,10 @@
         <v>8</v>
       </c>
       <c r="K193" t="n">
-        <v>7.53</v>
+        <v>6.56</v>
       </c>
       <c r="L193" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M193" t="n">
         <v>8.69</v>
@@ -13362,10 +13362,10 @@
         <v>7.6</v>
       </c>
       <c r="O193" t="n">
-        <v>8.196</v>
+        <v>7.45</v>
       </c>
       <c r="P193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q193" t="n">
         <v>2.547530455171008</v>
@@ -13417,10 +13417,10 @@
         <v>3</v>
       </c>
       <c r="K194" t="n">
-        <v>9.82</v>
+        <v>9.66</v>
       </c>
       <c r="L194" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M194" t="n">
         <v>5.13</v>
@@ -13429,10 +13429,10 @@
         <v>2.2</v>
       </c>
       <c r="O194" t="n">
-        <v>7.802</v>
+        <v>7.621</v>
       </c>
       <c r="P194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q194" t="n">
         <v>0.916444458800617</v>
@@ -13484,10 +13484,10 @@
         <v>5</v>
       </c>
       <c r="K195" t="n">
-        <v>8.960000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L195" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M195" t="n">
         <v>7.04</v>
@@ -13496,10 +13496,10 @@
         <v>3.48</v>
       </c>
       <c r="O195" t="n">
-        <v>7.859000000000001</v>
+        <v>7.3955</v>
       </c>
       <c r="P195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q195" t="n">
         <v>1.527407431334362</v>
@@ -13551,10 +13551,10 @@
         <v>8</v>
       </c>
       <c r="K196" t="n">
-        <v>7.67</v>
+        <v>6.76</v>
       </c>
       <c r="L196" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M196" t="n">
         <v>9.390000000000001</v>
@@ -13563,7 +13563,7 @@
         <v>4.64</v>
       </c>
       <c r="O196" t="n">
-        <v>7.727499999999999</v>
+        <v>6.845499999999999</v>
       </c>
       <c r="P196" t="n">
         <v>3</v>
@@ -13685,10 +13685,10 @@
         <v>5</v>
       </c>
       <c r="K198" t="n">
-        <v>9.619999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L198" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M198" t="n">
         <v>7.37</v>
@@ -13697,7 +13697,7 @@
         <v>3.48</v>
       </c>
       <c r="O198" t="n">
-        <v>8.2525</v>
+        <v>7.9495</v>
       </c>
       <c r="P198" t="n">
         <v>2</v>
@@ -13752,10 +13752,10 @@
         <v>8</v>
       </c>
       <c r="K199" t="n">
-        <v>8.720000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="L199" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M199" t="n">
         <v>9.99</v>
@@ -13764,7 +13764,7 @@
         <v>7.6</v>
       </c>
       <c r="O199" t="n">
-        <v>8.813000000000001</v>
+        <v>8.193</v>
       </c>
       <c r="P199" t="n">
         <v>1</v>
@@ -13819,10 +13819,10 @@
         <v>3</v>
       </c>
       <c r="K200" t="n">
-        <v>9.73</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L200" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M200" t="n">
         <v>5.13</v>
@@ -13831,10 +13831,10 @@
         <v>2.2</v>
       </c>
       <c r="O200" t="n">
-        <v>7.775</v>
+        <v>7.584999999999999</v>
       </c>
       <c r="P200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q200" t="n">
         <v>0.9812435619481353</v>
@@ -13886,10 +13886,10 @@
         <v>5</v>
       </c>
       <c r="K201" t="n">
-        <v>8.81</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L201" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M201" t="n">
         <v>6.9</v>
@@ -13898,10 +13898,10 @@
         <v>3.48</v>
       </c>
       <c r="O201" t="n">
-        <v>7.786</v>
+        <v>7.3045</v>
       </c>
       <c r="P201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q201" t="n">
         <v>1.635405936580226</v>
@@ -13953,10 +13953,10 @@
         <v>7</v>
       </c>
       <c r="K202" t="n">
-        <v>7.89</v>
+        <v>7.05</v>
       </c>
       <c r="L202" t="n">
-        <v>8.52</v>
+        <v>7.05</v>
       </c>
       <c r="M202" t="n">
         <v>8.42</v>
@@ -13965,7 +13965,7 @@
         <v>3.07</v>
       </c>
       <c r="O202" t="n">
-        <v>7.4935</v>
+        <v>6.726999999999999</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
@@ -14035,7 +14035,7 @@
         <v>7.856</v>
       </c>
       <c r="P203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q203" t="n">
         <v>0.7331555670404936</v>
@@ -14087,10 +14087,10 @@
         <v>5</v>
       </c>
       <c r="K204" t="n">
-        <v>9.390000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="L204" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M204" t="n">
         <v>7.04</v>
@@ -14099,10 +14099,10 @@
         <v>3.48</v>
       </c>
       <c r="O204" t="n">
-        <v>8.1175</v>
+        <v>7.793500000000001</v>
       </c>
       <c r="P204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q204" t="n">
         <v>1.221925945067489</v>
@@ -14154,10 +14154,10 @@
         <v>8</v>
       </c>
       <c r="K205" t="n">
-        <v>8.359999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="L205" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M205" t="n">
         <v>9.390000000000001</v>
@@ -14166,7 +14166,7 @@
         <v>7.6</v>
       </c>
       <c r="O205" t="n">
-        <v>8.584999999999999</v>
+        <v>7.928999999999999</v>
       </c>
       <c r="P205" t="n">
         <v>1</v>
@@ -14221,10 +14221,10 @@
         <v>3</v>
       </c>
       <c r="K206" t="n">
-        <v>9.640000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="L206" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M206" t="n">
         <v>5.13</v>
@@ -14233,7 +14233,7 @@
         <v>2.2</v>
       </c>
       <c r="O206" t="n">
-        <v>7.747999999999999</v>
+        <v>7.545999999999999</v>
       </c>
       <c r="P206" t="n">
         <v>1</v>
@@ -14288,10 +14288,10 @@
         <v>5</v>
       </c>
       <c r="K207" t="n">
-        <v>8.66</v>
+        <v>8.09</v>
       </c>
       <c r="L207" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M207" t="n">
         <v>6.78</v>
@@ -14300,7 +14300,7 @@
         <v>3.48</v>
       </c>
       <c r="O207" t="n">
-        <v>7.717</v>
+        <v>7.220499999999999</v>
       </c>
       <c r="P207" t="n">
         <v>2</v>
@@ -14355,10 +14355,10 @@
         <v>8</v>
       </c>
       <c r="K208" t="n">
-        <v>7.19</v>
+        <v>6.1</v>
       </c>
       <c r="L208" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M208" t="n">
         <v>8.859999999999999</v>
@@ -14367,7 +14367,7 @@
         <v>4.64</v>
       </c>
       <c r="O208" t="n">
-        <v>7.4775</v>
+        <v>6.5415</v>
       </c>
       <c r="P208" t="n">
         <v>3</v>
@@ -14489,10 +14489,10 @@
         <v>5</v>
       </c>
       <c r="K210" t="n">
-        <v>9.529999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="L210" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M210" t="n">
         <v>7.23</v>
@@ -14501,7 +14501,7 @@
         <v>3.48</v>
       </c>
       <c r="O210" t="n">
-        <v>8.1975</v>
+        <v>7.888500000000001</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -14556,10 +14556,10 @@
         <v>7</v>
       </c>
       <c r="K211" t="n">
-        <v>8.9</v>
+        <v>8.41</v>
       </c>
       <c r="L211" t="n">
-        <v>9.039999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="M211" t="n">
         <v>8.99</v>
@@ -14568,7 +14568,7 @@
         <v>6.37</v>
       </c>
       <c r="O211" t="n">
-        <v>8.5875</v>
+        <v>8.059000000000001</v>
       </c>
       <c r="P211" t="n">
         <v>1</v>
@@ -14623,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="K212" t="n">
-        <v>9.83</v>
+        <v>9.67</v>
       </c>
       <c r="L212" t="n">
         <v>10</v>
@@ -14635,7 +14635,7 @@
         <v>2.86</v>
       </c>
       <c r="O212" t="n">
-        <v>7.648</v>
+        <v>7.6</v>
       </c>
       <c r="P212" t="n">
         <v>3</v>
@@ -14690,10 +14690,10 @@
         <v>6</v>
       </c>
       <c r="K213" t="n">
-        <v>9.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L213" t="n">
-        <v>9.779999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="M213" t="n">
         <v>5.6</v>
@@ -14702,7 +14702,7 @@
         <v>5.01</v>
       </c>
       <c r="O213" t="n">
-        <v>8.051499999999999</v>
+        <v>7.742</v>
       </c>
       <c r="P213" t="n">
         <v>2</v>
@@ -14757,10 +14757,10 @@
         <v>10</v>
       </c>
       <c r="K214" t="n">
-        <v>7.91</v>
+        <v>7.07</v>
       </c>
       <c r="L214" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M214" t="n">
         <v>8.43</v>
@@ -14769,7 +14769,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O214" t="n">
-        <v>8.437999999999999</v>
+        <v>7.766</v>
       </c>
       <c r="P214" t="n">
         <v>1</v>
@@ -14824,10 +14824,10 @@
         <v>4</v>
       </c>
       <c r="K215" t="n">
-        <v>9.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L215" t="n">
-        <v>9.93</v>
+        <v>9.49</v>
       </c>
       <c r="M215" t="n">
         <v>5.96</v>
@@ -14836,10 +14836,10 @@
         <v>2.86</v>
       </c>
       <c r="O215" t="n">
-        <v>7.9465</v>
+        <v>7.708500000000001</v>
       </c>
       <c r="P215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q215" t="n">
         <v>1.145401289921848</v>
@@ -14891,10 +14891,10 @@
         <v>6</v>
       </c>
       <c r="K216" t="n">
-        <v>8.69</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L216" t="n">
-        <v>9.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M216" t="n">
         <v>7.45</v>
@@ -14903,7 +14903,7 @@
         <v>5.01</v>
       </c>
       <c r="O216" t="n">
-        <v>8.113999999999999</v>
+        <v>7.644500000000001</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -14958,10 +14958,10 @@
         <v>10</v>
       </c>
       <c r="K217" t="n">
-        <v>7.08</v>
+        <v>5.96</v>
       </c>
       <c r="L217" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M217" t="n">
         <v>9.94</v>
@@ -14970,10 +14970,10 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O217" t="n">
-        <v>8.231999999999999</v>
+        <v>7.287000000000001</v>
       </c>
       <c r="P217" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q217" t="n">
         <v>2.863503224804621</v>
@@ -15025,7 +15025,7 @@
         <v>3</v>
       </c>
       <c r="K218" t="n">
-        <v>9.98</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L218" t="n">
         <v>10</v>
@@ -15037,10 +15037,10 @@
         <v>2.2</v>
       </c>
       <c r="O218" t="n">
-        <v>7.85</v>
+        <v>7.817</v>
       </c>
       <c r="P218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q218" t="n">
         <v>0.8072116849233715</v>
@@ -15092,10 +15092,10 @@
         <v>5</v>
       </c>
       <c r="K219" t="n">
-        <v>9.220000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="L219" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M219" t="n">
         <v>6.85</v>
@@ -15104,10 +15104,10 @@
         <v>3.48</v>
       </c>
       <c r="O219" t="n">
-        <v>8.028499999999999</v>
+        <v>7.6835</v>
       </c>
       <c r="P219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q219" t="n">
         <v>1.345352808205619</v>
@@ -15159,10 +15159,10 @@
         <v>8</v>
       </c>
       <c r="K220" t="n">
-        <v>8.08</v>
+        <v>7.31</v>
       </c>
       <c r="L220" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M220" t="n">
         <v>9</v>
@@ -15171,10 +15171,10 @@
         <v>7.6</v>
       </c>
       <c r="O220" t="n">
-        <v>8.423</v>
+        <v>7.736999999999999</v>
       </c>
       <c r="P220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q220" t="n">
         <v>2.152564493128991</v>
@@ -15226,10 +15226,10 @@
         <v>3</v>
       </c>
       <c r="K221" t="n">
-        <v>9.640000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="L221" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M221" t="n">
         <v>5.13</v>
@@ -15238,7 +15238,7 @@
         <v>2.2</v>
       </c>
       <c r="O221" t="n">
-        <v>7.747999999999999</v>
+        <v>7.545999999999999</v>
       </c>
       <c r="P221" t="n">
         <v>1</v>
@@ -15293,10 +15293,10 @@
         <v>5</v>
       </c>
       <c r="K222" t="n">
-        <v>8.66</v>
+        <v>8.09</v>
       </c>
       <c r="L222" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M222" t="n">
         <v>6.78</v>
@@ -15305,7 +15305,7 @@
         <v>3.48</v>
       </c>
       <c r="O222" t="n">
-        <v>7.717</v>
+        <v>7.220499999999999</v>
       </c>
       <c r="P222" t="n">
         <v>2</v>
@@ -15360,10 +15360,10 @@
         <v>8</v>
       </c>
       <c r="K223" t="n">
-        <v>7.19</v>
+        <v>6.1</v>
       </c>
       <c r="L223" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M223" t="n">
         <v>8.859999999999999</v>
@@ -15372,7 +15372,7 @@
         <v>4.64</v>
       </c>
       <c r="O223" t="n">
-        <v>7.4775</v>
+        <v>6.5415</v>
       </c>
       <c r="P223" t="n">
         <v>3</v>
@@ -15427,7 +15427,7 @@
         <v>3</v>
       </c>
       <c r="K224" t="n">
-        <v>9.800000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L224" t="n">
         <v>10</v>
@@ -15439,10 +15439,10 @@
         <v>2.2</v>
       </c>
       <c r="O224" t="n">
-        <v>7.795999999999999</v>
+        <v>7.745</v>
       </c>
       <c r="P224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q224" t="n">
         <v>0.9331070853242645</v>
@@ -15494,10 +15494,10 @@
         <v>5</v>
       </c>
       <c r="K225" t="n">
-        <v>8.92</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L225" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M225" t="n">
         <v>6.7</v>
@@ -15506,7 +15506,7 @@
         <v>3.48</v>
       </c>
       <c r="O225" t="n">
-        <v>7.9085</v>
+        <v>7.5365</v>
       </c>
       <c r="P225" t="n">
         <v>2</v>
@@ -15561,10 +15561,10 @@
         <v>8</v>
       </c>
       <c r="K226" t="n">
-        <v>7.61</v>
+        <v>6.67</v>
       </c>
       <c r="L226" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M226" t="n">
         <v>8.69</v>
@@ -15573,10 +15573,10 @@
         <v>7.6</v>
       </c>
       <c r="O226" t="n">
-        <v>8.220000000000001</v>
+        <v>7.483</v>
       </c>
       <c r="P226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q226" t="n">
         <v>2.488285560864705</v>
@@ -15628,10 +15628,10 @@
         <v>3</v>
       </c>
       <c r="K227" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L227" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M227" t="n">
         <v>5.13</v>
@@ -15640,10 +15640,10 @@
         <v>2.2</v>
       </c>
       <c r="O227" t="n">
-        <v>7.795999999999999</v>
+        <v>7.608999999999999</v>
       </c>
       <c r="P227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q227" t="n">
         <v>0.9349584882713364</v>
@@ -15695,10 +15695,10 @@
         <v>5</v>
       </c>
       <c r="K228" t="n">
-        <v>8.92</v>
+        <v>8.44</v>
       </c>
       <c r="L228" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M228" t="n">
         <v>7</v>
@@ -15707,10 +15707,10 @@
         <v>3.48</v>
       </c>
       <c r="O228" t="n">
-        <v>7.839</v>
+        <v>7.3695</v>
       </c>
       <c r="P228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q228" t="n">
         <v>1.558264147118894</v>
@@ -15762,10 +15762,10 @@
         <v>8</v>
       </c>
       <c r="K229" t="n">
-        <v>7.6</v>
+        <v>6.66</v>
       </c>
       <c r="L229" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M229" t="n">
         <v>9.31</v>
@@ -15774,7 +15774,7 @@
         <v>4.64</v>
       </c>
       <c r="O229" t="n">
-        <v>7.6905</v>
+        <v>6.7995</v>
       </c>
       <c r="P229" t="n">
         <v>3</v>
@@ -15829,7 +15829,7 @@
         <v>3</v>
       </c>
       <c r="K230" t="n">
-        <v>9.869999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="L230" t="n">
         <v>10</v>
@@ -15841,10 +15841,10 @@
         <v>2.2</v>
       </c>
       <c r="O230" t="n">
-        <v>7.817</v>
+        <v>7.775</v>
       </c>
       <c r="P230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q230" t="n">
         <v>0.8812678028062497</v>
@@ -15896,10 +15896,10 @@
         <v>5</v>
       </c>
       <c r="K231" t="n">
-        <v>9.039999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L231" t="n">
-        <v>9.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M231" t="n">
         <v>6.7</v>
@@ -15908,7 +15908,7 @@
         <v>3.48</v>
       </c>
       <c r="O231" t="n">
-        <v>7.9445</v>
+        <v>7.5845</v>
       </c>
       <c r="P231" t="n">
         <v>2</v>
@@ -15963,10 +15963,10 @@
         <v>8</v>
       </c>
       <c r="K232" t="n">
-        <v>7.8</v>
+        <v>6.93</v>
       </c>
       <c r="L232" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="M232" t="n">
         <v>8.69</v>
@@ -15975,10 +15975,10 @@
         <v>7.6</v>
       </c>
       <c r="O232" t="n">
-        <v>8.276999999999999</v>
+        <v>7.560999999999999</v>
       </c>
       <c r="P232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q232" t="n">
         <v>2.350047474149999</v>
@@ -16030,10 +16030,10 @@
         <v>4</v>
       </c>
       <c r="K233" t="n">
-        <v>7.97</v>
+        <v>7.16</v>
       </c>
       <c r="L233" t="n">
-        <v>9.039999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="M233" t="n">
         <v>5.94</v>
@@ -16042,7 +16042,7 @@
         <v>1.51</v>
       </c>
       <c r="O233" t="n">
-        <v>6.9695</v>
+        <v>6.345000000000001</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -16097,10 +16097,10 @@
         <v>6</v>
       </c>
       <c r="K234" t="n">
-        <v>6.41</v>
+        <v>5.05</v>
       </c>
       <c r="L234" t="n">
-        <v>8</v>
+        <v>6.15</v>
       </c>
       <c r="M234" t="n">
         <v>7.4</v>
@@ -16109,7 +16109,7 @@
         <v>1.51</v>
       </c>
       <c r="O234" t="n">
-        <v>6.4295</v>
+        <v>5.374</v>
       </c>
       <c r="P234" t="n">
         <v>2</v>
@@ -16164,10 +16164,10 @@
         <v>8</v>
       </c>
       <c r="K235" t="n">
-        <v>4.84</v>
+        <v>2.93</v>
       </c>
       <c r="L235" t="n">
-        <v>6.96</v>
+        <v>4.36</v>
       </c>
       <c r="M235" t="n">
         <v>8.619999999999999</v>
@@ -16176,7 +16176,7 @@
         <v>4.64</v>
       </c>
       <c r="O235" t="n">
-        <v>6.308</v>
+        <v>4.825</v>
       </c>
       <c r="P235" t="n">
         <v>3</v>
@@ -16298,10 +16298,10 @@
         <v>7</v>
       </c>
       <c r="K237" t="n">
-        <v>9.539999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L237" t="n">
-        <v>9.56</v>
+        <v>8.85</v>
       </c>
       <c r="M237" t="n">
         <v>9.32</v>
@@ -16310,7 +16310,7 @@
         <v>6.37</v>
       </c>
       <c r="O237" t="n">
-        <v>9.027500000000002</v>
+        <v>8.700999999999999</v>
       </c>
       <c r="P237" t="n">
         <v>1</v>
@@ -16365,10 +16365,10 @@
         <v>10</v>
       </c>
       <c r="K238" t="n">
-        <v>8.869999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L238" t="n">
-        <v>8.890000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M238" t="n">
         <v>9.59</v>
@@ -16377,7 +16377,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O238" t="n">
-        <v>8.957999999999998</v>
+        <v>8.388</v>
       </c>
       <c r="P238" t="n">
         <v>2</v>
@@ -16432,10 +16432,10 @@
         <v>5</v>
       </c>
       <c r="K239" t="n">
-        <v>8.48</v>
+        <v>7.85</v>
       </c>
       <c r="L239" t="n">
-        <v>9.26</v>
+        <v>8.33</v>
       </c>
       <c r="M239" t="n">
         <v>6.7</v>
@@ -16444,7 +16444,7 @@
         <v>1.51</v>
       </c>
       <c r="O239" t="n">
-        <v>7.3515</v>
+        <v>6.837</v>
       </c>
       <c r="P239" t="n">
         <v>1</v>
@@ -16499,10 +16499,10 @@
         <v>8</v>
       </c>
       <c r="K240" t="n">
-        <v>6.91</v>
+        <v>5.72</v>
       </c>
       <c r="L240" t="n">
-        <v>8.15</v>
+        <v>6.41</v>
       </c>
       <c r="M240" t="n">
         <v>8.619999999999999</v>
@@ -16511,7 +16511,7 @@
         <v>4.64</v>
       </c>
       <c r="O240" t="n">
-        <v>7.345499999999999</v>
+        <v>6.3795</v>
       </c>
       <c r="P240" t="n">
         <v>2</v>
@@ -16566,10 +16566,10 @@
         <v>12</v>
       </c>
       <c r="K241" t="n">
-        <v>4.81</v>
+        <v>2.89</v>
       </c>
       <c r="L241" t="n">
-        <v>6.67</v>
+        <v>3.85</v>
       </c>
       <c r="M241" t="n">
         <v>7.97</v>
@@ -16578,7 +16578,7 @@
         <v>6.69</v>
       </c>
       <c r="O241" t="n">
-        <v>6.375</v>
+        <v>4.812</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -553,19 +553,19 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O2" t="n">
-        <v>7.402</v>
+        <v>0.741</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -620,19 +620,19 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>9.130000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="L3" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>4.76</v>
+        <v>0.48</v>
       </c>
       <c r="N3" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O3" t="n">
-        <v>7.58</v>
+        <v>0.7575</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -687,19 +687,19 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>7.77</v>
+        <v>0.78</v>
       </c>
       <c r="L4" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>7.11</v>
+        <v>0.71</v>
       </c>
       <c r="N4" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O4" t="n">
-        <v>7.854</v>
+        <v>0.7875</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -754,19 +754,19 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>8.196999999999999</v>
+        <v>0.8194999999999999</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -821,19 +821,19 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>9.279999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="L6" t="n">
-        <v>8.85</v>
+        <v>0.88</v>
       </c>
       <c r="M6" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="N6" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O6" t="n">
-        <v>8.700999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -888,19 +888,19 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L7" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M7" t="n">
-        <v>9.59</v>
+        <v>0.96</v>
       </c>
       <c r="N7" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O7" t="n">
-        <v>8.388</v>
+        <v>0.841</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -955,19 +955,19 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>9.130000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="L8" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M8" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N8" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O8" t="n">
-        <v>7.968</v>
+        <v>0.7955</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -1022,19 +1022,19 @@
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>7.77</v>
+        <v>0.78</v>
       </c>
       <c r="L9" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N9" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O9" t="n">
-        <v>8.17</v>
+        <v>0.8195</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1089,19 +1089,19 @@
         <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>5.95</v>
+        <v>0.6</v>
       </c>
       <c r="L10" t="n">
-        <v>6.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>9.51</v>
+        <v>0.95</v>
       </c>
       <c r="N10" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O10" t="n">
-        <v>7.4965</v>
+        <v>0.7509999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1156,19 +1156,19 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>8.880000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="L11" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M11" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="N11" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O11" t="n">
-        <v>7.5755</v>
+        <v>0.758</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -1223,19 +1223,19 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>7.87</v>
+        <v>0.79</v>
       </c>
       <c r="L12" t="n">
-        <v>7.05</v>
+        <v>0.71</v>
       </c>
       <c r="M12" t="n">
-        <v>9.220000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N12" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O12" t="n">
-        <v>7.628</v>
+        <v>0.7655</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1290,19 +1290,19 @@
         <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>6.36</v>
+        <v>0.64</v>
       </c>
       <c r="L13" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M13" t="n">
-        <v>9.609999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="N13" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O13" t="n">
-        <v>6.481999999999999</v>
+        <v>0.648</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
@@ -1357,19 +1357,19 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>9.890000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="L14" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M14" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N14" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O14" t="n">
-        <v>8.341999999999999</v>
+        <v>0.8335</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -1424,19 +1424,19 @@
         <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>9.279999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="L15" t="n">
-        <v>8.85</v>
+        <v>0.88</v>
       </c>
       <c r="M15" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="N15" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O15" t="n">
-        <v>8.700999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1491,19 +1491,19 @@
         <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L16" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M16" t="n">
-        <v>8.82</v>
+        <v>0.88</v>
       </c>
       <c r="N16" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O16" t="n">
-        <v>8.234</v>
+        <v>0.825</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
@@ -1558,19 +1558,19 @@
         <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>6.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M17" t="n">
-        <v>7.4</v>
+        <v>0.74</v>
       </c>
       <c r="N17" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>6.981</v>
+        <v>0.6994999999999999</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1625,19 +1625,19 @@
         <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.59</v>
+        <v>0.46</v>
       </c>
       <c r="L18" t="n">
-        <v>5.77</v>
+        <v>0.58</v>
       </c>
       <c r="M18" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N18" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O18" t="n">
-        <v>5.947</v>
+        <v>0.597</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1692,19 +1692,19 @@
         <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>2.32</v>
+        <v>0.23</v>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M19" t="n">
-        <v>7.97</v>
+        <v>0.8</v>
       </c>
       <c r="N19" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O19" t="n">
-        <v>4.641</v>
+        <v>0.4625</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1759,19 +1759,19 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>9.130000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="L20" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M20" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N20" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O20" t="n">
-        <v>7.968</v>
+        <v>0.7955</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1826,19 +1826,19 @@
         <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>8.220000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="L21" t="n">
-        <v>8.85</v>
+        <v>0.88</v>
       </c>
       <c r="M21" t="n">
-        <v>8.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O21" t="n">
-        <v>8.132999999999999</v>
+        <v>0.8119999999999999</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1893,19 +1893,19 @@
         <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>6.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M22" t="n">
-        <v>9.85</v>
+        <v>0.98</v>
       </c>
       <c r="N22" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O22" t="n">
-        <v>7.986999999999999</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -1960,19 +1960,19 @@
         <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O23" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -2027,19 +2027,19 @@
         <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>8.68</v>
+        <v>0.87</v>
       </c>
       <c r="L24" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="M24" t="n">
-        <v>7.4</v>
+        <v>0.74</v>
       </c>
       <c r="N24" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O24" t="n">
-        <v>8.066000000000001</v>
+        <v>0.8059999999999999</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2094,19 +2094,19 @@
         <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>7.32</v>
+        <v>0.73</v>
       </c>
       <c r="L25" t="n">
-        <v>8.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N25" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O25" t="n">
-        <v>7.5745</v>
+        <v>0.7585</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2161,19 +2161,19 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>8.880000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="L26" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M26" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N26" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O26" t="n">
-        <v>7.587499999999999</v>
+        <v>0.758</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2228,19 +2228,19 @@
         <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="L27" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M27" t="n">
-        <v>9.9</v>
+        <v>0.99</v>
       </c>
       <c r="N27" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O27" t="n">
-        <v>7.1305</v>
+        <v>0.7129999999999999</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -2295,19 +2295,19 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L28" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M28" t="n">
-        <v>7.62</v>
+        <v>0.76</v>
       </c>
       <c r="N28" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O28" t="n">
-        <v>5.48</v>
+        <v>0.5445</v>
       </c>
       <c r="P28" t="n">
         <v>3</v>
@@ -2362,19 +2362,19 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>2.93</v>
+        <v>0.29</v>
       </c>
       <c r="L29" t="n">
-        <v>4.36</v>
+        <v>0.44</v>
       </c>
       <c r="M29" t="n">
-        <v>7.85</v>
+        <v>0.79</v>
       </c>
       <c r="N29" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O29" t="n">
-        <v>4.671</v>
+        <v>0.468</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
       <c r="M30" t="n">
-        <v>7.15</v>
+        <v>0.72</v>
       </c>
       <c r="N30" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O30" t="n">
-        <v>2.703</v>
+        <v>0.2725</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.36</v>
+        <v>0.34</v>
       </c>
       <c r="N31" t="n">
-        <v>4.81</v>
+        <v>0.48</v>
       </c>
       <c r="O31" t="n">
-        <v>1.3935</v>
+        <v>0.14</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -2563,19 +2563,19 @@
         <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>4.34</v>
+        <v>0.43</v>
       </c>
       <c r="L32" t="n">
-        <v>2.56</v>
+        <v>0.26</v>
       </c>
       <c r="M32" t="n">
-        <v>8.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O32" t="n">
-        <v>4.666499999999999</v>
+        <v>0.4675</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2630,19 +2630,19 @@
         <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="N33" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O33" t="n">
-        <v>1.9215</v>
+        <v>0.192</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2703,13 +2703,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="N34" t="n">
-        <v>4.02</v>
+        <v>0.4</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7309999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -2764,19 +2764,19 @@
         <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>6.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M35" t="n">
-        <v>7.4</v>
+        <v>0.74</v>
       </c>
       <c r="N35" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O35" t="n">
-        <v>6.981</v>
+        <v>0.6994999999999999</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2831,19 +2831,19 @@
         <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>3.84</v>
+        <v>0.38</v>
       </c>
       <c r="L36" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M36" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="N36" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O36" t="n">
-        <v>5.621999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
@@ -2898,19 +2898,19 @@
         <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="L37" t="n">
-        <v>1.92</v>
+        <v>0.19</v>
       </c>
       <c r="M37" t="n">
-        <v>5.53</v>
+        <v>0.55</v>
       </c>
       <c r="N37" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O37" t="n">
-        <v>2.5745</v>
+        <v>0.2575</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
@@ -2965,19 +2965,19 @@
         <v>6</v>
       </c>
       <c r="K38" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L38" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M38" t="n">
-        <v>8.42</v>
+        <v>0.84</v>
       </c>
       <c r="N38" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O38" t="n">
-        <v>7.638</v>
+        <v>0.7645</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3032,19 +3032,19 @@
         <v>9</v>
       </c>
       <c r="K39" t="n">
-        <v>6.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>5.77</v>
+        <v>0.58</v>
       </c>
       <c r="M39" t="n">
-        <v>9.779999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="N39" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O39" t="n">
-        <v>6.812</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
@@ -3099,19 +3099,19 @@
         <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L40" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M40" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N40" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O40" t="n">
-        <v>5.798</v>
+        <v>0.5765</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
@@ -3166,19 +3166,19 @@
         <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>5.05</v>
+        <v>0.5</v>
       </c>
       <c r="L41" t="n">
-        <v>6.15</v>
+        <v>0.62</v>
       </c>
       <c r="M41" t="n">
-        <v>7.4</v>
+        <v>0.74</v>
       </c>
       <c r="N41" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O41" t="n">
-        <v>5.374</v>
+        <v>0.5375</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3233,19 +3233,19 @@
         <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L42" t="n">
-        <v>2.56</v>
+        <v>0.26</v>
       </c>
       <c r="M42" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="N42" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O42" t="n">
-        <v>3.8135</v>
+        <v>0.3825000000000001</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
@@ -3306,13 +3306,13 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>5.53</v>
+        <v>0.55</v>
       </c>
       <c r="N43" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O43" t="n">
-        <v>1.8845</v>
+        <v>0.188</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
@@ -3367,19 +3367,19 @@
         <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>6.46</v>
+        <v>0.65</v>
       </c>
       <c r="L44" t="n">
-        <v>5.26</v>
+        <v>0.53</v>
       </c>
       <c r="M44" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="N44" t="n">
-        <v>3.07</v>
+        <v>0.31</v>
       </c>
       <c r="O44" t="n">
-        <v>6.103499999999999</v>
+        <v>0.613</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3434,19 +3434,19 @@
         <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>2.93</v>
+        <v>0.29</v>
       </c>
       <c r="L45" t="n">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
       <c r="M45" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N45" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3.994</v>
+        <v>0.3995000000000001</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3501,19 +3501,19 @@
         <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>8.23</v>
+        <v>0.82</v>
       </c>
       <c r="N46" t="n">
-        <v>4.81</v>
+        <v>0.48</v>
       </c>
       <c r="O46" t="n">
-        <v>2.4005</v>
+        <v>0.239</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7.15</v>
+        <v>0.72</v>
       </c>
       <c r="N47" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O47" t="n">
-        <v>2.4335</v>
+        <v>0.2445</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3641,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="N48" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O48" t="n">
-        <v>1.6785</v>
+        <v>0.168</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="N49" t="n">
-        <v>4.02</v>
+        <v>0.4</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7309999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
@@ -3769,19 +3769,19 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>9.380000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M50" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N50" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O50" t="n">
-        <v>7.9615</v>
+        <v>0.7975</v>
       </c>
       <c r="P50" t="n">
         <v>2</v>
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="L51" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M51" t="n">
-        <v>9.960000000000001</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O51" t="n">
-        <v>8.186999999999999</v>
+        <v>0.8190000000000001</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3903,19 +3903,19 @@
         <v>12</v>
       </c>
       <c r="K52" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L52" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M52" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N52" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O52" t="n">
-        <v>6.696499999999999</v>
+        <v>0.6715000000000001</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -3970,19 +3970,19 @@
         <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>3.33</v>
+        <v>0.33</v>
       </c>
       <c r="L53" t="n">
-        <v>1.28</v>
+        <v>0.13</v>
       </c>
       <c r="M53" t="n">
-        <v>8.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O53" t="n">
-        <v>3.9155</v>
+        <v>0.392</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4037,19 +4037,19 @@
         <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>5.31</v>
+        <v>0.53</v>
       </c>
       <c r="N54" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O54" t="n">
-        <v>1.9515</v>
+        <v>0.1945</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
@@ -4110,13 +4110,13 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="N55" t="n">
-        <v>4.02</v>
+        <v>0.4</v>
       </c>
       <c r="O55" t="n">
-        <v>0.7309999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
@@ -4171,19 +4171,19 @@
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O56" t="n">
-        <v>6.7265</v>
+        <v>0.6724999999999999</v>
       </c>
       <c r="P56" t="n">
         <v>3</v>
@@ -4238,19 +4238,19 @@
         <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>9.58</v>
+        <v>0.96</v>
       </c>
       <c r="L57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="N57" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O57" t="n">
-        <v>7.276000000000001</v>
+        <v>0.729</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -4305,19 +4305,19 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L58" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M58" t="n">
-        <v>4.76</v>
+        <v>0.48</v>
       </c>
       <c r="N58" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O58" t="n">
-        <v>6.828999999999999</v>
+        <v>0.6854999999999999</v>
       </c>
       <c r="P58" t="n">
         <v>2</v>
@@ -4372,19 +4372,19 @@
         <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>9.890000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="L59" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M59" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N59" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O59" t="n">
-        <v>7.586499999999999</v>
+        <v>0.7575</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
@@ -4439,19 +4439,19 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>8.880000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="L60" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M60" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N60" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O60" t="n">
-        <v>7.291999999999999</v>
+        <v>0.728</v>
       </c>
       <c r="P60" t="n">
         <v>2</v>
@@ -4506,19 +4506,19 @@
         <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="L61" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M61" t="n">
-        <v>9.9</v>
+        <v>0.99</v>
       </c>
       <c r="N61" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O61" t="n">
-        <v>7.1305</v>
+        <v>0.7129999999999999</v>
       </c>
       <c r="P61" t="n">
         <v>3</v>
@@ -4573,19 +4573,19 @@
         <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>4.14</v>
+        <v>0.41</v>
       </c>
       <c r="L62" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M62" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="N62" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O62" t="n">
-        <v>5.544999999999999</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4640,19 +4640,19 @@
         <v>12</v>
       </c>
       <c r="K63" t="n">
-        <v>0.51</v>
+        <v>0.05</v>
       </c>
       <c r="L63" t="n">
-        <v>2.31</v>
+        <v>0.23</v>
       </c>
       <c r="M63" t="n">
-        <v>7.97</v>
+        <v>0.8</v>
       </c>
       <c r="N63" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O63" t="n">
-        <v>3.559</v>
+        <v>0.3560000000000001</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>5.53</v>
+        <v>0.55</v>
       </c>
       <c r="N64" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O64" t="n">
-        <v>1.8845</v>
+        <v>0.188</v>
       </c>
       <c r="P64" t="n">
         <v>3</v>
@@ -4774,19 +4774,19 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>9.380000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M65" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N65" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O65" t="n">
-        <v>7.9615</v>
+        <v>0.7975</v>
       </c>
       <c r="P65" t="n">
         <v>2</v>
@@ -4841,19 +4841,19 @@
         <v>8</v>
       </c>
       <c r="K66" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="L66" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M66" t="n">
-        <v>9.960000000000001</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O66" t="n">
-        <v>8.186999999999999</v>
+        <v>0.8190000000000001</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -4908,19 +4908,19 @@
         <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L67" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M67" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N67" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O67" t="n">
-        <v>7.0805</v>
+        <v>0.7105000000000001</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
@@ -4975,19 +4975,19 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="L68" t="n">
-        <v>7.05</v>
+        <v>0.71</v>
       </c>
       <c r="M68" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N68" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O68" t="n">
-        <v>5.866999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5042,19 +5042,19 @@
         <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>2.93</v>
+        <v>0.29</v>
       </c>
       <c r="L69" t="n">
-        <v>4.36</v>
+        <v>0.44</v>
       </c>
       <c r="M69" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N69" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O69" t="n">
-        <v>4.839</v>
+        <v>0.484</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5112,16 +5112,16 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
       <c r="M70" t="n">
-        <v>9.51</v>
+        <v>0.95</v>
       </c>
       <c r="N70" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O70" t="n">
-        <v>3.175</v>
+        <v>0.3185</v>
       </c>
       <c r="P70" t="n">
         <v>3</v>
@@ -5176,19 +5176,19 @@
         <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>8.41</v>
+        <v>0.84</v>
       </c>
       <c r="L71" t="n">
-        <v>7.95</v>
+        <v>0.79</v>
       </c>
       <c r="M71" t="n">
-        <v>6.23</v>
+        <v>0.62</v>
       </c>
       <c r="N71" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O71" t="n">
-        <v>6.980500000000001</v>
+        <v>0.696</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5243,19 +5243,19 @@
         <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>6.17</v>
+        <v>0.62</v>
       </c>
       <c r="L72" t="n">
-        <v>5.26</v>
+        <v>0.53</v>
       </c>
       <c r="M72" t="n">
-        <v>8.99</v>
+        <v>0.9</v>
       </c>
       <c r="N72" t="n">
-        <v>3.07</v>
+        <v>0.31</v>
       </c>
       <c r="O72" t="n">
-        <v>5.9505</v>
+        <v>0.598</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
@@ -5310,19 +5310,19 @@
         <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>3.93</v>
+        <v>0.39</v>
       </c>
       <c r="L73" t="n">
-        <v>2.56</v>
+        <v>0.26</v>
       </c>
       <c r="M73" t="n">
-        <v>9.66</v>
+        <v>0.97</v>
       </c>
       <c r="N73" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O73" t="n">
-        <v>4.8635</v>
+        <v>0.4875</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
@@ -5377,19 +5377,19 @@
         <v>4</v>
       </c>
       <c r="K74" t="n">
-        <v>7.42</v>
+        <v>0.74</v>
       </c>
       <c r="L74" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M74" t="n">
-        <v>6.05</v>
+        <v>0.61</v>
       </c>
       <c r="N74" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O74" t="n">
-        <v>6.469</v>
+        <v>0.6465</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -5444,19 +5444,19 @@
         <v>7</v>
       </c>
       <c r="K75" t="n">
-        <v>4.44</v>
+        <v>0.44</v>
       </c>
       <c r="L75" t="n">
-        <v>4.36</v>
+        <v>0.44</v>
       </c>
       <c r="M75" t="n">
-        <v>8.42</v>
+        <v>0.84</v>
       </c>
       <c r="N75" t="n">
-        <v>3.07</v>
+        <v>0.31</v>
       </c>
       <c r="O75" t="n">
-        <v>5.0025</v>
+        <v>0.5005000000000001</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5511,19 +5511,19 @@
         <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>1.46</v>
+        <v>0.15</v>
       </c>
       <c r="L76" t="n">
-        <v>1.28</v>
+        <v>0.13</v>
       </c>
       <c r="M76" t="n">
-        <v>9.1</v>
+        <v>0.91</v>
       </c>
       <c r="N76" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O76" t="n">
-        <v>3.5625</v>
+        <v>0.358</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
@@ -5578,19 +5578,19 @@
         <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>9.949999999999999</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N77" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O77" t="n">
-        <v>7.840999999999999</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -5645,19 +5645,19 @@
         <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>7.54</v>
+        <v>0.75</v>
       </c>
       <c r="L78" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M78" t="n">
-        <v>9.16</v>
+        <v>0.92</v>
       </c>
       <c r="N78" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O78" t="n">
-        <v>7.393999999999999</v>
+        <v>0.7370000000000001</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
@@ -5712,19 +5712,19 @@
         <v>15</v>
       </c>
       <c r="K79" t="n">
-        <v>4.15</v>
+        <v>0.42</v>
       </c>
       <c r="L79" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M79" t="n">
-        <v>5.53</v>
+        <v>0.55</v>
       </c>
       <c r="N79" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O79" t="n">
-        <v>4.477</v>
+        <v>0.447</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
@@ -5779,19 +5779,19 @@
         <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>9.15</v>
+        <v>0.91</v>
       </c>
       <c r="L80" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M80" t="n">
-        <v>6.16</v>
+        <v>0.62</v>
       </c>
       <c r="N80" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O80" t="n">
-        <v>7.545500000000001</v>
+        <v>0.7555000000000001</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -5846,19 +5846,19 @@
         <v>10</v>
       </c>
       <c r="K81" t="n">
-        <v>5.77</v>
+        <v>0.58</v>
       </c>
       <c r="L81" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M81" t="n">
-        <v>9.720000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="N81" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O81" t="n">
-        <v>6.326999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
@@ -5913,19 +5913,19 @@
         <v>18</v>
       </c>
       <c r="K82" t="n">
-        <v>1.27</v>
+        <v>0.13</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N82" t="n">
-        <v>4.02</v>
+        <v>0.4</v>
       </c>
       <c r="O82" t="n">
-        <v>2.47</v>
+        <v>0.247</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
@@ -5980,19 +5980,19 @@
         <v>5</v>
       </c>
       <c r="K83" t="n">
-        <v>8.800000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="L83" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M83" t="n">
-        <v>6.81</v>
+        <v>0.68</v>
       </c>
       <c r="N83" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O83" t="n">
-        <v>7.663500000000001</v>
+        <v>0.7675</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -6047,19 +6047,19 @@
         <v>12</v>
       </c>
       <c r="K84" t="n">
-        <v>5.15</v>
+        <v>0.52</v>
       </c>
       <c r="L84" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M84" t="n">
-        <v>7.87</v>
+        <v>0.79</v>
       </c>
       <c r="N84" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O84" t="n">
-        <v>6.0055</v>
+        <v>0.6035</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
@@ -6114,19 +6114,19 @@
         <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>0.99</v>
+        <v>0.1</v>
       </c>
       <c r="L85" t="n">
-        <v>1.28</v>
+        <v>0.13</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.17</v>
+        <v>0.32</v>
       </c>
       <c r="O85" t="n">
-        <v>1.2205</v>
+        <v>0.1235</v>
       </c>
       <c r="P85" t="n">
         <v>3</v>
@@ -6181,19 +6181,19 @@
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>9.98</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>1.79</v>
+        <v>0.18</v>
       </c>
       <c r="N86" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O86" t="n">
-        <v>7.078499999999999</v>
+        <v>0.7084999999999999</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -6248,19 +6248,19 @@
         <v>7</v>
       </c>
       <c r="K87" t="n">
-        <v>6.43</v>
+        <v>0.64</v>
       </c>
       <c r="L87" t="n">
-        <v>7.05</v>
+        <v>0.71</v>
       </c>
       <c r="M87" t="n">
-        <v>8.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N87" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O87" t="n">
-        <v>6.965999999999999</v>
+        <v>0.6985</v>
       </c>
       <c r="P87" t="n">
         <v>2</v>
@@ -6315,19 +6315,19 @@
         <v>14</v>
       </c>
       <c r="K88" t="n">
-        <v>1.47</v>
+        <v>0.15</v>
       </c>
       <c r="L88" t="n">
-        <v>2.56</v>
+        <v>0.26</v>
       </c>
       <c r="M88" t="n">
-        <v>8.92</v>
+        <v>0.89</v>
       </c>
       <c r="N88" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O88" t="n">
-        <v>3.9775</v>
+        <v>0.3995000000000001</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6382,19 +6382,19 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>8.9</v>
+        <v>0.89</v>
       </c>
       <c r="L89" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M89" t="n">
-        <v>8.220000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="N89" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O89" t="n">
-        <v>8.0265</v>
+        <v>0.8035</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -6449,19 +6449,19 @@
         <v>10</v>
       </c>
       <c r="K90" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="L90" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M90" t="n">
-        <v>9.640000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="N90" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O90" t="n">
-        <v>7.196999999999999</v>
+        <v>0.7174999999999999</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6516,19 +6516,19 @@
         <v>16</v>
       </c>
       <c r="K91" t="n">
-        <v>4.72</v>
+        <v>0.47</v>
       </c>
       <c r="L91" t="n">
-        <v>3.33</v>
+        <v>0.33</v>
       </c>
       <c r="M91" t="n">
-        <v>8.23</v>
+        <v>0.82</v>
       </c>
       <c r="N91" t="n">
-        <v>4.81</v>
+        <v>0.48</v>
       </c>
       <c r="O91" t="n">
-        <v>4.949</v>
+        <v>0.4925</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
@@ -6583,19 +6583,19 @@
         <v>5</v>
       </c>
       <c r="K92" t="n">
-        <v>8.84</v>
+        <v>0.88</v>
       </c>
       <c r="L92" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M92" t="n">
-        <v>4.94</v>
+        <v>0.49</v>
       </c>
       <c r="N92" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O92" t="n">
-        <v>7.3015</v>
+        <v>0.7294999999999999</v>
       </c>
       <c r="P92" t="n">
         <v>2</v>
@@ -6650,19 +6650,19 @@
         <v>8</v>
       </c>
       <c r="K93" t="n">
-        <v>7.31</v>
+        <v>0.73</v>
       </c>
       <c r="L93" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M93" t="n">
-        <v>7.46</v>
+        <v>0.75</v>
       </c>
       <c r="N93" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O93" t="n">
-        <v>7.428999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -6717,19 +6717,19 @@
         <v>12</v>
       </c>
       <c r="K94" t="n">
-        <v>5.27</v>
+        <v>0.53</v>
       </c>
       <c r="L94" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M94" t="n">
-        <v>7.92</v>
+        <v>0.79</v>
       </c>
       <c r="N94" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O94" t="n">
-        <v>6.0515</v>
+        <v>0.6065</v>
       </c>
       <c r="P94" t="n">
         <v>3</v>
@@ -6784,19 +6784,19 @@
         <v>5</v>
       </c>
       <c r="K95" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="L95" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M95" t="n">
-        <v>4.8</v>
+        <v>0.48</v>
       </c>
       <c r="N95" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O95" t="n">
-        <v>6.7975</v>
+        <v>0.6789999999999999</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6851,19 +6851,19 @@
         <v>8</v>
       </c>
       <c r="K96" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="L96" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M96" t="n">
-        <v>7.19</v>
+        <v>0.72</v>
       </c>
       <c r="N96" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O96" t="n">
-        <v>6.1655</v>
+        <v>0.617</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -6918,19 +6918,19 @@
         <v>12</v>
       </c>
       <c r="K97" t="n">
-        <v>3.24</v>
+        <v>0.32</v>
       </c>
       <c r="L97" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M97" t="n">
-        <v>8.01</v>
+        <v>0.8</v>
       </c>
       <c r="N97" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O97" t="n">
-        <v>4.925</v>
+        <v>0.4895</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -6985,19 +6985,19 @@
         <v>5</v>
       </c>
       <c r="K98" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L98" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M98" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="N98" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O98" t="n">
-        <v>7.7705</v>
+        <v>0.7775</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7052,19 +7052,19 @@
         <v>8</v>
       </c>
       <c r="K99" t="n">
-        <v>7.61</v>
+        <v>0.76</v>
       </c>
       <c r="L99" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M99" t="n">
-        <v>9.31</v>
+        <v>0.93</v>
       </c>
       <c r="N99" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O99" t="n">
-        <v>7.889</v>
+        <v>0.787</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7119,19 +7119,19 @@
         <v>12</v>
       </c>
       <c r="K100" t="n">
-        <v>5.72</v>
+        <v>0.57</v>
       </c>
       <c r="L100" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M100" t="n">
-        <v>9.33</v>
+        <v>0.93</v>
       </c>
       <c r="N100" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O100" t="n">
-        <v>6.4685</v>
+        <v>0.6465000000000001</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
@@ -7186,19 +7186,19 @@
         <v>5</v>
       </c>
       <c r="K101" t="n">
-        <v>8.289999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="L101" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M101" t="n">
-        <v>6.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N101" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O101" t="n">
-        <v>7.3045</v>
+        <v>0.73</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
@@ -7253,19 +7253,19 @@
         <v>8</v>
       </c>
       <c r="K102" t="n">
-        <v>6.43</v>
+        <v>0.64</v>
       </c>
       <c r="L102" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M102" t="n">
-        <v>9.109999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="N102" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O102" t="n">
-        <v>7.134499999999999</v>
+        <v>0.712</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
@@ -7320,19 +7320,19 @@
         <v>12</v>
       </c>
       <c r="K103" t="n">
-        <v>3.94</v>
+        <v>0.39</v>
       </c>
       <c r="L103" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M103" t="n">
-        <v>9.369999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N103" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O103" t="n">
-        <v>5.406999999999999</v>
+        <v>0.5385</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
@@ -7387,19 +7387,19 @@
         <v>5</v>
       </c>
       <c r="K104" t="n">
-        <v>8.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L104" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M104" t="n">
-        <v>5.86</v>
+        <v>0.59</v>
       </c>
       <c r="N104" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O104" t="n">
-        <v>7.0365</v>
+        <v>0.704</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -7454,19 +7454,19 @@
         <v>8</v>
       </c>
       <c r="K105" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="L105" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M105" t="n">
-        <v>8.029999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="N105" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O105" t="n">
-        <v>6.3755</v>
+        <v>0.6359999999999999</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7521,19 +7521,19 @@
         <v>12</v>
       </c>
       <c r="K106" t="n">
-        <v>3.45</v>
+        <v>0.35</v>
       </c>
       <c r="L106" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M106" t="n">
-        <v>7.07</v>
+        <v>0.71</v>
       </c>
       <c r="N106" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O106" t="n">
-        <v>4.8</v>
+        <v>0.4805</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -7588,19 +7588,19 @@
         <v>8</v>
       </c>
       <c r="K107" t="n">
-        <v>6.43</v>
+        <v>0.64</v>
       </c>
       <c r="L107" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M107" t="n">
-        <v>9.039999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N107" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O107" t="n">
-        <v>6.676499999999999</v>
+        <v>0.665</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
@@ -7655,19 +7655,19 @@
         <v>10</v>
       </c>
       <c r="K108" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="L108" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M108" t="n">
-        <v>9.1</v>
+        <v>0.91</v>
       </c>
       <c r="N108" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O108" t="n">
-        <v>6.029</v>
+        <v>0.6020000000000001</v>
       </c>
       <c r="P108" t="n">
         <v>2</v>
@@ -7722,19 +7722,19 @@
         <v>12</v>
       </c>
       <c r="K109" t="n">
-        <v>3.94</v>
+        <v>0.39</v>
       </c>
       <c r="L109" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M109" t="n">
-        <v>7.81</v>
+        <v>0.78</v>
       </c>
       <c r="N109" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O109" t="n">
-        <v>5.095</v>
+        <v>0.5065000000000001</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
@@ -7789,19 +7789,19 @@
         <v>8</v>
       </c>
       <c r="K110" t="n">
-        <v>5.15</v>
+        <v>0.52</v>
       </c>
       <c r="L110" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M110" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N110" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O110" t="n">
-        <v>5.896</v>
+        <v>0.5920000000000001</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
@@ -7856,19 +7856,19 @@
         <v>10</v>
       </c>
       <c r="K111" t="n">
-        <v>3.59</v>
+        <v>0.36</v>
       </c>
       <c r="L111" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M111" t="n">
-        <v>9.19</v>
+        <v>0.92</v>
       </c>
       <c r="N111" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O111" t="n">
-        <v>5.119</v>
+        <v>0.5105000000000001</v>
       </c>
       <c r="P111" t="n">
         <v>2</v>
@@ -7923,19 +7923,19 @@
         <v>12</v>
       </c>
       <c r="K112" t="n">
-        <v>2.03</v>
+        <v>0.2</v>
       </c>
       <c r="L112" t="n">
-        <v>2.31</v>
+        <v>0.23</v>
       </c>
       <c r="M112" t="n">
-        <v>7.87</v>
+        <v>0.79</v>
       </c>
       <c r="N112" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O112" t="n">
-        <v>3.995</v>
+        <v>0.399</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
@@ -7990,19 +7990,19 @@
         <v>8</v>
       </c>
       <c r="K113" t="n">
-        <v>6.66</v>
+        <v>0.67</v>
       </c>
       <c r="L113" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M113" t="n">
-        <v>9.24</v>
+        <v>0.92</v>
       </c>
       <c r="N113" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O113" t="n">
-        <v>6.7855</v>
+        <v>0.6779999999999999</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -8057,19 +8057,19 @@
         <v>10</v>
       </c>
       <c r="K114" t="n">
-        <v>5.48</v>
+        <v>0.55</v>
       </c>
       <c r="L114" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M114" t="n">
-        <v>9.02</v>
+        <v>0.9</v>
       </c>
       <c r="N114" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O114" t="n">
-        <v>6.1</v>
+        <v>0.6090000000000001</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -8124,19 +8124,19 @@
         <v>12</v>
       </c>
       <c r="K115" t="n">
-        <v>4.29</v>
+        <v>0.43</v>
       </c>
       <c r="L115" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M115" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="N115" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O115" t="n">
-        <v>5.19</v>
+        <v>0.5185000000000001</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8191,19 +8191,19 @@
         <v>8</v>
       </c>
       <c r="K116" t="n">
-        <v>7.42</v>
+        <v>0.74</v>
       </c>
       <c r="L116" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M116" t="n">
-        <v>9.039999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N116" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O116" t="n">
-        <v>7.334</v>
+        <v>0.73</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
@@ -8258,19 +8258,19 @@
         <v>10</v>
       </c>
       <c r="K117" t="n">
-        <v>6.43</v>
+        <v>0.64</v>
       </c>
       <c r="L117" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M117" t="n">
-        <v>9.1</v>
+        <v>0.91</v>
       </c>
       <c r="N117" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O117" t="n">
-        <v>6.848999999999999</v>
+        <v>0.6835</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
@@ -8325,19 +8325,19 @@
         <v>12</v>
       </c>
       <c r="K118" t="n">
-        <v>5.43</v>
+        <v>0.54</v>
       </c>
       <c r="L118" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M118" t="n">
-        <v>7.81</v>
+        <v>0.78</v>
       </c>
       <c r="N118" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O118" t="n">
-        <v>6.0775</v>
+        <v>0.6075</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
@@ -8392,19 +8392,19 @@
         <v>8</v>
       </c>
       <c r="K119" t="n">
-        <v>6.57</v>
+        <v>0.66</v>
       </c>
       <c r="L119" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M119" t="n">
-        <v>9.16</v>
+        <v>0.92</v>
       </c>
       <c r="N119" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O119" t="n">
-        <v>6.7425</v>
+        <v>0.675</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
@@ -8459,19 +8459,19 @@
         <v>10</v>
       </c>
       <c r="K120" t="n">
-        <v>5.36</v>
+        <v>0.54</v>
       </c>
       <c r="L120" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M120" t="n">
-        <v>9.050000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N120" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O120" t="n">
-        <v>6.07</v>
+        <v>0.6080000000000001</v>
       </c>
       <c r="P120" t="n">
         <v>2</v>
@@ -8526,19 +8526,19 @@
         <v>12</v>
       </c>
       <c r="K121" t="n">
-        <v>4.15</v>
+        <v>0.42</v>
       </c>
       <c r="L121" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M121" t="n">
-        <v>7.78</v>
+        <v>0.78</v>
       </c>
       <c r="N121" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O121" t="n">
-        <v>5.152</v>
+        <v>0.5155000000000001</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
@@ -8593,19 +8593,19 @@
         <v>5</v>
       </c>
       <c r="K122" t="n">
-        <v>7.62</v>
+        <v>0.76</v>
       </c>
       <c r="L122" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M122" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N122" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O122" t="n">
-        <v>7.063499999999999</v>
+        <v>0.705</v>
       </c>
       <c r="P122" t="n">
         <v>1</v>
@@ -8660,19 +8660,19 @@
         <v>8</v>
       </c>
       <c r="K123" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L123" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M123" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N123" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O123" t="n">
-        <v>6.282499999999999</v>
+        <v>0.6260000000000001</v>
       </c>
       <c r="P123" t="n">
         <v>2</v>
@@ -8727,19 +8727,19 @@
         <v>12</v>
       </c>
       <c r="K124" t="n">
-        <v>2.32</v>
+        <v>0.23</v>
       </c>
       <c r="L124" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M124" t="n">
-        <v>9.51</v>
+        <v>0.95</v>
       </c>
       <c r="N124" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O124" t="n">
-        <v>4.949</v>
+        <v>0.4925</v>
       </c>
       <c r="P124" t="n">
         <v>3</v>
@@ -8794,19 +8794,19 @@
         <v>5</v>
       </c>
       <c r="K125" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L125" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M125" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N125" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O125" t="n">
-        <v>7.512499999999999</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="P125" t="n">
         <v>1</v>
@@ -8861,19 +8861,19 @@
         <v>8</v>
       </c>
       <c r="K126" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L126" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M126" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N126" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O126" t="n">
-        <v>7.45</v>
+        <v>0.745</v>
       </c>
       <c r="P126" t="n">
         <v>2</v>
@@ -8928,19 +8928,19 @@
         <v>12</v>
       </c>
       <c r="K127" t="n">
-        <v>4.14</v>
+        <v>0.41</v>
       </c>
       <c r="L127" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M127" t="n">
-        <v>9.51</v>
+        <v>0.95</v>
       </c>
       <c r="N127" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O127" t="n">
-        <v>6.030499999999999</v>
+        <v>0.6025</v>
       </c>
       <c r="P127" t="n">
         <v>3</v>
@@ -8995,19 +8995,19 @@
         <v>5</v>
       </c>
       <c r="K128" t="n">
-        <v>7.62</v>
+        <v>0.76</v>
       </c>
       <c r="L128" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M128" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N128" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O128" t="n">
-        <v>7.063499999999999</v>
+        <v>0.705</v>
       </c>
       <c r="P128" t="n">
         <v>1</v>
@@ -9062,19 +9062,19 @@
         <v>8</v>
       </c>
       <c r="K129" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L129" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M129" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N129" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O129" t="n">
-        <v>6.282499999999999</v>
+        <v>0.6260000000000001</v>
       </c>
       <c r="P129" t="n">
         <v>2</v>
@@ -9129,19 +9129,19 @@
         <v>12</v>
       </c>
       <c r="K130" t="n">
-        <v>2.32</v>
+        <v>0.23</v>
       </c>
       <c r="L130" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M130" t="n">
-        <v>9.51</v>
+        <v>0.95</v>
       </c>
       <c r="N130" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O130" t="n">
-        <v>4.949</v>
+        <v>0.4925</v>
       </c>
       <c r="P130" t="n">
         <v>3</v>
@@ -9196,19 +9196,19 @@
         <v>5</v>
       </c>
       <c r="K131" t="n">
-        <v>9.380000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L131" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M131" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="N131" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O131" t="n">
-        <v>7.9495</v>
+        <v>0.7975</v>
       </c>
       <c r="P131" t="n">
         <v>2</v>
@@ -9263,19 +9263,19 @@
         <v>8</v>
       </c>
       <c r="K132" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="L132" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M132" t="n">
-        <v>9.99</v>
+        <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O132" t="n">
-        <v>8.193</v>
+        <v>0.8190000000000001</v>
       </c>
       <c r="P132" t="n">
         <v>1</v>
@@ -9330,19 +9330,19 @@
         <v>12</v>
       </c>
       <c r="K133" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L133" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M133" t="n">
-        <v>9.220000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N133" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O133" t="n">
-        <v>6.6985</v>
+        <v>0.6715000000000001</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
@@ -9397,19 +9397,19 @@
         <v>5</v>
       </c>
       <c r="K134" t="n">
-        <v>8.880000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="L134" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M134" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N134" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O134" t="n">
-        <v>7.587499999999999</v>
+        <v>0.758</v>
       </c>
       <c r="P134" t="n">
         <v>1</v>
@@ -9464,19 +9464,19 @@
         <v>8</v>
       </c>
       <c r="K135" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="L135" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M135" t="n">
-        <v>9.960000000000001</v>
+        <v>1</v>
       </c>
       <c r="N135" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O135" t="n">
-        <v>7.142499999999999</v>
+        <v>0.7149999999999999</v>
       </c>
       <c r="P135" t="n">
         <v>2</v>
@@ -9531,19 +9531,19 @@
         <v>12</v>
       </c>
       <c r="K136" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L136" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M136" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N136" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O136" t="n">
-        <v>5.798</v>
+        <v>0.5765</v>
       </c>
       <c r="P136" t="n">
         <v>3</v>
@@ -9598,19 +9598,19 @@
         <v>4</v>
       </c>
       <c r="K137" t="n">
-        <v>8.050000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L137" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M137" t="n">
-        <v>5.94</v>
+        <v>0.59</v>
       </c>
       <c r="N137" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O137" t="n">
-        <v>6.993</v>
+        <v>0.702</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
@@ -9665,19 +9665,19 @@
         <v>7</v>
       </c>
       <c r="K138" t="n">
-        <v>5.54</v>
+        <v>0.55</v>
       </c>
       <c r="L138" t="n">
-        <v>6.15</v>
+        <v>0.62</v>
       </c>
       <c r="M138" t="n">
-        <v>8.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N138" t="n">
-        <v>3.07</v>
+        <v>0.31</v>
       </c>
       <c r="O138" t="n">
-        <v>5.888999999999999</v>
+        <v>0.5905</v>
       </c>
       <c r="P138" t="n">
         <v>2</v>
@@ -9732,19 +9732,19 @@
         <v>10</v>
       </c>
       <c r="K139" t="n">
-        <v>3.03</v>
+        <v>0.3</v>
       </c>
       <c r="L139" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M139" t="n">
-        <v>9.85</v>
+        <v>0.98</v>
       </c>
       <c r="N139" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O139" t="n">
-        <v>5.082999999999999</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="P139" t="n">
         <v>3</v>
@@ -9799,19 +9799,19 @@
         <v>4</v>
       </c>
       <c r="K140" t="n">
-        <v>6.78</v>
+        <v>0.68</v>
       </c>
       <c r="L140" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M140" t="n">
-        <v>5.94</v>
+        <v>0.59</v>
       </c>
       <c r="N140" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O140" t="n">
-        <v>6.0525</v>
+        <v>0.6034999999999999</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
@@ -9866,19 +9866,19 @@
         <v>7</v>
       </c>
       <c r="K141" t="n">
-        <v>3.32</v>
+        <v>0.33</v>
       </c>
       <c r="L141" t="n">
-        <v>4.36</v>
+        <v>0.44</v>
       </c>
       <c r="M141" t="n">
-        <v>8.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N141" t="n">
-        <v>3.07</v>
+        <v>0.31</v>
       </c>
       <c r="O141" t="n">
-        <v>4.5965</v>
+        <v>0.4615</v>
       </c>
       <c r="P141" t="n">
         <v>2</v>
@@ -9936,16 +9936,16 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>1.28</v>
+        <v>0.13</v>
       </c>
       <c r="M142" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="N142" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O142" t="n">
-        <v>3.1225</v>
+        <v>0.3130000000000001</v>
       </c>
       <c r="P142" t="n">
         <v>3</v>
@@ -10000,19 +10000,19 @@
         <v>1</v>
       </c>
       <c r="K143" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L143" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="N143" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O143" t="n">
-        <v>6.7745</v>
+        <v>0.6764999999999999</v>
       </c>
       <c r="P143" t="n">
         <v>2</v>
@@ -10067,19 +10067,19 @@
         <v>6</v>
       </c>
       <c r="K144" t="n">
-        <v>8.42</v>
+        <v>0.84</v>
       </c>
       <c r="L144" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M144" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="N144" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O144" t="n">
-        <v>7.7765</v>
+        <v>0.7785</v>
       </c>
       <c r="P144" t="n">
         <v>1</v>
@@ -10134,19 +10134,19 @@
         <v>12</v>
       </c>
       <c r="K145" t="n">
-        <v>5.43</v>
+        <v>0.54</v>
       </c>
       <c r="L145" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M145" t="n">
-        <v>9.369999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N145" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O145" t="n">
-        <v>6.389499999999999</v>
+        <v>0.6395</v>
       </c>
       <c r="P145" t="n">
         <v>3</v>
@@ -10201,19 +10201,19 @@
         <v>7</v>
       </c>
       <c r="K146" t="n">
-        <v>7.34</v>
+        <v>0.73</v>
       </c>
       <c r="L146" t="n">
-        <v>7.05</v>
+        <v>0.71</v>
       </c>
       <c r="M146" t="n">
-        <v>8.66</v>
+        <v>0.87</v>
       </c>
       <c r="N146" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O146" t="n">
-        <v>7.356999999999999</v>
+        <v>0.7374999999999999</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
@@ -10268,19 +10268,19 @@
         <v>14</v>
       </c>
       <c r="K147" t="n">
-        <v>3.27</v>
+        <v>0.33</v>
       </c>
       <c r="L147" t="n">
-        <v>2.56</v>
+        <v>0.26</v>
       </c>
       <c r="M147" t="n">
-        <v>8.85</v>
+        <v>0.88</v>
       </c>
       <c r="N147" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O147" t="n">
-        <v>4.5035</v>
+        <v>0.4515</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
@@ -10341,13 +10341,13 @@
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>5.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N148" t="n">
-        <v>2.27</v>
+        <v>0.23</v>
       </c>
       <c r="O148" t="n">
-        <v>1.4665</v>
+        <v>0.1465</v>
       </c>
       <c r="P148" t="n">
         <v>3</v>
@@ -10402,19 +10402,19 @@
         <v>5</v>
       </c>
       <c r="K149" t="n">
-        <v>8.800000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="L149" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M149" t="n">
-        <v>4.9</v>
+        <v>0.49</v>
       </c>
       <c r="N149" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O149" t="n">
-        <v>7.281500000000001</v>
+        <v>0.7294999999999999</v>
       </c>
       <c r="P149" t="n">
         <v>1</v>
@@ -10469,19 +10469,19 @@
         <v>8</v>
       </c>
       <c r="K150" t="n">
-        <v>7.24</v>
+        <v>0.72</v>
       </c>
       <c r="L150" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M150" t="n">
-        <v>7.38</v>
+        <v>0.74</v>
       </c>
       <c r="N150" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O150" t="n">
-        <v>6.948</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="P150" t="n">
         <v>2</v>
@@ -10536,19 +10536,19 @@
         <v>12</v>
       </c>
       <c r="K151" t="n">
-        <v>5.15</v>
+        <v>0.52</v>
       </c>
       <c r="L151" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M151" t="n">
-        <v>7.95</v>
+        <v>0.79</v>
       </c>
       <c r="N151" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O151" t="n">
-        <v>6.0215</v>
+        <v>0.6035</v>
       </c>
       <c r="P151" t="n">
         <v>3</v>
@@ -10603,19 +10603,19 @@
         <v>5</v>
       </c>
       <c r="K152" t="n">
-        <v>8.380000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="L152" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M152" t="n">
-        <v>6.06</v>
+        <v>0.61</v>
       </c>
       <c r="N152" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O152" t="n">
-        <v>7.1635</v>
+        <v>0.717</v>
       </c>
       <c r="P152" t="n">
         <v>1</v>
@@ -10670,19 +10670,19 @@
         <v>8</v>
       </c>
       <c r="K153" t="n">
-        <v>6.57</v>
+        <v>0.66</v>
       </c>
       <c r="L153" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M153" t="n">
-        <v>8.5</v>
+        <v>0.85</v>
       </c>
       <c r="N153" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O153" t="n">
-        <v>7.0545</v>
+        <v>0.706</v>
       </c>
       <c r="P153" t="n">
         <v>2</v>
@@ -10737,19 +10737,19 @@
         <v>12</v>
       </c>
       <c r="K154" t="n">
-        <v>4.15</v>
+        <v>0.42</v>
       </c>
       <c r="L154" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M154" t="n">
-        <v>8.630000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="N154" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O154" t="n">
-        <v>5.322</v>
+        <v>0.5315000000000001</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -10804,19 +10804,19 @@
         <v>6</v>
       </c>
       <c r="K155" t="n">
-        <v>7.67</v>
+        <v>0.77</v>
       </c>
       <c r="L155" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M155" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="N155" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O155" t="n">
-        <v>6.757</v>
+        <v>0.6769999999999999</v>
       </c>
       <c r="P155" t="n">
         <v>1</v>
@@ -10871,19 +10871,19 @@
         <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>6.43</v>
+        <v>0.64</v>
       </c>
       <c r="L156" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M156" t="n">
-        <v>9.039999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N156" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O156" t="n">
-        <v>6.676499999999999</v>
+        <v>0.665</v>
       </c>
       <c r="P156" t="n">
         <v>2</v>
@@ -10938,19 +10938,19 @@
         <v>10</v>
       </c>
       <c r="K157" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="L157" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M157" t="n">
-        <v>9.1</v>
+        <v>0.91</v>
       </c>
       <c r="N157" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O157" t="n">
-        <v>6.029</v>
+        <v>0.6020000000000001</v>
       </c>
       <c r="P157" t="n">
         <v>3</v>
@@ -11005,19 +11005,19 @@
         <v>8</v>
       </c>
       <c r="K158" t="n">
-        <v>6.57</v>
+        <v>0.66</v>
       </c>
       <c r="L158" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M158" t="n">
-        <v>9.16</v>
+        <v>0.92</v>
       </c>
       <c r="N158" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O158" t="n">
-        <v>6.7425</v>
+        <v>0.675</v>
       </c>
       <c r="P158" t="n">
         <v>1</v>
@@ -11072,19 +11072,19 @@
         <v>10</v>
       </c>
       <c r="K159" t="n">
-        <v>5.36</v>
+        <v>0.54</v>
       </c>
       <c r="L159" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M159" t="n">
-        <v>9.050000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N159" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O159" t="n">
-        <v>6.07</v>
+        <v>0.6080000000000001</v>
       </c>
       <c r="P159" t="n">
         <v>2</v>
@@ -11139,19 +11139,19 @@
         <v>12</v>
       </c>
       <c r="K160" t="n">
-        <v>4.15</v>
+        <v>0.42</v>
       </c>
       <c r="L160" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M160" t="n">
-        <v>7.78</v>
+        <v>0.78</v>
       </c>
       <c r="N160" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O160" t="n">
-        <v>5.152</v>
+        <v>0.5155000000000001</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
@@ -11206,19 +11206,19 @@
         <v>5</v>
       </c>
       <c r="K161" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L161" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M161" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N161" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O161" t="n">
-        <v>7.512499999999999</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="P161" t="n">
         <v>1</v>
@@ -11273,19 +11273,19 @@
         <v>8</v>
       </c>
       <c r="K162" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L162" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M162" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N162" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O162" t="n">
-        <v>7.45</v>
+        <v>0.745</v>
       </c>
       <c r="P162" t="n">
         <v>2</v>
@@ -11340,19 +11340,19 @@
         <v>12</v>
       </c>
       <c r="K163" t="n">
-        <v>4.14</v>
+        <v>0.41</v>
       </c>
       <c r="L163" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M163" t="n">
-        <v>9.51</v>
+        <v>0.95</v>
       </c>
       <c r="N163" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O163" t="n">
-        <v>6.030499999999999</v>
+        <v>0.6025</v>
       </c>
       <c r="P163" t="n">
         <v>3</v>
@@ -11407,19 +11407,19 @@
         <v>5</v>
       </c>
       <c r="K164" t="n">
-        <v>8.880000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="L164" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M164" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N164" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O164" t="n">
-        <v>7.587499999999999</v>
+        <v>0.758</v>
       </c>
       <c r="P164" t="n">
         <v>1</v>
@@ -11474,19 +11474,19 @@
         <v>8</v>
       </c>
       <c r="K165" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="L165" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M165" t="n">
-        <v>9.960000000000001</v>
+        <v>1</v>
       </c>
       <c r="N165" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O165" t="n">
-        <v>7.142499999999999</v>
+        <v>0.7149999999999999</v>
       </c>
       <c r="P165" t="n">
         <v>2</v>
@@ -11541,19 +11541,19 @@
         <v>12</v>
       </c>
       <c r="K166" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L166" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M166" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N166" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O166" t="n">
-        <v>5.798</v>
+        <v>0.5765</v>
       </c>
       <c r="P166" t="n">
         <v>3</v>
@@ -11608,19 +11608,19 @@
         <v>3</v>
       </c>
       <c r="K167" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L167" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N167" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O167" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="P167" t="n">
         <v>2</v>
@@ -11675,19 +11675,19 @@
         <v>5</v>
       </c>
       <c r="K168" t="n">
-        <v>9.15</v>
+        <v>0.91</v>
       </c>
       <c r="L168" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M168" t="n">
-        <v>7.11</v>
+        <v>0.71</v>
       </c>
       <c r="N168" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O168" t="n">
-        <v>7.8285</v>
+        <v>0.7825000000000001</v>
       </c>
       <c r="P168" t="n">
         <v>3</v>
@@ -11742,19 +11742,19 @@
         <v>8</v>
       </c>
       <c r="K169" t="n">
-        <v>7.8</v>
+        <v>0.78</v>
       </c>
       <c r="L169" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M169" t="n">
-        <v>9.529999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="N169" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O169" t="n">
-        <v>7.989999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="P169" t="n">
         <v>1</v>
@@ -11809,19 +11809,19 @@
         <v>3</v>
       </c>
       <c r="K170" t="n">
-        <v>9.890000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="L170" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M170" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N170" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O170" t="n">
-        <v>7.69</v>
+        <v>0.768</v>
       </c>
       <c r="P170" t="n">
         <v>1</v>
@@ -11876,19 +11876,19 @@
         <v>5</v>
       </c>
       <c r="K171" t="n">
-        <v>8.880000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="L171" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M171" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N171" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O171" t="n">
-        <v>7.587499999999999</v>
+        <v>0.758</v>
       </c>
       <c r="P171" t="n">
         <v>2</v>
@@ -11943,19 +11943,19 @@
         <v>8</v>
       </c>
       <c r="K172" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="L172" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M172" t="n">
-        <v>9.960000000000001</v>
+        <v>1</v>
       </c>
       <c r="N172" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O172" t="n">
-        <v>7.142499999999999</v>
+        <v>0.7149999999999999</v>
       </c>
       <c r="P172" t="n">
         <v>3</v>
@@ -12010,19 +12010,19 @@
         <v>3</v>
       </c>
       <c r="K173" t="n">
-        <v>9.83</v>
+        <v>0.98</v>
       </c>
       <c r="L173" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M173" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N173" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O173" t="n">
-        <v>7.671999999999999</v>
+        <v>0.7649999999999999</v>
       </c>
       <c r="P173" t="n">
         <v>1</v>
@@ -12077,19 +12077,19 @@
         <v>5</v>
       </c>
       <c r="K174" t="n">
-        <v>8.789999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="L174" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M174" t="n">
-        <v>7.28</v>
+        <v>0.73</v>
       </c>
       <c r="N174" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O174" t="n">
-        <v>7.5305</v>
+        <v>0.753</v>
       </c>
       <c r="P174" t="n">
         <v>2</v>
@@ -12144,19 +12144,19 @@
         <v>8</v>
       </c>
       <c r="K175" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="L175" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M175" t="n">
-        <v>9.880000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="N175" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O175" t="n">
-        <v>7.084499999999999</v>
+        <v>0.7069999999999999</v>
       </c>
       <c r="P175" t="n">
         <v>3</v>
@@ -12211,22 +12211,22 @@
         <v>3</v>
       </c>
       <c r="K176" t="n">
-        <v>9.949999999999999</v>
+        <v>1</v>
       </c>
       <c r="L176" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N176" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O176" t="n">
-        <v>7.840999999999999</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="P176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q176" t="n">
         <v>0.7627780141936447</v>
@@ -12278,19 +12278,19 @@
         <v>5</v>
       </c>
       <c r="K177" t="n">
-        <v>8.98</v>
+        <v>0.9</v>
       </c>
       <c r="L177" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M177" t="n">
-        <v>6.96</v>
+        <v>0.7</v>
       </c>
       <c r="N177" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O177" t="n">
-        <v>7.7475</v>
+        <v>0.7775</v>
       </c>
       <c r="P177" t="n">
         <v>3</v>
@@ -12345,22 +12345,22 @@
         <v>8</v>
       </c>
       <c r="K178" t="n">
-        <v>7.54</v>
+        <v>0.75</v>
       </c>
       <c r="L178" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M178" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="N178" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O178" t="n">
-        <v>7.851999999999999</v>
+        <v>0.782</v>
       </c>
       <c r="P178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q178" t="n">
         <v>2.034074704516386</v>
@@ -12412,19 +12412,19 @@
         <v>4</v>
       </c>
       <c r="K179" t="n">
-        <v>9.630000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="L179" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>3.85</v>
+        <v>0.39</v>
       </c>
       <c r="N179" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O179" t="n">
-        <v>7.588000000000001</v>
+        <v>0.7595</v>
       </c>
       <c r="P179" t="n">
         <v>3</v>
@@ -12479,19 +12479,19 @@
         <v>6</v>
       </c>
       <c r="K180" t="n">
-        <v>8.74</v>
+        <v>0.87</v>
       </c>
       <c r="L180" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="M180" t="n">
-        <v>5.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N180" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O180" t="n">
-        <v>7.724</v>
+        <v>0.7699999999999999</v>
       </c>
       <c r="P180" t="n">
         <v>2</v>
@@ -12546,19 +12546,19 @@
         <v>10</v>
       </c>
       <c r="K181" t="n">
-        <v>6.97</v>
+        <v>0.7</v>
       </c>
       <c r="L181" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M181" t="n">
-        <v>8.43</v>
+        <v>0.84</v>
       </c>
       <c r="N181" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O181" t="n">
-        <v>7.736</v>
+        <v>0.7749999999999999</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
@@ -12613,19 +12613,19 @@
         <v>4</v>
       </c>
       <c r="K182" t="n">
-        <v>9.279999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="L182" t="n">
-        <v>9.49</v>
+        <v>0.95</v>
       </c>
       <c r="M182" t="n">
-        <v>5.99</v>
+        <v>0.6</v>
       </c>
       <c r="N182" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O182" t="n">
-        <v>7.7325</v>
+        <v>0.7749999999999999</v>
       </c>
       <c r="P182" t="n">
         <v>1</v>
@@ -12680,19 +12680,19 @@
         <v>6</v>
       </c>
       <c r="K183" t="n">
-        <v>8.220000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="L183" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M183" t="n">
-        <v>7.52</v>
+        <v>0.75</v>
       </c>
       <c r="N183" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O183" t="n">
-        <v>7.682500000000001</v>
+        <v>0.7685</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
@@ -12747,19 +12747,19 @@
         <v>10</v>
       </c>
       <c r="K184" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="L184" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M184" t="n">
-        <v>9.970000000000001</v>
+        <v>1</v>
       </c>
       <c r="N184" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O184" t="n">
-        <v>7.335000000000001</v>
+        <v>0.7344999999999999</v>
       </c>
       <c r="P184" t="n">
         <v>3</v>
@@ -12814,19 +12814,19 @@
         <v>3</v>
       </c>
       <c r="K185" t="n">
-        <v>9.66</v>
+        <v>0.97</v>
       </c>
       <c r="L185" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M185" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N185" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O185" t="n">
-        <v>7.621</v>
+        <v>0.762</v>
       </c>
       <c r="P185" t="n">
         <v>1</v>
@@ -12881,19 +12881,19 @@
         <v>5</v>
       </c>
       <c r="K186" t="n">
-        <v>8.5</v>
+        <v>0.85</v>
       </c>
       <c r="L186" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M186" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="N186" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O186" t="n">
-        <v>7.3955</v>
+        <v>0.738</v>
       </c>
       <c r="P186" t="n">
         <v>2</v>
@@ -12948,19 +12948,19 @@
         <v>8</v>
       </c>
       <c r="K187" t="n">
-        <v>6.76</v>
+        <v>0.68</v>
       </c>
       <c r="L187" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M187" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N187" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O187" t="n">
-        <v>6.845499999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="P187" t="n">
         <v>3</v>
@@ -13015,19 +13015,19 @@
         <v>3</v>
       </c>
       <c r="K188" t="n">
-        <v>9.48</v>
+        <v>0.95</v>
       </c>
       <c r="L188" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="M188" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N188" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O188" t="n">
-        <v>7.4305</v>
+        <v>0.742</v>
       </c>
       <c r="P188" t="n">
         <v>1</v>
@@ -13082,19 +13082,19 @@
         <v>4</v>
       </c>
       <c r="K189" t="n">
-        <v>8.84</v>
+        <v>0.88</v>
       </c>
       <c r="L189" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M189" t="n">
-        <v>6.23</v>
+        <v>0.62</v>
       </c>
       <c r="N189" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O189" t="n">
-        <v>7.288</v>
+        <v>0.729</v>
       </c>
       <c r="P189" t="n">
         <v>2</v>
@@ -13149,19 +13149,19 @@
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>7.56</v>
+        <v>0.76</v>
       </c>
       <c r="L190" t="n">
-        <v>6.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M190" t="n">
-        <v>8.140000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N190" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O190" t="n">
-        <v>6.544499999999999</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
@@ -13216,19 +13216,19 @@
         <v>3</v>
       </c>
       <c r="K191" t="n">
-        <v>9.58</v>
+        <v>0.96</v>
       </c>
       <c r="L191" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N191" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O191" t="n">
-        <v>7.73</v>
+        <v>0.7729999999999999</v>
       </c>
       <c r="P191" t="n">
         <v>1</v>
@@ -13283,19 +13283,19 @@
         <v>5</v>
       </c>
       <c r="K192" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L192" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M192" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N192" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O192" t="n">
-        <v>7.512499999999999</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="P192" t="n">
         <v>2</v>
@@ -13350,19 +13350,19 @@
         <v>8</v>
       </c>
       <c r="K193" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L193" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M193" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N193" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O193" t="n">
-        <v>7.45</v>
+        <v>0.745</v>
       </c>
       <c r="P193" t="n">
         <v>3</v>
@@ -13417,19 +13417,19 @@
         <v>3</v>
       </c>
       <c r="K194" t="n">
-        <v>9.66</v>
+        <v>0.97</v>
       </c>
       <c r="L194" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M194" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N194" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O194" t="n">
-        <v>7.621</v>
+        <v>0.762</v>
       </c>
       <c r="P194" t="n">
         <v>1</v>
@@ -13484,19 +13484,19 @@
         <v>5</v>
       </c>
       <c r="K195" t="n">
-        <v>8.5</v>
+        <v>0.85</v>
       </c>
       <c r="L195" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M195" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="N195" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O195" t="n">
-        <v>7.3955</v>
+        <v>0.738</v>
       </c>
       <c r="P195" t="n">
         <v>2</v>
@@ -13551,19 +13551,19 @@
         <v>8</v>
       </c>
       <c r="K196" t="n">
-        <v>6.76</v>
+        <v>0.68</v>
       </c>
       <c r="L196" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M196" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N196" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O196" t="n">
-        <v>6.845499999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="P196" t="n">
         <v>3</v>
@@ -13618,19 +13618,19 @@
         <v>3</v>
       </c>
       <c r="K197" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L197" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N197" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O197" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="P197" t="n">
         <v>3</v>
@@ -13685,19 +13685,19 @@
         <v>5</v>
       </c>
       <c r="K198" t="n">
-        <v>9.380000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L198" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M198" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="N198" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O198" t="n">
-        <v>7.9495</v>
+        <v>0.7975</v>
       </c>
       <c r="P198" t="n">
         <v>2</v>
@@ -13752,19 +13752,19 @@
         <v>8</v>
       </c>
       <c r="K199" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="L199" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M199" t="n">
-        <v>9.99</v>
+        <v>1</v>
       </c>
       <c r="N199" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O199" t="n">
-        <v>8.193</v>
+        <v>0.8190000000000001</v>
       </c>
       <c r="P199" t="n">
         <v>1</v>
@@ -13819,19 +13819,19 @@
         <v>3</v>
       </c>
       <c r="K200" t="n">
-        <v>9.539999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="L200" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M200" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N200" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O200" t="n">
-        <v>7.584999999999999</v>
+        <v>0.756</v>
       </c>
       <c r="P200" t="n">
         <v>1</v>
@@ -13886,19 +13886,19 @@
         <v>5</v>
       </c>
       <c r="K201" t="n">
-        <v>8.289999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="L201" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M201" t="n">
-        <v>6.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N201" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O201" t="n">
-        <v>7.3045</v>
+        <v>0.73</v>
       </c>
       <c r="P201" t="n">
         <v>2</v>
@@ -13953,19 +13953,19 @@
         <v>7</v>
       </c>
       <c r="K202" t="n">
-        <v>7.05</v>
+        <v>0.7</v>
       </c>
       <c r="L202" t="n">
-        <v>7.05</v>
+        <v>0.71</v>
       </c>
       <c r="M202" t="n">
-        <v>8.42</v>
+        <v>0.84</v>
       </c>
       <c r="N202" t="n">
-        <v>3.07</v>
+        <v>0.31</v>
       </c>
       <c r="O202" t="n">
-        <v>6.726999999999999</v>
+        <v>0.6729999999999999</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
@@ -14020,19 +14020,19 @@
         <v>3</v>
       </c>
       <c r="K203" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L203" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N203" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O203" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="P203" t="n">
         <v>2</v>
@@ -14087,19 +14087,19 @@
         <v>5</v>
       </c>
       <c r="K204" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="L204" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M204" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="N204" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O204" t="n">
-        <v>7.793500000000001</v>
+        <v>0.7805000000000001</v>
       </c>
       <c r="P204" t="n">
         <v>3</v>
@@ -14154,19 +14154,19 @@
         <v>8</v>
       </c>
       <c r="K205" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="L205" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M205" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N205" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O205" t="n">
-        <v>7.928999999999999</v>
+        <v>0.7919999999999999</v>
       </c>
       <c r="P205" t="n">
         <v>1</v>
@@ -14221,19 +14221,19 @@
         <v>3</v>
       </c>
       <c r="K206" t="n">
-        <v>9.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L206" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M206" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N206" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O206" t="n">
-        <v>7.545999999999999</v>
+        <v>0.7529999999999999</v>
       </c>
       <c r="P206" t="n">
         <v>1</v>
@@ -14288,19 +14288,19 @@
         <v>5</v>
       </c>
       <c r="K207" t="n">
-        <v>8.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L207" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M207" t="n">
-        <v>6.78</v>
+        <v>0.68</v>
       </c>
       <c r="N207" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O207" t="n">
-        <v>7.220499999999999</v>
+        <v>0.722</v>
       </c>
       <c r="P207" t="n">
         <v>2</v>
@@ -14355,19 +14355,19 @@
         <v>8</v>
       </c>
       <c r="K208" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="L208" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M208" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N208" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O208" t="n">
-        <v>6.5415</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="P208" t="n">
         <v>3</v>
@@ -14422,19 +14422,19 @@
         <v>3</v>
       </c>
       <c r="K209" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L209" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N209" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O209" t="n">
-        <v>7.856</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="P209" t="n">
         <v>3</v>
@@ -14489,19 +14489,19 @@
         <v>5</v>
       </c>
       <c r="K210" t="n">
-        <v>9.27</v>
+        <v>0.93</v>
       </c>
       <c r="L210" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M210" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="N210" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O210" t="n">
-        <v>7.888500000000001</v>
+        <v>0.7905000000000001</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -14556,19 +14556,19 @@
         <v>7</v>
       </c>
       <c r="K211" t="n">
-        <v>8.41</v>
+        <v>0.84</v>
       </c>
       <c r="L211" t="n">
-        <v>7.95</v>
+        <v>0.79</v>
       </c>
       <c r="M211" t="n">
-        <v>8.99</v>
+        <v>0.9</v>
       </c>
       <c r="N211" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O211" t="n">
-        <v>8.059000000000001</v>
+        <v>0.8045</v>
       </c>
       <c r="P211" t="n">
         <v>1</v>
@@ -14623,19 +14623,19 @@
         <v>4</v>
       </c>
       <c r="K212" t="n">
-        <v>9.67</v>
+        <v>0.97</v>
       </c>
       <c r="L212" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M212" t="n">
-        <v>3.85</v>
+        <v>0.39</v>
       </c>
       <c r="N212" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O212" t="n">
-        <v>7.6</v>
+        <v>0.7625000000000001</v>
       </c>
       <c r="P212" t="n">
         <v>3</v>
@@ -14690,19 +14690,19 @@
         <v>6</v>
       </c>
       <c r="K213" t="n">
-        <v>8.800000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="L213" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="M213" t="n">
-        <v>5.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N213" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O213" t="n">
-        <v>7.742</v>
+        <v>0.773</v>
       </c>
       <c r="P213" t="n">
         <v>2</v>
@@ -14757,19 +14757,19 @@
         <v>10</v>
       </c>
       <c r="K214" t="n">
-        <v>7.07</v>
+        <v>0.71</v>
       </c>
       <c r="L214" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M214" t="n">
-        <v>8.43</v>
+        <v>0.84</v>
       </c>
       <c r="N214" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O214" t="n">
-        <v>7.766</v>
+        <v>0.778</v>
       </c>
       <c r="P214" t="n">
         <v>1</v>
@@ -14824,19 +14824,19 @@
         <v>4</v>
       </c>
       <c r="K215" t="n">
-        <v>9.220000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="L215" t="n">
-        <v>9.49</v>
+        <v>0.95</v>
       </c>
       <c r="M215" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="N215" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O215" t="n">
-        <v>7.708500000000001</v>
+        <v>0.772</v>
       </c>
       <c r="P215" t="n">
         <v>1</v>
@@ -14891,19 +14891,19 @@
         <v>6</v>
       </c>
       <c r="K216" t="n">
-        <v>8.140000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L216" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M216" t="n">
-        <v>7.45</v>
+        <v>0.75</v>
       </c>
       <c r="N216" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="O216" t="n">
-        <v>7.644500000000001</v>
+        <v>0.7655</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -14958,19 +14958,19 @@
         <v>10</v>
       </c>
       <c r="K217" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="L217" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M217" t="n">
-        <v>9.94</v>
+        <v>0.99</v>
       </c>
       <c r="N217" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O217" t="n">
-        <v>7.287000000000001</v>
+        <v>0.7295</v>
       </c>
       <c r="P217" t="n">
         <v>3</v>
@@ -15025,19 +15025,19 @@
         <v>3</v>
       </c>
       <c r="K218" t="n">
-        <v>9.869999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="L218" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N218" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O218" t="n">
-        <v>7.817</v>
+        <v>0.782</v>
       </c>
       <c r="P218" t="n">
         <v>1</v>
@@ -15092,19 +15092,19 @@
         <v>5</v>
       </c>
       <c r="K219" t="n">
-        <v>8.84</v>
+        <v>0.88</v>
       </c>
       <c r="L219" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M219" t="n">
-        <v>6.85</v>
+        <v>0.68</v>
       </c>
       <c r="N219" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O219" t="n">
-        <v>7.6835</v>
+        <v>0.7675</v>
       </c>
       <c r="P219" t="n">
         <v>3</v>
@@ -15159,19 +15159,19 @@
         <v>8</v>
       </c>
       <c r="K220" t="n">
-        <v>7.31</v>
+        <v>0.73</v>
       </c>
       <c r="L220" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M220" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="N220" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O220" t="n">
-        <v>7.736999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="P220" t="n">
         <v>2</v>
@@ -15226,19 +15226,19 @@
         <v>3</v>
       </c>
       <c r="K221" t="n">
-        <v>9.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L221" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M221" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N221" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O221" t="n">
-        <v>7.545999999999999</v>
+        <v>0.7529999999999999</v>
       </c>
       <c r="P221" t="n">
         <v>1</v>
@@ -15293,19 +15293,19 @@
         <v>5</v>
       </c>
       <c r="K222" t="n">
-        <v>8.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L222" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M222" t="n">
-        <v>6.78</v>
+        <v>0.68</v>
       </c>
       <c r="N222" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O222" t="n">
-        <v>7.220499999999999</v>
+        <v>0.722</v>
       </c>
       <c r="P222" t="n">
         <v>2</v>
@@ -15360,19 +15360,19 @@
         <v>8</v>
       </c>
       <c r="K223" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="L223" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M223" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N223" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O223" t="n">
-        <v>6.5415</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="P223" t="n">
         <v>3</v>
@@ -15427,19 +15427,19 @@
         <v>3</v>
       </c>
       <c r="K224" t="n">
-        <v>9.630000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="L224" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N224" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O224" t="n">
-        <v>7.745</v>
+        <v>0.7729999999999999</v>
       </c>
       <c r="P224" t="n">
         <v>1</v>
@@ -15494,19 +15494,19 @@
         <v>5</v>
       </c>
       <c r="K225" t="n">
-        <v>8.449999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L225" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M225" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N225" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O225" t="n">
-        <v>7.5365</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="P225" t="n">
         <v>2</v>
@@ -15561,19 +15561,19 @@
         <v>8</v>
       </c>
       <c r="K226" t="n">
-        <v>6.67</v>
+        <v>0.67</v>
       </c>
       <c r="L226" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M226" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N226" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O226" t="n">
-        <v>7.483</v>
+        <v>0.748</v>
       </c>
       <c r="P226" t="n">
         <v>3</v>
@@ -15628,19 +15628,19 @@
         <v>3</v>
       </c>
       <c r="K227" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L227" t="n">
-        <v>9.619999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M227" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N227" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O227" t="n">
-        <v>7.608999999999999</v>
+        <v>0.7589999999999999</v>
       </c>
       <c r="P227" t="n">
         <v>1</v>
@@ -15695,19 +15695,19 @@
         <v>5</v>
       </c>
       <c r="K228" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="L228" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M228" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="N228" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O228" t="n">
-        <v>7.3695</v>
+        <v>0.735</v>
       </c>
       <c r="P228" t="n">
         <v>2</v>
@@ -15762,19 +15762,19 @@
         <v>8</v>
       </c>
       <c r="K229" t="n">
-        <v>6.66</v>
+        <v>0.67</v>
       </c>
       <c r="L229" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M229" t="n">
-        <v>9.31</v>
+        <v>0.93</v>
       </c>
       <c r="N229" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O229" t="n">
-        <v>6.7995</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="P229" t="n">
         <v>3</v>
@@ -15829,19 +15829,19 @@
         <v>3</v>
       </c>
       <c r="K230" t="n">
-        <v>9.73</v>
+        <v>0.97</v>
       </c>
       <c r="L230" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M230" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N230" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O230" t="n">
-        <v>7.775</v>
+        <v>0.776</v>
       </c>
       <c r="P230" t="n">
         <v>1</v>
@@ -15896,19 +15896,19 @@
         <v>5</v>
       </c>
       <c r="K231" t="n">
-        <v>8.609999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="L231" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="M231" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N231" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="O231" t="n">
-        <v>7.5845</v>
+        <v>0.7595</v>
       </c>
       <c r="P231" t="n">
         <v>2</v>
@@ -15963,19 +15963,19 @@
         <v>8</v>
       </c>
       <c r="K232" t="n">
-        <v>6.93</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L232" t="n">
-        <v>7.44</v>
+        <v>0.74</v>
       </c>
       <c r="M232" t="n">
-        <v>8.69</v>
+        <v>0.87</v>
       </c>
       <c r="N232" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="O232" t="n">
-        <v>7.560999999999999</v>
+        <v>0.754</v>
       </c>
       <c r="P232" t="n">
         <v>3</v>
@@ -16030,19 +16030,19 @@
         <v>4</v>
       </c>
       <c r="K233" t="n">
-        <v>7.16</v>
+        <v>0.72</v>
       </c>
       <c r="L233" t="n">
-        <v>7.95</v>
+        <v>0.79</v>
       </c>
       <c r="M233" t="n">
-        <v>5.94</v>
+        <v>0.59</v>
       </c>
       <c r="N233" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O233" t="n">
-        <v>6.345000000000001</v>
+        <v>0.6329999999999999</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -16097,19 +16097,19 @@
         <v>6</v>
       </c>
       <c r="K234" t="n">
-        <v>5.05</v>
+        <v>0.5</v>
       </c>
       <c r="L234" t="n">
-        <v>6.15</v>
+        <v>0.62</v>
       </c>
       <c r="M234" t="n">
-        <v>7.4</v>
+        <v>0.74</v>
       </c>
       <c r="N234" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O234" t="n">
-        <v>5.374</v>
+        <v>0.5375</v>
       </c>
       <c r="P234" t="n">
         <v>2</v>
@@ -16164,19 +16164,19 @@
         <v>8</v>
       </c>
       <c r="K235" t="n">
-        <v>2.93</v>
+        <v>0.29</v>
       </c>
       <c r="L235" t="n">
-        <v>4.36</v>
+        <v>0.44</v>
       </c>
       <c r="M235" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="N235" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O235" t="n">
-        <v>4.825</v>
+        <v>0.482</v>
       </c>
       <c r="P235" t="n">
         <v>3</v>
@@ -16231,19 +16231,19 @@
         <v>4</v>
       </c>
       <c r="K236" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L236" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="N236" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O236" t="n">
-        <v>8.196999999999999</v>
+        <v>0.8194999999999999</v>
       </c>
       <c r="P236" t="n">
         <v>3</v>
@@ -16298,19 +16298,19 @@
         <v>7</v>
       </c>
       <c r="K237" t="n">
-        <v>9.279999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="L237" t="n">
-        <v>8.85</v>
+        <v>0.88</v>
       </c>
       <c r="M237" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="N237" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="O237" t="n">
-        <v>8.700999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="P237" t="n">
         <v>1</v>
@@ -16365,19 +16365,19 @@
         <v>10</v>
       </c>
       <c r="K238" t="n">
-        <v>8.369999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="L238" t="n">
-        <v>7.69</v>
+        <v>0.77</v>
       </c>
       <c r="M238" t="n">
-        <v>9.59</v>
+        <v>0.96</v>
       </c>
       <c r="N238" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O238" t="n">
-        <v>8.388</v>
+        <v>0.841</v>
       </c>
       <c r="P238" t="n">
         <v>2</v>
@@ -16432,19 +16432,19 @@
         <v>5</v>
       </c>
       <c r="K239" t="n">
-        <v>7.85</v>
+        <v>0.79</v>
       </c>
       <c r="L239" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="M239" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N239" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O239" t="n">
-        <v>6.837</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="P239" t="n">
         <v>1</v>
@@ -16499,19 +16499,19 @@
         <v>8</v>
       </c>
       <c r="K240" t="n">
-        <v>5.72</v>
+        <v>0.57</v>
       </c>
       <c r="L240" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="M240" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="N240" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O240" t="n">
-        <v>6.3795</v>
+        <v>0.6359999999999999</v>
       </c>
       <c r="P240" t="n">
         <v>2</v>
@@ -16566,19 +16566,19 @@
         <v>12</v>
       </c>
       <c r="K241" t="n">
-        <v>2.89</v>
+        <v>0.29</v>
       </c>
       <c r="L241" t="n">
-        <v>3.85</v>
+        <v>0.38</v>
       </c>
       <c r="M241" t="n">
-        <v>7.97</v>
+        <v>0.8</v>
       </c>
       <c r="N241" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O241" t="n">
-        <v>4.812</v>
+        <v>0.4805</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -1631,13 +1631,13 @@
         <v>0.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="N18" t="n">
         <v>0.52</v>
       </c>
       <c r="O18" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1698,13 +1698,13 @@
         <v>0.38</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="N19" t="n">
         <v>0.67</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -2100,13 +2100,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="N25" t="n">
         <v>0.52</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7585</v>
+        <v>0.7665</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2435,13 +2435,13 @@
         <v>0.08</v>
       </c>
       <c r="M30" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="N30" t="n">
         <v>0.67</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2725</v>
+        <v>0.2925</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="N31" t="n">
         <v>0.48</v>
       </c>
       <c r="O31" t="n">
-        <v>0.14</v>
+        <v>0.168</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -2837,13 +2837,13 @@
         <v>0.51</v>
       </c>
       <c r="M36" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="N36" t="n">
         <v>0.57</v>
       </c>
       <c r="O36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
@@ -2904,13 +2904,13 @@
         <v>0.19</v>
       </c>
       <c r="M37" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="N37" t="n">
         <v>0.52</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
@@ -3239,13 +3239,13 @@
         <v>0.26</v>
       </c>
       <c r="M42" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="N42" t="n">
         <v>0.57</v>
       </c>
       <c r="O42" t="n">
-        <v>0.3825000000000001</v>
+        <v>0.3965</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
@@ -3306,13 +3306,13 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="N43" t="n">
         <v>0.52</v>
       </c>
       <c r="O43" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="N47" t="n">
         <v>0.67</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2445</v>
+        <v>0.2645</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3641,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="N48" t="n">
         <v>0.52</v>
       </c>
       <c r="O48" t="n">
-        <v>0.168</v>
+        <v>0.194</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="N49" t="n">
         <v>0.4</v>
       </c>
       <c r="O49" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
@@ -4579,13 +4579,13 @@
         <v>0.54</v>
       </c>
       <c r="M62" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="N62" t="n">
         <v>0.46</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4646,13 +4646,13 @@
         <v>0.23</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="N63" t="n">
         <v>0.67</v>
       </c>
       <c r="O63" t="n">
-        <v>0.3560000000000001</v>
+        <v>0.374</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="N64" t="n">
         <v>0.52</v>
       </c>
       <c r="O64" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
       <c r="P64" t="n">
         <v>3</v>
@@ -5517,13 +5517,13 @@
         <v>0.13</v>
       </c>
       <c r="M76" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="N76" t="n">
         <v>0.57</v>
       </c>
       <c r="O76" t="n">
-        <v>0.358</v>
+        <v>0.37</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
@@ -5718,13 +5718,13 @@
         <v>0.38</v>
       </c>
       <c r="M79" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="N79" t="n">
         <v>0.52</v>
       </c>
       <c r="O79" t="n">
-        <v>0.447</v>
+        <v>0.461</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
@@ -6053,13 +6053,13 @@
         <v>0.54</v>
       </c>
       <c r="M84" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="N84" t="n">
         <v>0.67</v>
       </c>
       <c r="O84" t="n">
-        <v>0.6035</v>
+        <v>0.6175</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
@@ -6120,13 +6120,13 @@
         <v>0.13</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N85" t="n">
         <v>0.32</v>
       </c>
       <c r="O85" t="n">
-        <v>0.1235</v>
+        <v>0.1355</v>
       </c>
       <c r="P85" t="n">
         <v>3</v>
@@ -7460,13 +7460,13 @@
         <v>0.64</v>
       </c>
       <c r="M105" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N105" t="n">
         <v>0.46</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6359999999999999</v>
+        <v>0.6379999999999999</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7527,13 +7527,13 @@
         <v>0.38</v>
       </c>
       <c r="M106" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="N106" t="n">
         <v>0.67</v>
       </c>
       <c r="O106" t="n">
-        <v>0.4805</v>
+        <v>0.4965000000000001</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -7594,13 +7594,13 @@
         <v>0.64</v>
       </c>
       <c r="M107" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="N107" t="n">
         <v>0.46</v>
       </c>
       <c r="O107" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
@@ -7661,13 +7661,13 @@
         <v>0.51</v>
       </c>
       <c r="M108" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="N108" t="n">
         <v>0.57</v>
       </c>
       <c r="O108" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="P108" t="n">
         <v>2</v>
@@ -7728,13 +7728,13 @@
         <v>0.38</v>
       </c>
       <c r="M109" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="N109" t="n">
         <v>0.67</v>
       </c>
       <c r="O109" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
@@ -7862,13 +7862,13 @@
         <v>0.38</v>
       </c>
       <c r="M111" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="N111" t="n">
         <v>0.57</v>
       </c>
       <c r="O111" t="n">
-        <v>0.5105000000000001</v>
+        <v>0.5245</v>
       </c>
       <c r="P111" t="n">
         <v>2</v>
@@ -7929,13 +7929,13 @@
         <v>0.23</v>
       </c>
       <c r="M112" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="N112" t="n">
         <v>0.67</v>
       </c>
       <c r="O112" t="n">
-        <v>0.399</v>
+        <v>0.413</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
@@ -7996,13 +7996,13 @@
         <v>0.64</v>
       </c>
       <c r="M113" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="N113" t="n">
         <v>0.46</v>
       </c>
       <c r="O113" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -8063,13 +8063,13 @@
         <v>0.51</v>
       </c>
       <c r="M114" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="N114" t="n">
         <v>0.57</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.6190000000000001</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -8130,13 +8130,13 @@
         <v>0.38</v>
       </c>
       <c r="M115" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="N115" t="n">
         <v>0.67</v>
       </c>
       <c r="O115" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265000000000001</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8197,13 +8197,13 @@
         <v>0.74</v>
       </c>
       <c r="M116" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="N116" t="n">
         <v>0.46</v>
       </c>
       <c r="O116" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
@@ -8264,13 +8264,13 @@
         <v>0.64</v>
       </c>
       <c r="M117" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="N117" t="n">
         <v>0.57</v>
       </c>
       <c r="O117" t="n">
-        <v>0.6835</v>
+        <v>0.6955</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
@@ -8331,13 +8331,13 @@
         <v>0.54</v>
       </c>
       <c r="M118" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="N118" t="n">
         <v>0.67</v>
       </c>
       <c r="O118" t="n">
-        <v>0.6075</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
@@ -8465,13 +8465,13 @@
         <v>0.51</v>
       </c>
       <c r="M120" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="N120" t="n">
         <v>0.57</v>
       </c>
       <c r="O120" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="P120" t="n">
         <v>2</v>
@@ -8532,13 +8532,13 @@
         <v>0.38</v>
       </c>
       <c r="M121" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="N121" t="n">
         <v>0.67</v>
       </c>
       <c r="O121" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255000000000001</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
@@ -9939,13 +9939,13 @@
         <v>0.13</v>
       </c>
       <c r="M142" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="N142" t="n">
         <v>0.57</v>
       </c>
       <c r="O142" t="n">
-        <v>0.3130000000000001</v>
+        <v>0.327</v>
       </c>
       <c r="P142" t="n">
         <v>3</v>
@@ -10877,13 +10877,13 @@
         <v>0.64</v>
       </c>
       <c r="M156" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="N156" t="n">
         <v>0.46</v>
       </c>
       <c r="O156" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
       <c r="P156" t="n">
         <v>2</v>
@@ -10944,13 +10944,13 @@
         <v>0.51</v>
       </c>
       <c r="M157" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="N157" t="n">
         <v>0.57</v>
       </c>
       <c r="O157" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="P157" t="n">
         <v>3</v>
@@ -11078,13 +11078,13 @@
         <v>0.51</v>
       </c>
       <c r="M159" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="N159" t="n">
         <v>0.57</v>
       </c>
       <c r="O159" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="P159" t="n">
         <v>2</v>
@@ -11145,13 +11145,13 @@
         <v>0.38</v>
       </c>
       <c r="M160" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="N160" t="n">
         <v>0.67</v>
       </c>
       <c r="O160" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255000000000001</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
@@ -16170,13 +16170,13 @@
         <v>0.44</v>
       </c>
       <c r="M235" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="N235" t="n">
         <v>0.46</v>
       </c>
       <c r="O235" t="n">
-        <v>0.482</v>
+        <v>0.484</v>
       </c>
       <c r="P235" t="n">
         <v>3</v>
@@ -16505,13 +16505,13 @@
         <v>0.64</v>
       </c>
       <c r="M240" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="N240" t="n">
         <v>0.46</v>
       </c>
       <c r="O240" t="n">
-        <v>0.6359999999999999</v>
+        <v>0.6379999999999999</v>
       </c>
       <c r="P240" t="n">
         <v>2</v>
@@ -16572,13 +16572,13 @@
         <v>0.38</v>
       </c>
       <c r="M241" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="N241" t="n">
         <v>0.67</v>
       </c>
       <c r="O241" t="n">
-        <v>0.4805</v>
+        <v>0.4985000000000001</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -760,13 +760,13 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="N5" t="n">
         <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8194999999999999</v>
+        <v>0.7794999999999999</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -827,13 +827,13 @@
         <v>0.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="N6" t="n">
         <v>0.64</v>
       </c>
       <c r="O6" t="n">
-        <v>0.869</v>
+        <v>0.839</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -894,13 +894,13 @@
         <v>0.77</v>
       </c>
       <c r="M7" t="n">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>0.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0.841</v>
+        <v>0.8109999999999999</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -2368,13 +2368,13 @@
         <v>0.44</v>
       </c>
       <c r="M29" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="N29" t="n">
         <v>0.46</v>
       </c>
       <c r="O29" t="n">
-        <v>0.468</v>
+        <v>0.484</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2435,13 +2435,13 @@
         <v>0.08</v>
       </c>
       <c r="M30" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="N30" t="n">
         <v>0.67</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2925</v>
+        <v>0.3065</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="N31" t="n">
         <v>0.48</v>
       </c>
       <c r="O31" t="n">
-        <v>0.168</v>
+        <v>0.188</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -2569,13 +2569,13 @@
         <v>0.26</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="N32" t="n">
         <v>0.57</v>
       </c>
       <c r="O32" t="n">
-        <v>0.4675</v>
+        <v>0.4815</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2636,13 +2636,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="N33" t="n">
         <v>0.52</v>
       </c>
       <c r="O33" t="n">
-        <v>0.192</v>
+        <v>0.212</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2703,13 +2703,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="N34" t="n">
         <v>0.4</v>
       </c>
       <c r="O34" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="N47" t="n">
         <v>0.67</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2645</v>
+        <v>0.2785</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3641,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="N48" t="n">
         <v>0.52</v>
       </c>
       <c r="O48" t="n">
-        <v>0.194</v>
+        <v>0.212</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="N49" t="n">
         <v>0.4</v>
       </c>
       <c r="O49" t="n">
-        <v>0.108</v>
+        <v>0.132</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
@@ -3976,13 +3976,13 @@
         <v>0.13</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="N53" t="n">
         <v>0.57</v>
       </c>
       <c r="O53" t="n">
-        <v>0.392</v>
+        <v>0.406</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4043,13 +4043,13 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="N54" t="n">
         <v>0.57</v>
       </c>
       <c r="O54" t="n">
-        <v>0.1945</v>
+        <v>0.2145</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
@@ -4110,13 +4110,13 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="N55" t="n">
         <v>0.4</v>
       </c>
       <c r="O55" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
@@ -4378,13 +4378,13 @@
         <v>0.96</v>
       </c>
       <c r="M59" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="N59" t="n">
         <v>0.15</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7575</v>
+        <v>0.7135</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
@@ -4445,13 +4445,13 @@
         <v>0.83</v>
       </c>
       <c r="M60" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N60" t="n">
         <v>0.15</v>
       </c>
       <c r="O60" t="n">
-        <v>0.728</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="P60" t="n">
         <v>2</v>
@@ -4512,13 +4512,13 @@
         <v>0.64</v>
       </c>
       <c r="M61" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="N61" t="n">
         <v>0.46</v>
       </c>
       <c r="O61" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="P61" t="n">
         <v>3</v>
@@ -6991,13 +6991,13 @@
         <v>0.9</v>
       </c>
       <c r="M98" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="N98" t="n">
         <v>0.35</v>
       </c>
       <c r="O98" t="n">
-        <v>0.7775</v>
+        <v>0.7394999999999999</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7058,13 +7058,13 @@
         <v>0.74</v>
       </c>
       <c r="M99" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="N99" t="n">
         <v>0.76</v>
       </c>
       <c r="O99" t="n">
-        <v>0.787</v>
+        <v>0.757</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7125,13 +7125,13 @@
         <v>0.54</v>
       </c>
       <c r="M100" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="N100" t="n">
         <v>0.67</v>
       </c>
       <c r="O100" t="n">
-        <v>0.6465000000000001</v>
+        <v>0.6165</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
@@ -7393,13 +7393,13 @@
         <v>0.83</v>
       </c>
       <c r="M104" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="N104" t="n">
         <v>0.35</v>
       </c>
       <c r="O104" t="n">
-        <v>0.704</v>
+        <v>0.722</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -7460,13 +7460,13 @@
         <v>0.64</v>
       </c>
       <c r="M105" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="N105" t="n">
         <v>0.46</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6379999999999999</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7527,13 +7527,13 @@
         <v>0.38</v>
       </c>
       <c r="M106" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="N106" t="n">
         <v>0.67</v>
       </c>
       <c r="O106" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125000000000001</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -10609,13 +10609,13 @@
         <v>0.83</v>
       </c>
       <c r="M152" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="N152" t="n">
         <v>0.35</v>
       </c>
       <c r="O152" t="n">
-        <v>0.717</v>
+        <v>0.735</v>
       </c>
       <c r="P152" t="n">
         <v>1</v>
@@ -10676,13 +10676,13 @@
         <v>0.64</v>
       </c>
       <c r="M153" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="N153" t="n">
         <v>0.76</v>
       </c>
       <c r="O153" t="n">
-        <v>0.706</v>
+        <v>0.72</v>
       </c>
       <c r="P153" t="n">
         <v>2</v>
@@ -10743,13 +10743,13 @@
         <v>0.38</v>
       </c>
       <c r="M154" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="N154" t="n">
         <v>0.67</v>
       </c>
       <c r="O154" t="n">
-        <v>0.5315000000000001</v>
+        <v>0.5455000000000001</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -12619,13 +12619,13 @@
         <v>0.95</v>
       </c>
       <c r="M182" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="N182" t="n">
         <v>0.29</v>
       </c>
       <c r="O182" t="n">
-        <v>0.7749999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="P182" t="n">
         <v>1</v>
@@ -12686,13 +12686,13 @@
         <v>0.85</v>
       </c>
       <c r="M183" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="N183" t="n">
         <v>0.5</v>
       </c>
       <c r="O183" t="n">
-        <v>0.7685</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
@@ -12753,13 +12753,13 @@
         <v>0.64</v>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="N184" t="n">
         <v>0.85</v>
       </c>
       <c r="O184" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7064999999999999</v>
       </c>
       <c r="P184" t="n">
         <v>3</v>
@@ -13624,13 +13624,13 @@
         <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="N197" t="n">
         <v>0.22</v>
       </c>
       <c r="O197" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="P197" t="n">
         <v>3</v>
@@ -13691,13 +13691,13 @@
         <v>0.9</v>
       </c>
       <c r="M198" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N198" t="n">
         <v>0.35</v>
       </c>
       <c r="O198" t="n">
-        <v>0.7975</v>
+        <v>0.7615</v>
       </c>
       <c r="P198" t="n">
         <v>2</v>
@@ -13758,13 +13758,13 @@
         <v>0.74</v>
       </c>
       <c r="M199" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="N199" t="n">
         <v>0.76</v>
       </c>
       <c r="O199" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.791</v>
       </c>
       <c r="P199" t="n">
         <v>1</v>
@@ -14026,16 +14026,16 @@
         <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="N203" t="n">
         <v>0.22</v>
       </c>
       <c r="O203" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="P203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q203" t="n">
         <v>0.7331555670404936</v>
@@ -14093,16 +14093,16 @@
         <v>0.9</v>
       </c>
       <c r="M204" t="n">
-        <v>0.7</v>
+        <v>0.52</v>
       </c>
       <c r="N204" t="n">
         <v>0.35</v>
       </c>
       <c r="O204" t="n">
-        <v>0.7805000000000001</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="P204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q204" t="n">
         <v>1.221925945067489</v>
@@ -14160,13 +14160,13 @@
         <v>0.74</v>
       </c>
       <c r="M205" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="N205" t="n">
         <v>0.76</v>
       </c>
       <c r="O205" t="n">
-        <v>0.7919999999999999</v>
+        <v>0.762</v>
       </c>
       <c r="P205" t="n">
         <v>1</v>
@@ -14830,13 +14830,13 @@
         <v>0.95</v>
       </c>
       <c r="M215" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="N215" t="n">
         <v>0.29</v>
       </c>
       <c r="O215" t="n">
-        <v>0.772</v>
+        <v>0.7300000000000001</v>
       </c>
       <c r="P215" t="n">
         <v>1</v>
@@ -14897,13 +14897,13 @@
         <v>0.85</v>
       </c>
       <c r="M216" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="N216" t="n">
         <v>0.5</v>
       </c>
       <c r="O216" t="n">
-        <v>0.7655</v>
+        <v>0.7294999999999999</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -14964,13 +14964,13 @@
         <v>0.64</v>
       </c>
       <c r="M217" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="N217" t="n">
         <v>0.85</v>
       </c>
       <c r="O217" t="n">
-        <v>0.7295</v>
+        <v>0.7015</v>
       </c>
       <c r="P217" t="n">
         <v>3</v>
@@ -15031,16 +15031,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="N218" t="n">
         <v>0.22</v>
       </c>
       <c r="O218" t="n">
-        <v>0.782</v>
+        <v>0.7380000000000001</v>
       </c>
       <c r="P218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q218" t="n">
         <v>0.8072116849233715</v>
@@ -15098,13 +15098,13 @@
         <v>0.9</v>
       </c>
       <c r="M219" t="n">
-        <v>0.68</v>
+        <v>0.49</v>
       </c>
       <c r="N219" t="n">
         <v>0.35</v>
       </c>
       <c r="O219" t="n">
-        <v>0.7675</v>
+        <v>0.7294999999999999</v>
       </c>
       <c r="P219" t="n">
         <v>3</v>
@@ -15165,16 +15165,16 @@
         <v>0.74</v>
       </c>
       <c r="M220" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="N220" t="n">
         <v>0.76</v>
       </c>
       <c r="O220" t="n">
-        <v>0.772</v>
+        <v>0.742</v>
       </c>
       <c r="P220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q220" t="n">
         <v>2.152564493128991</v>
@@ -16237,13 +16237,13 @@
         <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="N236" t="n">
         <v>0.29</v>
       </c>
       <c r="O236" t="n">
-        <v>0.8194999999999999</v>
+        <v>0.7794999999999999</v>
       </c>
       <c r="P236" t="n">
         <v>3</v>
@@ -16304,13 +16304,13 @@
         <v>0.88</v>
       </c>
       <c r="M237" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="N237" t="n">
         <v>0.64</v>
       </c>
       <c r="O237" t="n">
-        <v>0.869</v>
+        <v>0.839</v>
       </c>
       <c r="P237" t="n">
         <v>1</v>
@@ -16371,13 +16371,13 @@
         <v>0.77</v>
       </c>
       <c r="M238" t="n">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N238" t="n">
         <v>0.85</v>
       </c>
       <c r="O238" t="n">
-        <v>0.841</v>
+        <v>0.8109999999999999</v>
       </c>
       <c r="P238" t="n">
         <v>2</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -766,7 +766,7 @@
         <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7794999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -900,7 +900,7 @@
         <v>0.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1101,7 +1101,7 @@
         <v>0.93</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1570,7 +1570,7 @@
         <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6994999999999999</v>
+        <v>0.6995</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         <v>0.64</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8119999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1905,7 +1905,7 @@
         <v>0.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -1972,7 +1972,7 @@
         <v>0.22</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -2039,7 +2039,7 @@
         <v>0.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2240,7 +2240,7 @@
         <v>0.46</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -2776,7 +2776,7 @@
         <v>0.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6994999999999999</v>
+        <v>0.6995</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -3044,7 +3044,7 @@
         <v>0.52</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
@@ -3446,7 +3446,7 @@
         <v>0.67</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3848,7 +3848,7 @@
         <v>0.76</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0.67</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -4183,7 +4183,7 @@
         <v>0.15</v>
       </c>
       <c r="O56" t="n">
-        <v>0.6724999999999999</v>
+        <v>0.6725</v>
       </c>
       <c r="P56" t="n">
         <v>3</v>
@@ -4317,7 +4317,7 @@
         <v>0.15</v>
       </c>
       <c r="O58" t="n">
-        <v>0.6854999999999999</v>
+        <v>0.6855</v>
       </c>
       <c r="P58" t="n">
         <v>2</v>
@@ -4585,7 +4585,7 @@
         <v>0.46</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5549999999999999</v>
+        <v>0.555</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4853,7 +4853,7 @@
         <v>0.76</v>
       </c>
       <c r="O66" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -4920,7 +4920,7 @@
         <v>0.93</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7105000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
@@ -5456,7 +5456,7 @@
         <v>0.31</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5005000000000001</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5590,7 +5590,7 @@
         <v>0.22</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -5657,7 +5657,7 @@
         <v>0.46</v>
       </c>
       <c r="O78" t="n">
-        <v>0.7370000000000001</v>
+        <v>0.737</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
@@ -5791,7 +5791,7 @@
         <v>0.29</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -6193,7 +6193,7 @@
         <v>0.15</v>
       </c>
       <c r="O86" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -6327,7 +6327,7 @@
         <v>0.57</v>
       </c>
       <c r="O88" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6461,7 +6461,7 @@
         <v>0.57</v>
       </c>
       <c r="O90" t="n">
-        <v>0.7174999999999999</v>
+        <v>0.7175</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         <v>0.35</v>
       </c>
       <c r="O92" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P92" t="n">
         <v>2</v>
@@ -6796,7 +6796,7 @@
         <v>0.35</v>
       </c>
       <c r="O95" t="n">
-        <v>0.6789999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6997,7 +6997,7 @@
         <v>0.35</v>
       </c>
       <c r="O98" t="n">
-        <v>0.7394999999999999</v>
+        <v>0.7395</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7466,7 +7466,7 @@
         <v>0.46</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7533,7 +7533,7 @@
         <v>0.67</v>
       </c>
       <c r="O106" t="n">
-        <v>0.5125000000000001</v>
+        <v>0.5125</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -7801,7 +7801,7 @@
         <v>0.46</v>
       </c>
       <c r="O110" t="n">
-        <v>0.5920000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
@@ -8002,7 +8002,7 @@
         <v>0.46</v>
       </c>
       <c r="O113" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -8069,7 +8069,7 @@
         <v>0.57</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6190000000000001</v>
+        <v>0.619</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -8136,7 +8136,7 @@
         <v>0.67</v>
       </c>
       <c r="O115" t="n">
-        <v>0.5265000000000001</v>
+        <v>0.5265</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8538,7 +8538,7 @@
         <v>0.67</v>
       </c>
       <c r="O121" t="n">
-        <v>0.5255000000000001</v>
+        <v>0.5255</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
@@ -8672,7 +8672,7 @@
         <v>0.46</v>
       </c>
       <c r="O123" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
       <c r="P123" t="n">
         <v>2</v>
@@ -9074,7 +9074,7 @@
         <v>0.46</v>
       </c>
       <c r="O129" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
       <c r="P129" t="n">
         <v>2</v>
@@ -9275,7 +9275,7 @@
         <v>0.76</v>
       </c>
       <c r="O132" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="P132" t="n">
         <v>1</v>
@@ -9342,7 +9342,7 @@
         <v>0.67</v>
       </c>
       <c r="O133" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
@@ -9476,7 +9476,7 @@
         <v>0.46</v>
       </c>
       <c r="O135" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="P135" t="n">
         <v>2</v>
@@ -9811,7 +9811,7 @@
         <v>0.15</v>
       </c>
       <c r="O140" t="n">
-        <v>0.6034999999999999</v>
+        <v>0.6035</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
@@ -10012,7 +10012,7 @@
         <v>0.15</v>
       </c>
       <c r="O143" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
       <c r="P143" t="n">
         <v>2</v>
@@ -10213,7 +10213,7 @@
         <v>0.64</v>
       </c>
       <c r="O146" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7375</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0.35</v>
       </c>
       <c r="O149" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P149" t="n">
         <v>1</v>
@@ -10749,7 +10749,7 @@
         <v>0.67</v>
       </c>
       <c r="O154" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -10816,7 +10816,7 @@
         <v>0.15</v>
       </c>
       <c r="O155" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="P155" t="n">
         <v>1</v>
@@ -11151,7 +11151,7 @@
         <v>0.67</v>
       </c>
       <c r="O160" t="n">
-        <v>0.5255000000000001</v>
+        <v>0.5255</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
@@ -11486,7 +11486,7 @@
         <v>0.46</v>
       </c>
       <c r="O165" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="P165" t="n">
         <v>2</v>
@@ -11620,7 +11620,7 @@
         <v>0.22</v>
       </c>
       <c r="O167" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P167" t="n">
         <v>2</v>
@@ -11687,7 +11687,7 @@
         <v>0.35</v>
       </c>
       <c r="O168" t="n">
-        <v>0.7825000000000001</v>
+        <v>0.7825</v>
       </c>
       <c r="P168" t="n">
         <v>3</v>
@@ -11955,7 +11955,7 @@
         <v>0.46</v>
       </c>
       <c r="O172" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="P172" t="n">
         <v>3</v>
@@ -12022,7 +12022,7 @@
         <v>0.22</v>
       </c>
       <c r="O173" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="P173" t="n">
         <v>1</v>
@@ -12156,7 +12156,7 @@
         <v>0.46</v>
       </c>
       <c r="O175" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="P175" t="n">
         <v>3</v>
@@ -12223,7 +12223,7 @@
         <v>0.22</v>
       </c>
       <c r="O176" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P176" t="n">
         <v>1</v>
@@ -12491,7 +12491,7 @@
         <v>0.5</v>
       </c>
       <c r="O180" t="n">
-        <v>0.7699999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="P180" t="n">
         <v>2</v>
@@ -12558,7 +12558,7 @@
         <v>0.85</v>
       </c>
       <c r="O181" t="n">
-        <v>0.7749999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
@@ -12692,7 +12692,7 @@
         <v>0.5</v>
       </c>
       <c r="O183" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
@@ -12759,7 +12759,7 @@
         <v>0.85</v>
       </c>
       <c r="O184" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="P184" t="n">
         <v>3</v>
@@ -13161,7 +13161,7 @@
         <v>0.15</v>
       </c>
       <c r="O190" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
@@ -13228,7 +13228,7 @@
         <v>0.22</v>
       </c>
       <c r="O191" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="P191" t="n">
         <v>1</v>
@@ -13965,7 +13965,7 @@
         <v>0.31</v>
       </c>
       <c r="O202" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
@@ -14233,7 +14233,7 @@
         <v>0.22</v>
       </c>
       <c r="O206" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="P206" t="n">
         <v>1</v>
@@ -14367,7 +14367,7 @@
         <v>0.46</v>
       </c>
       <c r="O208" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P208" t="n">
         <v>3</v>
@@ -14434,7 +14434,7 @@
         <v>0.22</v>
       </c>
       <c r="O209" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P209" t="n">
         <v>3</v>
@@ -14501,7 +14501,7 @@
         <v>0.35</v>
       </c>
       <c r="O210" t="n">
-        <v>0.7905000000000001</v>
+        <v>0.7905</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -14635,7 +14635,7 @@
         <v>0.29</v>
       </c>
       <c r="O212" t="n">
-        <v>0.7625000000000001</v>
+        <v>0.7625</v>
       </c>
       <c r="P212" t="n">
         <v>3</v>
@@ -14836,7 +14836,7 @@
         <v>0.29</v>
       </c>
       <c r="O215" t="n">
-        <v>0.7300000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="P215" t="n">
         <v>1</v>
@@ -14903,7 +14903,7 @@
         <v>0.5</v>
       </c>
       <c r="O216" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -15037,7 +15037,7 @@
         <v>0.22</v>
       </c>
       <c r="O218" t="n">
-        <v>0.7380000000000001</v>
+        <v>0.738</v>
       </c>
       <c r="P218" t="n">
         <v>2</v>
@@ -15104,7 +15104,7 @@
         <v>0.35</v>
       </c>
       <c r="O219" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P219" t="n">
         <v>3</v>
@@ -15238,7 +15238,7 @@
         <v>0.22</v>
       </c>
       <c r="O221" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="P221" t="n">
         <v>1</v>
@@ -15372,7 +15372,7 @@
         <v>0.46</v>
       </c>
       <c r="O223" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P223" t="n">
         <v>3</v>
@@ -15439,7 +15439,7 @@
         <v>0.22</v>
       </c>
       <c r="O224" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="P224" t="n">
         <v>1</v>
@@ -15640,7 +15640,7 @@
         <v>0.22</v>
       </c>
       <c r="O227" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="P227" t="n">
         <v>1</v>
@@ -15774,7 +15774,7 @@
         <v>0.46</v>
       </c>
       <c r="O229" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="P229" t="n">
         <v>3</v>
@@ -16042,7 +16042,7 @@
         <v>0.15</v>
       </c>
       <c r="O233" t="n">
-        <v>0.6329999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -16243,7 +16243,7 @@
         <v>0.29</v>
       </c>
       <c r="O236" t="n">
-        <v>0.7794999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="P236" t="n">
         <v>3</v>
@@ -16377,7 +16377,7 @@
         <v>0.85</v>
       </c>
       <c r="O238" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="P238" t="n">
         <v>2</v>
@@ -16444,7 +16444,7 @@
         <v>0.15</v>
       </c>
       <c r="O239" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="P239" t="n">
         <v>1</v>
@@ -16511,7 +16511,7 @@
         <v>0.46</v>
       </c>
       <c r="O240" t="n">
-        <v>0.6379999999999999</v>
+        <v>0.638</v>
       </c>
       <c r="P240" t="n">
         <v>2</v>
@@ -16578,7 +16578,7 @@
         <v>0.67</v>
       </c>
       <c r="O241" t="n">
-        <v>0.4985000000000001</v>
+        <v>0.4985</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>

--- a/workbooks/ground_truth/ground_truth_shower.xlsx
+++ b/workbooks/ground_truth/ground_truth_shower.xlsx
@@ -571,10 +571,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7164929405168461</v>
+        <v>0.6746975189866966</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1361336586982008</v>
+        <v>0.1281925286074724</v>
       </c>
       <c r="S2" t="n">
         <v>4.5</v>
@@ -638,10 +638,10 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.19415490086141</v>
+        <v>1.124495864977828</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2268894311636679</v>
+        <v>0.2136542143457873</v>
       </c>
       <c r="S3" t="n">
         <v>7.5</v>
@@ -687,7 +687,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="L4" t="n">
         <v>0.85</v>
@@ -699,16 +699,16 @@
         <v>0.76</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7875</v>
+        <v>0.7845</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.910647841378256</v>
+        <v>1.799193383964524</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3630230898618687</v>
+        <v>0.3418467429532597</v>
       </c>
       <c r="S4" t="n">
         <v>12</v>
@@ -772,10 +772,10 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6368826137927519</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="S5" t="n">
         <v>6</v>
@@ -839,10 +839,10 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.114544574137316</v>
+        <v>1.02538100820633</v>
       </c>
       <c r="R6" t="n">
-        <v>0.21176346908609</v>
+        <v>0.1948223915592028</v>
       </c>
       <c r="S6" t="n">
         <v>10.5</v>
@@ -906,10 +906,10 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274325</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -973,10 +973,10 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.19415490086141</v>
+        <v>1.124495864977828</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268894311636679</v>
+        <v>0.2136542143457873</v>
       </c>
       <c r="S8" t="n">
         <v>7.5</v>
@@ -1022,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="L9" t="n">
         <v>0.85</v>
@@ -1034,16 +1034,16 @@
         <v>0.76</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8195</v>
+        <v>0.8165</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.910647841378256</v>
+        <v>1.799193383964524</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3630230898618687</v>
+        <v>0.3418467429532597</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1089,7 +1089,7 @@
         <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L10" t="n">
         <v>0.6899999999999999</v>
@@ -1101,16 +1101,16 @@
         <v>0.93</v>
       </c>
       <c r="O10" t="n">
-        <v>0.751</v>
+        <v>0.748</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.865971762067384</v>
+        <v>2.698790075946786</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5445346347928031</v>
+        <v>0.5127701144298894</v>
       </c>
       <c r="S10" t="n">
         <v>18</v>
@@ -1174,10 +1174,10 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S11" t="n">
         <v>12.5</v>
@@ -1241,10 +1241,10 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85757429022886</v>
+        <v>1.708968347010551</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3529391151434834</v>
+        <v>0.3247039859320047</v>
       </c>
       <c r="S12" t="n">
         <v>17.5</v>
@@ -1308,10 +1308,10 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6536775574698</v>
+        <v>2.441383352872215</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5041987359192619</v>
+        <v>0.4638628370457208</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1375,10 +1375,10 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.79610326724094</v>
+        <v>0.7324150058616647</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1512596207757786</v>
+        <v>0.1391588511137163</v>
       </c>
       <c r="S14" t="n">
         <v>7.5</v>
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.114544574137316</v>
+        <v>1.025381008206331</v>
       </c>
       <c r="R15" t="n">
-        <v>0.21176346908609</v>
+        <v>0.1948223915592029</v>
       </c>
       <c r="S15" t="n">
         <v>10.5</v>
@@ -1509,10 +1509,10 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -1558,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L17" t="n">
         <v>0.77</v>
@@ -1570,16 +1570,16 @@
         <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6995</v>
+        <v>0.6965</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38830980172282</v>
+        <v>2.248991729955655</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4273084286915745</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -1643,10 +1643,10 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.58246470258423</v>
+        <v>3.373487594933482</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6806682934910037</v>
+        <v>0.6409626430373616</v>
       </c>
       <c r="S18" t="n">
         <v>22.5</v>
@@ -1710,10 +1710,10 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.776619603445639</v>
+        <v>4.49798345991131</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9075577246546715</v>
+        <v>0.854616857383149</v>
       </c>
       <c r="S19" t="n">
         <v>30</v>
@@ -1777,10 +1777,10 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.19415490086141</v>
+        <v>1.124495864977828</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268894311636679</v>
+        <v>0.2136542143457873</v>
       </c>
       <c r="S20" t="n">
         <v>7.5</v>
@@ -1844,10 +1844,10 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.671816861205974</v>
+        <v>1.574294210968959</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3176452036291351</v>
+        <v>0.2991159000841022</v>
       </c>
       <c r="S21" t="n">
         <v>10.5</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L22" t="n">
         <v>0.77</v>
@@ -1905,16 +1905,16 @@
         <v>0.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.38830980172282</v>
+        <v>2.248991729955656</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4273084286915746</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -1978,10 +1978,10 @@
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7164929405168461</v>
+        <v>0.6746975189866966</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1361336586982008</v>
+        <v>0.1281925286074724</v>
       </c>
       <c r="S23" t="n">
         <v>4.5</v>
@@ -2045,10 +2045,10 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.432985881033692</v>
+        <v>1.349395037973393</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2722673173964015</v>
+        <v>0.2563850572149447</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -2112,10 +2112,10 @@
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.149478821550538</v>
+        <v>2.02409255696009</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4084009760946022</v>
+        <v>0.3845775858224171</v>
       </c>
       <c r="S25" t="n">
         <v>13.5</v>
@@ -2179,10 +2179,10 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S26" t="n">
         <v>12.5</v>
@@ -2246,10 +2246,10 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -2295,7 +2295,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L28" t="n">
         <v>0.38</v>
@@ -2307,16 +2307,16 @@
         <v>0.67</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5445</v>
+        <v>0.5505</v>
       </c>
       <c r="P28" t="n">
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S28" t="n">
         <v>30</v>
@@ -2380,10 +2380,10 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.458178296549263</v>
+        <v>4.198117895917224</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8470538763443599</v>
+        <v>0.7976424002242726</v>
       </c>
       <c r="S29" t="n">
         <v>28</v>
@@ -2447,10 +2447,10 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.687267444823894</v>
+        <v>6.297176843875836</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27058081451654</v>
+        <v>1.196463600336409</v>
       </c>
       <c r="S30" t="n">
         <v>42</v>
@@ -2514,10 +2514,10 @@
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.916356593098525</v>
+        <v>8.396235791834448</v>
       </c>
       <c r="R31" t="n">
-        <v>1.69410775268872</v>
+        <v>1.595284800448545</v>
       </c>
       <c r="S31" t="n">
         <v>56</v>
@@ -2563,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="L32" t="n">
         <v>0.26</v>
@@ -2575,16 +2575,16 @@
         <v>0.57</v>
       </c>
       <c r="O32" t="n">
-        <v>0.4815</v>
+        <v>0.4875</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71514858045772</v>
+        <v>3.417936694021102</v>
       </c>
       <c r="R32" t="n">
-        <v>0.7058782302869667</v>
+        <v>0.6494079718640094</v>
       </c>
       <c r="S32" t="n">
         <v>35</v>
@@ -2630,7 +2630,7 @@
         <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2642,16 +2642,16 @@
         <v>0.52</v>
       </c>
       <c r="O33" t="n">
-        <v>0.212</v>
+        <v>0.218</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.572722870686579</v>
+        <v>5.126905041031653</v>
       </c>
       <c r="R33" t="n">
-        <v>1.05881734543045</v>
+        <v>0.974111957796014</v>
       </c>
       <c r="S33" t="n">
         <v>52.5</v>
@@ -2715,10 +2715,10 @@
         <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.687267444823896</v>
+        <v>6.152286049237984</v>
       </c>
       <c r="R34" t="n">
-        <v>1.27058081451654</v>
+        <v>1.168934349355217</v>
       </c>
       <c r="S34" t="n">
         <v>63</v>
@@ -2764,7 +2764,7 @@
         <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L35" t="n">
         <v>0.77</v>
@@ -2776,16 +2776,16 @@
         <v>0.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6995</v>
+        <v>0.6965</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.38830980172282</v>
+        <v>2.248991729955655</v>
       </c>
       <c r="R35" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4273084286915745</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -2849,10 +2849,10 @@
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.980516336204699</v>
+        <v>3.748319549926092</v>
       </c>
       <c r="R36" t="n">
-        <v>0.7562981038788928</v>
+        <v>0.7121807144859575</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -2898,7 +2898,7 @@
         <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0.19</v>
@@ -2910,16 +2910,16 @@
         <v>0.52</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2815</v>
+        <v>0.2785</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.970774504307049</v>
+        <v>5.622479324889138</v>
       </c>
       <c r="R37" t="n">
-        <v>1.134447155818339</v>
+        <v>1.068271071728936</v>
       </c>
       <c r="S37" t="n">
         <v>37.5</v>
@@ -2983,10 +2983,10 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -3050,10 +3050,10 @@
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.38830980172282</v>
+        <v>2.197245017584994</v>
       </c>
       <c r="R39" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4174765533411489</v>
       </c>
       <c r="S39" t="n">
         <v>22.5</v>
@@ -3099,7 +3099,7 @@
         <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L40" t="n">
         <v>0.38</v>
@@ -3111,16 +3111,16 @@
         <v>0.67</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R40" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S40" t="n">
         <v>30</v>
@@ -3184,10 +3184,10 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.343633722411948</v>
+        <v>3.148588421937917</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6352904072582701</v>
+        <v>0.5982318001682043</v>
       </c>
       <c r="S41" t="n">
         <v>21</v>
@@ -3251,10 +3251,10 @@
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.572722870686579</v>
+        <v>5.247647369896529</v>
       </c>
       <c r="R42" t="n">
-        <v>1.05881734543045</v>
+        <v>0.9970530002803405</v>
       </c>
       <c r="S42" t="n">
         <v>35</v>
@@ -3318,10 +3318,10 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>8.359084306029871</v>
+        <v>7.871471054844793</v>
       </c>
       <c r="R43" t="n">
-        <v>1.588226018145676</v>
+        <v>1.495579500420511</v>
       </c>
       <c r="S43" t="n">
         <v>52.5</v>
@@ -3385,10 +3385,10 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.600604006320404</v>
+        <v>2.392555685814771</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4941147612008768</v>
+        <v>0.4545855803048066</v>
       </c>
       <c r="S44" t="n">
         <v>24.5</v>
@@ -3434,7 +3434,7 @@
         <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="L45" t="n">
         <v>0.08</v>
@@ -3446,16 +3446,16 @@
         <v>0.67</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3995</v>
+        <v>0.4055</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.458178296549264</v>
+        <v>4.101524032825322</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7792895662368112</v>
       </c>
       <c r="S45" t="n">
         <v>42</v>
@@ -3501,7 +3501,7 @@
         <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3513,16 +3513,16 @@
         <v>0.48</v>
       </c>
       <c r="O46" t="n">
-        <v>0.239</v>
+        <v>0.245</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.944237728732352</v>
+        <v>5.468698710433763</v>
       </c>
       <c r="R46" t="n">
-        <v>1.129405168459147</v>
+        <v>1.039052754982415</v>
       </c>
       <c r="S46" t="n">
         <v>56</v>
@@ -3586,10 +3586,10 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.642591365513023</v>
+        <v>7.196773535858097</v>
       </c>
       <c r="R47" t="n">
-        <v>1.452092359447474</v>
+        <v>1.367386971813038</v>
       </c>
       <c r="S47" t="n">
         <v>48</v>
@@ -3653,10 +3653,10 @@
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>9.553239206891277</v>
+        <v>8.995966919822621</v>
       </c>
       <c r="R48" t="n">
-        <v>1.815115449309343</v>
+        <v>1.709233714766298</v>
       </c>
       <c r="S48" t="n">
         <v>60</v>
@@ -3720,10 +3720,10 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.46388704826953</v>
+        <v>10.79516030378715</v>
       </c>
       <c r="R49" t="n">
-        <v>2.178138539171211</v>
+        <v>2.051080457719558</v>
       </c>
       <c r="S49" t="n">
         <v>72</v>
@@ -3787,10 +3787,10 @@
         <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -3854,10 +3854,10 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S51" t="n">
         <v>16</v>
@@ -3921,10 +3921,10 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="R52" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="S52" t="n">
         <v>24</v>
@@ -3970,7 +3970,7 @@
         <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="L53" t="n">
         <v>0.13</v>
@@ -3982,16 +3982,16 @@
         <v>0.57</v>
       </c>
       <c r="O53" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.245884091951679</v>
+        <v>3.906213364595545</v>
       </c>
       <c r="R53" t="n">
-        <v>0.8067179774708191</v>
+        <v>0.7421805392731535</v>
       </c>
       <c r="S53" t="n">
         <v>40</v>
@@ -4037,7 +4037,7 @@
         <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4049,16 +4049,16 @@
         <v>0.57</v>
       </c>
       <c r="O54" t="n">
-        <v>0.2145</v>
+        <v>0.2205</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.944237728732352</v>
+        <v>5.468698710433763</v>
       </c>
       <c r="R54" t="n">
-        <v>1.129405168459147</v>
+        <v>1.039052754982415</v>
       </c>
       <c r="S54" t="n">
         <v>56</v>
@@ -4122,10 +4122,10 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>7.642591365513023</v>
+        <v>7.031184056271981</v>
       </c>
       <c r="R55" t="n">
-        <v>1.452092359447474</v>
+        <v>1.335924970691676</v>
       </c>
       <c r="S55" t="n">
         <v>72</v>
@@ -4189,10 +4189,10 @@
         <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.6368826137927519</v>
+        <v>0.5997311279881747</v>
       </c>
       <c r="R56" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.1139489143177532</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -4256,10 +4256,10 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.955323920689128</v>
+        <v>0.8995966919822621</v>
       </c>
       <c r="R57" t="n">
-        <v>0.1815115449309343</v>
+        <v>0.1709233714766298</v>
       </c>
       <c r="S57" t="n">
         <v>6</v>
@@ -4323,10 +4323,10 @@
         <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R58" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.284872285794383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -4390,10 +4390,10 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.79610326724094</v>
+        <v>0.7324150058616647</v>
       </c>
       <c r="R59" t="n">
-        <v>0.1512596207757786</v>
+        <v>0.1391588511137163</v>
       </c>
       <c r="S59" t="n">
         <v>7.5</v>
@@ -4457,10 +4457,10 @@
         <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R60" t="n">
-        <v>0.252099367959631</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S60" t="n">
         <v>12.5</v>
@@ -4524,10 +4524,10 @@
         <v>3</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4033589887354097</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -4591,10 +4591,10 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.821295682756512</v>
+        <v>3.598386767929048</v>
       </c>
       <c r="R62" t="n">
-        <v>0.7260461797237373</v>
+        <v>0.6836934859065192</v>
       </c>
       <c r="S62" t="n">
         <v>24</v>
@@ -4658,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.731943524134769</v>
+        <v>5.397580151893573</v>
       </c>
       <c r="R63" t="n">
-        <v>1.089069269585606</v>
+        <v>1.025540228859779</v>
       </c>
       <c r="S63" t="n">
         <v>36</v>
@@ -4725,10 +4725,10 @@
         <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.16492940516846</v>
+        <v>6.746975189866965</v>
       </c>
       <c r="R64" t="n">
-        <v>1.361336586982007</v>
+        <v>1.281925286074723</v>
       </c>
       <c r="S64" t="n">
         <v>45</v>
@@ -4792,10 +4792,10 @@
         <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R65" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -4859,10 +4859,10 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R66" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S66" t="n">
         <v>16</v>
@@ -4926,10 +4926,10 @@
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="R67" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="S67" t="n">
         <v>24</v>
@@ -4993,10 +4993,10 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.78636143534329</v>
+        <v>2.623823684948265</v>
       </c>
       <c r="R68" t="n">
-        <v>0.5294086727152251</v>
+        <v>0.4985265001401702</v>
       </c>
       <c r="S68" t="n">
         <v>17.5</v>
@@ -5060,10 +5060,10 @@
         <v>2</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.458178296549264</v>
+        <v>4.198117895917223</v>
       </c>
       <c r="R69" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7976424002242724</v>
       </c>
       <c r="S69" t="n">
         <v>28</v>
@@ -5127,10 +5127,10 @@
         <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.687267444823896</v>
+        <v>6.297176843875834</v>
       </c>
       <c r="R70" t="n">
-        <v>1.27058081451654</v>
+        <v>1.196463600336409</v>
       </c>
       <c r="S70" t="n">
         <v>42</v>
@@ -5194,10 +5194,10 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.572458236379779</v>
+        <v>1.452277499742181</v>
       </c>
       <c r="R71" t="n">
-        <v>0.298767064912158</v>
+        <v>0.2759327249510145</v>
       </c>
       <c r="S71" t="n">
         <v>14</v>
@@ -5261,10 +5261,10 @@
         <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.751801913664612</v>
+        <v>2.541485624548817</v>
       </c>
       <c r="R72" t="n">
-        <v>0.5228423635962763</v>
+        <v>0.4828822686642753</v>
       </c>
       <c r="S72" t="n">
         <v>24.5</v>
@@ -5310,7 +5310,7 @@
         <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="L73" t="n">
         <v>0.26</v>
@@ -5322,16 +5322,16 @@
         <v>0.57</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4875</v>
+        <v>0.4905</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.931145590949447</v>
+        <v>3.630693749355454</v>
       </c>
       <c r="R73" t="n">
-        <v>0.7469176622803949</v>
+        <v>0.6898318123775362</v>
       </c>
       <c r="S73" t="n">
         <v>35</v>
@@ -5395,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.093319598822689</v>
+        <v>1.951526818449605</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3977307237763109</v>
+        <v>0.3707900955054249</v>
       </c>
       <c r="S74" t="n">
         <v>16</v>
@@ -5444,7 +5444,7 @@
         <v>7</v>
       </c>
       <c r="K75" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="L75" t="n">
         <v>0.44</v>
@@ -5456,16 +5456,16 @@
         <v>0.31</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.663309297939705</v>
+        <v>3.415171932286808</v>
       </c>
       <c r="R75" t="n">
-        <v>0.696028766608544</v>
+        <v>0.6488826671344936</v>
       </c>
       <c r="S75" t="n">
         <v>28</v>
@@ -5529,10 +5529,10 @@
         <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.233298997056721</v>
+        <v>4.878817046124012</v>
       </c>
       <c r="R76" t="n">
-        <v>0.994326809440777</v>
+        <v>0.9269752387635622</v>
       </c>
       <c r="S76" t="n">
         <v>40</v>
@@ -5578,7 +5578,7 @@
         <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
@@ -5590,16 +5590,16 @@
         <v>0.22</v>
       </c>
       <c r="O77" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.7627780141936447</v>
+        <v>0.7099389740842112</v>
       </c>
       <c r="R77" t="n">
-        <v>0.1449278226967925</v>
+        <v>0.1348884050760001</v>
       </c>
       <c r="S77" t="n">
         <v>6</v>
@@ -5645,7 +5645,7 @@
         <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L78" t="n">
         <v>0.74</v>
@@ -5657,16 +5657,16 @@
         <v>0.46</v>
       </c>
       <c r="O78" t="n">
-        <v>0.737</v>
+        <v>0.74</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.034074704516386</v>
+        <v>1.893170597557897</v>
       </c>
       <c r="R78" t="n">
-        <v>0.3864741938581134</v>
+        <v>0.3597024135360004</v>
       </c>
       <c r="S78" t="n">
         <v>16</v>
@@ -5730,10 +5730,10 @@
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421056</v>
       </c>
       <c r="R79" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800006</v>
       </c>
       <c r="S79" t="n">
         <v>30</v>
@@ -5779,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L80" t="n">
         <v>0.9</v>
@@ -5791,16 +5791,16 @@
         <v>0.29</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7585</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.18489788612605</v>
+        <v>1.098128801339945</v>
       </c>
       <c r="R80" t="n">
-        <v>0.2251305983639495</v>
+        <v>0.2086444722545895</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
         <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.962244715315125</v>
+        <v>2.745322003349862</v>
       </c>
       <c r="R81" t="n">
-        <v>0.5628264959098738</v>
+        <v>0.5216111806364737</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -5913,7 +5913,7 @@
         <v>18</v>
       </c>
       <c r="K82" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -5925,16 +5925,16 @@
         <v>0.4</v>
       </c>
       <c r="O82" t="n">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.332040487567225</v>
+        <v>4.941579606029751</v>
       </c>
       <c r="R82" t="n">
-        <v>1.013087692637773</v>
+        <v>0.9389001251456527</v>
       </c>
       <c r="S82" t="n">
         <v>45</v>
@@ -5998,10 +5998,10 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.370038180833246</v>
+        <v>1.280491991626532</v>
       </c>
       <c r="R83" t="n">
-        <v>0.2603072543583166</v>
+        <v>0.2432934784090411</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.288091633999789</v>
+        <v>3.073180779903677</v>
       </c>
       <c r="R84" t="n">
-        <v>0.62473741045996</v>
+        <v>0.5839043481816986</v>
       </c>
       <c r="S84" t="n">
         <v>24</v>
@@ -6132,10 +6132,10 @@
         <v>3</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.480152723332982</v>
+        <v>5.121967966506128</v>
       </c>
       <c r="R85" t="n">
-        <v>1.041229017433267</v>
+        <v>0.9731739136361643</v>
       </c>
       <c r="S85" t="n">
         <v>40</v>
@@ -6199,10 +6199,10 @@
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.7467325219856878</v>
+        <v>0.7010337259087951</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1418791791772807</v>
+        <v>0.1331964079226711</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -6266,10 +6266,10 @@
         <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.613563826949908</v>
+        <v>2.453618040680783</v>
       </c>
       <c r="R87" t="n">
-        <v>0.4965771271204825</v>
+        <v>0.4661874277293487</v>
       </c>
       <c r="S87" t="n">
         <v>17.5</v>
@@ -6333,10 +6333,10 @@
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.227127653899815</v>
+        <v>4.907236081361566</v>
       </c>
       <c r="R88" t="n">
-        <v>0.9931542542409649</v>
+        <v>0.9323748554586975</v>
       </c>
       <c r="S88" t="n">
         <v>35</v>
@@ -6400,10 +6400,10 @@
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.318198898315231</v>
+        <v>1.215631175047444</v>
       </c>
       <c r="R89" t="n">
-        <v>0.2504577906798938</v>
+        <v>0.2309699232590144</v>
       </c>
       <c r="S89" t="n">
         <v>12</v>
@@ -6449,7 +6449,7 @@
         <v>10</v>
       </c>
       <c r="K90" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="L90" t="n">
         <v>0.64</v>
@@ -6461,16 +6461,16 @@
         <v>0.57</v>
       </c>
       <c r="O90" t="n">
-        <v>0.7175</v>
+        <v>0.7205</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.196998163858717</v>
+        <v>2.026051958412407</v>
       </c>
       <c r="R90" t="n">
-        <v>0.4174296511331563</v>
+        <v>0.3849498720983573</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -6516,7 +6516,7 @@
         <v>16</v>
       </c>
       <c r="K91" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L91" t="n">
         <v>0.33</v>
@@ -6528,16 +6528,16 @@
         <v>0.48</v>
       </c>
       <c r="O91" t="n">
-        <v>0.4925</v>
+        <v>0.4955</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.515197062173948</v>
+        <v>3.241683133459851</v>
       </c>
       <c r="R91" t="n">
-        <v>0.6678874418130502</v>
+        <v>0.6159197953573717</v>
       </c>
       <c r="S91" t="n">
         <v>32</v>
@@ -6601,10 +6601,10 @@
         <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.345352808205619</v>
+        <v>1.25617689958832</v>
       </c>
       <c r="R92" t="n">
-        <v>0.2556170335590677</v>
+        <v>0.2386736109217809</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -6668,10 +6668,10 @@
         <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.152564493128991</v>
+        <v>2.009883039341312</v>
       </c>
       <c r="R93" t="n">
-        <v>0.4089872536945083</v>
+        <v>0.3818777774748494</v>
       </c>
       <c r="S93" t="n">
         <v>16</v>
@@ -6735,10 +6735,10 @@
         <v>3</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.228846739693486</v>
+        <v>3.014824559011969</v>
       </c>
       <c r="R94" t="n">
-        <v>0.6134808805417624</v>
+        <v>0.572816666212274</v>
       </c>
       <c r="S94" t="n">
         <v>24</v>
@@ -6802,10 +6802,10 @@
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.789689515502888</v>
+        <v>1.676599652152576</v>
       </c>
       <c r="R95" t="n">
-        <v>0.3400410079455487</v>
+        <v>0.3185539339089895</v>
       </c>
       <c r="S95" t="n">
         <v>12.5</v>
@@ -6869,10 +6869,10 @@
         <v>2</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.863503224804621</v>
+        <v>2.682559443444122</v>
       </c>
       <c r="R96" t="n">
-        <v>0.544065612712878</v>
+        <v>0.5096862942543832</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -6936,10 +6936,10 @@
         <v>3</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.295254837206931</v>
+        <v>4.023839165166183</v>
       </c>
       <c r="R97" t="n">
-        <v>0.8160984190693169</v>
+        <v>0.7645294413815747</v>
       </c>
       <c r="S97" t="n">
         <v>30</v>
@@ -7003,10 +7003,10 @@
         <v>2</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.246611317695115</v>
+        <v>1.158916531435473</v>
       </c>
       <c r="R98" t="n">
-        <v>0.2368561503620719</v>
+        <v>0.22019414097274</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -7070,10 +7070,10 @@
         <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.994578108312184</v>
+        <v>1.854266450296758</v>
       </c>
       <c r="R99" t="n">
-        <v>0.378969840579315</v>
+        <v>0.352310625556384</v>
       </c>
       <c r="S99" t="n">
         <v>16</v>
@@ -7119,7 +7119,7 @@
         <v>12</v>
       </c>
       <c r="K100" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="L100" t="n">
         <v>0.54</v>
@@ -7131,16 +7131,16 @@
         <v>0.67</v>
       </c>
       <c r="O100" t="n">
-        <v>0.6165</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.991867162468276</v>
+        <v>2.781399675445137</v>
       </c>
       <c r="R100" t="n">
-        <v>0.5684547608689725</v>
+        <v>0.528465938334576</v>
       </c>
       <c r="S100" t="n">
         <v>24</v>
@@ -7204,10 +7204,10 @@
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.635405936580226</v>
+        <v>1.524630326913753</v>
       </c>
       <c r="R101" t="n">
-        <v>0.3107271279502429</v>
+        <v>0.2896797621136131</v>
       </c>
       <c r="S101" t="n">
         <v>12.5</v>
@@ -7253,7 +7253,7 @@
         <v>8</v>
       </c>
       <c r="K102" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L102" t="n">
         <v>0.64</v>
@@ -7265,16 +7265,16 @@
         <v>0.76</v>
       </c>
       <c r="O102" t="n">
-        <v>0.712</v>
+        <v>0.715</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R102" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -7320,7 +7320,7 @@
         <v>12</v>
       </c>
       <c r="K103" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="L103" t="n">
         <v>0.38</v>
@@ -7332,16 +7332,16 @@
         <v>0.67</v>
       </c>
       <c r="O103" t="n">
-        <v>0.5385</v>
+        <v>0.5415</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.924974247792541</v>
+        <v>3.659112784593008</v>
       </c>
       <c r="R103" t="n">
-        <v>0.7457451070805828</v>
+        <v>0.6952314290726715</v>
       </c>
       <c r="S103" t="n">
         <v>30</v>
@@ -7405,10 +7405,10 @@
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="R104" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="S104" t="n">
         <v>12.5</v>
@@ -7463,19 +7463,19 @@
         <v>0.89</v>
       </c>
       <c r="N105" t="n">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="O105" t="n">
-        <v>0.654</v>
+        <v>0.699</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R105" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -7539,10 +7539,10 @@
         <v>3</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.184170660382614</v>
+        <v>3.914421250994231</v>
       </c>
       <c r="R106" t="n">
-        <v>0.7949924254726968</v>
+        <v>0.743740037688904</v>
       </c>
       <c r="S106" t="n">
         <v>30</v>
@@ -7588,7 +7588,7 @@
         <v>8</v>
       </c>
       <c r="K107" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L107" t="n">
         <v>0.64</v>
@@ -7600,16 +7600,16 @@
         <v>0.46</v>
       </c>
       <c r="O107" t="n">
-        <v>0.667</v>
+        <v>0.67</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R107" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -7673,10 +7673,10 @@
         <v>2</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.270811873160451</v>
+        <v>3.049260653827508</v>
       </c>
       <c r="R108" t="n">
-        <v>0.6214542559004858</v>
+        <v>0.5793595242272265</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -7722,7 +7722,7 @@
         <v>12</v>
       </c>
       <c r="K109" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="L109" t="n">
         <v>0.38</v>
@@ -7734,16 +7734,16 @@
         <v>0.67</v>
       </c>
       <c r="O109" t="n">
-        <v>0.5185</v>
+        <v>0.5215</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.924974247792541</v>
+        <v>3.659112784593009</v>
       </c>
       <c r="R109" t="n">
-        <v>0.7457451070805828</v>
+        <v>0.6952314290726717</v>
       </c>
       <c r="S109" t="n">
         <v>30</v>
@@ -7807,10 +7807,10 @@
         <v>1</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.288091633999789</v>
+        <v>3.073180779903677</v>
       </c>
       <c r="R110" t="n">
-        <v>0.62473741045996</v>
+        <v>0.5839043481816986</v>
       </c>
       <c r="S110" t="n">
         <v>24</v>
@@ -7874,10 +7874,10 @@
         <v>2</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.110114542499736</v>
+        <v>3.841475974879596</v>
       </c>
       <c r="R111" t="n">
-        <v>0.7809217630749499</v>
+        <v>0.7298804352271232</v>
       </c>
       <c r="S111" t="n">
         <v>30</v>
@@ -7923,7 +7923,7 @@
         <v>12</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="L112" t="n">
         <v>0.23</v>
@@ -7935,16 +7935,16 @@
         <v>0.67</v>
       </c>
       <c r="O112" t="n">
-        <v>0.413</v>
+        <v>0.416</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.932137450999684</v>
+        <v>4.609771169855515</v>
       </c>
       <c r="R112" t="n">
-        <v>0.93710611568994</v>
+        <v>0.8758565222725478</v>
       </c>
       <c r="S112" t="n">
         <v>36</v>
@@ -8008,10 +8008,10 @@
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.49322263539023</v>
+        <v>2.317833062870947</v>
       </c>
       <c r="R113" t="n">
-        <v>0.4737123007241438</v>
+        <v>0.44038828194548</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -8075,10 +8075,10 @@
         <v>2</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.116528294237788</v>
+        <v>2.897291328588684</v>
       </c>
       <c r="R114" t="n">
-        <v>0.5921403759051797</v>
+        <v>0.55048535243185</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -8124,7 +8124,7 @@
         <v>12</v>
       </c>
       <c r="K115" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="L115" t="n">
         <v>0.38</v>
@@ -8136,16 +8136,16 @@
         <v>0.67</v>
       </c>
       <c r="O115" t="n">
-        <v>0.5265</v>
+        <v>0.5295</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.739833953085346</v>
+        <v>3.476749594306421</v>
       </c>
       <c r="R115" t="n">
-        <v>0.7105684510862157</v>
+        <v>0.66058242291822</v>
       </c>
       <c r="S115" t="n">
         <v>30</v>
@@ -8209,10 +8209,10 @@
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.093319598822689</v>
+        <v>1.951526818449605</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3977307237763109</v>
+        <v>0.3707900955054249</v>
       </c>
       <c r="S116" t="n">
         <v>16</v>
@@ -8258,7 +8258,7 @@
         <v>10</v>
       </c>
       <c r="K117" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L117" t="n">
         <v>0.64</v>
@@ -8270,16 +8270,16 @@
         <v>0.57</v>
       </c>
       <c r="O117" t="n">
-        <v>0.6955</v>
+        <v>0.6985</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R117" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -8325,7 +8325,7 @@
         <v>12</v>
       </c>
       <c r="K118" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="L118" t="n">
         <v>0.54</v>
@@ -8337,16 +8337,16 @@
         <v>0.67</v>
       </c>
       <c r="O118" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.139979398234034</v>
+        <v>2.927290227674407</v>
       </c>
       <c r="R118" t="n">
-        <v>0.5965960856644664</v>
+        <v>0.5561851432581373</v>
       </c>
       <c r="S118" t="n">
         <v>24</v>
@@ -8410,10 +8410,10 @@
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>2.542593380645482</v>
+        <v>2.366463246947371</v>
       </c>
       <c r="R119" t="n">
-        <v>0.4830927423226417</v>
+        <v>0.4496280169200005</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -8477,10 +8477,10 @@
         <v>2</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.178241725806853</v>
+        <v>2.958079058684214</v>
       </c>
       <c r="R120" t="n">
-        <v>0.6038659279033021</v>
+        <v>0.5620350211500006</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -8544,10 +8544,10 @@
         <v>3</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421056</v>
       </c>
       <c r="R121" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800006</v>
       </c>
       <c r="S121" t="n">
         <v>30</v>
@@ -8611,10 +8611,10 @@
         <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.99025816810235</v>
+        <v>1.874159774963046</v>
       </c>
       <c r="R122" t="n">
-        <v>0.3781490519394464</v>
+        <v>0.3560903572429788</v>
       </c>
       <c r="S122" t="n">
         <v>12.5</v>
@@ -8678,10 +8678,10 @@
         <v>2</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.18441306896376</v>
+        <v>2.998655639940873</v>
       </c>
       <c r="R123" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.569744571588766</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -8745,10 +8745,10 @@
         <v>3</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.776619603445639</v>
+        <v>4.49798345991131</v>
       </c>
       <c r="R124" t="n">
-        <v>0.9075577246546715</v>
+        <v>0.854616857383149</v>
       </c>
       <c r="S124" t="n">
         <v>30</v>
@@ -8812,10 +8812,10 @@
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R125" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -8861,7 +8861,7 @@
         <v>8</v>
       </c>
       <c r="K126" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L126" t="n">
         <v>0.74</v>
@@ -8873,16 +8873,16 @@
         <v>0.76</v>
       </c>
       <c r="O126" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="P126" t="n">
         <v>2</v>
       </c>
       <c r="Q126" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="R126" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="S126" t="n">
         <v>16</v>
@@ -8946,10 +8946,10 @@
         <v>3</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.821295682756512</v>
+        <v>3.598386767929049</v>
       </c>
       <c r="R127" t="n">
-        <v>0.7260461797237373</v>
+        <v>0.6836934859065193</v>
       </c>
       <c r="S127" t="n">
         <v>24</v>
@@ -9013,10 +9013,10 @@
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.99025816810235</v>
+        <v>1.874159774963046</v>
       </c>
       <c r="R128" t="n">
-        <v>0.3781490519394464</v>
+        <v>0.3560903572429788</v>
       </c>
       <c r="S128" t="n">
         <v>12.5</v>
@@ -9080,10 +9080,10 @@
         <v>2</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.18441306896376</v>
+        <v>2.998655639940873</v>
       </c>
       <c r="R129" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.569744571588766</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -9147,10 +9147,10 @@
         <v>3</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.776619603445639</v>
+        <v>4.49798345991131</v>
       </c>
       <c r="R130" t="n">
-        <v>0.9075577246546715</v>
+        <v>0.854616857383149</v>
       </c>
       <c r="S130" t="n">
         <v>30</v>
@@ -9214,10 +9214,10 @@
         <v>2</v>
       </c>
       <c r="Q131" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R131" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -9281,10 +9281,10 @@
         <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R132" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S132" t="n">
         <v>16</v>
@@ -9348,10 +9348,10 @@
         <v>3</v>
       </c>
       <c r="Q133" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="R133" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="S133" t="n">
         <v>24</v>
@@ -9415,10 +9415,10 @@
         <v>1</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R134" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S134" t="n">
         <v>12.5</v>
@@ -9482,10 +9482,10 @@
         <v>2</v>
       </c>
       <c r="Q135" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R135" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S135" t="n">
         <v>20</v>
@@ -9531,7 +9531,7 @@
         <v>12</v>
       </c>
       <c r="K136" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L136" t="n">
         <v>0.38</v>
@@ -9543,16 +9543,16 @@
         <v>0.67</v>
       </c>
       <c r="O136" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="P136" t="n">
         <v>3</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R136" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S136" t="n">
         <v>30</v>
@@ -9598,7 +9598,7 @@
         <v>4</v>
       </c>
       <c r="K137" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L137" t="n">
         <v>0.85</v>
@@ -9610,16 +9610,16 @@
         <v>0.29</v>
       </c>
       <c r="O137" t="n">
-        <v>0.702</v>
+        <v>0.699</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>1.7625356056125</v>
+        <v>1.653302831735254</v>
       </c>
       <c r="R137" t="n">
-        <v>0.334881765066375</v>
+        <v>0.3141275380296983</v>
       </c>
       <c r="S137" t="n">
         <v>12</v>
@@ -9683,10 +9683,10 @@
         <v>2</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.084437309821875</v>
+        <v>2.893279955536695</v>
       </c>
       <c r="R138" t="n">
-        <v>0.5860430888661562</v>
+        <v>0.5497231915519721</v>
       </c>
       <c r="S138" t="n">
         <v>21</v>
@@ -9750,10 +9750,10 @@
         <v>3</v>
       </c>
       <c r="Q139" t="n">
-        <v>4.406339014031249</v>
+        <v>4.133257079338136</v>
       </c>
       <c r="R139" t="n">
-        <v>0.8372044126659374</v>
+        <v>0.7853188450742458</v>
       </c>
       <c r="S139" t="n">
         <v>30</v>
@@ -9817,10 +9817,10 @@
         <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.429040666558403</v>
+        <v>2.282212070169283</v>
       </c>
       <c r="R140" t="n">
-        <v>0.4615177266460965</v>
+        <v>0.4336202933321637</v>
       </c>
       <c r="S140" t="n">
         <v>16</v>
@@ -9884,10 +9884,10 @@
         <v>2</v>
       </c>
       <c r="Q141" t="n">
-        <v>4.250821166477206</v>
+        <v>3.993871122796245</v>
       </c>
       <c r="R141" t="n">
-        <v>0.8076560216306691</v>
+        <v>0.7588355133312866</v>
       </c>
       <c r="S141" t="n">
         <v>28</v>
@@ -9951,10 +9951,10 @@
         <v>3</v>
       </c>
       <c r="Q142" t="n">
-        <v>6.072601666396007</v>
+        <v>5.705530175423207</v>
       </c>
       <c r="R142" t="n">
-        <v>1.153794316615241</v>
+        <v>1.084050733330409</v>
       </c>
       <c r="S142" t="n">
         <v>40</v>
@@ -10018,10 +10018,10 @@
         <v>2</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.2616649498528361</v>
+        <v>0.2439408523062006</v>
       </c>
       <c r="R143" t="n">
-        <v>0.04971634047203886</v>
+        <v>0.04634876193817811</v>
       </c>
       <c r="S143" t="n">
         <v>2</v>
@@ -10085,10 +10085,10 @@
         <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>1.569989699117017</v>
+        <v>1.463645113837203</v>
       </c>
       <c r="R144" t="n">
-        <v>0.2982980428322332</v>
+        <v>0.2780925716290686</v>
       </c>
       <c r="S144" t="n">
         <v>12</v>
@@ -10134,7 +10134,7 @@
         <v>12</v>
       </c>
       <c r="K145" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="L145" t="n">
         <v>0.54</v>
@@ -10146,16 +10146,16 @@
         <v>0.67</v>
       </c>
       <c r="O145" t="n">
-        <v>0.6395</v>
+        <v>0.6425</v>
       </c>
       <c r="P145" t="n">
         <v>3</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.139979398234034</v>
+        <v>2.927290227674407</v>
       </c>
       <c r="R145" t="n">
-        <v>0.5965960856644664</v>
+        <v>0.5561851432581373</v>
       </c>
       <c r="S145" t="n">
         <v>24</v>
@@ -10201,7 +10201,7 @@
         <v>7</v>
       </c>
       <c r="K146" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="L146" t="n">
         <v>0.71</v>
@@ -10213,16 +10213,16 @@
         <v>0.64</v>
       </c>
       <c r="O146" t="n">
-        <v>0.7375</v>
+        <v>0.7405</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
       </c>
       <c r="Q146" t="n">
-        <v>2.138370403868106</v>
+        <v>1.985552518945208</v>
       </c>
       <c r="R146" t="n">
-        <v>0.4062903767349402</v>
+        <v>0.3772549785995896</v>
       </c>
       <c r="S146" t="n">
         <v>17.5</v>
@@ -10268,7 +10268,7 @@
         <v>14</v>
       </c>
       <c r="K147" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="L147" t="n">
         <v>0.26</v>
@@ -10280,16 +10280,16 @@
         <v>0.57</v>
       </c>
       <c r="O147" t="n">
-        <v>0.4515</v>
+        <v>0.4545</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
       </c>
       <c r="Q147" t="n">
-        <v>4.276740807736212</v>
+        <v>3.971105037890417</v>
       </c>
       <c r="R147" t="n">
-        <v>0.8125807534698803</v>
+        <v>0.7545099571991791</v>
       </c>
       <c r="S147" t="n">
         <v>35</v>
@@ -10353,10 +10353,10 @@
         <v>3</v>
       </c>
       <c r="Q148" t="n">
-        <v>6.720592697871191</v>
+        <v>6.24030791668494</v>
       </c>
       <c r="R148" t="n">
-        <v>1.276912612595526</v>
+        <v>1.185658504170139</v>
       </c>
       <c r="S148" t="n">
         <v>55</v>
@@ -10420,10 +10420,10 @@
         <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>1.370038180833246</v>
+        <v>1.280491991626532</v>
       </c>
       <c r="R149" t="n">
-        <v>0.2603072543583166</v>
+        <v>0.2432934784090411</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -10487,10 +10487,10 @@
         <v>2</v>
       </c>
       <c r="Q150" t="n">
-        <v>2.192061089333193</v>
+        <v>2.048787186602451</v>
       </c>
       <c r="R150" t="n">
-        <v>0.4164916069733066</v>
+        <v>0.3892695654544657</v>
       </c>
       <c r="S150" t="n">
         <v>16</v>
@@ -10554,10 +10554,10 @@
         <v>3</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.288091633999789</v>
+        <v>3.073180779903677</v>
       </c>
       <c r="R151" t="n">
-        <v>0.62473741045996</v>
+        <v>0.5839043481816986</v>
       </c>
       <c r="S151" t="n">
         <v>24</v>
@@ -10621,10 +10621,10 @@
         <v>1</v>
       </c>
       <c r="Q152" t="n">
-        <v>1.589120862903426</v>
+        <v>1.479039529342106</v>
       </c>
       <c r="R152" t="n">
-        <v>0.301932963951651</v>
+        <v>0.2810175105750002</v>
       </c>
       <c r="S152" t="n">
         <v>12.5</v>
@@ -10688,10 +10688,10 @@
         <v>2</v>
       </c>
       <c r="Q153" t="n">
-        <v>2.542593380645482</v>
+        <v>2.36646324694737</v>
       </c>
       <c r="R153" t="n">
-        <v>0.4830927423226417</v>
+        <v>0.4496280169200003</v>
       </c>
       <c r="S153" t="n">
         <v>20</v>
@@ -10755,10 +10755,10 @@
         <v>3</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421055</v>
       </c>
       <c r="R154" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800005</v>
       </c>
       <c r="S154" t="n">
         <v>30</v>
@@ -10822,10 +10822,10 @@
         <v>1</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.962487123896271</v>
+        <v>1.829556392296504</v>
       </c>
       <c r="R155" t="n">
-        <v>0.3728725535402914</v>
+        <v>0.3476157145363358</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L156" t="n">
         <v>0.64</v>
@@ -10883,16 +10883,16 @@
         <v>0.46</v>
       </c>
       <c r="O156" t="n">
-        <v>0.667</v>
+        <v>0.67</v>
       </c>
       <c r="P156" t="n">
         <v>2</v>
       </c>
       <c r="Q156" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R156" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S156" t="n">
         <v>20</v>
@@ -10956,10 +10956,10 @@
         <v>3</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.270811873160451</v>
+        <v>3.049260653827508</v>
       </c>
       <c r="R157" t="n">
-        <v>0.6214542559004858</v>
+        <v>0.5793595242272265</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -11023,10 +11023,10 @@
         <v>1</v>
       </c>
       <c r="Q158" t="n">
-        <v>2.542593380645482</v>
+        <v>2.366463246947371</v>
       </c>
       <c r="R158" t="n">
-        <v>0.4830927423226417</v>
+        <v>0.4496280169200005</v>
       </c>
       <c r="S158" t="n">
         <v>20</v>
@@ -11090,10 +11090,10 @@
         <v>2</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.178241725806853</v>
+        <v>2.958079058684214</v>
       </c>
       <c r="R159" t="n">
-        <v>0.6038659279033021</v>
+        <v>0.5620350211500006</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -11157,10 +11157,10 @@
         <v>3</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421056</v>
       </c>
       <c r="R160" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800006</v>
       </c>
       <c r="S160" t="n">
         <v>30</v>
@@ -11224,10 +11224,10 @@
         <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R161" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>8</v>
       </c>
       <c r="K162" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L162" t="n">
         <v>0.74</v>
@@ -11285,16 +11285,16 @@
         <v>0.76</v>
       </c>
       <c r="O162" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="P162" t="n">
         <v>2</v>
       </c>
       <c r="Q162" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="R162" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="S162" t="n">
         <v>16</v>
@@ -11358,10 +11358,10 @@
         <v>3</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.821295682756512</v>
+        <v>3.598386767929049</v>
       </c>
       <c r="R163" t="n">
-        <v>0.7260461797237373</v>
+        <v>0.6836934859065193</v>
       </c>
       <c r="S163" t="n">
         <v>24</v>
@@ -11425,10 +11425,10 @@
         <v>1</v>
       </c>
       <c r="Q164" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R164" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S164" t="n">
         <v>12.5</v>
@@ -11492,10 +11492,10 @@
         <v>2</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R165" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S165" t="n">
         <v>20</v>
@@ -11541,7 +11541,7 @@
         <v>12</v>
       </c>
       <c r="K166" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L166" t="n">
         <v>0.38</v>
@@ -11553,16 +11553,16 @@
         <v>0.67</v>
       </c>
       <c r="O166" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="P166" t="n">
         <v>3</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R166" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S166" t="n">
         <v>30</v>
@@ -11623,13 +11623,13 @@
         <v>0.785</v>
       </c>
       <c r="P167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q167" t="n">
-        <v>0.7109387316756299</v>
+        <v>0.6588772808039668</v>
       </c>
       <c r="R167" t="n">
-        <v>0.1350783590183697</v>
+        <v>0.1251866833527537</v>
       </c>
       <c r="S167" t="n">
         <v>6</v>
@@ -11675,7 +11675,7 @@
         <v>5</v>
       </c>
       <c r="K168" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L168" t="n">
         <v>0.9</v>
@@ -11687,16 +11687,16 @@
         <v>0.35</v>
       </c>
       <c r="O168" t="n">
-        <v>0.7825</v>
+        <v>0.7855</v>
       </c>
       <c r="P168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q168" t="n">
-        <v>1.18489788612605</v>
+        <v>1.098128801339945</v>
       </c>
       <c r="R168" t="n">
-        <v>0.2251305983639495</v>
+        <v>0.2086444722545895</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -11760,10 +11760,10 @@
         <v>1</v>
       </c>
       <c r="Q169" t="n">
-        <v>1.89583661780168</v>
+        <v>1.757006082143911</v>
       </c>
       <c r="R169" t="n">
-        <v>0.3602089573823192</v>
+        <v>0.3338311556073432</v>
       </c>
       <c r="S169" t="n">
         <v>16</v>
@@ -11827,10 +11827,10 @@
         <v>1</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.7961032672409399</v>
+        <v>0.7324150058616647</v>
       </c>
       <c r="R170" t="n">
-        <v>0.1512596207757786</v>
+        <v>0.1391588511137163</v>
       </c>
       <c r="S170" t="n">
         <v>7.5</v>
@@ -11894,10 +11894,10 @@
         <v>2</v>
       </c>
       <c r="Q171" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R171" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S171" t="n">
         <v>12.5</v>
@@ -11961,10 +11961,10 @@
         <v>3</v>
       </c>
       <c r="Q172" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R172" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -12028,10 +12028,10 @@
         <v>1</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.8238743114470191</v>
+        <v>0.7597694844046526</v>
       </c>
       <c r="R173" t="n">
-        <v>0.1565361191749336</v>
+        <v>0.144356202036884</v>
       </c>
       <c r="S173" t="n">
         <v>7.5</v>
@@ -12095,10 +12095,10 @@
         <v>2</v>
       </c>
       <c r="Q174" t="n">
-        <v>1.373123852411698</v>
+        <v>1.266282474007754</v>
       </c>
       <c r="R174" t="n">
-        <v>0.2608935319582227</v>
+        <v>0.2405936700614733</v>
       </c>
       <c r="S174" t="n">
         <v>12.5</v>
@@ -12144,7 +12144,7 @@
         <v>8</v>
       </c>
       <c r="K175" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="L175" t="n">
         <v>0.64</v>
@@ -12156,16 +12156,16 @@
         <v>0.46</v>
       </c>
       <c r="O175" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="P175" t="n">
         <v>3</v>
       </c>
       <c r="Q175" t="n">
-        <v>2.196998163858717</v>
+        <v>2.026051958412407</v>
       </c>
       <c r="R175" t="n">
-        <v>0.4174296511331563</v>
+        <v>0.3849498720983573</v>
       </c>
       <c r="S175" t="n">
         <v>20</v>
@@ -12211,7 +12211,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
@@ -12223,16 +12223,16 @@
         <v>0.22</v>
       </c>
       <c r="O176" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="P176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.7627780141936447</v>
+        <v>0.7099389740842112</v>
       </c>
       <c r="R176" t="n">
-        <v>0.1449278226967925</v>
+        <v>0.1348884050760001</v>
       </c>
       <c r="S176" t="n">
         <v>6</v>
@@ -12296,10 +12296,10 @@
         <v>3</v>
       </c>
       <c r="Q177" t="n">
-        <v>1.271296690322741</v>
+        <v>1.183231623473685</v>
       </c>
       <c r="R177" t="n">
-        <v>0.2415463711613208</v>
+        <v>0.2248140084600002</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -12345,7 +12345,7 @@
         <v>8</v>
       </c>
       <c r="K178" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L178" t="n">
         <v>0.74</v>
@@ -12357,16 +12357,16 @@
         <v>0.76</v>
       </c>
       <c r="O178" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="P178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q178" t="n">
-        <v>2.034074704516386</v>
+        <v>1.893170597557897</v>
       </c>
       <c r="R178" t="n">
-        <v>0.3864741938581134</v>
+        <v>0.3597024135360004</v>
       </c>
       <c r="S178" t="n">
         <v>16</v>
@@ -12430,10 +12430,10 @@
         <v>3</v>
       </c>
       <c r="Q179" t="n">
-        <v>0.9331070853242646</v>
+        <v>0.8777131091478717</v>
       </c>
       <c r="R179" t="n">
-        <v>0.1772903462116103</v>
+        <v>0.1667654907380956</v>
       </c>
       <c r="S179" t="n">
         <v>6</v>
@@ -12497,10 +12497,10 @@
         <v>2</v>
       </c>
       <c r="Q180" t="n">
-        <v>1.399660627986397</v>
+        <v>1.316569663721808</v>
       </c>
       <c r="R180" t="n">
-        <v>0.2659355193174154</v>
+        <v>0.2501482361071434</v>
       </c>
       <c r="S180" t="n">
         <v>9</v>
@@ -12546,7 +12546,7 @@
         <v>10</v>
       </c>
       <c r="K181" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L181" t="n">
         <v>0.77</v>
@@ -12558,16 +12558,16 @@
         <v>0.85</v>
       </c>
       <c r="O181" t="n">
-        <v>0.775</v>
+        <v>0.772</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
       </c>
       <c r="Q181" t="n">
-        <v>2.332767713310661</v>
+        <v>2.194282772869679</v>
       </c>
       <c r="R181" t="n">
-        <v>0.4432258655290257</v>
+        <v>0.416913726845239</v>
       </c>
       <c r="S181" t="n">
         <v>15</v>
@@ -12631,10 +12631,10 @@
         <v>1</v>
       </c>
       <c r="Q182" t="n">
-        <v>1.115778842768697</v>
+        <v>1.043845666931795</v>
       </c>
       <c r="R182" t="n">
-        <v>0.2119979801260525</v>
+        <v>0.198330676717041</v>
       </c>
       <c r="S182" t="n">
         <v>8</v>
@@ -12698,10 +12698,10 @@
         <v>2</v>
       </c>
       <c r="Q183" t="n">
-        <v>1.673668264153046</v>
+        <v>1.565768500397692</v>
       </c>
       <c r="R183" t="n">
-        <v>0.3179969701890787</v>
+        <v>0.2974960150755615</v>
       </c>
       <c r="S183" t="n">
         <v>12</v>
@@ -12765,10 +12765,10 @@
         <v>3</v>
       </c>
       <c r="Q184" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R184" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -12832,10 +12832,10 @@
         <v>1</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="R185" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="S185" t="n">
         <v>7.5</v>
@@ -12899,10 +12899,10 @@
         <v>2</v>
       </c>
       <c r="Q186" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="R186" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="S186" t="n">
         <v>12.5</v>
@@ -12966,10 +12966,10 @@
         <v>3</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="R187" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="S187" t="n">
         <v>20</v>
@@ -13033,10 +13033,10 @@
         <v>1</v>
       </c>
       <c r="Q188" t="n">
-        <v>1.010866009101286</v>
+        <v>0.9336069641199739</v>
       </c>
       <c r="R188" t="n">
-        <v>0.1920645417292444</v>
+        <v>0.177385323182795</v>
       </c>
       <c r="S188" t="n">
         <v>9</v>
@@ -13082,7 +13082,7 @@
         <v>4</v>
       </c>
       <c r="K189" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="L189" t="n">
         <v>0.85</v>
@@ -13094,16 +13094,16 @@
         <v>0.29</v>
       </c>
       <c r="O189" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="P189" t="n">
         <v>2</v>
       </c>
       <c r="Q189" t="n">
-        <v>1.347821345468382</v>
+        <v>1.244809285493299</v>
       </c>
       <c r="R189" t="n">
-        <v>0.2560860556389926</v>
+        <v>0.2365137642437267</v>
       </c>
       <c r="S189" t="n">
         <v>12</v>
@@ -13158,19 +13158,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N190" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="O190" t="n">
-        <v>0.654</v>
+        <v>0.7065</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
       </c>
       <c r="Q190" t="n">
-        <v>2.021732018202572</v>
+        <v>1.867213928239948</v>
       </c>
       <c r="R190" t="n">
-        <v>0.3841290834584888</v>
+        <v>0.3547706463655901</v>
       </c>
       <c r="S190" t="n">
         <v>18</v>
@@ -13234,10 +13234,10 @@
         <v>1</v>
       </c>
       <c r="Q191" t="n">
-        <v>0.955323920689128</v>
+        <v>0.8995966919822622</v>
       </c>
       <c r="R191" t="n">
-        <v>0.1815115449309343</v>
+        <v>0.1709233714766298</v>
       </c>
       <c r="S191" t="n">
         <v>6</v>
@@ -13301,10 +13301,10 @@
         <v>2</v>
       </c>
       <c r="Q192" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R192" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -13350,7 +13350,7 @@
         <v>8</v>
       </c>
       <c r="K193" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L193" t="n">
         <v>0.74</v>
@@ -13362,16 +13362,16 @@
         <v>0.76</v>
       </c>
       <c r="O193" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="P193" t="n">
         <v>3</v>
       </c>
       <c r="Q193" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="R193" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="S193" t="n">
         <v>16</v>
@@ -13435,10 +13435,10 @@
         <v>1</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="R194" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="S194" t="n">
         <v>7.5</v>
@@ -13502,10 +13502,10 @@
         <v>2</v>
       </c>
       <c r="Q195" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="R195" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="S195" t="n">
         <v>12.5</v>
@@ -13569,10 +13569,10 @@
         <v>3</v>
       </c>
       <c r="Q196" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="R196" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="S196" t="n">
         <v>20</v>
@@ -13636,10 +13636,10 @@
         <v>3</v>
       </c>
       <c r="Q197" t="n">
-        <v>0.636882613792752</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="R197" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="S197" t="n">
         <v>6</v>
@@ -13703,10 +13703,10 @@
         <v>2</v>
       </c>
       <c r="Q198" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R198" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -13770,10 +13770,10 @@
         <v>1</v>
       </c>
       <c r="Q199" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R199" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S199" t="n">
         <v>16</v>
@@ -13837,10 +13837,10 @@
         <v>1</v>
       </c>
       <c r="Q200" t="n">
-        <v>0.9812435619481353</v>
+        <v>0.9147781961482522</v>
       </c>
       <c r="R200" t="n">
-        <v>0.1864362767701457</v>
+        <v>0.1738078572681679</v>
       </c>
       <c r="S200" t="n">
         <v>7.5</v>
@@ -13904,10 +13904,10 @@
         <v>2</v>
       </c>
       <c r="Q201" t="n">
-        <v>1.635405936580226</v>
+        <v>1.524630326913754</v>
       </c>
       <c r="R201" t="n">
-        <v>0.3107271279502429</v>
+        <v>0.2896797621136132</v>
       </c>
       <c r="S201" t="n">
         <v>12.5</v>
@@ -13953,7 +13953,7 @@
         <v>7</v>
       </c>
       <c r="K202" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="L202" t="n">
         <v>0.71</v>
@@ -13965,16 +13965,16 @@
         <v>0.31</v>
       </c>
       <c r="O202" t="n">
-        <v>0.673</v>
+        <v>0.676</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
       </c>
       <c r="Q202" t="n">
-        <v>2.289568311212316</v>
+        <v>2.134482457679255</v>
       </c>
       <c r="R202" t="n">
-        <v>0.43501797913034</v>
+        <v>0.4055516669590585</v>
       </c>
       <c r="S202" t="n">
         <v>17.5</v>
@@ -14038,10 +14038,10 @@
         <v>3</v>
       </c>
       <c r="Q203" t="n">
-        <v>0.7331555670404936</v>
+        <v>0.6807608636383572</v>
       </c>
       <c r="R203" t="n">
-        <v>0.1392995577376938</v>
+        <v>0.1293445640912879</v>
       </c>
       <c r="S203" t="n">
         <v>6</v>
@@ -14105,10 +14105,10 @@
         <v>2</v>
       </c>
       <c r="Q204" t="n">
-        <v>1.221925945067489</v>
+        <v>1.134601439397262</v>
       </c>
       <c r="R204" t="n">
-        <v>0.232165929562823</v>
+        <v>0.2155742734854798</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -14172,10 +14172,10 @@
         <v>1</v>
       </c>
       <c r="Q205" t="n">
-        <v>1.955081512107983</v>
+        <v>1.815362303035619</v>
       </c>
       <c r="R205" t="n">
-        <v>0.3714654873005167</v>
+        <v>0.3449188375767677</v>
       </c>
       <c r="S205" t="n">
         <v>16</v>
@@ -14239,10 +14239,10 @@
         <v>1</v>
       </c>
       <c r="Q206" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="R206" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="S206" t="n">
         <v>7.5</v>
@@ -14306,10 +14306,10 @@
         <v>2</v>
       </c>
       <c r="Q207" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="R207" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="S207" t="n">
         <v>12.5</v>
@@ -14373,10 +14373,10 @@
         <v>3</v>
       </c>
       <c r="Q208" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R208" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S208" t="n">
         <v>20</v>
@@ -14440,10 +14440,10 @@
         <v>3</v>
       </c>
       <c r="Q209" t="n">
-        <v>0.6739106727341909</v>
+        <v>0.6224046427466493</v>
       </c>
       <c r="R209" t="n">
-        <v>0.1280430278194963</v>
+        <v>0.1182568821218634</v>
       </c>
       <c r="S209" t="n">
         <v>6</v>
@@ -14507,10 +14507,10 @@
         <v>2</v>
       </c>
       <c r="Q210" t="n">
-        <v>1.123184454556985</v>
+        <v>1.037341071244415</v>
       </c>
       <c r="R210" t="n">
-        <v>0.2134050463658271</v>
+        <v>0.1970948035364389</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -14574,10 +14574,10 @@
         <v>1</v>
       </c>
       <c r="Q211" t="n">
-        <v>1.572458236379779</v>
+        <v>1.452277499742181</v>
       </c>
       <c r="R211" t="n">
-        <v>0.298767064912158</v>
+        <v>0.2759327249510145</v>
       </c>
       <c r="S211" t="n">
         <v>14</v>
@@ -14641,10 +14641,10 @@
         <v>3</v>
       </c>
       <c r="Q212" t="n">
-        <v>0.9108902499594012</v>
+        <v>0.8558295263134812</v>
       </c>
       <c r="R212" t="n">
-        <v>0.1730691474922862</v>
+        <v>0.1626076099995614</v>
       </c>
       <c r="S212" t="n">
         <v>6</v>
@@ -14708,10 +14708,10 @@
         <v>2</v>
       </c>
       <c r="Q213" t="n">
-        <v>1.366335374939102</v>
+        <v>1.283744289470222</v>
       </c>
       <c r="R213" t="n">
-        <v>0.2596037212384293</v>
+        <v>0.2439114149993421</v>
       </c>
       <c r="S213" t="n">
         <v>9</v>
@@ -14775,10 +14775,10 @@
         <v>1</v>
       </c>
       <c r="Q214" t="n">
-        <v>2.277225624898503</v>
+        <v>2.139573815783703</v>
       </c>
       <c r="R214" t="n">
-        <v>0.4326728687307156</v>
+        <v>0.4065190249989036</v>
       </c>
       <c r="S214" t="n">
         <v>15</v>
@@ -14842,10 +14842,10 @@
         <v>1</v>
       </c>
       <c r="Q215" t="n">
-        <v>1.145401289921848</v>
+        <v>1.073023777377649</v>
       </c>
       <c r="R215" t="n">
-        <v>0.2176262450851512</v>
+        <v>0.2038745177017533</v>
       </c>
       <c r="S215" t="n">
         <v>8</v>
@@ -14909,10 +14909,10 @@
         <v>2</v>
       </c>
       <c r="Q216" t="n">
-        <v>1.718101934882773</v>
+        <v>1.609535666066473</v>
       </c>
       <c r="R216" t="n">
-        <v>0.3264393676277268</v>
+        <v>0.3058117765526299</v>
       </c>
       <c r="S216" t="n">
         <v>12</v>
@@ -14976,10 +14976,10 @@
         <v>3</v>
       </c>
       <c r="Q217" t="n">
-        <v>2.863503224804621</v>
+        <v>2.682559443444122</v>
       </c>
       <c r="R217" t="n">
-        <v>0.544065612712878</v>
+        <v>0.5096862942543832</v>
       </c>
       <c r="S217" t="n">
         <v>20</v>
@@ -15043,10 +15043,10 @@
         <v>2</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.8072116849233715</v>
+        <v>0.7537061397529922</v>
       </c>
       <c r="R218" t="n">
-        <v>0.1533702201354406</v>
+        <v>0.1432041665530685</v>
       </c>
       <c r="S218" t="n">
         <v>6</v>
@@ -15110,10 +15110,10 @@
         <v>3</v>
       </c>
       <c r="Q219" t="n">
-        <v>1.345352808205619</v>
+        <v>1.25617689958832</v>
       </c>
       <c r="R219" t="n">
-        <v>0.2556170335590677</v>
+        <v>0.2386736109217809</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -15177,10 +15177,10 @@
         <v>1</v>
       </c>
       <c r="Q220" t="n">
-        <v>2.152564493128991</v>
+        <v>2.009883039341312</v>
       </c>
       <c r="R220" t="n">
-        <v>0.4089872536945083</v>
+        <v>0.3818777774748494</v>
       </c>
       <c r="S220" t="n">
         <v>16</v>
@@ -15244,10 +15244,10 @@
         <v>1</v>
       </c>
       <c r="Q221" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="R221" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="S221" t="n">
         <v>7.5</v>
@@ -15311,10 +15311,10 @@
         <v>2</v>
       </c>
       <c r="Q222" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="R222" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="S222" t="n">
         <v>12.5</v>
@@ -15378,10 +15378,10 @@
         <v>3</v>
       </c>
       <c r="Q223" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R223" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -15445,10 +15445,10 @@
         <v>1</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.9331070853242645</v>
+        <v>0.8777131091478716</v>
       </c>
       <c r="R224" t="n">
-        <v>0.1772903462116102</v>
+        <v>0.1667654907380956</v>
       </c>
       <c r="S224" t="n">
         <v>6</v>
@@ -15512,10 +15512,10 @@
         <v>2</v>
       </c>
       <c r="Q225" t="n">
-        <v>1.555178475540441</v>
+        <v>1.462855181913119</v>
       </c>
       <c r="R225" t="n">
-        <v>0.2954839103526837</v>
+        <v>0.2779424845634927</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
         <v>3</v>
       </c>
       <c r="Q226" t="n">
-        <v>2.488285560864705</v>
+        <v>2.340568291060991</v>
       </c>
       <c r="R226" t="n">
-        <v>0.472774256564294</v>
+        <v>0.4447079753015883</v>
       </c>
       <c r="S226" t="n">
         <v>16</v>
@@ -15646,10 +15646,10 @@
         <v>1</v>
       </c>
       <c r="Q227" t="n">
-        <v>0.9349584882713364</v>
+        <v>0.8691873985766052</v>
       </c>
       <c r="R227" t="n">
-        <v>0.1776421127715539</v>
+        <v>0.165145605729555</v>
       </c>
       <c r="S227" t="n">
         <v>7.5</v>
@@ -15695,7 +15695,7 @@
         <v>5</v>
       </c>
       <c r="K228" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="L228" t="n">
         <v>0.83</v>
@@ -15707,16 +15707,16 @@
         <v>0.35</v>
       </c>
       <c r="O228" t="n">
-        <v>0.735</v>
+        <v>0.738</v>
       </c>
       <c r="P228" t="n">
         <v>2</v>
       </c>
       <c r="Q228" t="n">
-        <v>1.558264147118894</v>
+        <v>1.448645664294342</v>
       </c>
       <c r="R228" t="n">
-        <v>0.2960701879525898</v>
+        <v>0.275242676215925</v>
       </c>
       <c r="S228" t="n">
         <v>12.5</v>
@@ -15780,10 +15780,10 @@
         <v>3</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.49322263539023</v>
+        <v>2.317833062870947</v>
       </c>
       <c r="R229" t="n">
-        <v>0.4737123007241438</v>
+        <v>0.44038828194548</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -15847,10 +15847,10 @@
         <v>1</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.8812678028062497</v>
+        <v>0.8266514158676271</v>
       </c>
       <c r="R230" t="n">
-        <v>0.1674408825331875</v>
+        <v>0.1570637690148492</v>
       </c>
       <c r="S230" t="n">
         <v>6</v>
@@ -15914,10 +15914,10 @@
         <v>2</v>
       </c>
       <c r="Q231" t="n">
-        <v>1.46877967134375</v>
+        <v>1.377752359779379</v>
       </c>
       <c r="R231" t="n">
-        <v>0.2790681375553124</v>
+        <v>0.261772948358082</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -15981,10 +15981,10 @@
         <v>3</v>
       </c>
       <c r="Q232" t="n">
-        <v>2.350047474149999</v>
+        <v>2.204403775647006</v>
       </c>
       <c r="R232" t="n">
-        <v>0.4465090200884999</v>
+        <v>0.4188367173729311</v>
       </c>
       <c r="S232" t="n">
         <v>16</v>
@@ -16030,7 +16030,7 @@
         <v>4</v>
       </c>
       <c r="K233" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="L233" t="n">
         <v>0.79</v>
@@ -16042,16 +16042,16 @@
         <v>0.15</v>
       </c>
       <c r="O233" t="n">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
       </c>
       <c r="Q233" t="n">
-        <v>2.229089148274632</v>
+        <v>2.099058947958611</v>
       </c>
       <c r="R233" t="n">
-        <v>0.4235269381721801</v>
+        <v>0.3988212001121362</v>
       </c>
       <c r="S233" t="n">
         <v>14</v>
@@ -16115,10 +16115,10 @@
         <v>2</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.343633722411948</v>
+        <v>3.148588421937917</v>
       </c>
       <c r="R234" t="n">
-        <v>0.6352904072582701</v>
+        <v>0.5982318001682043</v>
       </c>
       <c r="S234" t="n">
         <v>21</v>
@@ -16182,10 +16182,10 @@
         <v>3</v>
       </c>
       <c r="Q235" t="n">
-        <v>4.458178296549264</v>
+        <v>4.198117895917223</v>
       </c>
       <c r="R235" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7976424002242724</v>
       </c>
       <c r="S235" t="n">
         <v>28</v>
@@ -16249,10 +16249,10 @@
         <v>3</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.6368826137927521</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="R236" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="S236" t="n">
         <v>6</v>
@@ -16316,10 +16316,10 @@
         <v>1</v>
       </c>
       <c r="Q237" t="n">
-        <v>1.114544574137316</v>
+        <v>1.025381008206331</v>
       </c>
       <c r="R237" t="n">
-        <v>0.2117634690860901</v>
+        <v>0.1948223915592028</v>
       </c>
       <c r="S237" t="n">
         <v>10.5</v>
@@ -16383,10 +16383,10 @@
         <v>2</v>
       </c>
       <c r="Q238" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R238" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="S238" t="n">
         <v>15</v>
@@ -16432,7 +16432,7 @@
         <v>5</v>
       </c>
       <c r="K239" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="L239" t="n">
         <v>0.83</v>
@@ -16444,16 +16444,16 @@
         <v>0.15</v>
       </c>
       <c r="O239" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="P239" t="n">
         <v>1</v>
       </c>
       <c r="Q239" t="n">
-        <v>1.86683130496422</v>
+        <v>1.752584314771988</v>
       </c>
       <c r="R239" t="n">
-        <v>0.3546979479432018</v>
+        <v>0.3329910198066777</v>
       </c>
       <c r="S239" t="n">
         <v>12.5</v>
@@ -16517,10 +16517,10 @@
         <v>2</v>
       </c>
       <c r="Q240" t="n">
-        <v>2.986930087942751</v>
+        <v>2.80413490363518</v>
       </c>
       <c r="R240" t="n">
-        <v>0.5675167167091227</v>
+        <v>0.5327856316906843</v>
       </c>
       <c r="S240" t="n">
         <v>20</v>
@@ -16584,10 +16584,10 @@
         <v>3</v>
       </c>
       <c r="Q241" t="n">
-        <v>4.480395131914127</v>
+        <v>4.206202355452771</v>
       </c>
       <c r="R241" t="n">
-        <v>0.8512750750636842</v>
+        <v>0.7991784475360264</v>
       </c>
       <c r="S241" t="n">
         <v>30</v>
